--- a/Controle_Locacao.xlsx
+++ b/Controle_Locacao.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Renato.Neves\Documents\TRABALHOS 2025\LOCAÇÃO PRAIA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB04FA44-93F8-414B-AA6D-25324EA312E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9C4D5B2-2677-4B63-8A05-7B1C52499F8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2031,7 +2031,7 @@
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="7" width="18" customWidth="1"/>
-    <col min="9" max="9" width="17" customWidth="1"/>
+    <col min="9" max="9" width="27.875" customWidth="1"/>
     <col min="10" max="10" width="22" customWidth="1"/>
     <col min="11" max="12" width="13" customWidth="1"/>
   </cols>
@@ -2776,7 +2776,10 @@
         <f t="shared" si="6"/>
         <v>0.98855357142857136</v>
       </c>
-      <c r="X7" s="47"/>
+      <c r="X7" s="47">
+        <f>G7</f>
+        <v>2800</v>
+      </c>
       <c r="Y7" s="51">
         <v>0</v>
       </c>

--- a/Controle_Locacao.xlsx
+++ b/Controle_Locacao.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Renato.Neves\Documents\TRABALHOS 2025\LOCAÇÃO PRAIA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9C4D5B2-2677-4B63-8A05-7B1C52499F8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C32F49AB-3A53-44B1-AE48-DABD717F70D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2700,7 +2700,7 @@
         <v>0</v>
       </c>
       <c r="Y6" s="58">
-        <f t="shared" ref="Y6:Y36" si="7">IF(B6="",0,IFERROR(MAX(0,G6-X6),G6))</f>
+        <f t="shared" ref="Y6:Y69" si="7">IF(B6="",0,IFERROR(MAX(0,G6-X6),G6))</f>
         <v>11000</v>
       </c>
       <c r="Z6" s="60" t="str">
@@ -2780,7 +2780,8 @@
         <f>G7</f>
         <v>2800</v>
       </c>
-      <c r="Y7" s="51">
+      <c r="Y7" s="58">
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="Z7" s="49" t="str">
@@ -2852,7 +2853,7 @@
         <v>0</v>
       </c>
       <c r="X8" s="47"/>
-      <c r="Y8" s="51">
+      <c r="Y8" s="58">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
@@ -2911,7 +2912,7 @@
         <v>0</v>
       </c>
       <c r="X9" s="47"/>
-      <c r="Y9" s="51">
+      <c r="Y9" s="58">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
@@ -2970,7 +2971,7 @@
         <v>0</v>
       </c>
       <c r="X10" s="47"/>
-      <c r="Y10" s="51">
+      <c r="Y10" s="58">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
@@ -3029,7 +3030,7 @@
         <v>0</v>
       </c>
       <c r="X11" s="47"/>
-      <c r="Y11" s="51">
+      <c r="Y11" s="58">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
@@ -3088,7 +3089,7 @@
         <v>0</v>
       </c>
       <c r="X12" s="47"/>
-      <c r="Y12" s="51">
+      <c r="Y12" s="58">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
@@ -3147,7 +3148,7 @@
         <v>0</v>
       </c>
       <c r="X13" s="47"/>
-      <c r="Y13" s="51">
+      <c r="Y13" s="58">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
@@ -3206,7 +3207,7 @@
         <v>0</v>
       </c>
       <c r="X14" s="47"/>
-      <c r="Y14" s="51">
+      <c r="Y14" s="58">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
@@ -3265,7 +3266,7 @@
         <v>0</v>
       </c>
       <c r="X15" s="47"/>
-      <c r="Y15" s="51">
+      <c r="Y15" s="58">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
@@ -3324,7 +3325,7 @@
         <v>0</v>
       </c>
       <c r="X16" s="47"/>
-      <c r="Y16" s="51">
+      <c r="Y16" s="58">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
@@ -3383,7 +3384,7 @@
         <v>0</v>
       </c>
       <c r="X17" s="47"/>
-      <c r="Y17" s="51">
+      <c r="Y17" s="58">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
@@ -3442,7 +3443,7 @@
         <v>0</v>
       </c>
       <c r="X18" s="47"/>
-      <c r="Y18" s="51">
+      <c r="Y18" s="58">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
@@ -3501,7 +3502,7 @@
         <v>0</v>
       </c>
       <c r="X19" s="47"/>
-      <c r="Y19" s="51">
+      <c r="Y19" s="58">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
@@ -3560,7 +3561,7 @@
         <v>0</v>
       </c>
       <c r="X20" s="47"/>
-      <c r="Y20" s="51">
+      <c r="Y20" s="58">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
@@ -3619,7 +3620,7 @@
         <v>0</v>
       </c>
       <c r="X21" s="47"/>
-      <c r="Y21" s="51">
+      <c r="Y21" s="58">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
@@ -3678,7 +3679,7 @@
         <v>0</v>
       </c>
       <c r="X22" s="47"/>
-      <c r="Y22" s="51">
+      <c r="Y22" s="58">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
@@ -3737,7 +3738,7 @@
         <v>0</v>
       </c>
       <c r="X23" s="47"/>
-      <c r="Y23" s="51">
+      <c r="Y23" s="58">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
@@ -3796,7 +3797,7 @@
         <v>0</v>
       </c>
       <c r="X24" s="47"/>
-      <c r="Y24" s="51">
+      <c r="Y24" s="58">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
@@ -3855,7 +3856,7 @@
         <v>0</v>
       </c>
       <c r="X25" s="47"/>
-      <c r="Y25" s="51">
+      <c r="Y25" s="58">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
@@ -3914,7 +3915,7 @@
         <v>0</v>
       </c>
       <c r="X26" s="47"/>
-      <c r="Y26" s="51">
+      <c r="Y26" s="58">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
@@ -3973,7 +3974,7 @@
         <v>0</v>
       </c>
       <c r="X27" s="47"/>
-      <c r="Y27" s="51">
+      <c r="Y27" s="58">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
@@ -4032,7 +4033,7 @@
         <v>0</v>
       </c>
       <c r="X28" s="47"/>
-      <c r="Y28" s="51">
+      <c r="Y28" s="58">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
@@ -4091,7 +4092,7 @@
         <v>0</v>
       </c>
       <c r="X29" s="47"/>
-      <c r="Y29" s="51">
+      <c r="Y29" s="58">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
@@ -4150,7 +4151,7 @@
         <v>0</v>
       </c>
       <c r="X30" s="47"/>
-      <c r="Y30" s="51">
+      <c r="Y30" s="58">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
@@ -4209,7 +4210,7 @@
         <v>0</v>
       </c>
       <c r="X31" s="47"/>
-      <c r="Y31" s="51">
+      <c r="Y31" s="58">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
@@ -4268,7 +4269,7 @@
         <v>0</v>
       </c>
       <c r="X32" s="47"/>
-      <c r="Y32" s="51">
+      <c r="Y32" s="58">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
@@ -4327,7 +4328,7 @@
         <v>0</v>
       </c>
       <c r="X33" s="47"/>
-      <c r="Y33" s="51">
+      <c r="Y33" s="58">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
@@ -4386,7 +4387,7 @@
         <v>0</v>
       </c>
       <c r="X34" s="47"/>
-      <c r="Y34" s="51">
+      <c r="Y34" s="58">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
@@ -4445,7 +4446,7 @@
         <v>0</v>
       </c>
       <c r="X35" s="47"/>
-      <c r="Y35" s="51">
+      <c r="Y35" s="58">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
@@ -4504,7 +4505,7 @@
         <v>0</v>
       </c>
       <c r="X36" s="47"/>
-      <c r="Y36" s="51">
+      <c r="Y36" s="58">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
@@ -4563,8 +4564,8 @@
         <v>0</v>
       </c>
       <c r="X37" s="47"/>
-      <c r="Y37" s="51">
-        <f t="shared" ref="Y37:Y68" si="16">IF(B37="",0,IFERROR(MAX(0,G37-X37),G37))</f>
+      <c r="Y37" s="58">
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="Z37" s="49" t="str">
@@ -4622,12 +4623,12 @@
         <v>0</v>
       </c>
       <c r="X38" s="47"/>
-      <c r="Y38" s="51">
-        <f t="shared" si="16"/>
+      <c r="Y38" s="58">
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="Z38" s="49" t="str">
-        <f t="shared" ref="Z38:Z69" si="17">IF(B38="","",IF(COUNTIFS($C$6:$C$204,"&lt;"&amp;D38,$D$6:$D$204,"&gt;"&amp;C38,$I$6:$I$204,"&lt;&gt;Cancelada",$I$6:$I$204,"&lt;&gt;Consulta")&gt;1,"CONFLITO","OK"))</f>
+        <f t="shared" ref="Z38:Z69" si="16">IF(B38="","",IF(COUNTIFS($C$6:$C$204,"&lt;"&amp;D38,$D$6:$D$204,"&gt;"&amp;C38,$I$6:$I$204,"&lt;&gt;Cancelada",$I$6:$I$204,"&lt;&gt;Consulta")&gt;1,"CONFLITO","OK"))</f>
         <v/>
       </c>
       <c r="AA38" s="63"/>
@@ -4681,12 +4682,12 @@
         <v>0</v>
       </c>
       <c r="X39" s="47"/>
-      <c r="Y39" s="51">
+      <c r="Y39" s="58">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="Z39" s="49" t="str">
         <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="Z39" s="49" t="str">
-        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="AA39" s="63"/>
@@ -4740,12 +4741,12 @@
         <v>0</v>
       </c>
       <c r="X40" s="47"/>
-      <c r="Y40" s="51">
+      <c r="Y40" s="58">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="Z40" s="49" t="str">
         <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="Z40" s="49" t="str">
-        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="AA40" s="63"/>
@@ -4799,12 +4800,12 @@
         <v>0</v>
       </c>
       <c r="X41" s="47"/>
-      <c r="Y41" s="51">
+      <c r="Y41" s="58">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="Z41" s="49" t="str">
         <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="Z41" s="49" t="str">
-        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="AA41" s="63"/>
@@ -4858,12 +4859,12 @@
         <v>0</v>
       </c>
       <c r="X42" s="47"/>
-      <c r="Y42" s="51">
+      <c r="Y42" s="58">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="Z42" s="49" t="str">
         <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="Z42" s="49" t="str">
-        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="AA42" s="63"/>
@@ -4917,12 +4918,12 @@
         <v>0</v>
       </c>
       <c r="X43" s="47"/>
-      <c r="Y43" s="51">
+      <c r="Y43" s="58">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="Z43" s="49" t="str">
         <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="Z43" s="49" t="str">
-        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="AA43" s="63"/>
@@ -4976,12 +4977,12 @@
         <v>0</v>
       </c>
       <c r="X44" s="47"/>
-      <c r="Y44" s="51">
+      <c r="Y44" s="58">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="Z44" s="49" t="str">
         <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="Z44" s="49" t="str">
-        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="AA44" s="63"/>
@@ -5035,12 +5036,12 @@
         <v>0</v>
       </c>
       <c r="X45" s="47"/>
-      <c r="Y45" s="51">
+      <c r="Y45" s="58">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="Z45" s="49" t="str">
         <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="Z45" s="49" t="str">
-        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="AA45" s="63"/>
@@ -5094,12 +5095,12 @@
         <v>0</v>
       </c>
       <c r="X46" s="47"/>
-      <c r="Y46" s="51">
+      <c r="Y46" s="58">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="Z46" s="49" t="str">
         <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="Z46" s="49" t="str">
-        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="AA46" s="63"/>
@@ -5153,12 +5154,12 @@
         <v>0</v>
       </c>
       <c r="X47" s="47"/>
-      <c r="Y47" s="51">
+      <c r="Y47" s="58">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="Z47" s="49" t="str">
         <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="Z47" s="49" t="str">
-        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="AA47" s="63"/>
@@ -5212,12 +5213,12 @@
         <v>0</v>
       </c>
       <c r="X48" s="47"/>
-      <c r="Y48" s="51">
+      <c r="Y48" s="58">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="Z48" s="49" t="str">
         <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="Z48" s="49" t="str">
-        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="AA48" s="63"/>
@@ -5271,12 +5272,12 @@
         <v>0</v>
       </c>
       <c r="X49" s="47"/>
-      <c r="Y49" s="51">
+      <c r="Y49" s="58">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="Z49" s="49" t="str">
         <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="Z49" s="49" t="str">
-        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="AA49" s="63"/>
@@ -5330,12 +5331,12 @@
         <v>0</v>
       </c>
       <c r="X50" s="47"/>
-      <c r="Y50" s="51">
+      <c r="Y50" s="58">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="Z50" s="49" t="str">
         <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="Z50" s="49" t="str">
-        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="AA50" s="63"/>
@@ -5389,12 +5390,12 @@
         <v>0</v>
       </c>
       <c r="X51" s="47"/>
-      <c r="Y51" s="51">
+      <c r="Y51" s="58">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="Z51" s="49" t="str">
         <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="Z51" s="49" t="str">
-        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="AA51" s="63"/>
@@ -5448,12 +5449,12 @@
         <v>0</v>
       </c>
       <c r="X52" s="47"/>
-      <c r="Y52" s="51">
+      <c r="Y52" s="58">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="Z52" s="49" t="str">
         <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="Z52" s="49" t="str">
-        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="AA52" s="63"/>
@@ -5507,12 +5508,12 @@
         <v>0</v>
       </c>
       <c r="X53" s="47"/>
-      <c r="Y53" s="51">
+      <c r="Y53" s="58">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="Z53" s="49" t="str">
         <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="Z53" s="49" t="str">
-        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="AA53" s="63"/>
@@ -5566,12 +5567,12 @@
         <v>0</v>
       </c>
       <c r="X54" s="47"/>
-      <c r="Y54" s="51">
+      <c r="Y54" s="58">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="Z54" s="49" t="str">
         <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="Z54" s="49" t="str">
-        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="AA54" s="63"/>
@@ -5625,12 +5626,12 @@
         <v>0</v>
       </c>
       <c r="X55" s="47"/>
-      <c r="Y55" s="51">
+      <c r="Y55" s="58">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="Z55" s="49" t="str">
         <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="Z55" s="49" t="str">
-        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="AA55" s="63"/>
@@ -5684,12 +5685,12 @@
         <v>0</v>
       </c>
       <c r="X56" s="47"/>
-      <c r="Y56" s="51">
+      <c r="Y56" s="58">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="Z56" s="49" t="str">
         <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="Z56" s="49" t="str">
-        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="AA56" s="63"/>
@@ -5743,12 +5744,12 @@
         <v>0</v>
       </c>
       <c r="X57" s="47"/>
-      <c r="Y57" s="51">
+      <c r="Y57" s="58">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="Z57" s="49" t="str">
         <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="Z57" s="49" t="str">
-        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="AA57" s="63"/>
@@ -5802,12 +5803,12 @@
         <v>0</v>
       </c>
       <c r="X58" s="47"/>
-      <c r="Y58" s="51">
+      <c r="Y58" s="58">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="Z58" s="49" t="str">
         <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="Z58" s="49" t="str">
-        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="AA58" s="63"/>
@@ -5861,12 +5862,12 @@
         <v>0</v>
       </c>
       <c r="X59" s="47"/>
-      <c r="Y59" s="51">
+      <c r="Y59" s="58">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="Z59" s="49" t="str">
         <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="Z59" s="49" t="str">
-        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="AA59" s="63"/>
@@ -5920,12 +5921,12 @@
         <v>0</v>
       </c>
       <c r="X60" s="47"/>
-      <c r="Y60" s="51">
+      <c r="Y60" s="58">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="Z60" s="49" t="str">
         <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="Z60" s="49" t="str">
-        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="AA60" s="63"/>
@@ -5979,12 +5980,12 @@
         <v>0</v>
       </c>
       <c r="X61" s="47"/>
-      <c r="Y61" s="51">
+      <c r="Y61" s="58">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="Z61" s="49" t="str">
         <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="Z61" s="49" t="str">
-        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="AA61" s="63"/>
@@ -6038,12 +6039,12 @@
         <v>0</v>
       </c>
       <c r="X62" s="47"/>
-      <c r="Y62" s="51">
+      <c r="Y62" s="58">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="Z62" s="49" t="str">
         <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="Z62" s="49" t="str">
-        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="AA62" s="63"/>
@@ -6097,12 +6098,12 @@
         <v>0</v>
       </c>
       <c r="X63" s="47"/>
-      <c r="Y63" s="51">
+      <c r="Y63" s="58">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="Z63" s="49" t="str">
         <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="Z63" s="49" t="str">
-        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="AA63" s="63"/>
@@ -6156,12 +6157,12 @@
         <v>0</v>
       </c>
       <c r="X64" s="47"/>
-      <c r="Y64" s="51">
+      <c r="Y64" s="58">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="Z64" s="49" t="str">
         <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="Z64" s="49" t="str">
-        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="AA64" s="63"/>
@@ -6215,12 +6216,12 @@
         <v>0</v>
       </c>
       <c r="X65" s="48"/>
-      <c r="Y65" s="51">
+      <c r="Y65" s="58">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="Z65" s="49" t="str">
         <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="Z65" s="49" t="str">
-        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="AA65" s="64"/>
@@ -6274,12 +6275,12 @@
         <v>0</v>
       </c>
       <c r="X66" s="48"/>
-      <c r="Y66" s="51">
+      <c r="Y66" s="58">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="Z66" s="49" t="str">
         <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="Z66" s="49" t="str">
-        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="AA66" s="64"/>
@@ -6333,12 +6334,12 @@
         <v>0</v>
       </c>
       <c r="X67" s="48"/>
-      <c r="Y67" s="51">
+      <c r="Y67" s="58">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="Z67" s="49" t="str">
         <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="Z67" s="49" t="str">
-        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="AA67" s="64"/>
@@ -6392,31 +6393,31 @@
         <v>0</v>
       </c>
       <c r="X68" s="48"/>
-      <c r="Y68" s="51">
+      <c r="Y68" s="58">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="Z68" s="49" t="str">
         <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="Z68" s="49" t="str">
-        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="AA68" s="64"/>
     </row>
     <row r="69" spans="1:27">
       <c r="A69" s="62" t="str">
-        <f t="shared" ref="A69:A100" si="18">IF(B69="","","LOC-"&amp;TEXT(ROW()-5,"000"))</f>
+        <f t="shared" ref="A69:A100" si="17">IF(B69="","","LOC-"&amp;TEXT(ROW()-5,"000"))</f>
         <v/>
       </c>
       <c r="B69" s="44"/>
       <c r="C69" s="46"/>
       <c r="D69" s="46"/>
       <c r="E69" s="50">
-        <f t="shared" ref="E69:E100" si="19">IF(OR(B69="",C69="",D69=""),0,MAX(0,D69-C69))</f>
+        <f t="shared" ref="E69:E100" si="18">IF(OR(B69="",C69="",D69=""),0,MAX(0,D69-C69))</f>
         <v>0</v>
       </c>
       <c r="F69" s="48"/>
       <c r="G69" s="51">
-        <f t="shared" ref="G69:G100" si="20">IF(OR(B69="",E69=0,F69=""),0,E69*F69)</f>
+        <f t="shared" ref="G69:G100" si="19">IF(OR(B69="",E69=0,F69=""),0,E69*F69)</f>
         <v>0</v>
       </c>
       <c r="H69" s="44"/>
@@ -6435,47 +6436,47 @@
         <v>0</v>
       </c>
       <c r="T69" s="51">
-        <f t="shared" ref="T69:T100" si="21">IF(OR(B69="",E69=0),0,S69/E69)</f>
+        <f t="shared" ref="T69:T100" si="20">IF(OR(B69="",E69=0),0,S69/E69)</f>
         <v>0</v>
       </c>
       <c r="U69" s="51">
-        <f t="shared" ref="U69:U100" si="22">IF(B69="",0,G69-S69)</f>
+        <f t="shared" ref="U69:U100" si="21">IF(B69="",0,G69-S69)</f>
         <v>0</v>
       </c>
       <c r="V69" s="51">
-        <f t="shared" ref="V69:V100" si="23">IF(OR(B69="",E69=0),0,U69/E69)</f>
+        <f t="shared" ref="V69:V100" si="22">IF(OR(B69="",E69=0),0,U69/E69)</f>
         <v>0</v>
       </c>
       <c r="W69" s="52">
-        <f t="shared" ref="W69:W100" si="24">IF(OR(B69="",G69=0),0,U69/G69)</f>
+        <f t="shared" ref="W69:W100" si="23">IF(OR(B69="",G69=0),0,U69/G69)</f>
         <v>0</v>
       </c>
       <c r="X69" s="48"/>
-      <c r="Y69" s="51">
-        <f t="shared" ref="Y69:Y100" si="25">IF(B69="",0,IFERROR(MAX(0,G69-X69),G69))</f>
+      <c r="Y69" s="58">
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="Z69" s="49" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="AA69" s="64"/>
     </row>
     <row r="70" spans="1:27">
       <c r="A70" s="62" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="B70" s="44"/>
       <c r="C70" s="46"/>
       <c r="D70" s="46"/>
       <c r="E70" s="50">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="F70" s="48"/>
       <c r="G70" s="51">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="H70" s="44"/>
@@ -6494,47 +6495,47 @@
         <v>0</v>
       </c>
       <c r="T70" s="51">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="U70" s="51">
         <f t="shared" si="21"/>
         <v>0</v>
       </c>
-      <c r="U70" s="51">
+      <c r="V70" s="51">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="V70" s="51">
+      <c r="W70" s="52">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="W70" s="52">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
       <c r="X70" s="48"/>
-      <c r="Y70" s="51">
-        <f t="shared" si="25"/>
+      <c r="Y70" s="58">
+        <f t="shared" ref="Y70:Y133" si="24">IF(B70="",0,IFERROR(MAX(0,G70-X70),G70))</f>
         <v>0</v>
       </c>
       <c r="Z70" s="49" t="str">
-        <f t="shared" ref="Z70:Z101" si="26">IF(B70="","",IF(COUNTIFS($C$6:$C$204,"&lt;"&amp;D70,$D$6:$D$204,"&gt;"&amp;C70,$I$6:$I$204,"&lt;&gt;Cancelada",$I$6:$I$204,"&lt;&gt;Consulta")&gt;1,"CONFLITO","OK"))</f>
+        <f t="shared" ref="Z70:Z101" si="25">IF(B70="","",IF(COUNTIFS($C$6:$C$204,"&lt;"&amp;D70,$D$6:$D$204,"&gt;"&amp;C70,$I$6:$I$204,"&lt;&gt;Cancelada",$I$6:$I$204,"&lt;&gt;Consulta")&gt;1,"CONFLITO","OK"))</f>
         <v/>
       </c>
       <c r="AA70" s="64"/>
     </row>
     <row r="71" spans="1:27">
       <c r="A71" s="62" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="B71" s="44"/>
       <c r="C71" s="46"/>
       <c r="D71" s="46"/>
       <c r="E71" s="50">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="F71" s="48"/>
       <c r="G71" s="51">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="H71" s="44"/>
@@ -6553,47 +6554,47 @@
         <v>0</v>
       </c>
       <c r="T71" s="51">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="U71" s="51">
         <f t="shared" si="21"/>
         <v>0</v>
       </c>
-      <c r="U71" s="51">
+      <c r="V71" s="51">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="V71" s="51">
+      <c r="W71" s="52">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="W71" s="52">
+      <c r="X71" s="48"/>
+      <c r="Y71" s="58">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="X71" s="48"/>
-      <c r="Y71" s="51">
+      <c r="Z71" s="49" t="str">
         <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="Z71" s="49" t="str">
-        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="AA71" s="64"/>
     </row>
     <row r="72" spans="1:27">
       <c r="A72" s="62" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="B72" s="44"/>
       <c r="C72" s="46"/>
       <c r="D72" s="46"/>
       <c r="E72" s="50">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="F72" s="48"/>
       <c r="G72" s="51">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="H72" s="44"/>
@@ -6612,47 +6613,47 @@
         <v>0</v>
       </c>
       <c r="T72" s="51">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="U72" s="51">
         <f t="shared" si="21"/>
         <v>0</v>
       </c>
-      <c r="U72" s="51">
+      <c r="V72" s="51">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="V72" s="51">
+      <c r="W72" s="52">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="W72" s="52">
+      <c r="X72" s="48"/>
+      <c r="Y72" s="58">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="X72" s="48"/>
-      <c r="Y72" s="51">
+      <c r="Z72" s="49" t="str">
         <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="Z72" s="49" t="str">
-        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="AA72" s="64"/>
     </row>
     <row r="73" spans="1:27">
       <c r="A73" s="62" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="B73" s="44"/>
       <c r="C73" s="46"/>
       <c r="D73" s="46"/>
       <c r="E73" s="50">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="F73" s="48"/>
       <c r="G73" s="51">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="H73" s="44"/>
@@ -6671,47 +6672,47 @@
         <v>0</v>
       </c>
       <c r="T73" s="51">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="U73" s="51">
         <f t="shared" si="21"/>
         <v>0</v>
       </c>
-      <c r="U73" s="51">
+      <c r="V73" s="51">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="V73" s="51">
+      <c r="W73" s="52">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="W73" s="52">
+      <c r="X73" s="48"/>
+      <c r="Y73" s="58">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="X73" s="48"/>
-      <c r="Y73" s="51">
+      <c r="Z73" s="49" t="str">
         <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="Z73" s="49" t="str">
-        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="AA73" s="64"/>
     </row>
     <row r="74" spans="1:27">
       <c r="A74" s="62" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="B74" s="44"/>
       <c r="C74" s="46"/>
       <c r="D74" s="46"/>
       <c r="E74" s="50">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="F74" s="48"/>
       <c r="G74" s="51">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="H74" s="44"/>
@@ -6730,47 +6731,47 @@
         <v>0</v>
       </c>
       <c r="T74" s="51">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="U74" s="51">
         <f t="shared" si="21"/>
         <v>0</v>
       </c>
-      <c r="U74" s="51">
+      <c r="V74" s="51">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="V74" s="51">
+      <c r="W74" s="52">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="W74" s="52">
+      <c r="X74" s="48"/>
+      <c r="Y74" s="58">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="X74" s="48"/>
-      <c r="Y74" s="51">
+      <c r="Z74" s="49" t="str">
         <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="Z74" s="49" t="str">
-        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="AA74" s="64"/>
     </row>
     <row r="75" spans="1:27">
       <c r="A75" s="62" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="B75" s="44"/>
       <c r="C75" s="46"/>
       <c r="D75" s="46"/>
       <c r="E75" s="50">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="F75" s="48"/>
       <c r="G75" s="51">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="H75" s="44"/>
@@ -6789,47 +6790,47 @@
         <v>0</v>
       </c>
       <c r="T75" s="51">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="U75" s="51">
         <f t="shared" si="21"/>
         <v>0</v>
       </c>
-      <c r="U75" s="51">
+      <c r="V75" s="51">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="V75" s="51">
+      <c r="W75" s="52">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="W75" s="52">
+      <c r="X75" s="48"/>
+      <c r="Y75" s="58">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="X75" s="48"/>
-      <c r="Y75" s="51">
+      <c r="Z75" s="49" t="str">
         <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="Z75" s="49" t="str">
-        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="AA75" s="64"/>
     </row>
     <row r="76" spans="1:27">
       <c r="A76" s="62" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="B76" s="44"/>
       <c r="C76" s="46"/>
       <c r="D76" s="46"/>
       <c r="E76" s="50">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="F76" s="48"/>
       <c r="G76" s="51">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="H76" s="44"/>
@@ -6848,47 +6849,47 @@
         <v>0</v>
       </c>
       <c r="T76" s="51">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="U76" s="51">
         <f t="shared" si="21"/>
         <v>0</v>
       </c>
-      <c r="U76" s="51">
+      <c r="V76" s="51">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="V76" s="51">
+      <c r="W76" s="52">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="W76" s="52">
+      <c r="X76" s="48"/>
+      <c r="Y76" s="58">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="X76" s="48"/>
-      <c r="Y76" s="51">
+      <c r="Z76" s="49" t="str">
         <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="Z76" s="49" t="str">
-        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="AA76" s="64"/>
     </row>
     <row r="77" spans="1:27">
       <c r="A77" s="62" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="B77" s="44"/>
       <c r="C77" s="46"/>
       <c r="D77" s="46"/>
       <c r="E77" s="50">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="F77" s="48"/>
       <c r="G77" s="51">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="H77" s="44"/>
@@ -6907,47 +6908,47 @@
         <v>0</v>
       </c>
       <c r="T77" s="51">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="U77" s="51">
         <f t="shared" si="21"/>
         <v>0</v>
       </c>
-      <c r="U77" s="51">
+      <c r="V77" s="51">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="V77" s="51">
+      <c r="W77" s="52">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="W77" s="52">
+      <c r="X77" s="48"/>
+      <c r="Y77" s="58">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="X77" s="48"/>
-      <c r="Y77" s="51">
+      <c r="Z77" s="49" t="str">
         <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="Z77" s="49" t="str">
-        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="AA77" s="64"/>
     </row>
     <row r="78" spans="1:27">
       <c r="A78" s="62" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="B78" s="44"/>
       <c r="C78" s="46"/>
       <c r="D78" s="46"/>
       <c r="E78" s="50">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="F78" s="48"/>
       <c r="G78" s="51">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="H78" s="44"/>
@@ -6966,47 +6967,47 @@
         <v>0</v>
       </c>
       <c r="T78" s="51">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="U78" s="51">
         <f t="shared" si="21"/>
         <v>0</v>
       </c>
-      <c r="U78" s="51">
+      <c r="V78" s="51">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="V78" s="51">
+      <c r="W78" s="52">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="W78" s="52">
+      <c r="X78" s="48"/>
+      <c r="Y78" s="58">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="X78" s="48"/>
-      <c r="Y78" s="51">
+      <c r="Z78" s="49" t="str">
         <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="Z78" s="49" t="str">
-        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="AA78" s="64"/>
     </row>
     <row r="79" spans="1:27">
       <c r="A79" s="62" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="B79" s="44"/>
       <c r="C79" s="46"/>
       <c r="D79" s="46"/>
       <c r="E79" s="50">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="F79" s="48"/>
       <c r="G79" s="51">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="H79" s="44"/>
@@ -7025,47 +7026,47 @@
         <v>0</v>
       </c>
       <c r="T79" s="51">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="U79" s="51">
         <f t="shared" si="21"/>
         <v>0</v>
       </c>
-      <c r="U79" s="51">
+      <c r="V79" s="51">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="V79" s="51">
+      <c r="W79" s="52">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="W79" s="52">
+      <c r="X79" s="48"/>
+      <c r="Y79" s="58">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="X79" s="48"/>
-      <c r="Y79" s="51">
+      <c r="Z79" s="49" t="str">
         <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="Z79" s="49" t="str">
-        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="AA79" s="64"/>
     </row>
     <row r="80" spans="1:27">
       <c r="A80" s="62" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="B80" s="44"/>
       <c r="C80" s="46"/>
       <c r="D80" s="46"/>
       <c r="E80" s="50">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="F80" s="48"/>
       <c r="G80" s="51">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="H80" s="44"/>
@@ -7084,47 +7085,47 @@
         <v>0</v>
       </c>
       <c r="T80" s="51">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="U80" s="51">
         <f t="shared" si="21"/>
         <v>0</v>
       </c>
-      <c r="U80" s="51">
+      <c r="V80" s="51">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="V80" s="51">
+      <c r="W80" s="52">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="W80" s="52">
+      <c r="X80" s="48"/>
+      <c r="Y80" s="58">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="X80" s="48"/>
-      <c r="Y80" s="51">
+      <c r="Z80" s="49" t="str">
         <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="Z80" s="49" t="str">
-        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="AA80" s="64"/>
     </row>
     <row r="81" spans="1:27">
       <c r="A81" s="62" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="B81" s="44"/>
       <c r="C81" s="46"/>
       <c r="D81" s="46"/>
       <c r="E81" s="50">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="F81" s="48"/>
       <c r="G81" s="51">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="H81" s="44"/>
@@ -7143,47 +7144,47 @@
         <v>0</v>
       </c>
       <c r="T81" s="51">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="U81" s="51">
         <f t="shared" si="21"/>
         <v>0</v>
       </c>
-      <c r="U81" s="51">
+      <c r="V81" s="51">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="V81" s="51">
+      <c r="W81" s="52">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="W81" s="52">
+      <c r="X81" s="48"/>
+      <c r="Y81" s="58">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="X81" s="48"/>
-      <c r="Y81" s="51">
+      <c r="Z81" s="49" t="str">
         <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="Z81" s="49" t="str">
-        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="AA81" s="64"/>
     </row>
     <row r="82" spans="1:27">
       <c r="A82" s="62" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="B82" s="44"/>
       <c r="C82" s="46"/>
       <c r="D82" s="46"/>
       <c r="E82" s="50">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="F82" s="48"/>
       <c r="G82" s="51">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="H82" s="44"/>
@@ -7202,47 +7203,47 @@
         <v>0</v>
       </c>
       <c r="T82" s="51">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="U82" s="51">
         <f t="shared" si="21"/>
         <v>0</v>
       </c>
-      <c r="U82" s="51">
+      <c r="V82" s="51">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="V82" s="51">
+      <c r="W82" s="52">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="W82" s="52">
+      <c r="X82" s="48"/>
+      <c r="Y82" s="58">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="X82" s="48"/>
-      <c r="Y82" s="51">
+      <c r="Z82" s="49" t="str">
         <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="Z82" s="49" t="str">
-        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="AA82" s="64"/>
     </row>
     <row r="83" spans="1:27">
       <c r="A83" s="62" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="B83" s="44"/>
       <c r="C83" s="46"/>
       <c r="D83" s="46"/>
       <c r="E83" s="50">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="F83" s="48"/>
       <c r="G83" s="51">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="H83" s="44"/>
@@ -7261,47 +7262,47 @@
         <v>0</v>
       </c>
       <c r="T83" s="51">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="U83" s="51">
         <f t="shared" si="21"/>
         <v>0</v>
       </c>
-      <c r="U83" s="51">
+      <c r="V83" s="51">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="V83" s="51">
+      <c r="W83" s="52">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="W83" s="52">
+      <c r="X83" s="48"/>
+      <c r="Y83" s="58">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="X83" s="48"/>
-      <c r="Y83" s="51">
+      <c r="Z83" s="49" t="str">
         <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="Z83" s="49" t="str">
-        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="AA83" s="64"/>
     </row>
     <row r="84" spans="1:27">
       <c r="A84" s="62" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="B84" s="44"/>
       <c r="C84" s="46"/>
       <c r="D84" s="46"/>
       <c r="E84" s="50">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="F84" s="48"/>
       <c r="G84" s="51">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="H84" s="44"/>
@@ -7320,47 +7321,47 @@
         <v>0</v>
       </c>
       <c r="T84" s="51">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="U84" s="51">
         <f t="shared" si="21"/>
         <v>0</v>
       </c>
-      <c r="U84" s="51">
+      <c r="V84" s="51">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="V84" s="51">
+      <c r="W84" s="52">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="W84" s="52">
+      <c r="X84" s="48"/>
+      <c r="Y84" s="58">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="X84" s="48"/>
-      <c r="Y84" s="51">
+      <c r="Z84" s="49" t="str">
         <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="Z84" s="49" t="str">
-        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="AA84" s="64"/>
     </row>
     <row r="85" spans="1:27">
       <c r="A85" s="62" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="B85" s="44"/>
       <c r="C85" s="46"/>
       <c r="D85" s="46"/>
       <c r="E85" s="50">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="F85" s="48"/>
       <c r="G85" s="51">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="H85" s="44"/>
@@ -7379,47 +7380,47 @@
         <v>0</v>
       </c>
       <c r="T85" s="51">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="U85" s="51">
         <f t="shared" si="21"/>
         <v>0</v>
       </c>
-      <c r="U85" s="51">
+      <c r="V85" s="51">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="V85" s="51">
+      <c r="W85" s="52">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="W85" s="52">
+      <c r="X85" s="48"/>
+      <c r="Y85" s="58">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="X85" s="48"/>
-      <c r="Y85" s="51">
+      <c r="Z85" s="49" t="str">
         <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="Z85" s="49" t="str">
-        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="AA85" s="64"/>
     </row>
     <row r="86" spans="1:27">
       <c r="A86" s="62" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="B86" s="44"/>
       <c r="C86" s="46"/>
       <c r="D86" s="46"/>
       <c r="E86" s="50">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="F86" s="48"/>
       <c r="G86" s="51">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="H86" s="44"/>
@@ -7438,47 +7439,47 @@
         <v>0</v>
       </c>
       <c r="T86" s="51">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="U86" s="51">
         <f t="shared" si="21"/>
         <v>0</v>
       </c>
-      <c r="U86" s="51">
+      <c r="V86" s="51">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="V86" s="51">
+      <c r="W86" s="52">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="W86" s="52">
+      <c r="X86" s="48"/>
+      <c r="Y86" s="58">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="X86" s="48"/>
-      <c r="Y86" s="51">
+      <c r="Z86" s="49" t="str">
         <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="Z86" s="49" t="str">
-        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="AA86" s="64"/>
     </row>
     <row r="87" spans="1:27">
       <c r="A87" s="62" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="B87" s="44"/>
       <c r="C87" s="46"/>
       <c r="D87" s="46"/>
       <c r="E87" s="50">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="F87" s="48"/>
       <c r="G87" s="51">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="H87" s="44"/>
@@ -7497,47 +7498,47 @@
         <v>0</v>
       </c>
       <c r="T87" s="51">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="U87" s="51">
         <f t="shared" si="21"/>
         <v>0</v>
       </c>
-      <c r="U87" s="51">
+      <c r="V87" s="51">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="V87" s="51">
+      <c r="W87" s="52">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="W87" s="52">
+      <c r="X87" s="48"/>
+      <c r="Y87" s="58">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="X87" s="48"/>
-      <c r="Y87" s="51">
+      <c r="Z87" s="49" t="str">
         <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="Z87" s="49" t="str">
-        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="AA87" s="64"/>
     </row>
     <row r="88" spans="1:27">
       <c r="A88" s="62" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="B88" s="44"/>
       <c r="C88" s="46"/>
       <c r="D88" s="46"/>
       <c r="E88" s="50">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="F88" s="48"/>
       <c r="G88" s="51">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="H88" s="44"/>
@@ -7556,47 +7557,47 @@
         <v>0</v>
       </c>
       <c r="T88" s="51">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="U88" s="51">
         <f t="shared" si="21"/>
         <v>0</v>
       </c>
-      <c r="U88" s="51">
+      <c r="V88" s="51">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="V88" s="51">
+      <c r="W88" s="52">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="W88" s="52">
+      <c r="X88" s="48"/>
+      <c r="Y88" s="58">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="X88" s="48"/>
-      <c r="Y88" s="51">
+      <c r="Z88" s="49" t="str">
         <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="Z88" s="49" t="str">
-        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="AA88" s="64"/>
     </row>
     <row r="89" spans="1:27">
       <c r="A89" s="62" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="B89" s="44"/>
       <c r="C89" s="46"/>
       <c r="D89" s="46"/>
       <c r="E89" s="50">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="F89" s="48"/>
       <c r="G89" s="51">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="H89" s="44"/>
@@ -7615,47 +7616,47 @@
         <v>0</v>
       </c>
       <c r="T89" s="51">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="U89" s="51">
         <f t="shared" si="21"/>
         <v>0</v>
       </c>
-      <c r="U89" s="51">
+      <c r="V89" s="51">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="V89" s="51">
+      <c r="W89" s="52">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="W89" s="52">
+      <c r="X89" s="48"/>
+      <c r="Y89" s="58">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="X89" s="48"/>
-      <c r="Y89" s="51">
+      <c r="Z89" s="49" t="str">
         <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="Z89" s="49" t="str">
-        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="AA89" s="64"/>
     </row>
     <row r="90" spans="1:27">
       <c r="A90" s="62" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="B90" s="44"/>
       <c r="C90" s="46"/>
       <c r="D90" s="46"/>
       <c r="E90" s="50">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="F90" s="48"/>
       <c r="G90" s="51">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="H90" s="44"/>
@@ -7674,47 +7675,47 @@
         <v>0</v>
       </c>
       <c r="T90" s="51">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="U90" s="51">
         <f t="shared" si="21"/>
         <v>0</v>
       </c>
-      <c r="U90" s="51">
+      <c r="V90" s="51">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="V90" s="51">
+      <c r="W90" s="52">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="W90" s="52">
+      <c r="X90" s="48"/>
+      <c r="Y90" s="58">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="X90" s="48"/>
-      <c r="Y90" s="51">
+      <c r="Z90" s="49" t="str">
         <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="Z90" s="49" t="str">
-        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="AA90" s="64"/>
     </row>
     <row r="91" spans="1:27">
       <c r="A91" s="62" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="B91" s="44"/>
       <c r="C91" s="46"/>
       <c r="D91" s="46"/>
       <c r="E91" s="50">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="F91" s="48"/>
       <c r="G91" s="51">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="H91" s="44"/>
@@ -7733,47 +7734,47 @@
         <v>0</v>
       </c>
       <c r="T91" s="51">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="U91" s="51">
         <f t="shared" si="21"/>
         <v>0</v>
       </c>
-      <c r="U91" s="51">
+      <c r="V91" s="51">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="V91" s="51">
+      <c r="W91" s="52">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="W91" s="52">
+      <c r="X91" s="48"/>
+      <c r="Y91" s="58">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="X91" s="48"/>
-      <c r="Y91" s="51">
+      <c r="Z91" s="49" t="str">
         <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="Z91" s="49" t="str">
-        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="AA91" s="64"/>
     </row>
     <row r="92" spans="1:27">
       <c r="A92" s="62" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="B92" s="44"/>
       <c r="C92" s="46"/>
       <c r="D92" s="46"/>
       <c r="E92" s="50">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="F92" s="48"/>
       <c r="G92" s="51">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="H92" s="44"/>
@@ -7792,47 +7793,47 @@
         <v>0</v>
       </c>
       <c r="T92" s="51">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="U92" s="51">
         <f t="shared" si="21"/>
         <v>0</v>
       </c>
-      <c r="U92" s="51">
+      <c r="V92" s="51">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="V92" s="51">
+      <c r="W92" s="52">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="W92" s="52">
+      <c r="X92" s="48"/>
+      <c r="Y92" s="58">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="X92" s="48"/>
-      <c r="Y92" s="51">
+      <c r="Z92" s="49" t="str">
         <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="Z92" s="49" t="str">
-        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="AA92" s="64"/>
     </row>
     <row r="93" spans="1:27">
       <c r="A93" s="62" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="B93" s="44"/>
       <c r="C93" s="46"/>
       <c r="D93" s="46"/>
       <c r="E93" s="50">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="F93" s="48"/>
       <c r="G93" s="51">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="H93" s="44"/>
@@ -7851,47 +7852,47 @@
         <v>0</v>
       </c>
       <c r="T93" s="51">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="U93" s="51">
         <f t="shared" si="21"/>
         <v>0</v>
       </c>
-      <c r="U93" s="51">
+      <c r="V93" s="51">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="V93" s="51">
+      <c r="W93" s="52">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="W93" s="52">
+      <c r="X93" s="48"/>
+      <c r="Y93" s="58">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="X93" s="48"/>
-      <c r="Y93" s="51">
+      <c r="Z93" s="49" t="str">
         <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="Z93" s="49" t="str">
-        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="AA93" s="64"/>
     </row>
     <row r="94" spans="1:27">
       <c r="A94" s="62" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="B94" s="44"/>
       <c r="C94" s="46"/>
       <c r="D94" s="46"/>
       <c r="E94" s="50">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="F94" s="48"/>
       <c r="G94" s="51">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="H94" s="44"/>
@@ -7910,47 +7911,47 @@
         <v>0</v>
       </c>
       <c r="T94" s="51">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="U94" s="51">
         <f t="shared" si="21"/>
         <v>0</v>
       </c>
-      <c r="U94" s="51">
+      <c r="V94" s="51">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="V94" s="51">
+      <c r="W94" s="52">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="W94" s="52">
+      <c r="X94" s="48"/>
+      <c r="Y94" s="58">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="X94" s="48"/>
-      <c r="Y94" s="51">
+      <c r="Z94" s="49" t="str">
         <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="Z94" s="49" t="str">
-        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="AA94" s="64"/>
     </row>
     <row r="95" spans="1:27">
       <c r="A95" s="62" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="B95" s="44"/>
       <c r="C95" s="46"/>
       <c r="D95" s="46"/>
       <c r="E95" s="50">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="F95" s="48"/>
       <c r="G95" s="51">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="H95" s="44"/>
@@ -7969,47 +7970,47 @@
         <v>0</v>
       </c>
       <c r="T95" s="51">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="U95" s="51">
         <f t="shared" si="21"/>
         <v>0</v>
       </c>
-      <c r="U95" s="51">
+      <c r="V95" s="51">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="V95" s="51">
+      <c r="W95" s="52">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="W95" s="52">
+      <c r="X95" s="48"/>
+      <c r="Y95" s="58">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="X95" s="48"/>
-      <c r="Y95" s="51">
+      <c r="Z95" s="49" t="str">
         <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="Z95" s="49" t="str">
-        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="AA95" s="64"/>
     </row>
     <row r="96" spans="1:27">
       <c r="A96" s="62" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="B96" s="44"/>
       <c r="C96" s="46"/>
       <c r="D96" s="46"/>
       <c r="E96" s="50">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="F96" s="48"/>
       <c r="G96" s="51">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="H96" s="44"/>
@@ -8028,47 +8029,47 @@
         <v>0</v>
       </c>
       <c r="T96" s="51">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="U96" s="51">
         <f t="shared" si="21"/>
         <v>0</v>
       </c>
-      <c r="U96" s="51">
+      <c r="V96" s="51">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="V96" s="51">
+      <c r="W96" s="52">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="W96" s="52">
+      <c r="X96" s="48"/>
+      <c r="Y96" s="58">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="X96" s="48"/>
-      <c r="Y96" s="51">
+      <c r="Z96" s="49" t="str">
         <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="Z96" s="49" t="str">
-        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="AA96" s="64"/>
     </row>
     <row r="97" spans="1:27">
       <c r="A97" s="62" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="B97" s="44"/>
       <c r="C97" s="46"/>
       <c r="D97" s="46"/>
       <c r="E97" s="50">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="F97" s="48"/>
       <c r="G97" s="51">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="H97" s="44"/>
@@ -8087,47 +8088,47 @@
         <v>0</v>
       </c>
       <c r="T97" s="51">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="U97" s="51">
         <f t="shared" si="21"/>
         <v>0</v>
       </c>
-      <c r="U97" s="51">
+      <c r="V97" s="51">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="V97" s="51">
+      <c r="W97" s="52">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="W97" s="52">
+      <c r="X97" s="48"/>
+      <c r="Y97" s="58">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="X97" s="48"/>
-      <c r="Y97" s="51">
+      <c r="Z97" s="49" t="str">
         <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="Z97" s="49" t="str">
-        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="AA97" s="64"/>
     </row>
     <row r="98" spans="1:27">
       <c r="A98" s="62" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="B98" s="44"/>
       <c r="C98" s="46"/>
       <c r="D98" s="46"/>
       <c r="E98" s="50">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="F98" s="48"/>
       <c r="G98" s="51">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="H98" s="44"/>
@@ -8146,47 +8147,47 @@
         <v>0</v>
       </c>
       <c r="T98" s="51">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="U98" s="51">
         <f t="shared" si="21"/>
         <v>0</v>
       </c>
-      <c r="U98" s="51">
+      <c r="V98" s="51">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="V98" s="51">
+      <c r="W98" s="52">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="W98" s="52">
+      <c r="X98" s="48"/>
+      <c r="Y98" s="58">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="X98" s="48"/>
-      <c r="Y98" s="51">
+      <c r="Z98" s="49" t="str">
         <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="Z98" s="49" t="str">
-        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="AA98" s="64"/>
     </row>
     <row r="99" spans="1:27">
       <c r="A99" s="62" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="B99" s="44"/>
       <c r="C99" s="46"/>
       <c r="D99" s="46"/>
       <c r="E99" s="50">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="F99" s="48"/>
       <c r="G99" s="51">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="H99" s="44"/>
@@ -8205,47 +8206,47 @@
         <v>0</v>
       </c>
       <c r="T99" s="51">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="U99" s="51">
         <f t="shared" si="21"/>
         <v>0</v>
       </c>
-      <c r="U99" s="51">
+      <c r="V99" s="51">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="V99" s="51">
+      <c r="W99" s="52">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="W99" s="52">
+      <c r="X99" s="48"/>
+      <c r="Y99" s="58">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="X99" s="48"/>
-      <c r="Y99" s="51">
+      <c r="Z99" s="49" t="str">
         <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="Z99" s="49" t="str">
-        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="AA99" s="64"/>
     </row>
     <row r="100" spans="1:27">
       <c r="A100" s="62" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="B100" s="44"/>
       <c r="C100" s="46"/>
       <c r="D100" s="46"/>
       <c r="E100" s="50">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="F100" s="48"/>
       <c r="G100" s="51">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="H100" s="44"/>
@@ -8264,47 +8265,47 @@
         <v>0</v>
       </c>
       <c r="T100" s="51">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="U100" s="51">
         <f t="shared" si="21"/>
         <v>0</v>
       </c>
-      <c r="U100" s="51">
+      <c r="V100" s="51">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="V100" s="51">
+      <c r="W100" s="52">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="W100" s="52">
+      <c r="X100" s="48"/>
+      <c r="Y100" s="58">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="X100" s="48"/>
-      <c r="Y100" s="51">
+      <c r="Z100" s="49" t="str">
         <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="Z100" s="49" t="str">
-        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="AA100" s="64"/>
     </row>
     <row r="101" spans="1:27">
       <c r="A101" s="62" t="str">
-        <f t="shared" ref="A101:A132" si="27">IF(B101="","","LOC-"&amp;TEXT(ROW()-5,"000"))</f>
+        <f t="shared" ref="A101:A132" si="26">IF(B101="","","LOC-"&amp;TEXT(ROW()-5,"000"))</f>
         <v/>
       </c>
       <c r="B101" s="44"/>
       <c r="C101" s="46"/>
       <c r="D101" s="46"/>
       <c r="E101" s="50">
-        <f t="shared" ref="E101:E132" si="28">IF(OR(B101="",C101="",D101=""),0,MAX(0,D101-C101))</f>
+        <f t="shared" ref="E101:E132" si="27">IF(OR(B101="",C101="",D101=""),0,MAX(0,D101-C101))</f>
         <v>0</v>
       </c>
       <c r="F101" s="48"/>
       <c r="G101" s="51">
-        <f t="shared" ref="G101:G132" si="29">IF(OR(B101="",E101=0,F101=""),0,E101*F101)</f>
+        <f t="shared" ref="G101:G132" si="28">IF(OR(B101="",E101=0,F101=""),0,E101*F101)</f>
         <v>0</v>
       </c>
       <c r="H101" s="44"/>
@@ -8323,47 +8324,47 @@
         <v>0</v>
       </c>
       <c r="T101" s="51">
-        <f t="shared" ref="T101:T132" si="30">IF(OR(B101="",E101=0),0,S101/E101)</f>
+        <f t="shared" ref="T101:T132" si="29">IF(OR(B101="",E101=0),0,S101/E101)</f>
         <v>0</v>
       </c>
       <c r="U101" s="51">
-        <f t="shared" ref="U101:U132" si="31">IF(B101="",0,G101-S101)</f>
+        <f t="shared" ref="U101:U132" si="30">IF(B101="",0,G101-S101)</f>
         <v>0</v>
       </c>
       <c r="V101" s="51">
-        <f t="shared" ref="V101:V132" si="32">IF(OR(B101="",E101=0),0,U101/E101)</f>
+        <f t="shared" ref="V101:V132" si="31">IF(OR(B101="",E101=0),0,U101/E101)</f>
         <v>0</v>
       </c>
       <c r="W101" s="52">
-        <f t="shared" ref="W101:W132" si="33">IF(OR(B101="",G101=0),0,U101/G101)</f>
+        <f t="shared" ref="W101:W132" si="32">IF(OR(B101="",G101=0),0,U101/G101)</f>
         <v>0</v>
       </c>
       <c r="X101" s="48"/>
-      <c r="Y101" s="51">
-        <f t="shared" ref="Y101:Y132" si="34">IF(B101="",0,IFERROR(MAX(0,G101-X101),G101))</f>
+      <c r="Y101" s="58">
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="Z101" s="49" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="AA101" s="64"/>
     </row>
     <row r="102" spans="1:27">
       <c r="A102" s="62" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="B102" s="44"/>
       <c r="C102" s="46"/>
       <c r="D102" s="46"/>
       <c r="E102" s="50">
-        <f t="shared" si="28"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="F102" s="48"/>
       <c r="G102" s="51">
-        <f t="shared" si="29"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="H102" s="44"/>
@@ -8382,47 +8383,47 @@
         <v>0</v>
       </c>
       <c r="T102" s="51">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="U102" s="51">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="U102" s="51">
+      <c r="V102" s="51">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="V102" s="51">
+      <c r="W102" s="52">
         <f t="shared" si="32"/>
         <v>0</v>
       </c>
-      <c r="W102" s="52">
-        <f t="shared" si="33"/>
-        <v>0</v>
-      </c>
       <c r="X102" s="48"/>
-      <c r="Y102" s="51">
-        <f t="shared" si="34"/>
+      <c r="Y102" s="58">
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="Z102" s="49" t="str">
-        <f t="shared" ref="Z102:Z133" si="35">IF(B102="","",IF(COUNTIFS($C$6:$C$204,"&lt;"&amp;D102,$D$6:$D$204,"&gt;"&amp;C102,$I$6:$I$204,"&lt;&gt;Cancelada",$I$6:$I$204,"&lt;&gt;Consulta")&gt;1,"CONFLITO","OK"))</f>
+        <f t="shared" ref="Z102:Z133" si="33">IF(B102="","",IF(COUNTIFS($C$6:$C$204,"&lt;"&amp;D102,$D$6:$D$204,"&gt;"&amp;C102,$I$6:$I$204,"&lt;&gt;Cancelada",$I$6:$I$204,"&lt;&gt;Consulta")&gt;1,"CONFLITO","OK"))</f>
         <v/>
       </c>
       <c r="AA102" s="64"/>
     </row>
     <row r="103" spans="1:27">
       <c r="A103" s="62" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="B103" s="44"/>
       <c r="C103" s="46"/>
       <c r="D103" s="46"/>
       <c r="E103" s="50">
-        <f t="shared" si="28"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="F103" s="48"/>
       <c r="G103" s="51">
-        <f t="shared" si="29"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="H103" s="44"/>
@@ -8441,47 +8442,47 @@
         <v>0</v>
       </c>
       <c r="T103" s="51">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="U103" s="51">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="U103" s="51">
+      <c r="V103" s="51">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="V103" s="51">
+      <c r="W103" s="52">
         <f t="shared" si="32"/>
         <v>0</v>
       </c>
-      <c r="W103" s="52">
+      <c r="X103" s="48"/>
+      <c r="Y103" s="58">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="Z103" s="49" t="str">
         <f t="shared" si="33"/>
-        <v>0</v>
-      </c>
-      <c r="X103" s="48"/>
-      <c r="Y103" s="51">
-        <f t="shared" si="34"/>
-        <v>0</v>
-      </c>
-      <c r="Z103" s="49" t="str">
-        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="AA103" s="64"/>
     </row>
     <row r="104" spans="1:27">
       <c r="A104" s="62" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="B104" s="44"/>
       <c r="C104" s="46"/>
       <c r="D104" s="46"/>
       <c r="E104" s="50">
-        <f t="shared" si="28"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="F104" s="48"/>
       <c r="G104" s="51">
-        <f t="shared" si="29"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="H104" s="44"/>
@@ -8500,47 +8501,47 @@
         <v>0</v>
       </c>
       <c r="T104" s="51">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="U104" s="51">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="U104" s="51">
+      <c r="V104" s="51">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="V104" s="51">
+      <c r="W104" s="52">
         <f t="shared" si="32"/>
         <v>0</v>
       </c>
-      <c r="W104" s="52">
+      <c r="X104" s="48"/>
+      <c r="Y104" s="58">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="Z104" s="49" t="str">
         <f t="shared" si="33"/>
-        <v>0</v>
-      </c>
-      <c r="X104" s="48"/>
-      <c r="Y104" s="51">
-        <f t="shared" si="34"/>
-        <v>0</v>
-      </c>
-      <c r="Z104" s="49" t="str">
-        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="AA104" s="64"/>
     </row>
     <row r="105" spans="1:27">
       <c r="A105" s="62" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="B105" s="44"/>
       <c r="C105" s="46"/>
       <c r="D105" s="46"/>
       <c r="E105" s="50">
-        <f t="shared" si="28"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="F105" s="48"/>
       <c r="G105" s="51">
-        <f t="shared" si="29"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="H105" s="44"/>
@@ -8559,47 +8560,47 @@
         <v>0</v>
       </c>
       <c r="T105" s="51">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="U105" s="51">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="U105" s="51">
+      <c r="V105" s="51">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="V105" s="51">
+      <c r="W105" s="52">
         <f t="shared" si="32"/>
         <v>0</v>
       </c>
-      <c r="W105" s="52">
+      <c r="X105" s="48"/>
+      <c r="Y105" s="58">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="Z105" s="49" t="str">
         <f t="shared" si="33"/>
-        <v>0</v>
-      </c>
-      <c r="X105" s="48"/>
-      <c r="Y105" s="51">
-        <f t="shared" si="34"/>
-        <v>0</v>
-      </c>
-      <c r="Z105" s="49" t="str">
-        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="AA105" s="64"/>
     </row>
     <row r="106" spans="1:27">
       <c r="A106" s="62" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="B106" s="44"/>
       <c r="C106" s="46"/>
       <c r="D106" s="46"/>
       <c r="E106" s="50">
-        <f t="shared" si="28"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="F106" s="48"/>
       <c r="G106" s="51">
-        <f t="shared" si="29"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="H106" s="44"/>
@@ -8618,47 +8619,47 @@
         <v>0</v>
       </c>
       <c r="T106" s="51">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="U106" s="51">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="U106" s="51">
+      <c r="V106" s="51">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="V106" s="51">
+      <c r="W106" s="52">
         <f t="shared" si="32"/>
         <v>0</v>
       </c>
-      <c r="W106" s="52">
+      <c r="X106" s="48"/>
+      <c r="Y106" s="58">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="Z106" s="49" t="str">
         <f t="shared" si="33"/>
-        <v>0</v>
-      </c>
-      <c r="X106" s="48"/>
-      <c r="Y106" s="51">
-        <f t="shared" si="34"/>
-        <v>0</v>
-      </c>
-      <c r="Z106" s="49" t="str">
-        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="AA106" s="64"/>
     </row>
     <row r="107" spans="1:27">
       <c r="A107" s="62" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="B107" s="44"/>
       <c r="C107" s="46"/>
       <c r="D107" s="46"/>
       <c r="E107" s="50">
-        <f t="shared" si="28"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="F107" s="48"/>
       <c r="G107" s="51">
-        <f t="shared" si="29"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="H107" s="44"/>
@@ -8677,47 +8678,47 @@
         <v>0</v>
       </c>
       <c r="T107" s="51">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="U107" s="51">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="U107" s="51">
+      <c r="V107" s="51">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="V107" s="51">
+      <c r="W107" s="52">
         <f t="shared" si="32"/>
         <v>0</v>
       </c>
-      <c r="W107" s="52">
+      <c r="X107" s="48"/>
+      <c r="Y107" s="58">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="Z107" s="49" t="str">
         <f t="shared" si="33"/>
-        <v>0</v>
-      </c>
-      <c r="X107" s="48"/>
-      <c r="Y107" s="51">
-        <f t="shared" si="34"/>
-        <v>0</v>
-      </c>
-      <c r="Z107" s="49" t="str">
-        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="AA107" s="64"/>
     </row>
     <row r="108" spans="1:27">
       <c r="A108" s="62" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="B108" s="44"/>
       <c r="C108" s="46"/>
       <c r="D108" s="46"/>
       <c r="E108" s="50">
-        <f t="shared" si="28"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="F108" s="48"/>
       <c r="G108" s="51">
-        <f t="shared" si="29"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="H108" s="44"/>
@@ -8736,47 +8737,47 @@
         <v>0</v>
       </c>
       <c r="T108" s="51">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="U108" s="51">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="U108" s="51">
+      <c r="V108" s="51">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="V108" s="51">
+      <c r="W108" s="52">
         <f t="shared" si="32"/>
         <v>0</v>
       </c>
-      <c r="W108" s="52">
+      <c r="X108" s="48"/>
+      <c r="Y108" s="58">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="Z108" s="49" t="str">
         <f t="shared" si="33"/>
-        <v>0</v>
-      </c>
-      <c r="X108" s="48"/>
-      <c r="Y108" s="51">
-        <f t="shared" si="34"/>
-        <v>0</v>
-      </c>
-      <c r="Z108" s="49" t="str">
-        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="AA108" s="64"/>
     </row>
     <row r="109" spans="1:27">
       <c r="A109" s="62" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="B109" s="44"/>
       <c r="C109" s="46"/>
       <c r="D109" s="46"/>
       <c r="E109" s="50">
-        <f t="shared" si="28"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="F109" s="48"/>
       <c r="G109" s="51">
-        <f t="shared" si="29"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="H109" s="44"/>
@@ -8795,47 +8796,47 @@
         <v>0</v>
       </c>
       <c r="T109" s="51">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="U109" s="51">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="U109" s="51">
+      <c r="V109" s="51">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="V109" s="51">
+      <c r="W109" s="52">
         <f t="shared" si="32"/>
         <v>0</v>
       </c>
-      <c r="W109" s="52">
+      <c r="X109" s="48"/>
+      <c r="Y109" s="58">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="Z109" s="49" t="str">
         <f t="shared" si="33"/>
-        <v>0</v>
-      </c>
-      <c r="X109" s="48"/>
-      <c r="Y109" s="51">
-        <f t="shared" si="34"/>
-        <v>0</v>
-      </c>
-      <c r="Z109" s="49" t="str">
-        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="AA109" s="64"/>
     </row>
     <row r="110" spans="1:27">
       <c r="A110" s="62" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="B110" s="44"/>
       <c r="C110" s="46"/>
       <c r="D110" s="46"/>
       <c r="E110" s="50">
-        <f t="shared" si="28"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="F110" s="48"/>
       <c r="G110" s="51">
-        <f t="shared" si="29"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="H110" s="44"/>
@@ -8854,47 +8855,47 @@
         <v>0</v>
       </c>
       <c r="T110" s="51">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="U110" s="51">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="U110" s="51">
+      <c r="V110" s="51">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="V110" s="51">
+      <c r="W110" s="52">
         <f t="shared" si="32"/>
         <v>0</v>
       </c>
-      <c r="W110" s="52">
+      <c r="X110" s="48"/>
+      <c r="Y110" s="58">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="Z110" s="49" t="str">
         <f t="shared" si="33"/>
-        <v>0</v>
-      </c>
-      <c r="X110" s="48"/>
-      <c r="Y110" s="51">
-        <f t="shared" si="34"/>
-        <v>0</v>
-      </c>
-      <c r="Z110" s="49" t="str">
-        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="AA110" s="64"/>
     </row>
     <row r="111" spans="1:27">
       <c r="A111" s="62" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="B111" s="44"/>
       <c r="C111" s="46"/>
       <c r="D111" s="46"/>
       <c r="E111" s="50">
-        <f t="shared" si="28"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="F111" s="48"/>
       <c r="G111" s="51">
-        <f t="shared" si="29"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="H111" s="44"/>
@@ -8913,47 +8914,47 @@
         <v>0</v>
       </c>
       <c r="T111" s="51">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="U111" s="51">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="U111" s="51">
+      <c r="V111" s="51">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="V111" s="51">
+      <c r="W111" s="52">
         <f t="shared" si="32"/>
         <v>0</v>
       </c>
-      <c r="W111" s="52">
+      <c r="X111" s="48"/>
+      <c r="Y111" s="58">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="Z111" s="49" t="str">
         <f t="shared" si="33"/>
-        <v>0</v>
-      </c>
-      <c r="X111" s="48"/>
-      <c r="Y111" s="51">
-        <f t="shared" si="34"/>
-        <v>0</v>
-      </c>
-      <c r="Z111" s="49" t="str">
-        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="AA111" s="64"/>
     </row>
     <row r="112" spans="1:27">
       <c r="A112" s="62" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="B112" s="44"/>
       <c r="C112" s="46"/>
       <c r="D112" s="46"/>
       <c r="E112" s="50">
-        <f t="shared" si="28"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="F112" s="48"/>
       <c r="G112" s="51">
-        <f t="shared" si="29"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="H112" s="44"/>
@@ -8972,47 +8973,47 @@
         <v>0</v>
       </c>
       <c r="T112" s="51">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="U112" s="51">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="U112" s="51">
+      <c r="V112" s="51">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="V112" s="51">
+      <c r="W112" s="52">
         <f t="shared" si="32"/>
         <v>0</v>
       </c>
-      <c r="W112" s="52">
+      <c r="X112" s="48"/>
+      <c r="Y112" s="58">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="Z112" s="49" t="str">
         <f t="shared" si="33"/>
-        <v>0</v>
-      </c>
-      <c r="X112" s="48"/>
-      <c r="Y112" s="51">
-        <f t="shared" si="34"/>
-        <v>0</v>
-      </c>
-      <c r="Z112" s="49" t="str">
-        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="AA112" s="64"/>
     </row>
     <row r="113" spans="1:27">
       <c r="A113" s="62" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="B113" s="44"/>
       <c r="C113" s="46"/>
       <c r="D113" s="46"/>
       <c r="E113" s="50">
-        <f t="shared" si="28"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="F113" s="48"/>
       <c r="G113" s="51">
-        <f t="shared" si="29"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="H113" s="44"/>
@@ -9031,47 +9032,47 @@
         <v>0</v>
       </c>
       <c r="T113" s="51">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="U113" s="51">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="U113" s="51">
+      <c r="V113" s="51">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="V113" s="51">
+      <c r="W113" s="52">
         <f t="shared" si="32"/>
         <v>0</v>
       </c>
-      <c r="W113" s="52">
+      <c r="X113" s="48"/>
+      <c r="Y113" s="58">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="Z113" s="49" t="str">
         <f t="shared" si="33"/>
-        <v>0</v>
-      </c>
-      <c r="X113" s="48"/>
-      <c r="Y113" s="51">
-        <f t="shared" si="34"/>
-        <v>0</v>
-      </c>
-      <c r="Z113" s="49" t="str">
-        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="AA113" s="64"/>
     </row>
     <row r="114" spans="1:27">
       <c r="A114" s="62" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="B114" s="44"/>
       <c r="C114" s="46"/>
       <c r="D114" s="46"/>
       <c r="E114" s="50">
-        <f t="shared" si="28"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="F114" s="48"/>
       <c r="G114" s="51">
-        <f t="shared" si="29"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="H114" s="44"/>
@@ -9090,47 +9091,47 @@
         <v>0</v>
       </c>
       <c r="T114" s="51">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="U114" s="51">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="U114" s="51">
+      <c r="V114" s="51">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="V114" s="51">
+      <c r="W114" s="52">
         <f t="shared" si="32"/>
         <v>0</v>
       </c>
-      <c r="W114" s="52">
+      <c r="X114" s="48"/>
+      <c r="Y114" s="58">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="Z114" s="49" t="str">
         <f t="shared" si="33"/>
-        <v>0</v>
-      </c>
-      <c r="X114" s="48"/>
-      <c r="Y114" s="51">
-        <f t="shared" si="34"/>
-        <v>0</v>
-      </c>
-      <c r="Z114" s="49" t="str">
-        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="AA114" s="64"/>
     </row>
     <row r="115" spans="1:27">
       <c r="A115" s="62" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="B115" s="44"/>
       <c r="C115" s="46"/>
       <c r="D115" s="46"/>
       <c r="E115" s="50">
-        <f t="shared" si="28"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="F115" s="48"/>
       <c r="G115" s="51">
-        <f t="shared" si="29"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="H115" s="44"/>
@@ -9149,47 +9150,47 @@
         <v>0</v>
       </c>
       <c r="T115" s="51">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="U115" s="51">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="U115" s="51">
+      <c r="V115" s="51">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="V115" s="51">
+      <c r="W115" s="52">
         <f t="shared" si="32"/>
         <v>0</v>
       </c>
-      <c r="W115" s="52">
+      <c r="X115" s="48"/>
+      <c r="Y115" s="58">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="Z115" s="49" t="str">
         <f t="shared" si="33"/>
-        <v>0</v>
-      </c>
-      <c r="X115" s="48"/>
-      <c r="Y115" s="51">
-        <f t="shared" si="34"/>
-        <v>0</v>
-      </c>
-      <c r="Z115" s="49" t="str">
-        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="AA115" s="64"/>
     </row>
     <row r="116" spans="1:27">
       <c r="A116" s="62" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="B116" s="44"/>
       <c r="C116" s="46"/>
       <c r="D116" s="46"/>
       <c r="E116" s="50">
-        <f t="shared" si="28"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="F116" s="48"/>
       <c r="G116" s="51">
-        <f t="shared" si="29"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="H116" s="44"/>
@@ -9208,47 +9209,47 @@
         <v>0</v>
       </c>
       <c r="T116" s="51">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="U116" s="51">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="U116" s="51">
+      <c r="V116" s="51">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="V116" s="51">
+      <c r="W116" s="52">
         <f t="shared" si="32"/>
         <v>0</v>
       </c>
-      <c r="W116" s="52">
+      <c r="X116" s="48"/>
+      <c r="Y116" s="58">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="Z116" s="49" t="str">
         <f t="shared" si="33"/>
-        <v>0</v>
-      </c>
-      <c r="X116" s="48"/>
-      <c r="Y116" s="51">
-        <f t="shared" si="34"/>
-        <v>0</v>
-      </c>
-      <c r="Z116" s="49" t="str">
-        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="AA116" s="64"/>
     </row>
     <row r="117" spans="1:27">
       <c r="A117" s="62" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="B117" s="44"/>
       <c r="C117" s="46"/>
       <c r="D117" s="46"/>
       <c r="E117" s="50">
-        <f t="shared" si="28"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="F117" s="48"/>
       <c r="G117" s="51">
-        <f t="shared" si="29"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="H117" s="44"/>
@@ -9267,47 +9268,47 @@
         <v>0</v>
       </c>
       <c r="T117" s="51">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="U117" s="51">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="U117" s="51">
+      <c r="V117" s="51">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="V117" s="51">
+      <c r="W117" s="52">
         <f t="shared" si="32"/>
         <v>0</v>
       </c>
-      <c r="W117" s="52">
+      <c r="X117" s="48"/>
+      <c r="Y117" s="58">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="Z117" s="49" t="str">
         <f t="shared" si="33"/>
-        <v>0</v>
-      </c>
-      <c r="X117" s="48"/>
-      <c r="Y117" s="51">
-        <f t="shared" si="34"/>
-        <v>0</v>
-      </c>
-      <c r="Z117" s="49" t="str">
-        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="AA117" s="64"/>
     </row>
     <row r="118" spans="1:27">
       <c r="A118" s="62" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="B118" s="44"/>
       <c r="C118" s="46"/>
       <c r="D118" s="46"/>
       <c r="E118" s="50">
-        <f t="shared" si="28"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="F118" s="48"/>
       <c r="G118" s="51">
-        <f t="shared" si="29"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="H118" s="44"/>
@@ -9326,47 +9327,47 @@
         <v>0</v>
       </c>
       <c r="T118" s="51">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="U118" s="51">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="U118" s="51">
+      <c r="V118" s="51">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="V118" s="51">
+      <c r="W118" s="52">
         <f t="shared" si="32"/>
         <v>0</v>
       </c>
-      <c r="W118" s="52">
+      <c r="X118" s="48"/>
+      <c r="Y118" s="58">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="Z118" s="49" t="str">
         <f t="shared" si="33"/>
-        <v>0</v>
-      </c>
-      <c r="X118" s="48"/>
-      <c r="Y118" s="51">
-        <f t="shared" si="34"/>
-        <v>0</v>
-      </c>
-      <c r="Z118" s="49" t="str">
-        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="AA118" s="64"/>
     </row>
     <row r="119" spans="1:27">
       <c r="A119" s="62" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="B119" s="44"/>
       <c r="C119" s="46"/>
       <c r="D119" s="46"/>
       <c r="E119" s="50">
-        <f t="shared" si="28"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="F119" s="48"/>
       <c r="G119" s="51">
-        <f t="shared" si="29"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="H119" s="44"/>
@@ -9385,47 +9386,47 @@
         <v>0</v>
       </c>
       <c r="T119" s="51">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="U119" s="51">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="U119" s="51">
+      <c r="V119" s="51">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="V119" s="51">
+      <c r="W119" s="52">
         <f t="shared" si="32"/>
         <v>0</v>
       </c>
-      <c r="W119" s="52">
+      <c r="X119" s="48"/>
+      <c r="Y119" s="58">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="Z119" s="49" t="str">
         <f t="shared" si="33"/>
-        <v>0</v>
-      </c>
-      <c r="X119" s="48"/>
-      <c r="Y119" s="51">
-        <f t="shared" si="34"/>
-        <v>0</v>
-      </c>
-      <c r="Z119" s="49" t="str">
-        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="AA119" s="64"/>
     </row>
     <row r="120" spans="1:27">
       <c r="A120" s="62" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="B120" s="44"/>
       <c r="C120" s="46"/>
       <c r="D120" s="46"/>
       <c r="E120" s="50">
-        <f t="shared" si="28"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="F120" s="48"/>
       <c r="G120" s="51">
-        <f t="shared" si="29"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="H120" s="44"/>
@@ -9444,47 +9445,47 @@
         <v>0</v>
       </c>
       <c r="T120" s="51">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="U120" s="51">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="U120" s="51">
+      <c r="V120" s="51">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="V120" s="51">
+      <c r="W120" s="52">
         <f t="shared" si="32"/>
         <v>0</v>
       </c>
-      <c r="W120" s="52">
+      <c r="X120" s="48"/>
+      <c r="Y120" s="58">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="Z120" s="49" t="str">
         <f t="shared" si="33"/>
-        <v>0</v>
-      </c>
-      <c r="X120" s="48"/>
-      <c r="Y120" s="51">
-        <f t="shared" si="34"/>
-        <v>0</v>
-      </c>
-      <c r="Z120" s="49" t="str">
-        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="AA120" s="64"/>
     </row>
     <row r="121" spans="1:27">
       <c r="A121" s="62" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="B121" s="44"/>
       <c r="C121" s="46"/>
       <c r="D121" s="46"/>
       <c r="E121" s="50">
-        <f t="shared" si="28"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="F121" s="48"/>
       <c r="G121" s="51">
-        <f t="shared" si="29"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="H121" s="44"/>
@@ -9503,47 +9504,47 @@
         <v>0</v>
       </c>
       <c r="T121" s="51">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="U121" s="51">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="U121" s="51">
+      <c r="V121" s="51">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="V121" s="51">
+      <c r="W121" s="52">
         <f t="shared" si="32"/>
         <v>0</v>
       </c>
-      <c r="W121" s="52">
+      <c r="X121" s="48"/>
+      <c r="Y121" s="58">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="Z121" s="49" t="str">
         <f t="shared" si="33"/>
-        <v>0</v>
-      </c>
-      <c r="X121" s="48"/>
-      <c r="Y121" s="51">
-        <f t="shared" si="34"/>
-        <v>0</v>
-      </c>
-      <c r="Z121" s="49" t="str">
-        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="AA121" s="64"/>
     </row>
     <row r="122" spans="1:27">
       <c r="A122" s="62" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="B122" s="44"/>
       <c r="C122" s="46"/>
       <c r="D122" s="46"/>
       <c r="E122" s="50">
-        <f t="shared" si="28"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="F122" s="48"/>
       <c r="G122" s="51">
-        <f t="shared" si="29"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="H122" s="44"/>
@@ -9562,47 +9563,47 @@
         <v>0</v>
       </c>
       <c r="T122" s="51">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="U122" s="51">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="U122" s="51">
+      <c r="V122" s="51">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="V122" s="51">
+      <c r="W122" s="52">
         <f t="shared" si="32"/>
         <v>0</v>
       </c>
-      <c r="W122" s="52">
+      <c r="X122" s="48"/>
+      <c r="Y122" s="58">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="Z122" s="49" t="str">
         <f t="shared" si="33"/>
-        <v>0</v>
-      </c>
-      <c r="X122" s="48"/>
-      <c r="Y122" s="51">
-        <f t="shared" si="34"/>
-        <v>0</v>
-      </c>
-      <c r="Z122" s="49" t="str">
-        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="AA122" s="64"/>
     </row>
     <row r="123" spans="1:27">
       <c r="A123" s="62" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="B123" s="44"/>
       <c r="C123" s="46"/>
       <c r="D123" s="46"/>
       <c r="E123" s="50">
-        <f t="shared" si="28"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="F123" s="48"/>
       <c r="G123" s="51">
-        <f t="shared" si="29"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="H123" s="44"/>
@@ -9621,47 +9622,47 @@
         <v>0</v>
       </c>
       <c r="T123" s="51">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="U123" s="51">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="U123" s="51">
+      <c r="V123" s="51">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="V123" s="51">
+      <c r="W123" s="52">
         <f t="shared" si="32"/>
         <v>0</v>
       </c>
-      <c r="W123" s="52">
+      <c r="X123" s="48"/>
+      <c r="Y123" s="58">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="Z123" s="49" t="str">
         <f t="shared" si="33"/>
-        <v>0</v>
-      </c>
-      <c r="X123" s="48"/>
-      <c r="Y123" s="51">
-        <f t="shared" si="34"/>
-        <v>0</v>
-      </c>
-      <c r="Z123" s="49" t="str">
-        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="AA123" s="64"/>
     </row>
     <row r="124" spans="1:27">
       <c r="A124" s="62" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="B124" s="44"/>
       <c r="C124" s="46"/>
       <c r="D124" s="46"/>
       <c r="E124" s="50">
-        <f t="shared" si="28"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="F124" s="48"/>
       <c r="G124" s="51">
-        <f t="shared" si="29"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="H124" s="44"/>
@@ -9680,47 +9681,47 @@
         <v>0</v>
       </c>
       <c r="T124" s="51">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="U124" s="51">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="U124" s="51">
+      <c r="V124" s="51">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="V124" s="51">
+      <c r="W124" s="52">
         <f t="shared" si="32"/>
         <v>0</v>
       </c>
-      <c r="W124" s="52">
+      <c r="X124" s="48"/>
+      <c r="Y124" s="58">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="Z124" s="49" t="str">
         <f t="shared" si="33"/>
-        <v>0</v>
-      </c>
-      <c r="X124" s="48"/>
-      <c r="Y124" s="51">
-        <f t="shared" si="34"/>
-        <v>0</v>
-      </c>
-      <c r="Z124" s="49" t="str">
-        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="AA124" s="64"/>
     </row>
     <row r="125" spans="1:27">
       <c r="A125" s="62" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="B125" s="44"/>
       <c r="C125" s="46"/>
       <c r="D125" s="46"/>
       <c r="E125" s="50">
-        <f t="shared" si="28"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="F125" s="48"/>
       <c r="G125" s="51">
-        <f t="shared" si="29"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="H125" s="44"/>
@@ -9739,47 +9740,47 @@
         <v>0</v>
       </c>
       <c r="T125" s="51">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="U125" s="51">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="U125" s="51">
+      <c r="V125" s="51">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="V125" s="51">
+      <c r="W125" s="52">
         <f t="shared" si="32"/>
         <v>0</v>
       </c>
-      <c r="W125" s="52">
+      <c r="X125" s="48"/>
+      <c r="Y125" s="58">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="Z125" s="49" t="str">
         <f t="shared" si="33"/>
-        <v>0</v>
-      </c>
-      <c r="X125" s="48"/>
-      <c r="Y125" s="51">
-        <f t="shared" si="34"/>
-        <v>0</v>
-      </c>
-      <c r="Z125" s="49" t="str">
-        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="AA125" s="64"/>
     </row>
     <row r="126" spans="1:27">
       <c r="A126" s="62" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="B126" s="44"/>
       <c r="C126" s="46"/>
       <c r="D126" s="46"/>
       <c r="E126" s="50">
-        <f t="shared" si="28"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="F126" s="48"/>
       <c r="G126" s="51">
-        <f t="shared" si="29"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="H126" s="44"/>
@@ -9798,47 +9799,47 @@
         <v>0</v>
       </c>
       <c r="T126" s="51">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="U126" s="51">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="U126" s="51">
+      <c r="V126" s="51">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="V126" s="51">
+      <c r="W126" s="52">
         <f t="shared" si="32"/>
         <v>0</v>
       </c>
-      <c r="W126" s="52">
+      <c r="X126" s="48"/>
+      <c r="Y126" s="58">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="Z126" s="49" t="str">
         <f t="shared" si="33"/>
-        <v>0</v>
-      </c>
-      <c r="X126" s="48"/>
-      <c r="Y126" s="51">
-        <f t="shared" si="34"/>
-        <v>0</v>
-      </c>
-      <c r="Z126" s="49" t="str">
-        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="AA126" s="64"/>
     </row>
     <row r="127" spans="1:27">
       <c r="A127" s="62" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="B127" s="44"/>
       <c r="C127" s="46"/>
       <c r="D127" s="46"/>
       <c r="E127" s="50">
-        <f t="shared" si="28"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="F127" s="48"/>
       <c r="G127" s="51">
-        <f t="shared" si="29"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="H127" s="44"/>
@@ -9857,47 +9858,47 @@
         <v>0</v>
       </c>
       <c r="T127" s="51">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="U127" s="51">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="U127" s="51">
+      <c r="V127" s="51">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="V127" s="51">
+      <c r="W127" s="52">
         <f t="shared" si="32"/>
         <v>0</v>
       </c>
-      <c r="W127" s="52">
+      <c r="X127" s="48"/>
+      <c r="Y127" s="58">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="Z127" s="49" t="str">
         <f t="shared" si="33"/>
-        <v>0</v>
-      </c>
-      <c r="X127" s="48"/>
-      <c r="Y127" s="51">
-        <f t="shared" si="34"/>
-        <v>0</v>
-      </c>
-      <c r="Z127" s="49" t="str">
-        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="AA127" s="64"/>
     </row>
     <row r="128" spans="1:27">
       <c r="A128" s="62" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="B128" s="44"/>
       <c r="C128" s="46"/>
       <c r="D128" s="46"/>
       <c r="E128" s="50">
-        <f t="shared" si="28"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="F128" s="48"/>
       <c r="G128" s="51">
-        <f t="shared" si="29"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="H128" s="44"/>
@@ -9916,47 +9917,47 @@
         <v>0</v>
       </c>
       <c r="T128" s="51">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="U128" s="51">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="U128" s="51">
+      <c r="V128" s="51">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="V128" s="51">
+      <c r="W128" s="52">
         <f t="shared" si="32"/>
         <v>0</v>
       </c>
-      <c r="W128" s="52">
+      <c r="X128" s="48"/>
+      <c r="Y128" s="58">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="Z128" s="49" t="str">
         <f t="shared" si="33"/>
-        <v>0</v>
-      </c>
-      <c r="X128" s="48"/>
-      <c r="Y128" s="51">
-        <f t="shared" si="34"/>
-        <v>0</v>
-      </c>
-      <c r="Z128" s="49" t="str">
-        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="AA128" s="64"/>
     </row>
     <row r="129" spans="1:27">
       <c r="A129" s="62" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="B129" s="44"/>
       <c r="C129" s="46"/>
       <c r="D129" s="46"/>
       <c r="E129" s="50">
-        <f t="shared" si="28"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="F129" s="48"/>
       <c r="G129" s="51">
-        <f t="shared" si="29"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="H129" s="44"/>
@@ -9975,47 +9976,47 @@
         <v>0</v>
       </c>
       <c r="T129" s="51">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="U129" s="51">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="U129" s="51">
+      <c r="V129" s="51">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="V129" s="51">
+      <c r="W129" s="52">
         <f t="shared" si="32"/>
         <v>0</v>
       </c>
-      <c r="W129" s="52">
+      <c r="X129" s="48"/>
+      <c r="Y129" s="58">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="Z129" s="49" t="str">
         <f t="shared" si="33"/>
-        <v>0</v>
-      </c>
-      <c r="X129" s="48"/>
-      <c r="Y129" s="51">
-        <f t="shared" si="34"/>
-        <v>0</v>
-      </c>
-      <c r="Z129" s="49" t="str">
-        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="AA129" s="64"/>
     </row>
     <row r="130" spans="1:27">
       <c r="A130" s="62" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="B130" s="44"/>
       <c r="C130" s="46"/>
       <c r="D130" s="46"/>
       <c r="E130" s="50">
-        <f t="shared" si="28"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="F130" s="48"/>
       <c r="G130" s="51">
-        <f t="shared" si="29"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="H130" s="44"/>
@@ -10034,47 +10035,47 @@
         <v>0</v>
       </c>
       <c r="T130" s="51">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="U130" s="51">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="U130" s="51">
+      <c r="V130" s="51">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="V130" s="51">
+      <c r="W130" s="52">
         <f t="shared" si="32"/>
         <v>0</v>
       </c>
-      <c r="W130" s="52">
+      <c r="X130" s="48"/>
+      <c r="Y130" s="58">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="Z130" s="49" t="str">
         <f t="shared" si="33"/>
-        <v>0</v>
-      </c>
-      <c r="X130" s="48"/>
-      <c r="Y130" s="51">
-        <f t="shared" si="34"/>
-        <v>0</v>
-      </c>
-      <c r="Z130" s="49" t="str">
-        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="AA130" s="64"/>
     </row>
     <row r="131" spans="1:27">
       <c r="A131" s="62" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="B131" s="44"/>
       <c r="C131" s="46"/>
       <c r="D131" s="46"/>
       <c r="E131" s="50">
-        <f t="shared" si="28"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="F131" s="48"/>
       <c r="G131" s="51">
-        <f t="shared" si="29"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="H131" s="44"/>
@@ -10093,47 +10094,47 @@
         <v>0</v>
       </c>
       <c r="T131" s="51">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="U131" s="51">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="U131" s="51">
+      <c r="V131" s="51">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="V131" s="51">
+      <c r="W131" s="52">
         <f t="shared" si="32"/>
         <v>0</v>
       </c>
-      <c r="W131" s="52">
+      <c r="X131" s="48"/>
+      <c r="Y131" s="58">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="Z131" s="49" t="str">
         <f t="shared" si="33"/>
-        <v>0</v>
-      </c>
-      <c r="X131" s="48"/>
-      <c r="Y131" s="51">
-        <f t="shared" si="34"/>
-        <v>0</v>
-      </c>
-      <c r="Z131" s="49" t="str">
-        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="AA131" s="64"/>
     </row>
     <row r="132" spans="1:27">
       <c r="A132" s="62" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="B132" s="44"/>
       <c r="C132" s="46"/>
       <c r="D132" s="46"/>
       <c r="E132" s="50">
-        <f t="shared" si="28"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="F132" s="48"/>
       <c r="G132" s="51">
-        <f t="shared" si="29"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="H132" s="44"/>
@@ -10152,47 +10153,47 @@
         <v>0</v>
       </c>
       <c r="T132" s="51">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="U132" s="51">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="U132" s="51">
+      <c r="V132" s="51">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="V132" s="51">
+      <c r="W132" s="52">
         <f t="shared" si="32"/>
         <v>0</v>
       </c>
-      <c r="W132" s="52">
+      <c r="X132" s="48"/>
+      <c r="Y132" s="58">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="Z132" s="49" t="str">
         <f t="shared" si="33"/>
-        <v>0</v>
-      </c>
-      <c r="X132" s="48"/>
-      <c r="Y132" s="51">
-        <f t="shared" si="34"/>
-        <v>0</v>
-      </c>
-      <c r="Z132" s="49" t="str">
-        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="AA132" s="64"/>
     </row>
     <row r="133" spans="1:27">
       <c r="A133" s="62" t="str">
-        <f t="shared" ref="A133:A164" si="36">IF(B133="","","LOC-"&amp;TEXT(ROW()-5,"000"))</f>
+        <f t="shared" ref="A133:A164" si="34">IF(B133="","","LOC-"&amp;TEXT(ROW()-5,"000"))</f>
         <v/>
       </c>
       <c r="B133" s="44"/>
       <c r="C133" s="46"/>
       <c r="D133" s="46"/>
       <c r="E133" s="50">
-        <f t="shared" ref="E133:E164" si="37">IF(OR(B133="",C133="",D133=""),0,MAX(0,D133-C133))</f>
+        <f t="shared" ref="E133:E164" si="35">IF(OR(B133="",C133="",D133=""),0,MAX(0,D133-C133))</f>
         <v>0</v>
       </c>
       <c r="F133" s="48"/>
       <c r="G133" s="51">
-        <f t="shared" ref="G133:G164" si="38">IF(OR(B133="",E133=0,F133=""),0,E133*F133)</f>
+        <f t="shared" ref="G133:G164" si="36">IF(OR(B133="",E133=0,F133=""),0,E133*F133)</f>
         <v>0</v>
       </c>
       <c r="H133" s="44"/>
@@ -10211,47 +10212,47 @@
         <v>0</v>
       </c>
       <c r="T133" s="51">
-        <f t="shared" ref="T133:T164" si="39">IF(OR(B133="",E133=0),0,S133/E133)</f>
+        <f t="shared" ref="T133:T164" si="37">IF(OR(B133="",E133=0),0,S133/E133)</f>
         <v>0</v>
       </c>
       <c r="U133" s="51">
-        <f t="shared" ref="U133:U164" si="40">IF(B133="",0,G133-S133)</f>
+        <f t="shared" ref="U133:U164" si="38">IF(B133="",0,G133-S133)</f>
         <v>0</v>
       </c>
       <c r="V133" s="51">
-        <f t="shared" ref="V133:V164" si="41">IF(OR(B133="",E133=0),0,U133/E133)</f>
+        <f t="shared" ref="V133:V164" si="39">IF(OR(B133="",E133=0),0,U133/E133)</f>
         <v>0</v>
       </c>
       <c r="W133" s="52">
-        <f t="shared" ref="W133:W164" si="42">IF(OR(B133="",G133=0),0,U133/G133)</f>
+        <f t="shared" ref="W133:W164" si="40">IF(OR(B133="",G133=0),0,U133/G133)</f>
         <v>0</v>
       </c>
       <c r="X133" s="48"/>
-      <c r="Y133" s="51">
-        <f t="shared" ref="Y133:Y164" si="43">IF(B133="",0,IFERROR(MAX(0,G133-X133),G133))</f>
+      <c r="Y133" s="58">
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="Z133" s="49" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="AA133" s="64"/>
     </row>
     <row r="134" spans="1:27">
       <c r="A134" s="62" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="B134" s="44"/>
       <c r="C134" s="46"/>
       <c r="D134" s="46"/>
       <c r="E134" s="50">
-        <f t="shared" si="37"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="F134" s="48"/>
       <c r="G134" s="51">
-        <f t="shared" si="38"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="H134" s="44"/>
@@ -10270,47 +10271,47 @@
         <v>0</v>
       </c>
       <c r="T134" s="51">
+        <f t="shared" si="37"/>
+        <v>0</v>
+      </c>
+      <c r="U134" s="51">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="V134" s="51">
         <f t="shared" si="39"/>
         <v>0</v>
       </c>
-      <c r="U134" s="51">
+      <c r="W134" s="52">
         <f t="shared" si="40"/>
         <v>0</v>
       </c>
-      <c r="V134" s="51">
-        <f t="shared" si="41"/>
-        <v>0</v>
-      </c>
-      <c r="W134" s="52">
-        <f t="shared" si="42"/>
-        <v>0</v>
-      </c>
       <c r="X134" s="48"/>
-      <c r="Y134" s="51">
-        <f t="shared" si="43"/>
+      <c r="Y134" s="58">
+        <f t="shared" ref="Y134:Y197" si="41">IF(B134="",0,IFERROR(MAX(0,G134-X134),G134))</f>
         <v>0</v>
       </c>
       <c r="Z134" s="49" t="str">
-        <f t="shared" ref="Z134:Z165" si="44">IF(B134="","",IF(COUNTIFS($C$6:$C$204,"&lt;"&amp;D134,$D$6:$D$204,"&gt;"&amp;C134,$I$6:$I$204,"&lt;&gt;Cancelada",$I$6:$I$204,"&lt;&gt;Consulta")&gt;1,"CONFLITO","OK"))</f>
+        <f t="shared" ref="Z134:Z165" si="42">IF(B134="","",IF(COUNTIFS($C$6:$C$204,"&lt;"&amp;D134,$D$6:$D$204,"&gt;"&amp;C134,$I$6:$I$204,"&lt;&gt;Cancelada",$I$6:$I$204,"&lt;&gt;Consulta")&gt;1,"CONFLITO","OK"))</f>
         <v/>
       </c>
       <c r="AA134" s="64"/>
     </row>
     <row r="135" spans="1:27">
       <c r="A135" s="62" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="B135" s="44"/>
       <c r="C135" s="46"/>
       <c r="D135" s="46"/>
       <c r="E135" s="50">
-        <f t="shared" si="37"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="F135" s="48"/>
       <c r="G135" s="51">
-        <f t="shared" si="38"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="H135" s="44"/>
@@ -10329,47 +10330,47 @@
         <v>0</v>
       </c>
       <c r="T135" s="51">
+        <f t="shared" si="37"/>
+        <v>0</v>
+      </c>
+      <c r="U135" s="51">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="V135" s="51">
         <f t="shared" si="39"/>
         <v>0</v>
       </c>
-      <c r="U135" s="51">
+      <c r="W135" s="52">
         <f t="shared" si="40"/>
         <v>0</v>
       </c>
-      <c r="V135" s="51">
+      <c r="X135" s="48"/>
+      <c r="Y135" s="58">
         <f t="shared" si="41"/>
         <v>0</v>
       </c>
-      <c r="W135" s="52">
+      <c r="Z135" s="49" t="str">
         <f t="shared" si="42"/>
-        <v>0</v>
-      </c>
-      <c r="X135" s="48"/>
-      <c r="Y135" s="51">
-        <f t="shared" si="43"/>
-        <v>0</v>
-      </c>
-      <c r="Z135" s="49" t="str">
-        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="AA135" s="64"/>
     </row>
     <row r="136" spans="1:27">
       <c r="A136" s="62" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="B136" s="44"/>
       <c r="C136" s="46"/>
       <c r="D136" s="46"/>
       <c r="E136" s="50">
-        <f t="shared" si="37"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="F136" s="48"/>
       <c r="G136" s="51">
-        <f t="shared" si="38"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="H136" s="44"/>
@@ -10388,47 +10389,47 @@
         <v>0</v>
       </c>
       <c r="T136" s="51">
+        <f t="shared" si="37"/>
+        <v>0</v>
+      </c>
+      <c r="U136" s="51">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="V136" s="51">
         <f t="shared" si="39"/>
         <v>0</v>
       </c>
-      <c r="U136" s="51">
+      <c r="W136" s="52">
         <f t="shared" si="40"/>
         <v>0</v>
       </c>
-      <c r="V136" s="51">
+      <c r="X136" s="48"/>
+      <c r="Y136" s="58">
         <f t="shared" si="41"/>
         <v>0</v>
       </c>
-      <c r="W136" s="52">
+      <c r="Z136" s="49" t="str">
         <f t="shared" si="42"/>
-        <v>0</v>
-      </c>
-      <c r="X136" s="48"/>
-      <c r="Y136" s="51">
-        <f t="shared" si="43"/>
-        <v>0</v>
-      </c>
-      <c r="Z136" s="49" t="str">
-        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="AA136" s="64"/>
     </row>
     <row r="137" spans="1:27">
       <c r="A137" s="62" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="B137" s="44"/>
       <c r="C137" s="46"/>
       <c r="D137" s="46"/>
       <c r="E137" s="50">
-        <f t="shared" si="37"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="F137" s="48"/>
       <c r="G137" s="51">
-        <f t="shared" si="38"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="H137" s="44"/>
@@ -10447,47 +10448,47 @@
         <v>0</v>
       </c>
       <c r="T137" s="51">
+        <f t="shared" si="37"/>
+        <v>0</v>
+      </c>
+      <c r="U137" s="51">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="V137" s="51">
         <f t="shared" si="39"/>
         <v>0</v>
       </c>
-      <c r="U137" s="51">
+      <c r="W137" s="52">
         <f t="shared" si="40"/>
         <v>0</v>
       </c>
-      <c r="V137" s="51">
+      <c r="X137" s="48"/>
+      <c r="Y137" s="58">
         <f t="shared" si="41"/>
         <v>0</v>
       </c>
-      <c r="W137" s="52">
+      <c r="Z137" s="49" t="str">
         <f t="shared" si="42"/>
-        <v>0</v>
-      </c>
-      <c r="X137" s="48"/>
-      <c r="Y137" s="51">
-        <f t="shared" si="43"/>
-        <v>0</v>
-      </c>
-      <c r="Z137" s="49" t="str">
-        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="AA137" s="64"/>
     </row>
     <row r="138" spans="1:27">
       <c r="A138" s="62" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="B138" s="44"/>
       <c r="C138" s="46"/>
       <c r="D138" s="46"/>
       <c r="E138" s="50">
-        <f t="shared" si="37"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="F138" s="48"/>
       <c r="G138" s="51">
-        <f t="shared" si="38"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="H138" s="44"/>
@@ -10506,47 +10507,47 @@
         <v>0</v>
       </c>
       <c r="T138" s="51">
+        <f t="shared" si="37"/>
+        <v>0</v>
+      </c>
+      <c r="U138" s="51">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="V138" s="51">
         <f t="shared" si="39"/>
         <v>0</v>
       </c>
-      <c r="U138" s="51">
+      <c r="W138" s="52">
         <f t="shared" si="40"/>
         <v>0</v>
       </c>
-      <c r="V138" s="51">
+      <c r="X138" s="48"/>
+      <c r="Y138" s="58">
         <f t="shared" si="41"/>
         <v>0</v>
       </c>
-      <c r="W138" s="52">
+      <c r="Z138" s="49" t="str">
         <f t="shared" si="42"/>
-        <v>0</v>
-      </c>
-      <c r="X138" s="48"/>
-      <c r="Y138" s="51">
-        <f t="shared" si="43"/>
-        <v>0</v>
-      </c>
-      <c r="Z138" s="49" t="str">
-        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="AA138" s="64"/>
     </row>
     <row r="139" spans="1:27">
       <c r="A139" s="62" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="B139" s="44"/>
       <c r="C139" s="46"/>
       <c r="D139" s="46"/>
       <c r="E139" s="50">
-        <f t="shared" si="37"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="F139" s="48"/>
       <c r="G139" s="51">
-        <f t="shared" si="38"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="H139" s="44"/>
@@ -10565,47 +10566,47 @@
         <v>0</v>
       </c>
       <c r="T139" s="51">
+        <f t="shared" si="37"/>
+        <v>0</v>
+      </c>
+      <c r="U139" s="51">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="V139" s="51">
         <f t="shared" si="39"/>
         <v>0</v>
       </c>
-      <c r="U139" s="51">
+      <c r="W139" s="52">
         <f t="shared" si="40"/>
         <v>0</v>
       </c>
-      <c r="V139" s="51">
+      <c r="X139" s="48"/>
+      <c r="Y139" s="58">
         <f t="shared" si="41"/>
         <v>0</v>
       </c>
-      <c r="W139" s="52">
+      <c r="Z139" s="49" t="str">
         <f t="shared" si="42"/>
-        <v>0</v>
-      </c>
-      <c r="X139" s="48"/>
-      <c r="Y139" s="51">
-        <f t="shared" si="43"/>
-        <v>0</v>
-      </c>
-      <c r="Z139" s="49" t="str">
-        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="AA139" s="64"/>
     </row>
     <row r="140" spans="1:27">
       <c r="A140" s="62" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="B140" s="44"/>
       <c r="C140" s="46"/>
       <c r="D140" s="46"/>
       <c r="E140" s="50">
-        <f t="shared" si="37"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="F140" s="48"/>
       <c r="G140" s="51">
-        <f t="shared" si="38"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="H140" s="44"/>
@@ -10624,47 +10625,47 @@
         <v>0</v>
       </c>
       <c r="T140" s="51">
+        <f t="shared" si="37"/>
+        <v>0</v>
+      </c>
+      <c r="U140" s="51">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="V140" s="51">
         <f t="shared" si="39"/>
         <v>0</v>
       </c>
-      <c r="U140" s="51">
+      <c r="W140" s="52">
         <f t="shared" si="40"/>
         <v>0</v>
       </c>
-      <c r="V140" s="51">
+      <c r="X140" s="48"/>
+      <c r="Y140" s="58">
         <f t="shared" si="41"/>
         <v>0</v>
       </c>
-      <c r="W140" s="52">
+      <c r="Z140" s="49" t="str">
         <f t="shared" si="42"/>
-        <v>0</v>
-      </c>
-      <c r="X140" s="48"/>
-      <c r="Y140" s="51">
-        <f t="shared" si="43"/>
-        <v>0</v>
-      </c>
-      <c r="Z140" s="49" t="str">
-        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="AA140" s="64"/>
     </row>
     <row r="141" spans="1:27">
       <c r="A141" s="62" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="B141" s="44"/>
       <c r="C141" s="46"/>
       <c r="D141" s="46"/>
       <c r="E141" s="50">
-        <f t="shared" si="37"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="F141" s="48"/>
       <c r="G141" s="51">
-        <f t="shared" si="38"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="H141" s="44"/>
@@ -10683,47 +10684,47 @@
         <v>0</v>
       </c>
       <c r="T141" s="51">
+        <f t="shared" si="37"/>
+        <v>0</v>
+      </c>
+      <c r="U141" s="51">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="V141" s="51">
         <f t="shared" si="39"/>
         <v>0</v>
       </c>
-      <c r="U141" s="51">
+      <c r="W141" s="52">
         <f t="shared" si="40"/>
         <v>0</v>
       </c>
-      <c r="V141" s="51">
+      <c r="X141" s="48"/>
+      <c r="Y141" s="58">
         <f t="shared" si="41"/>
         <v>0</v>
       </c>
-      <c r="W141" s="52">
+      <c r="Z141" s="49" t="str">
         <f t="shared" si="42"/>
-        <v>0</v>
-      </c>
-      <c r="X141" s="48"/>
-      <c r="Y141" s="51">
-        <f t="shared" si="43"/>
-        <v>0</v>
-      </c>
-      <c r="Z141" s="49" t="str">
-        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="AA141" s="64"/>
     </row>
     <row r="142" spans="1:27">
       <c r="A142" s="62" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="B142" s="44"/>
       <c r="C142" s="46"/>
       <c r="D142" s="46"/>
       <c r="E142" s="50">
-        <f t="shared" si="37"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="F142" s="48"/>
       <c r="G142" s="51">
-        <f t="shared" si="38"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="H142" s="44"/>
@@ -10742,47 +10743,47 @@
         <v>0</v>
       </c>
       <c r="T142" s="51">
+        <f t="shared" si="37"/>
+        <v>0</v>
+      </c>
+      <c r="U142" s="51">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="V142" s="51">
         <f t="shared" si="39"/>
         <v>0</v>
       </c>
-      <c r="U142" s="51">
+      <c r="W142" s="52">
         <f t="shared" si="40"/>
         <v>0</v>
       </c>
-      <c r="V142" s="51">
+      <c r="X142" s="48"/>
+      <c r="Y142" s="58">
         <f t="shared" si="41"/>
         <v>0</v>
       </c>
-      <c r="W142" s="52">
+      <c r="Z142" s="49" t="str">
         <f t="shared" si="42"/>
-        <v>0</v>
-      </c>
-      <c r="X142" s="48"/>
-      <c r="Y142" s="51">
-        <f t="shared" si="43"/>
-        <v>0</v>
-      </c>
-      <c r="Z142" s="49" t="str">
-        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="AA142" s="64"/>
     </row>
     <row r="143" spans="1:27">
       <c r="A143" s="62" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="B143" s="44"/>
       <c r="C143" s="46"/>
       <c r="D143" s="46"/>
       <c r="E143" s="50">
-        <f t="shared" si="37"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="F143" s="48"/>
       <c r="G143" s="51">
-        <f t="shared" si="38"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="H143" s="44"/>
@@ -10801,47 +10802,47 @@
         <v>0</v>
       </c>
       <c r="T143" s="51">
+        <f t="shared" si="37"/>
+        <v>0</v>
+      </c>
+      <c r="U143" s="51">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="V143" s="51">
         <f t="shared" si="39"/>
         <v>0</v>
       </c>
-      <c r="U143" s="51">
+      <c r="W143" s="52">
         <f t="shared" si="40"/>
         <v>0</v>
       </c>
-      <c r="V143" s="51">
+      <c r="X143" s="48"/>
+      <c r="Y143" s="58">
         <f t="shared" si="41"/>
         <v>0</v>
       </c>
-      <c r="W143" s="52">
+      <c r="Z143" s="49" t="str">
         <f t="shared" si="42"/>
-        <v>0</v>
-      </c>
-      <c r="X143" s="48"/>
-      <c r="Y143" s="51">
-        <f t="shared" si="43"/>
-        <v>0</v>
-      </c>
-      <c r="Z143" s="49" t="str">
-        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="AA143" s="64"/>
     </row>
     <row r="144" spans="1:27">
       <c r="A144" s="62" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="B144" s="44"/>
       <c r="C144" s="46"/>
       <c r="D144" s="46"/>
       <c r="E144" s="50">
-        <f t="shared" si="37"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="F144" s="48"/>
       <c r="G144" s="51">
-        <f t="shared" si="38"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="H144" s="44"/>
@@ -10860,47 +10861,47 @@
         <v>0</v>
       </c>
       <c r="T144" s="51">
+        <f t="shared" si="37"/>
+        <v>0</v>
+      </c>
+      <c r="U144" s="51">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="V144" s="51">
         <f t="shared" si="39"/>
         <v>0</v>
       </c>
-      <c r="U144" s="51">
+      <c r="W144" s="52">
         <f t="shared" si="40"/>
         <v>0</v>
       </c>
-      <c r="V144" s="51">
+      <c r="X144" s="48"/>
+      <c r="Y144" s="58">
         <f t="shared" si="41"/>
         <v>0</v>
       </c>
-      <c r="W144" s="52">
+      <c r="Z144" s="49" t="str">
         <f t="shared" si="42"/>
-        <v>0</v>
-      </c>
-      <c r="X144" s="48"/>
-      <c r="Y144" s="51">
-        <f t="shared" si="43"/>
-        <v>0</v>
-      </c>
-      <c r="Z144" s="49" t="str">
-        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="AA144" s="64"/>
     </row>
     <row r="145" spans="1:27">
       <c r="A145" s="62" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="B145" s="44"/>
       <c r="C145" s="46"/>
       <c r="D145" s="46"/>
       <c r="E145" s="50">
-        <f t="shared" si="37"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="F145" s="48"/>
       <c r="G145" s="51">
-        <f t="shared" si="38"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="H145" s="44"/>
@@ -10919,47 +10920,47 @@
         <v>0</v>
       </c>
       <c r="T145" s="51">
+        <f t="shared" si="37"/>
+        <v>0</v>
+      </c>
+      <c r="U145" s="51">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="V145" s="51">
         <f t="shared" si="39"/>
         <v>0</v>
       </c>
-      <c r="U145" s="51">
+      <c r="W145" s="52">
         <f t="shared" si="40"/>
         <v>0</v>
       </c>
-      <c r="V145" s="51">
+      <c r="X145" s="48"/>
+      <c r="Y145" s="58">
         <f t="shared" si="41"/>
         <v>0</v>
       </c>
-      <c r="W145" s="52">
+      <c r="Z145" s="49" t="str">
         <f t="shared" si="42"/>
-        <v>0</v>
-      </c>
-      <c r="X145" s="48"/>
-      <c r="Y145" s="51">
-        <f t="shared" si="43"/>
-        <v>0</v>
-      </c>
-      <c r="Z145" s="49" t="str">
-        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="AA145" s="64"/>
     </row>
     <row r="146" spans="1:27">
       <c r="A146" s="62" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="B146" s="44"/>
       <c r="C146" s="46"/>
       <c r="D146" s="46"/>
       <c r="E146" s="50">
-        <f t="shared" si="37"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="F146" s="48"/>
       <c r="G146" s="51">
-        <f t="shared" si="38"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="H146" s="44"/>
@@ -10978,47 +10979,47 @@
         <v>0</v>
       </c>
       <c r="T146" s="51">
+        <f t="shared" si="37"/>
+        <v>0</v>
+      </c>
+      <c r="U146" s="51">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="V146" s="51">
         <f t="shared" si="39"/>
         <v>0</v>
       </c>
-      <c r="U146" s="51">
+      <c r="W146" s="52">
         <f t="shared" si="40"/>
         <v>0</v>
       </c>
-      <c r="V146" s="51">
+      <c r="X146" s="48"/>
+      <c r="Y146" s="58">
         <f t="shared" si="41"/>
         <v>0</v>
       </c>
-      <c r="W146" s="52">
+      <c r="Z146" s="49" t="str">
         <f t="shared" si="42"/>
-        <v>0</v>
-      </c>
-      <c r="X146" s="48"/>
-      <c r="Y146" s="51">
-        <f t="shared" si="43"/>
-        <v>0</v>
-      </c>
-      <c r="Z146" s="49" t="str">
-        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="AA146" s="64"/>
     </row>
     <row r="147" spans="1:27">
       <c r="A147" s="62" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="B147" s="44"/>
       <c r="C147" s="46"/>
       <c r="D147" s="46"/>
       <c r="E147" s="50">
-        <f t="shared" si="37"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="F147" s="48"/>
       <c r="G147" s="51">
-        <f t="shared" si="38"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="H147" s="44"/>
@@ -11037,47 +11038,47 @@
         <v>0</v>
       </c>
       <c r="T147" s="51">
+        <f t="shared" si="37"/>
+        <v>0</v>
+      </c>
+      <c r="U147" s="51">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="V147" s="51">
         <f t="shared" si="39"/>
         <v>0</v>
       </c>
-      <c r="U147" s="51">
+      <c r="W147" s="52">
         <f t="shared" si="40"/>
         <v>0</v>
       </c>
-      <c r="V147" s="51">
+      <c r="X147" s="48"/>
+      <c r="Y147" s="58">
         <f t="shared" si="41"/>
         <v>0</v>
       </c>
-      <c r="W147" s="52">
+      <c r="Z147" s="49" t="str">
         <f t="shared" si="42"/>
-        <v>0</v>
-      </c>
-      <c r="X147" s="48"/>
-      <c r="Y147" s="51">
-        <f t="shared" si="43"/>
-        <v>0</v>
-      </c>
-      <c r="Z147" s="49" t="str">
-        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="AA147" s="64"/>
     </row>
     <row r="148" spans="1:27">
       <c r="A148" s="62" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="B148" s="44"/>
       <c r="C148" s="46"/>
       <c r="D148" s="46"/>
       <c r="E148" s="50">
-        <f t="shared" si="37"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="F148" s="48"/>
       <c r="G148" s="51">
-        <f t="shared" si="38"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="H148" s="44"/>
@@ -11096,47 +11097,47 @@
         <v>0</v>
       </c>
       <c r="T148" s="51">
+        <f t="shared" si="37"/>
+        <v>0</v>
+      </c>
+      <c r="U148" s="51">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="V148" s="51">
         <f t="shared" si="39"/>
         <v>0</v>
       </c>
-      <c r="U148" s="51">
+      <c r="W148" s="52">
         <f t="shared" si="40"/>
         <v>0</v>
       </c>
-      <c r="V148" s="51">
+      <c r="X148" s="48"/>
+      <c r="Y148" s="58">
         <f t="shared" si="41"/>
         <v>0</v>
       </c>
-      <c r="W148" s="52">
+      <c r="Z148" s="49" t="str">
         <f t="shared" si="42"/>
-        <v>0</v>
-      </c>
-      <c r="X148" s="48"/>
-      <c r="Y148" s="51">
-        <f t="shared" si="43"/>
-        <v>0</v>
-      </c>
-      <c r="Z148" s="49" t="str">
-        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="AA148" s="64"/>
     </row>
     <row r="149" spans="1:27">
       <c r="A149" s="62" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="B149" s="44"/>
       <c r="C149" s="46"/>
       <c r="D149" s="46"/>
       <c r="E149" s="50">
-        <f t="shared" si="37"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="F149" s="48"/>
       <c r="G149" s="51">
-        <f t="shared" si="38"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="H149" s="44"/>
@@ -11155,47 +11156,47 @@
         <v>0</v>
       </c>
       <c r="T149" s="51">
+        <f t="shared" si="37"/>
+        <v>0</v>
+      </c>
+      <c r="U149" s="51">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="V149" s="51">
         <f t="shared" si="39"/>
         <v>0</v>
       </c>
-      <c r="U149" s="51">
+      <c r="W149" s="52">
         <f t="shared" si="40"/>
         <v>0</v>
       </c>
-      <c r="V149" s="51">
+      <c r="X149" s="48"/>
+      <c r="Y149" s="58">
         <f t="shared" si="41"/>
         <v>0</v>
       </c>
-      <c r="W149" s="52">
+      <c r="Z149" s="49" t="str">
         <f t="shared" si="42"/>
-        <v>0</v>
-      </c>
-      <c r="X149" s="48"/>
-      <c r="Y149" s="51">
-        <f t="shared" si="43"/>
-        <v>0</v>
-      </c>
-      <c r="Z149" s="49" t="str">
-        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="AA149" s="64"/>
     </row>
     <row r="150" spans="1:27">
       <c r="A150" s="62" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="B150" s="44"/>
       <c r="C150" s="46"/>
       <c r="D150" s="46"/>
       <c r="E150" s="50">
-        <f t="shared" si="37"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="F150" s="48"/>
       <c r="G150" s="51">
-        <f t="shared" si="38"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="H150" s="44"/>
@@ -11214,47 +11215,47 @@
         <v>0</v>
       </c>
       <c r="T150" s="51">
+        <f t="shared" si="37"/>
+        <v>0</v>
+      </c>
+      <c r="U150" s="51">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="V150" s="51">
         <f t="shared" si="39"/>
         <v>0</v>
       </c>
-      <c r="U150" s="51">
+      <c r="W150" s="52">
         <f t="shared" si="40"/>
         <v>0</v>
       </c>
-      <c r="V150" s="51">
+      <c r="X150" s="48"/>
+      <c r="Y150" s="58">
         <f t="shared" si="41"/>
         <v>0</v>
       </c>
-      <c r="W150" s="52">
+      <c r="Z150" s="49" t="str">
         <f t="shared" si="42"/>
-        <v>0</v>
-      </c>
-      <c r="X150" s="48"/>
-      <c r="Y150" s="51">
-        <f t="shared" si="43"/>
-        <v>0</v>
-      </c>
-      <c r="Z150" s="49" t="str">
-        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="AA150" s="64"/>
     </row>
     <row r="151" spans="1:27">
       <c r="A151" s="62" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="B151" s="44"/>
       <c r="C151" s="46"/>
       <c r="D151" s="46"/>
       <c r="E151" s="50">
-        <f t="shared" si="37"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="F151" s="48"/>
       <c r="G151" s="51">
-        <f t="shared" si="38"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="H151" s="44"/>
@@ -11273,47 +11274,47 @@
         <v>0</v>
       </c>
       <c r="T151" s="51">
+        <f t="shared" si="37"/>
+        <v>0</v>
+      </c>
+      <c r="U151" s="51">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="V151" s="51">
         <f t="shared" si="39"/>
         <v>0</v>
       </c>
-      <c r="U151" s="51">
+      <c r="W151" s="52">
         <f t="shared" si="40"/>
         <v>0</v>
       </c>
-      <c r="V151" s="51">
+      <c r="X151" s="48"/>
+      <c r="Y151" s="58">
         <f t="shared" si="41"/>
         <v>0</v>
       </c>
-      <c r="W151" s="52">
+      <c r="Z151" s="49" t="str">
         <f t="shared" si="42"/>
-        <v>0</v>
-      </c>
-      <c r="X151" s="48"/>
-      <c r="Y151" s="51">
-        <f t="shared" si="43"/>
-        <v>0</v>
-      </c>
-      <c r="Z151" s="49" t="str">
-        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="AA151" s="64"/>
     </row>
     <row r="152" spans="1:27">
       <c r="A152" s="62" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="B152" s="44"/>
       <c r="C152" s="46"/>
       <c r="D152" s="46"/>
       <c r="E152" s="50">
-        <f t="shared" si="37"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="F152" s="48"/>
       <c r="G152" s="51">
-        <f t="shared" si="38"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="H152" s="44"/>
@@ -11332,47 +11333,47 @@
         <v>0</v>
       </c>
       <c r="T152" s="51">
+        <f t="shared" si="37"/>
+        <v>0</v>
+      </c>
+      <c r="U152" s="51">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="V152" s="51">
         <f t="shared" si="39"/>
         <v>0</v>
       </c>
-      <c r="U152" s="51">
+      <c r="W152" s="52">
         <f t="shared" si="40"/>
         <v>0</v>
       </c>
-      <c r="V152" s="51">
+      <c r="X152" s="48"/>
+      <c r="Y152" s="58">
         <f t="shared" si="41"/>
         <v>0</v>
       </c>
-      <c r="W152" s="52">
+      <c r="Z152" s="49" t="str">
         <f t="shared" si="42"/>
-        <v>0</v>
-      </c>
-      <c r="X152" s="48"/>
-      <c r="Y152" s="51">
-        <f t="shared" si="43"/>
-        <v>0</v>
-      </c>
-      <c r="Z152" s="49" t="str">
-        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="AA152" s="64"/>
     </row>
     <row r="153" spans="1:27">
       <c r="A153" s="62" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="B153" s="44"/>
       <c r="C153" s="46"/>
       <c r="D153" s="46"/>
       <c r="E153" s="50">
-        <f t="shared" si="37"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="F153" s="48"/>
       <c r="G153" s="51">
-        <f t="shared" si="38"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="H153" s="44"/>
@@ -11391,47 +11392,47 @@
         <v>0</v>
       </c>
       <c r="T153" s="51">
+        <f t="shared" si="37"/>
+        <v>0</v>
+      </c>
+      <c r="U153" s="51">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="V153" s="51">
         <f t="shared" si="39"/>
         <v>0</v>
       </c>
-      <c r="U153" s="51">
+      <c r="W153" s="52">
         <f t="shared" si="40"/>
         <v>0</v>
       </c>
-      <c r="V153" s="51">
+      <c r="X153" s="48"/>
+      <c r="Y153" s="58">
         <f t="shared" si="41"/>
         <v>0</v>
       </c>
-      <c r="W153" s="52">
+      <c r="Z153" s="49" t="str">
         <f t="shared" si="42"/>
-        <v>0</v>
-      </c>
-      <c r="X153" s="48"/>
-      <c r="Y153" s="51">
-        <f t="shared" si="43"/>
-        <v>0</v>
-      </c>
-      <c r="Z153" s="49" t="str">
-        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="AA153" s="64"/>
     </row>
     <row r="154" spans="1:27">
       <c r="A154" s="62" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="B154" s="44"/>
       <c r="C154" s="46"/>
       <c r="D154" s="46"/>
       <c r="E154" s="50">
-        <f t="shared" si="37"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="F154" s="48"/>
       <c r="G154" s="51">
-        <f t="shared" si="38"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="H154" s="44"/>
@@ -11450,47 +11451,47 @@
         <v>0</v>
       </c>
       <c r="T154" s="51">
+        <f t="shared" si="37"/>
+        <v>0</v>
+      </c>
+      <c r="U154" s="51">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="V154" s="51">
         <f t="shared" si="39"/>
         <v>0</v>
       </c>
-      <c r="U154" s="51">
+      <c r="W154" s="52">
         <f t="shared" si="40"/>
         <v>0</v>
       </c>
-      <c r="V154" s="51">
+      <c r="X154" s="48"/>
+      <c r="Y154" s="58">
         <f t="shared" si="41"/>
         <v>0</v>
       </c>
-      <c r="W154" s="52">
+      <c r="Z154" s="49" t="str">
         <f t="shared" si="42"/>
-        <v>0</v>
-      </c>
-      <c r="X154" s="48"/>
-      <c r="Y154" s="51">
-        <f t="shared" si="43"/>
-        <v>0</v>
-      </c>
-      <c r="Z154" s="49" t="str">
-        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="AA154" s="64"/>
     </row>
     <row r="155" spans="1:27">
       <c r="A155" s="62" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="B155" s="44"/>
       <c r="C155" s="46"/>
       <c r="D155" s="46"/>
       <c r="E155" s="50">
-        <f t="shared" si="37"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="F155" s="48"/>
       <c r="G155" s="51">
-        <f t="shared" si="38"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="H155" s="44"/>
@@ -11509,47 +11510,47 @@
         <v>0</v>
       </c>
       <c r="T155" s="51">
+        <f t="shared" si="37"/>
+        <v>0</v>
+      </c>
+      <c r="U155" s="51">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="V155" s="51">
         <f t="shared" si="39"/>
         <v>0</v>
       </c>
-      <c r="U155" s="51">
+      <c r="W155" s="52">
         <f t="shared" si="40"/>
         <v>0</v>
       </c>
-      <c r="V155" s="51">
+      <c r="X155" s="48"/>
+      <c r="Y155" s="58">
         <f t="shared" si="41"/>
         <v>0</v>
       </c>
-      <c r="W155" s="52">
+      <c r="Z155" s="49" t="str">
         <f t="shared" si="42"/>
-        <v>0</v>
-      </c>
-      <c r="X155" s="48"/>
-      <c r="Y155" s="51">
-        <f t="shared" si="43"/>
-        <v>0</v>
-      </c>
-      <c r="Z155" s="49" t="str">
-        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="AA155" s="64"/>
     </row>
     <row r="156" spans="1:27">
       <c r="A156" s="62" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="B156" s="44"/>
       <c r="C156" s="46"/>
       <c r="D156" s="46"/>
       <c r="E156" s="50">
-        <f t="shared" si="37"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="F156" s="48"/>
       <c r="G156" s="51">
-        <f t="shared" si="38"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="H156" s="44"/>
@@ -11568,47 +11569,47 @@
         <v>0</v>
       </c>
       <c r="T156" s="51">
+        <f t="shared" si="37"/>
+        <v>0</v>
+      </c>
+      <c r="U156" s="51">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="V156" s="51">
         <f t="shared" si="39"/>
         <v>0</v>
       </c>
-      <c r="U156" s="51">
+      <c r="W156" s="52">
         <f t="shared" si="40"/>
         <v>0</v>
       </c>
-      <c r="V156" s="51">
+      <c r="X156" s="48"/>
+      <c r="Y156" s="58">
         <f t="shared" si="41"/>
         <v>0</v>
       </c>
-      <c r="W156" s="52">
+      <c r="Z156" s="49" t="str">
         <f t="shared" si="42"/>
-        <v>0</v>
-      </c>
-      <c r="X156" s="48"/>
-      <c r="Y156" s="51">
-        <f t="shared" si="43"/>
-        <v>0</v>
-      </c>
-      <c r="Z156" s="49" t="str">
-        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="AA156" s="64"/>
     </row>
     <row r="157" spans="1:27">
       <c r="A157" s="62" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="B157" s="44"/>
       <c r="C157" s="46"/>
       <c r="D157" s="46"/>
       <c r="E157" s="50">
-        <f t="shared" si="37"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="F157" s="48"/>
       <c r="G157" s="51">
-        <f t="shared" si="38"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="H157" s="44"/>
@@ -11627,47 +11628,47 @@
         <v>0</v>
       </c>
       <c r="T157" s="51">
+        <f t="shared" si="37"/>
+        <v>0</v>
+      </c>
+      <c r="U157" s="51">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="V157" s="51">
         <f t="shared" si="39"/>
         <v>0</v>
       </c>
-      <c r="U157" s="51">
+      <c r="W157" s="52">
         <f t="shared" si="40"/>
         <v>0</v>
       </c>
-      <c r="V157" s="51">
+      <c r="X157" s="48"/>
+      <c r="Y157" s="58">
         <f t="shared" si="41"/>
         <v>0</v>
       </c>
-      <c r="W157" s="52">
+      <c r="Z157" s="49" t="str">
         <f t="shared" si="42"/>
-        <v>0</v>
-      </c>
-      <c r="X157" s="48"/>
-      <c r="Y157" s="51">
-        <f t="shared" si="43"/>
-        <v>0</v>
-      </c>
-      <c r="Z157" s="49" t="str">
-        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="AA157" s="64"/>
     </row>
     <row r="158" spans="1:27">
       <c r="A158" s="62" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="B158" s="44"/>
       <c r="C158" s="46"/>
       <c r="D158" s="46"/>
       <c r="E158" s="50">
-        <f t="shared" si="37"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="F158" s="48"/>
       <c r="G158" s="51">
-        <f t="shared" si="38"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="H158" s="44"/>
@@ -11686,47 +11687,47 @@
         <v>0</v>
       </c>
       <c r="T158" s="51">
+        <f t="shared" si="37"/>
+        <v>0</v>
+      </c>
+      <c r="U158" s="51">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="V158" s="51">
         <f t="shared" si="39"/>
         <v>0</v>
       </c>
-      <c r="U158" s="51">
+      <c r="W158" s="52">
         <f t="shared" si="40"/>
         <v>0</v>
       </c>
-      <c r="V158" s="51">
+      <c r="X158" s="48"/>
+      <c r="Y158" s="58">
         <f t="shared" si="41"/>
         <v>0</v>
       </c>
-      <c r="W158" s="52">
+      <c r="Z158" s="49" t="str">
         <f t="shared" si="42"/>
-        <v>0</v>
-      </c>
-      <c r="X158" s="48"/>
-      <c r="Y158" s="51">
-        <f t="shared" si="43"/>
-        <v>0</v>
-      </c>
-      <c r="Z158" s="49" t="str">
-        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="AA158" s="64"/>
     </row>
     <row r="159" spans="1:27">
       <c r="A159" s="62" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="B159" s="44"/>
       <c r="C159" s="46"/>
       <c r="D159" s="46"/>
       <c r="E159" s="50">
-        <f t="shared" si="37"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="F159" s="48"/>
       <c r="G159" s="51">
-        <f t="shared" si="38"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="H159" s="44"/>
@@ -11745,47 +11746,47 @@
         <v>0</v>
       </c>
       <c r="T159" s="51">
+        <f t="shared" si="37"/>
+        <v>0</v>
+      </c>
+      <c r="U159" s="51">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="V159" s="51">
         <f t="shared" si="39"/>
         <v>0</v>
       </c>
-      <c r="U159" s="51">
+      <c r="W159" s="52">
         <f t="shared" si="40"/>
         <v>0</v>
       </c>
-      <c r="V159" s="51">
+      <c r="X159" s="48"/>
+      <c r="Y159" s="58">
         <f t="shared" si="41"/>
         <v>0</v>
       </c>
-      <c r="W159" s="52">
+      <c r="Z159" s="49" t="str">
         <f t="shared" si="42"/>
-        <v>0</v>
-      </c>
-      <c r="X159" s="48"/>
-      <c r="Y159" s="51">
-        <f t="shared" si="43"/>
-        <v>0</v>
-      </c>
-      <c r="Z159" s="49" t="str">
-        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="AA159" s="64"/>
     </row>
     <row r="160" spans="1:27">
       <c r="A160" s="62" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="B160" s="44"/>
       <c r="C160" s="46"/>
       <c r="D160" s="46"/>
       <c r="E160" s="50">
-        <f t="shared" si="37"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="F160" s="48"/>
       <c r="G160" s="51">
-        <f t="shared" si="38"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="H160" s="44"/>
@@ -11804,47 +11805,47 @@
         <v>0</v>
       </c>
       <c r="T160" s="51">
+        <f t="shared" si="37"/>
+        <v>0</v>
+      </c>
+      <c r="U160" s="51">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="V160" s="51">
         <f t="shared" si="39"/>
         <v>0</v>
       </c>
-      <c r="U160" s="51">
+      <c r="W160" s="52">
         <f t="shared" si="40"/>
         <v>0</v>
       </c>
-      <c r="V160" s="51">
+      <c r="X160" s="48"/>
+      <c r="Y160" s="58">
         <f t="shared" si="41"/>
         <v>0</v>
       </c>
-      <c r="W160" s="52">
+      <c r="Z160" s="49" t="str">
         <f t="shared" si="42"/>
-        <v>0</v>
-      </c>
-      <c r="X160" s="48"/>
-      <c r="Y160" s="51">
-        <f t="shared" si="43"/>
-        <v>0</v>
-      </c>
-      <c r="Z160" s="49" t="str">
-        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="AA160" s="64"/>
     </row>
     <row r="161" spans="1:27">
       <c r="A161" s="62" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="B161" s="44"/>
       <c r="C161" s="46"/>
       <c r="D161" s="46"/>
       <c r="E161" s="50">
-        <f t="shared" si="37"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="F161" s="48"/>
       <c r="G161" s="51">
-        <f t="shared" si="38"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="H161" s="44"/>
@@ -11863,47 +11864,47 @@
         <v>0</v>
       </c>
       <c r="T161" s="51">
+        <f t="shared" si="37"/>
+        <v>0</v>
+      </c>
+      <c r="U161" s="51">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="V161" s="51">
         <f t="shared" si="39"/>
         <v>0</v>
       </c>
-      <c r="U161" s="51">
+      <c r="W161" s="52">
         <f t="shared" si="40"/>
         <v>0</v>
       </c>
-      <c r="V161" s="51">
+      <c r="X161" s="48"/>
+      <c r="Y161" s="58">
         <f t="shared" si="41"/>
         <v>0</v>
       </c>
-      <c r="W161" s="52">
+      <c r="Z161" s="49" t="str">
         <f t="shared" si="42"/>
-        <v>0</v>
-      </c>
-      <c r="X161" s="48"/>
-      <c r="Y161" s="51">
-        <f t="shared" si="43"/>
-        <v>0</v>
-      </c>
-      <c r="Z161" s="49" t="str">
-        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="AA161" s="64"/>
     </row>
     <row r="162" spans="1:27">
       <c r="A162" s="62" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="B162" s="44"/>
       <c r="C162" s="46"/>
       <c r="D162" s="46"/>
       <c r="E162" s="50">
-        <f t="shared" si="37"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="F162" s="48"/>
       <c r="G162" s="51">
-        <f t="shared" si="38"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="H162" s="44"/>
@@ -11922,47 +11923,47 @@
         <v>0</v>
       </c>
       <c r="T162" s="51">
+        <f t="shared" si="37"/>
+        <v>0</v>
+      </c>
+      <c r="U162" s="51">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="V162" s="51">
         <f t="shared" si="39"/>
         <v>0</v>
       </c>
-      <c r="U162" s="51">
+      <c r="W162" s="52">
         <f t="shared" si="40"/>
         <v>0</v>
       </c>
-      <c r="V162" s="51">
+      <c r="X162" s="48"/>
+      <c r="Y162" s="58">
         <f t="shared" si="41"/>
         <v>0</v>
       </c>
-      <c r="W162" s="52">
+      <c r="Z162" s="49" t="str">
         <f t="shared" si="42"/>
-        <v>0</v>
-      </c>
-      <c r="X162" s="48"/>
-      <c r="Y162" s="51">
-        <f t="shared" si="43"/>
-        <v>0</v>
-      </c>
-      <c r="Z162" s="49" t="str">
-        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="AA162" s="64"/>
     </row>
     <row r="163" spans="1:27">
       <c r="A163" s="62" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="B163" s="44"/>
       <c r="C163" s="46"/>
       <c r="D163" s="46"/>
       <c r="E163" s="50">
-        <f t="shared" si="37"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="F163" s="48"/>
       <c r="G163" s="51">
-        <f t="shared" si="38"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="H163" s="44"/>
@@ -11981,47 +11982,47 @@
         <v>0</v>
       </c>
       <c r="T163" s="51">
+        <f t="shared" si="37"/>
+        <v>0</v>
+      </c>
+      <c r="U163" s="51">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="V163" s="51">
         <f t="shared" si="39"/>
         <v>0</v>
       </c>
-      <c r="U163" s="51">
+      <c r="W163" s="52">
         <f t="shared" si="40"/>
         <v>0</v>
       </c>
-      <c r="V163" s="51">
+      <c r="X163" s="48"/>
+      <c r="Y163" s="58">
         <f t="shared" si="41"/>
         <v>0</v>
       </c>
-      <c r="W163" s="52">
+      <c r="Z163" s="49" t="str">
         <f t="shared" si="42"/>
-        <v>0</v>
-      </c>
-      <c r="X163" s="48"/>
-      <c r="Y163" s="51">
-        <f t="shared" si="43"/>
-        <v>0</v>
-      </c>
-      <c r="Z163" s="49" t="str">
-        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="AA163" s="64"/>
     </row>
     <row r="164" spans="1:27">
       <c r="A164" s="62" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="B164" s="44"/>
       <c r="C164" s="46"/>
       <c r="D164" s="46"/>
       <c r="E164" s="50">
-        <f t="shared" si="37"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="F164" s="48"/>
       <c r="G164" s="51">
-        <f t="shared" si="38"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="H164" s="44"/>
@@ -12040,47 +12041,47 @@
         <v>0</v>
       </c>
       <c r="T164" s="51">
+        <f t="shared" si="37"/>
+        <v>0</v>
+      </c>
+      <c r="U164" s="51">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="V164" s="51">
         <f t="shared" si="39"/>
         <v>0</v>
       </c>
-      <c r="U164" s="51">
+      <c r="W164" s="52">
         <f t="shared" si="40"/>
         <v>0</v>
       </c>
-      <c r="V164" s="51">
+      <c r="X164" s="48"/>
+      <c r="Y164" s="58">
         <f t="shared" si="41"/>
         <v>0</v>
       </c>
-      <c r="W164" s="52">
+      <c r="Z164" s="49" t="str">
         <f t="shared" si="42"/>
-        <v>0</v>
-      </c>
-      <c r="X164" s="48"/>
-      <c r="Y164" s="51">
-        <f t="shared" si="43"/>
-        <v>0</v>
-      </c>
-      <c r="Z164" s="49" t="str">
-        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="AA164" s="64"/>
     </row>
     <row r="165" spans="1:27">
       <c r="A165" s="62" t="str">
-        <f t="shared" ref="A165:A196" si="45">IF(B165="","","LOC-"&amp;TEXT(ROW()-5,"000"))</f>
+        <f t="shared" ref="A165:A196" si="43">IF(B165="","","LOC-"&amp;TEXT(ROW()-5,"000"))</f>
         <v/>
       </c>
       <c r="B165" s="44"/>
       <c r="C165" s="46"/>
       <c r="D165" s="46"/>
       <c r="E165" s="50">
-        <f t="shared" ref="E165:E196" si="46">IF(OR(B165="",C165="",D165=""),0,MAX(0,D165-C165))</f>
+        <f t="shared" ref="E165:E196" si="44">IF(OR(B165="",C165="",D165=""),0,MAX(0,D165-C165))</f>
         <v>0</v>
       </c>
       <c r="F165" s="48"/>
       <c r="G165" s="51">
-        <f t="shared" ref="G165:G196" si="47">IF(OR(B165="",E165=0,F165=""),0,E165*F165)</f>
+        <f t="shared" ref="G165:G196" si="45">IF(OR(B165="",E165=0,F165=""),0,E165*F165)</f>
         <v>0</v>
       </c>
       <c r="H165" s="44"/>
@@ -12099,47 +12100,47 @@
         <v>0</v>
       </c>
       <c r="T165" s="51">
-        <f t="shared" ref="T165:T196" si="48">IF(OR(B165="",E165=0),0,S165/E165)</f>
+        <f t="shared" ref="T165:T196" si="46">IF(OR(B165="",E165=0),0,S165/E165)</f>
         <v>0</v>
       </c>
       <c r="U165" s="51">
-        <f t="shared" ref="U165:U196" si="49">IF(B165="",0,G165-S165)</f>
+        <f t="shared" ref="U165:U196" si="47">IF(B165="",0,G165-S165)</f>
         <v>0</v>
       </c>
       <c r="V165" s="51">
-        <f t="shared" ref="V165:V196" si="50">IF(OR(B165="",E165=0),0,U165/E165)</f>
+        <f t="shared" ref="V165:V196" si="48">IF(OR(B165="",E165=0),0,U165/E165)</f>
         <v>0</v>
       </c>
       <c r="W165" s="52">
-        <f t="shared" ref="W165:W196" si="51">IF(OR(B165="",G165=0),0,U165/G165)</f>
+        <f t="shared" ref="W165:W196" si="49">IF(OR(B165="",G165=0),0,U165/G165)</f>
         <v>0</v>
       </c>
       <c r="X165" s="48"/>
-      <c r="Y165" s="51">
-        <f t="shared" ref="Y165:Y196" si="52">IF(B165="",0,IFERROR(MAX(0,G165-X165),G165))</f>
+      <c r="Y165" s="58">
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="Z165" s="49" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="AA165" s="64"/>
     </row>
     <row r="166" spans="1:27">
       <c r="A166" s="62" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="B166" s="44"/>
       <c r="C166" s="46"/>
       <c r="D166" s="46"/>
       <c r="E166" s="50">
-        <f t="shared" si="46"/>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="F166" s="48"/>
       <c r="G166" s="51">
-        <f t="shared" si="47"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="H166" s="44"/>
@@ -12158,47 +12159,47 @@
         <v>0</v>
       </c>
       <c r="T166" s="51">
+        <f t="shared" si="46"/>
+        <v>0</v>
+      </c>
+      <c r="U166" s="51">
+        <f t="shared" si="47"/>
+        <v>0</v>
+      </c>
+      <c r="V166" s="51">
         <f t="shared" si="48"/>
         <v>0</v>
       </c>
-      <c r="U166" s="51">
+      <c r="W166" s="52">
         <f t="shared" si="49"/>
         <v>0</v>
       </c>
-      <c r="V166" s="51">
-        <f t="shared" si="50"/>
-        <v>0</v>
-      </c>
-      <c r="W166" s="52">
-        <f t="shared" si="51"/>
-        <v>0</v>
-      </c>
       <c r="X166" s="48"/>
-      <c r="Y166" s="51">
-        <f t="shared" si="52"/>
+      <c r="Y166" s="58">
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="Z166" s="49" t="str">
-        <f t="shared" ref="Z166:Z197" si="53">IF(B166="","",IF(COUNTIFS($C$6:$C$204,"&lt;"&amp;D166,$D$6:$D$204,"&gt;"&amp;C166,$I$6:$I$204,"&lt;&gt;Cancelada",$I$6:$I$204,"&lt;&gt;Consulta")&gt;1,"CONFLITO","OK"))</f>
+        <f t="shared" ref="Z166:Z197" si="50">IF(B166="","",IF(COUNTIFS($C$6:$C$204,"&lt;"&amp;D166,$D$6:$D$204,"&gt;"&amp;C166,$I$6:$I$204,"&lt;&gt;Cancelada",$I$6:$I$204,"&lt;&gt;Consulta")&gt;1,"CONFLITO","OK"))</f>
         <v/>
       </c>
       <c r="AA166" s="64"/>
     </row>
     <row r="167" spans="1:27">
       <c r="A167" s="62" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="B167" s="44"/>
       <c r="C167" s="46"/>
       <c r="D167" s="46"/>
       <c r="E167" s="50">
-        <f t="shared" si="46"/>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="F167" s="48"/>
       <c r="G167" s="51">
-        <f t="shared" si="47"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="H167" s="44"/>
@@ -12217,47 +12218,47 @@
         <v>0</v>
       </c>
       <c r="T167" s="51">
+        <f t="shared" si="46"/>
+        <v>0</v>
+      </c>
+      <c r="U167" s="51">
+        <f t="shared" si="47"/>
+        <v>0</v>
+      </c>
+      <c r="V167" s="51">
         <f t="shared" si="48"/>
         <v>0</v>
       </c>
-      <c r="U167" s="51">
+      <c r="W167" s="52">
         <f t="shared" si="49"/>
         <v>0</v>
       </c>
-      <c r="V167" s="51">
+      <c r="X167" s="48"/>
+      <c r="Y167" s="58">
+        <f t="shared" si="41"/>
+        <v>0</v>
+      </c>
+      <c r="Z167" s="49" t="str">
         <f t="shared" si="50"/>
-        <v>0</v>
-      </c>
-      <c r="W167" s="52">
-        <f t="shared" si="51"/>
-        <v>0</v>
-      </c>
-      <c r="X167" s="48"/>
-      <c r="Y167" s="51">
-        <f t="shared" si="52"/>
-        <v>0</v>
-      </c>
-      <c r="Z167" s="49" t="str">
-        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="AA167" s="64"/>
     </row>
     <row r="168" spans="1:27">
       <c r="A168" s="62" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="B168" s="44"/>
       <c r="C168" s="46"/>
       <c r="D168" s="46"/>
       <c r="E168" s="50">
-        <f t="shared" si="46"/>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="F168" s="48"/>
       <c r="G168" s="51">
-        <f t="shared" si="47"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="H168" s="44"/>
@@ -12276,47 +12277,47 @@
         <v>0</v>
       </c>
       <c r="T168" s="51">
+        <f t="shared" si="46"/>
+        <v>0</v>
+      </c>
+      <c r="U168" s="51">
+        <f t="shared" si="47"/>
+        <v>0</v>
+      </c>
+      <c r="V168" s="51">
         <f t="shared" si="48"/>
         <v>0</v>
       </c>
-      <c r="U168" s="51">
+      <c r="W168" s="52">
         <f t="shared" si="49"/>
         <v>0</v>
       </c>
-      <c r="V168" s="51">
+      <c r="X168" s="48"/>
+      <c r="Y168" s="58">
+        <f t="shared" si="41"/>
+        <v>0</v>
+      </c>
+      <c r="Z168" s="49" t="str">
         <f t="shared" si="50"/>
-        <v>0</v>
-      </c>
-      <c r="W168" s="52">
-        <f t="shared" si="51"/>
-        <v>0</v>
-      </c>
-      <c r="X168" s="48"/>
-      <c r="Y168" s="51">
-        <f t="shared" si="52"/>
-        <v>0</v>
-      </c>
-      <c r="Z168" s="49" t="str">
-        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="AA168" s="64"/>
     </row>
     <row r="169" spans="1:27">
       <c r="A169" s="62" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="B169" s="44"/>
       <c r="C169" s="46"/>
       <c r="D169" s="46"/>
       <c r="E169" s="50">
-        <f t="shared" si="46"/>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="F169" s="48"/>
       <c r="G169" s="51">
-        <f t="shared" si="47"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="H169" s="44"/>
@@ -12335,47 +12336,47 @@
         <v>0</v>
       </c>
       <c r="T169" s="51">
+        <f t="shared" si="46"/>
+        <v>0</v>
+      </c>
+      <c r="U169" s="51">
+        <f t="shared" si="47"/>
+        <v>0</v>
+      </c>
+      <c r="V169" s="51">
         <f t="shared" si="48"/>
         <v>0</v>
       </c>
-      <c r="U169" s="51">
+      <c r="W169" s="52">
         <f t="shared" si="49"/>
         <v>0</v>
       </c>
-      <c r="V169" s="51">
+      <c r="X169" s="48"/>
+      <c r="Y169" s="58">
+        <f t="shared" si="41"/>
+        <v>0</v>
+      </c>
+      <c r="Z169" s="49" t="str">
         <f t="shared" si="50"/>
-        <v>0</v>
-      </c>
-      <c r="W169" s="52">
-        <f t="shared" si="51"/>
-        <v>0</v>
-      </c>
-      <c r="X169" s="48"/>
-      <c r="Y169" s="51">
-        <f t="shared" si="52"/>
-        <v>0</v>
-      </c>
-      <c r="Z169" s="49" t="str">
-        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="AA169" s="64"/>
     </row>
     <row r="170" spans="1:27">
       <c r="A170" s="62" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="B170" s="44"/>
       <c r="C170" s="46"/>
       <c r="D170" s="46"/>
       <c r="E170" s="50">
-        <f t="shared" si="46"/>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="F170" s="48"/>
       <c r="G170" s="51">
-        <f t="shared" si="47"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="H170" s="44"/>
@@ -12394,47 +12395,47 @@
         <v>0</v>
       </c>
       <c r="T170" s="51">
+        <f t="shared" si="46"/>
+        <v>0</v>
+      </c>
+      <c r="U170" s="51">
+        <f t="shared" si="47"/>
+        <v>0</v>
+      </c>
+      <c r="V170" s="51">
         <f t="shared" si="48"/>
         <v>0</v>
       </c>
-      <c r="U170" s="51">
+      <c r="W170" s="52">
         <f t="shared" si="49"/>
         <v>0</v>
       </c>
-      <c r="V170" s="51">
+      <c r="X170" s="48"/>
+      <c r="Y170" s="58">
+        <f t="shared" si="41"/>
+        <v>0</v>
+      </c>
+      <c r="Z170" s="49" t="str">
         <f t="shared" si="50"/>
-        <v>0</v>
-      </c>
-      <c r="W170" s="52">
-        <f t="shared" si="51"/>
-        <v>0</v>
-      </c>
-      <c r="X170" s="48"/>
-      <c r="Y170" s="51">
-        <f t="shared" si="52"/>
-        <v>0</v>
-      </c>
-      <c r="Z170" s="49" t="str">
-        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="AA170" s="64"/>
     </row>
     <row r="171" spans="1:27">
       <c r="A171" s="62" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="B171" s="44"/>
       <c r="C171" s="46"/>
       <c r="D171" s="46"/>
       <c r="E171" s="50">
-        <f t="shared" si="46"/>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="F171" s="48"/>
       <c r="G171" s="51">
-        <f t="shared" si="47"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="H171" s="44"/>
@@ -12453,47 +12454,47 @@
         <v>0</v>
       </c>
       <c r="T171" s="51">
+        <f t="shared" si="46"/>
+        <v>0</v>
+      </c>
+      <c r="U171" s="51">
+        <f t="shared" si="47"/>
+        <v>0</v>
+      </c>
+      <c r="V171" s="51">
         <f t="shared" si="48"/>
         <v>0</v>
       </c>
-      <c r="U171" s="51">
+      <c r="W171" s="52">
         <f t="shared" si="49"/>
         <v>0</v>
       </c>
-      <c r="V171" s="51">
+      <c r="X171" s="48"/>
+      <c r="Y171" s="58">
+        <f t="shared" si="41"/>
+        <v>0</v>
+      </c>
+      <c r="Z171" s="49" t="str">
         <f t="shared" si="50"/>
-        <v>0</v>
-      </c>
-      <c r="W171" s="52">
-        <f t="shared" si="51"/>
-        <v>0</v>
-      </c>
-      <c r="X171" s="48"/>
-      <c r="Y171" s="51">
-        <f t="shared" si="52"/>
-        <v>0</v>
-      </c>
-      <c r="Z171" s="49" t="str">
-        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="AA171" s="64"/>
     </row>
     <row r="172" spans="1:27">
       <c r="A172" s="62" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="B172" s="44"/>
       <c r="C172" s="46"/>
       <c r="D172" s="46"/>
       <c r="E172" s="50">
-        <f t="shared" si="46"/>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="F172" s="48"/>
       <c r="G172" s="51">
-        <f t="shared" si="47"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="H172" s="44"/>
@@ -12512,47 +12513,47 @@
         <v>0</v>
       </c>
       <c r="T172" s="51">
+        <f t="shared" si="46"/>
+        <v>0</v>
+      </c>
+      <c r="U172" s="51">
+        <f t="shared" si="47"/>
+        <v>0</v>
+      </c>
+      <c r="V172" s="51">
         <f t="shared" si="48"/>
         <v>0</v>
       </c>
-      <c r="U172" s="51">
+      <c r="W172" s="52">
         <f t="shared" si="49"/>
         <v>0</v>
       </c>
-      <c r="V172" s="51">
+      <c r="X172" s="48"/>
+      <c r="Y172" s="58">
+        <f t="shared" si="41"/>
+        <v>0</v>
+      </c>
+      <c r="Z172" s="49" t="str">
         <f t="shared" si="50"/>
-        <v>0</v>
-      </c>
-      <c r="W172" s="52">
-        <f t="shared" si="51"/>
-        <v>0</v>
-      </c>
-      <c r="X172" s="48"/>
-      <c r="Y172" s="51">
-        <f t="shared" si="52"/>
-        <v>0</v>
-      </c>
-      <c r="Z172" s="49" t="str">
-        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="AA172" s="64"/>
     </row>
     <row r="173" spans="1:27">
       <c r="A173" s="62" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="B173" s="44"/>
       <c r="C173" s="46"/>
       <c r="D173" s="46"/>
       <c r="E173" s="50">
-        <f t="shared" si="46"/>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="F173" s="48"/>
       <c r="G173" s="51">
-        <f t="shared" si="47"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="H173" s="44"/>
@@ -12571,47 +12572,47 @@
         <v>0</v>
       </c>
       <c r="T173" s="51">
+        <f t="shared" si="46"/>
+        <v>0</v>
+      </c>
+      <c r="U173" s="51">
+        <f t="shared" si="47"/>
+        <v>0</v>
+      </c>
+      <c r="V173" s="51">
         <f t="shared" si="48"/>
         <v>0</v>
       </c>
-      <c r="U173" s="51">
+      <c r="W173" s="52">
         <f t="shared" si="49"/>
         <v>0</v>
       </c>
-      <c r="V173" s="51">
+      <c r="X173" s="48"/>
+      <c r="Y173" s="58">
+        <f t="shared" si="41"/>
+        <v>0</v>
+      </c>
+      <c r="Z173" s="49" t="str">
         <f t="shared" si="50"/>
-        <v>0</v>
-      </c>
-      <c r="W173" s="52">
-        <f t="shared" si="51"/>
-        <v>0</v>
-      </c>
-      <c r="X173" s="48"/>
-      <c r="Y173" s="51">
-        <f t="shared" si="52"/>
-        <v>0</v>
-      </c>
-      <c r="Z173" s="49" t="str">
-        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="AA173" s="64"/>
     </row>
     <row r="174" spans="1:27">
       <c r="A174" s="62" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="B174" s="44"/>
       <c r="C174" s="46"/>
       <c r="D174" s="46"/>
       <c r="E174" s="50">
-        <f t="shared" si="46"/>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="F174" s="48"/>
       <c r="G174" s="51">
-        <f t="shared" si="47"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="H174" s="44"/>
@@ -12630,47 +12631,47 @@
         <v>0</v>
       </c>
       <c r="T174" s="51">
+        <f t="shared" si="46"/>
+        <v>0</v>
+      </c>
+      <c r="U174" s="51">
+        <f t="shared" si="47"/>
+        <v>0</v>
+      </c>
+      <c r="V174" s="51">
         <f t="shared" si="48"/>
         <v>0</v>
       </c>
-      <c r="U174" s="51">
+      <c r="W174" s="52">
         <f t="shared" si="49"/>
         <v>0</v>
       </c>
-      <c r="V174" s="51">
+      <c r="X174" s="48"/>
+      <c r="Y174" s="58">
+        <f t="shared" si="41"/>
+        <v>0</v>
+      </c>
+      <c r="Z174" s="49" t="str">
         <f t="shared" si="50"/>
-        <v>0</v>
-      </c>
-      <c r="W174" s="52">
-        <f t="shared" si="51"/>
-        <v>0</v>
-      </c>
-      <c r="X174" s="48"/>
-      <c r="Y174" s="51">
-        <f t="shared" si="52"/>
-        <v>0</v>
-      </c>
-      <c r="Z174" s="49" t="str">
-        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="AA174" s="64"/>
     </row>
     <row r="175" spans="1:27">
       <c r="A175" s="62" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="B175" s="44"/>
       <c r="C175" s="46"/>
       <c r="D175" s="46"/>
       <c r="E175" s="50">
-        <f t="shared" si="46"/>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="F175" s="48"/>
       <c r="G175" s="51">
-        <f t="shared" si="47"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="H175" s="44"/>
@@ -12689,47 +12690,47 @@
         <v>0</v>
       </c>
       <c r="T175" s="51">
+        <f t="shared" si="46"/>
+        <v>0</v>
+      </c>
+      <c r="U175" s="51">
+        <f t="shared" si="47"/>
+        <v>0</v>
+      </c>
+      <c r="V175" s="51">
         <f t="shared" si="48"/>
         <v>0</v>
       </c>
-      <c r="U175" s="51">
+      <c r="W175" s="52">
         <f t="shared" si="49"/>
         <v>0</v>
       </c>
-      <c r="V175" s="51">
+      <c r="X175" s="48"/>
+      <c r="Y175" s="58">
+        <f t="shared" si="41"/>
+        <v>0</v>
+      </c>
+      <c r="Z175" s="49" t="str">
         <f t="shared" si="50"/>
-        <v>0</v>
-      </c>
-      <c r="W175" s="52">
-        <f t="shared" si="51"/>
-        <v>0</v>
-      </c>
-      <c r="X175" s="48"/>
-      <c r="Y175" s="51">
-        <f t="shared" si="52"/>
-        <v>0</v>
-      </c>
-      <c r="Z175" s="49" t="str">
-        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="AA175" s="64"/>
     </row>
     <row r="176" spans="1:27">
       <c r="A176" s="62" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="B176" s="44"/>
       <c r="C176" s="46"/>
       <c r="D176" s="46"/>
       <c r="E176" s="50">
-        <f t="shared" si="46"/>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="F176" s="48"/>
       <c r="G176" s="51">
-        <f t="shared" si="47"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="H176" s="44"/>
@@ -12748,47 +12749,47 @@
         <v>0</v>
       </c>
       <c r="T176" s="51">
+        <f t="shared" si="46"/>
+        <v>0</v>
+      </c>
+      <c r="U176" s="51">
+        <f t="shared" si="47"/>
+        <v>0</v>
+      </c>
+      <c r="V176" s="51">
         <f t="shared" si="48"/>
         <v>0</v>
       </c>
-      <c r="U176" s="51">
+      <c r="W176" s="52">
         <f t="shared" si="49"/>
         <v>0</v>
       </c>
-      <c r="V176" s="51">
+      <c r="X176" s="48"/>
+      <c r="Y176" s="58">
+        <f t="shared" si="41"/>
+        <v>0</v>
+      </c>
+      <c r="Z176" s="49" t="str">
         <f t="shared" si="50"/>
-        <v>0</v>
-      </c>
-      <c r="W176" s="52">
-        <f t="shared" si="51"/>
-        <v>0</v>
-      </c>
-      <c r="X176" s="48"/>
-      <c r="Y176" s="51">
-        <f t="shared" si="52"/>
-        <v>0</v>
-      </c>
-      <c r="Z176" s="49" t="str">
-        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="AA176" s="64"/>
     </row>
     <row r="177" spans="1:27">
       <c r="A177" s="62" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="B177" s="44"/>
       <c r="C177" s="46"/>
       <c r="D177" s="46"/>
       <c r="E177" s="50">
-        <f t="shared" si="46"/>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="F177" s="48"/>
       <c r="G177" s="51">
-        <f t="shared" si="47"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="H177" s="44"/>
@@ -12807,47 +12808,47 @@
         <v>0</v>
       </c>
       <c r="T177" s="51">
+        <f t="shared" si="46"/>
+        <v>0</v>
+      </c>
+      <c r="U177" s="51">
+        <f t="shared" si="47"/>
+        <v>0</v>
+      </c>
+      <c r="V177" s="51">
         <f t="shared" si="48"/>
         <v>0</v>
       </c>
-      <c r="U177" s="51">
+      <c r="W177" s="52">
         <f t="shared" si="49"/>
         <v>0</v>
       </c>
-      <c r="V177" s="51">
+      <c r="X177" s="48"/>
+      <c r="Y177" s="58">
+        <f t="shared" si="41"/>
+        <v>0</v>
+      </c>
+      <c r="Z177" s="49" t="str">
         <f t="shared" si="50"/>
-        <v>0</v>
-      </c>
-      <c r="W177" s="52">
-        <f t="shared" si="51"/>
-        <v>0</v>
-      </c>
-      <c r="X177" s="48"/>
-      <c r="Y177" s="51">
-        <f t="shared" si="52"/>
-        <v>0</v>
-      </c>
-      <c r="Z177" s="49" t="str">
-        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="AA177" s="64"/>
     </row>
     <row r="178" spans="1:27">
       <c r="A178" s="62" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="B178" s="44"/>
       <c r="C178" s="46"/>
       <c r="D178" s="46"/>
       <c r="E178" s="50">
-        <f t="shared" si="46"/>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="F178" s="48"/>
       <c r="G178" s="51">
-        <f t="shared" si="47"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="H178" s="44"/>
@@ -12866,47 +12867,47 @@
         <v>0</v>
       </c>
       <c r="T178" s="51">
+        <f t="shared" si="46"/>
+        <v>0</v>
+      </c>
+      <c r="U178" s="51">
+        <f t="shared" si="47"/>
+        <v>0</v>
+      </c>
+      <c r="V178" s="51">
         <f t="shared" si="48"/>
         <v>0</v>
       </c>
-      <c r="U178" s="51">
+      <c r="W178" s="52">
         <f t="shared" si="49"/>
         <v>0</v>
       </c>
-      <c r="V178" s="51">
+      <c r="X178" s="48"/>
+      <c r="Y178" s="58">
+        <f t="shared" si="41"/>
+        <v>0</v>
+      </c>
+      <c r="Z178" s="49" t="str">
         <f t="shared" si="50"/>
-        <v>0</v>
-      </c>
-      <c r="W178" s="52">
-        <f t="shared" si="51"/>
-        <v>0</v>
-      </c>
-      <c r="X178" s="48"/>
-      <c r="Y178" s="51">
-        <f t="shared" si="52"/>
-        <v>0</v>
-      </c>
-      <c r="Z178" s="49" t="str">
-        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="AA178" s="64"/>
     </row>
     <row r="179" spans="1:27">
       <c r="A179" s="62" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="B179" s="44"/>
       <c r="C179" s="46"/>
       <c r="D179" s="46"/>
       <c r="E179" s="50">
-        <f t="shared" si="46"/>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="F179" s="48"/>
       <c r="G179" s="51">
-        <f t="shared" si="47"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="H179" s="44"/>
@@ -12925,47 +12926,47 @@
         <v>0</v>
       </c>
       <c r="T179" s="51">
+        <f t="shared" si="46"/>
+        <v>0</v>
+      </c>
+      <c r="U179" s="51">
+        <f t="shared" si="47"/>
+        <v>0</v>
+      </c>
+      <c r="V179" s="51">
         <f t="shared" si="48"/>
         <v>0</v>
       </c>
-      <c r="U179" s="51">
+      <c r="W179" s="52">
         <f t="shared" si="49"/>
         <v>0</v>
       </c>
-      <c r="V179" s="51">
+      <c r="X179" s="48"/>
+      <c r="Y179" s="58">
+        <f t="shared" si="41"/>
+        <v>0</v>
+      </c>
+      <c r="Z179" s="49" t="str">
         <f t="shared" si="50"/>
-        <v>0</v>
-      </c>
-      <c r="W179" s="52">
-        <f t="shared" si="51"/>
-        <v>0</v>
-      </c>
-      <c r="X179" s="48"/>
-      <c r="Y179" s="51">
-        <f t="shared" si="52"/>
-        <v>0</v>
-      </c>
-      <c r="Z179" s="49" t="str">
-        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="AA179" s="64"/>
     </row>
     <row r="180" spans="1:27">
       <c r="A180" s="62" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="B180" s="44"/>
       <c r="C180" s="46"/>
       <c r="D180" s="46"/>
       <c r="E180" s="50">
-        <f t="shared" si="46"/>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="F180" s="48"/>
       <c r="G180" s="51">
-        <f t="shared" si="47"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="H180" s="44"/>
@@ -12984,47 +12985,47 @@
         <v>0</v>
       </c>
       <c r="T180" s="51">
+        <f t="shared" si="46"/>
+        <v>0</v>
+      </c>
+      <c r="U180" s="51">
+        <f t="shared" si="47"/>
+        <v>0</v>
+      </c>
+      <c r="V180" s="51">
         <f t="shared" si="48"/>
         <v>0</v>
       </c>
-      <c r="U180" s="51">
+      <c r="W180" s="52">
         <f t="shared" si="49"/>
         <v>0</v>
       </c>
-      <c r="V180" s="51">
+      <c r="X180" s="48"/>
+      <c r="Y180" s="58">
+        <f t="shared" si="41"/>
+        <v>0</v>
+      </c>
+      <c r="Z180" s="49" t="str">
         <f t="shared" si="50"/>
-        <v>0</v>
-      </c>
-      <c r="W180" s="52">
-        <f t="shared" si="51"/>
-        <v>0</v>
-      </c>
-      <c r="X180" s="48"/>
-      <c r="Y180" s="51">
-        <f t="shared" si="52"/>
-        <v>0</v>
-      </c>
-      <c r="Z180" s="49" t="str">
-        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="AA180" s="64"/>
     </row>
     <row r="181" spans="1:27">
       <c r="A181" s="62" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="B181" s="44"/>
       <c r="C181" s="46"/>
       <c r="D181" s="46"/>
       <c r="E181" s="50">
-        <f t="shared" si="46"/>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="F181" s="48"/>
       <c r="G181" s="51">
-        <f t="shared" si="47"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="H181" s="44"/>
@@ -13043,47 +13044,47 @@
         <v>0</v>
       </c>
       <c r="T181" s="51">
+        <f t="shared" si="46"/>
+        <v>0</v>
+      </c>
+      <c r="U181" s="51">
+        <f t="shared" si="47"/>
+        <v>0</v>
+      </c>
+      <c r="V181" s="51">
         <f t="shared" si="48"/>
         <v>0</v>
       </c>
-      <c r="U181" s="51">
+      <c r="W181" s="52">
         <f t="shared" si="49"/>
         <v>0</v>
       </c>
-      <c r="V181" s="51">
+      <c r="X181" s="48"/>
+      <c r="Y181" s="58">
+        <f t="shared" si="41"/>
+        <v>0</v>
+      </c>
+      <c r="Z181" s="49" t="str">
         <f t="shared" si="50"/>
-        <v>0</v>
-      </c>
-      <c r="W181" s="52">
-        <f t="shared" si="51"/>
-        <v>0</v>
-      </c>
-      <c r="X181" s="48"/>
-      <c r="Y181" s="51">
-        <f t="shared" si="52"/>
-        <v>0</v>
-      </c>
-      <c r="Z181" s="49" t="str">
-        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="AA181" s="64"/>
     </row>
     <row r="182" spans="1:27">
       <c r="A182" s="62" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="B182" s="44"/>
       <c r="C182" s="46"/>
       <c r="D182" s="46"/>
       <c r="E182" s="50">
-        <f t="shared" si="46"/>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="F182" s="48"/>
       <c r="G182" s="51">
-        <f t="shared" si="47"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="H182" s="44"/>
@@ -13102,47 +13103,47 @@
         <v>0</v>
       </c>
       <c r="T182" s="51">
+        <f t="shared" si="46"/>
+        <v>0</v>
+      </c>
+      <c r="U182" s="51">
+        <f t="shared" si="47"/>
+        <v>0</v>
+      </c>
+      <c r="V182" s="51">
         <f t="shared" si="48"/>
         <v>0</v>
       </c>
-      <c r="U182" s="51">
+      <c r="W182" s="52">
         <f t="shared" si="49"/>
         <v>0</v>
       </c>
-      <c r="V182" s="51">
+      <c r="X182" s="48"/>
+      <c r="Y182" s="58">
+        <f t="shared" si="41"/>
+        <v>0</v>
+      </c>
+      <c r="Z182" s="49" t="str">
         <f t="shared" si="50"/>
-        <v>0</v>
-      </c>
-      <c r="W182" s="52">
-        <f t="shared" si="51"/>
-        <v>0</v>
-      </c>
-      <c r="X182" s="48"/>
-      <c r="Y182" s="51">
-        <f t="shared" si="52"/>
-        <v>0</v>
-      </c>
-      <c r="Z182" s="49" t="str">
-        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="AA182" s="64"/>
     </row>
     <row r="183" spans="1:27">
       <c r="A183" s="62" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="B183" s="44"/>
       <c r="C183" s="46"/>
       <c r="D183" s="46"/>
       <c r="E183" s="50">
-        <f t="shared" si="46"/>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="F183" s="48"/>
       <c r="G183" s="51">
-        <f t="shared" si="47"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="H183" s="44"/>
@@ -13161,47 +13162,47 @@
         <v>0</v>
       </c>
       <c r="T183" s="51">
+        <f t="shared" si="46"/>
+        <v>0</v>
+      </c>
+      <c r="U183" s="51">
+        <f t="shared" si="47"/>
+        <v>0</v>
+      </c>
+      <c r="V183" s="51">
         <f t="shared" si="48"/>
         <v>0</v>
       </c>
-      <c r="U183" s="51">
+      <c r="W183" s="52">
         <f t="shared" si="49"/>
         <v>0</v>
       </c>
-      <c r="V183" s="51">
+      <c r="X183" s="48"/>
+      <c r="Y183" s="58">
+        <f t="shared" si="41"/>
+        <v>0</v>
+      </c>
+      <c r="Z183" s="49" t="str">
         <f t="shared" si="50"/>
-        <v>0</v>
-      </c>
-      <c r="W183" s="52">
-        <f t="shared" si="51"/>
-        <v>0</v>
-      </c>
-      <c r="X183" s="48"/>
-      <c r="Y183" s="51">
-        <f t="shared" si="52"/>
-        <v>0</v>
-      </c>
-      <c r="Z183" s="49" t="str">
-        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="AA183" s="64"/>
     </row>
     <row r="184" spans="1:27">
       <c r="A184" s="62" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="B184" s="44"/>
       <c r="C184" s="46"/>
       <c r="D184" s="46"/>
       <c r="E184" s="50">
-        <f t="shared" si="46"/>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="F184" s="48"/>
       <c r="G184" s="51">
-        <f t="shared" si="47"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="H184" s="44"/>
@@ -13220,47 +13221,47 @@
         <v>0</v>
       </c>
       <c r="T184" s="51">
+        <f t="shared" si="46"/>
+        <v>0</v>
+      </c>
+      <c r="U184" s="51">
+        <f t="shared" si="47"/>
+        <v>0</v>
+      </c>
+      <c r="V184" s="51">
         <f t="shared" si="48"/>
         <v>0</v>
       </c>
-      <c r="U184" s="51">
+      <c r="W184" s="52">
         <f t="shared" si="49"/>
         <v>0</v>
       </c>
-      <c r="V184" s="51">
+      <c r="X184" s="48"/>
+      <c r="Y184" s="58">
+        <f t="shared" si="41"/>
+        <v>0</v>
+      </c>
+      <c r="Z184" s="49" t="str">
         <f t="shared" si="50"/>
-        <v>0</v>
-      </c>
-      <c r="W184" s="52">
-        <f t="shared" si="51"/>
-        <v>0</v>
-      </c>
-      <c r="X184" s="48"/>
-      <c r="Y184" s="51">
-        <f t="shared" si="52"/>
-        <v>0</v>
-      </c>
-      <c r="Z184" s="49" t="str">
-        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="AA184" s="64"/>
     </row>
     <row r="185" spans="1:27">
       <c r="A185" s="62" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="B185" s="44"/>
       <c r="C185" s="46"/>
       <c r="D185" s="46"/>
       <c r="E185" s="50">
-        <f t="shared" si="46"/>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="F185" s="48"/>
       <c r="G185" s="51">
-        <f t="shared" si="47"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="H185" s="44"/>
@@ -13279,47 +13280,47 @@
         <v>0</v>
       </c>
       <c r="T185" s="51">
+        <f t="shared" si="46"/>
+        <v>0</v>
+      </c>
+      <c r="U185" s="51">
+        <f t="shared" si="47"/>
+        <v>0</v>
+      </c>
+      <c r="V185" s="51">
         <f t="shared" si="48"/>
         <v>0</v>
       </c>
-      <c r="U185" s="51">
+      <c r="W185" s="52">
         <f t="shared" si="49"/>
         <v>0</v>
       </c>
-      <c r="V185" s="51">
+      <c r="X185" s="48"/>
+      <c r="Y185" s="58">
+        <f t="shared" si="41"/>
+        <v>0</v>
+      </c>
+      <c r="Z185" s="49" t="str">
         <f t="shared" si="50"/>
-        <v>0</v>
-      </c>
-      <c r="W185" s="52">
-        <f t="shared" si="51"/>
-        <v>0</v>
-      </c>
-      <c r="X185" s="48"/>
-      <c r="Y185" s="51">
-        <f t="shared" si="52"/>
-        <v>0</v>
-      </c>
-      <c r="Z185" s="49" t="str">
-        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="AA185" s="64"/>
     </row>
     <row r="186" spans="1:27">
       <c r="A186" s="62" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="B186" s="44"/>
       <c r="C186" s="46"/>
       <c r="D186" s="46"/>
       <c r="E186" s="50">
-        <f t="shared" si="46"/>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="F186" s="48"/>
       <c r="G186" s="51">
-        <f t="shared" si="47"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="H186" s="44"/>
@@ -13338,47 +13339,47 @@
         <v>0</v>
       </c>
       <c r="T186" s="51">
+        <f t="shared" si="46"/>
+        <v>0</v>
+      </c>
+      <c r="U186" s="51">
+        <f t="shared" si="47"/>
+        <v>0</v>
+      </c>
+      <c r="V186" s="51">
         <f t="shared" si="48"/>
         <v>0</v>
       </c>
-      <c r="U186" s="51">
+      <c r="W186" s="52">
         <f t="shared" si="49"/>
         <v>0</v>
       </c>
-      <c r="V186" s="51">
+      <c r="X186" s="48"/>
+      <c r="Y186" s="58">
+        <f t="shared" si="41"/>
+        <v>0</v>
+      </c>
+      <c r="Z186" s="49" t="str">
         <f t="shared" si="50"/>
-        <v>0</v>
-      </c>
-      <c r="W186" s="52">
-        <f t="shared" si="51"/>
-        <v>0</v>
-      </c>
-      <c r="X186" s="48"/>
-      <c r="Y186" s="51">
-        <f t="shared" si="52"/>
-        <v>0</v>
-      </c>
-      <c r="Z186" s="49" t="str">
-        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="AA186" s="64"/>
     </row>
     <row r="187" spans="1:27">
       <c r="A187" s="62" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="B187" s="44"/>
       <c r="C187" s="46"/>
       <c r="D187" s="46"/>
       <c r="E187" s="50">
-        <f t="shared" si="46"/>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="F187" s="48"/>
       <c r="G187" s="51">
-        <f t="shared" si="47"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="H187" s="44"/>
@@ -13397,47 +13398,47 @@
         <v>0</v>
       </c>
       <c r="T187" s="51">
+        <f t="shared" si="46"/>
+        <v>0</v>
+      </c>
+      <c r="U187" s="51">
+        <f t="shared" si="47"/>
+        <v>0</v>
+      </c>
+      <c r="V187" s="51">
         <f t="shared" si="48"/>
         <v>0</v>
       </c>
-      <c r="U187" s="51">
+      <c r="W187" s="52">
         <f t="shared" si="49"/>
         <v>0</v>
       </c>
-      <c r="V187" s="51">
+      <c r="X187" s="48"/>
+      <c r="Y187" s="58">
+        <f t="shared" si="41"/>
+        <v>0</v>
+      </c>
+      <c r="Z187" s="49" t="str">
         <f t="shared" si="50"/>
-        <v>0</v>
-      </c>
-      <c r="W187" s="52">
-        <f t="shared" si="51"/>
-        <v>0</v>
-      </c>
-      <c r="X187" s="48"/>
-      <c r="Y187" s="51">
-        <f t="shared" si="52"/>
-        <v>0</v>
-      </c>
-      <c r="Z187" s="49" t="str">
-        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="AA187" s="64"/>
     </row>
     <row r="188" spans="1:27">
       <c r="A188" s="62" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="B188" s="44"/>
       <c r="C188" s="46"/>
       <c r="D188" s="46"/>
       <c r="E188" s="50">
-        <f t="shared" si="46"/>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="F188" s="48"/>
       <c r="G188" s="51">
-        <f t="shared" si="47"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="H188" s="44"/>
@@ -13456,47 +13457,47 @@
         <v>0</v>
       </c>
       <c r="T188" s="51">
+        <f t="shared" si="46"/>
+        <v>0</v>
+      </c>
+      <c r="U188" s="51">
+        <f t="shared" si="47"/>
+        <v>0</v>
+      </c>
+      <c r="V188" s="51">
         <f t="shared" si="48"/>
         <v>0</v>
       </c>
-      <c r="U188" s="51">
+      <c r="W188" s="52">
         <f t="shared" si="49"/>
         <v>0</v>
       </c>
-      <c r="V188" s="51">
+      <c r="X188" s="48"/>
+      <c r="Y188" s="58">
+        <f t="shared" si="41"/>
+        <v>0</v>
+      </c>
+      <c r="Z188" s="49" t="str">
         <f t="shared" si="50"/>
-        <v>0</v>
-      </c>
-      <c r="W188" s="52">
-        <f t="shared" si="51"/>
-        <v>0</v>
-      </c>
-      <c r="X188" s="48"/>
-      <c r="Y188" s="51">
-        <f t="shared" si="52"/>
-        <v>0</v>
-      </c>
-      <c r="Z188" s="49" t="str">
-        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="AA188" s="64"/>
     </row>
     <row r="189" spans="1:27">
       <c r="A189" s="62" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="B189" s="44"/>
       <c r="C189" s="46"/>
       <c r="D189" s="46"/>
       <c r="E189" s="50">
-        <f t="shared" si="46"/>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="F189" s="48"/>
       <c r="G189" s="51">
-        <f t="shared" si="47"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="H189" s="44"/>
@@ -13515,47 +13516,47 @@
         <v>0</v>
       </c>
       <c r="T189" s="51">
+        <f t="shared" si="46"/>
+        <v>0</v>
+      </c>
+      <c r="U189" s="51">
+        <f t="shared" si="47"/>
+        <v>0</v>
+      </c>
+      <c r="V189" s="51">
         <f t="shared" si="48"/>
         <v>0</v>
       </c>
-      <c r="U189" s="51">
+      <c r="W189" s="52">
         <f t="shared" si="49"/>
         <v>0</v>
       </c>
-      <c r="V189" s="51">
+      <c r="X189" s="48"/>
+      <c r="Y189" s="58">
+        <f t="shared" si="41"/>
+        <v>0</v>
+      </c>
+      <c r="Z189" s="49" t="str">
         <f t="shared" si="50"/>
-        <v>0</v>
-      </c>
-      <c r="W189" s="52">
-        <f t="shared" si="51"/>
-        <v>0</v>
-      </c>
-      <c r="X189" s="48"/>
-      <c r="Y189" s="51">
-        <f t="shared" si="52"/>
-        <v>0</v>
-      </c>
-      <c r="Z189" s="49" t="str">
-        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="AA189" s="64"/>
     </row>
     <row r="190" spans="1:27">
       <c r="A190" s="62" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="B190" s="44"/>
       <c r="C190" s="46"/>
       <c r="D190" s="46"/>
       <c r="E190" s="50">
-        <f t="shared" si="46"/>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="F190" s="48"/>
       <c r="G190" s="51">
-        <f t="shared" si="47"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="H190" s="44"/>
@@ -13574,47 +13575,47 @@
         <v>0</v>
       </c>
       <c r="T190" s="51">
+        <f t="shared" si="46"/>
+        <v>0</v>
+      </c>
+      <c r="U190" s="51">
+        <f t="shared" si="47"/>
+        <v>0</v>
+      </c>
+      <c r="V190" s="51">
         <f t="shared" si="48"/>
         <v>0</v>
       </c>
-      <c r="U190" s="51">
+      <c r="W190" s="52">
         <f t="shared" si="49"/>
         <v>0</v>
       </c>
-      <c r="V190" s="51">
+      <c r="X190" s="48"/>
+      <c r="Y190" s="58">
+        <f t="shared" si="41"/>
+        <v>0</v>
+      </c>
+      <c r="Z190" s="49" t="str">
         <f t="shared" si="50"/>
-        <v>0</v>
-      </c>
-      <c r="W190" s="52">
-        <f t="shared" si="51"/>
-        <v>0</v>
-      </c>
-      <c r="X190" s="48"/>
-      <c r="Y190" s="51">
-        <f t="shared" si="52"/>
-        <v>0</v>
-      </c>
-      <c r="Z190" s="49" t="str">
-        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="AA190" s="64"/>
     </row>
     <row r="191" spans="1:27">
       <c r="A191" s="62" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="B191" s="44"/>
       <c r="C191" s="46"/>
       <c r="D191" s="46"/>
       <c r="E191" s="50">
-        <f t="shared" si="46"/>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="F191" s="48"/>
       <c r="G191" s="51">
-        <f t="shared" si="47"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="H191" s="44"/>
@@ -13633,47 +13634,47 @@
         <v>0</v>
       </c>
       <c r="T191" s="51">
+        <f t="shared" si="46"/>
+        <v>0</v>
+      </c>
+      <c r="U191" s="51">
+        <f t="shared" si="47"/>
+        <v>0</v>
+      </c>
+      <c r="V191" s="51">
         <f t="shared" si="48"/>
         <v>0</v>
       </c>
-      <c r="U191" s="51">
+      <c r="W191" s="52">
         <f t="shared" si="49"/>
         <v>0</v>
       </c>
-      <c r="V191" s="51">
+      <c r="X191" s="48"/>
+      <c r="Y191" s="58">
+        <f t="shared" si="41"/>
+        <v>0</v>
+      </c>
+      <c r="Z191" s="49" t="str">
         <f t="shared" si="50"/>
-        <v>0</v>
-      </c>
-      <c r="W191" s="52">
-        <f t="shared" si="51"/>
-        <v>0</v>
-      </c>
-      <c r="X191" s="48"/>
-      <c r="Y191" s="51">
-        <f t="shared" si="52"/>
-        <v>0</v>
-      </c>
-      <c r="Z191" s="49" t="str">
-        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="AA191" s="64"/>
     </row>
     <row r="192" spans="1:27">
       <c r="A192" s="62" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="B192" s="44"/>
       <c r="C192" s="46"/>
       <c r="D192" s="46"/>
       <c r="E192" s="50">
-        <f t="shared" si="46"/>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="F192" s="48"/>
       <c r="G192" s="51">
-        <f t="shared" si="47"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="H192" s="44"/>
@@ -13692,47 +13693,47 @@
         <v>0</v>
       </c>
       <c r="T192" s="51">
+        <f t="shared" si="46"/>
+        <v>0</v>
+      </c>
+      <c r="U192" s="51">
+        <f t="shared" si="47"/>
+        <v>0</v>
+      </c>
+      <c r="V192" s="51">
         <f t="shared" si="48"/>
         <v>0</v>
       </c>
-      <c r="U192" s="51">
+      <c r="W192" s="52">
         <f t="shared" si="49"/>
         <v>0</v>
       </c>
-      <c r="V192" s="51">
+      <c r="X192" s="48"/>
+      <c r="Y192" s="58">
+        <f t="shared" si="41"/>
+        <v>0</v>
+      </c>
+      <c r="Z192" s="49" t="str">
         <f t="shared" si="50"/>
-        <v>0</v>
-      </c>
-      <c r="W192" s="52">
-        <f t="shared" si="51"/>
-        <v>0</v>
-      </c>
-      <c r="X192" s="48"/>
-      <c r="Y192" s="51">
-        <f t="shared" si="52"/>
-        <v>0</v>
-      </c>
-      <c r="Z192" s="49" t="str">
-        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="AA192" s="64"/>
     </row>
     <row r="193" spans="1:27">
       <c r="A193" s="62" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="B193" s="44"/>
       <c r="C193" s="46"/>
       <c r="D193" s="46"/>
       <c r="E193" s="50">
-        <f t="shared" si="46"/>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="F193" s="48"/>
       <c r="G193" s="51">
-        <f t="shared" si="47"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="H193" s="44"/>
@@ -13751,47 +13752,47 @@
         <v>0</v>
       </c>
       <c r="T193" s="51">
+        <f t="shared" si="46"/>
+        <v>0</v>
+      </c>
+      <c r="U193" s="51">
+        <f t="shared" si="47"/>
+        <v>0</v>
+      </c>
+      <c r="V193" s="51">
         <f t="shared" si="48"/>
         <v>0</v>
       </c>
-      <c r="U193" s="51">
+      <c r="W193" s="52">
         <f t="shared" si="49"/>
         <v>0</v>
       </c>
-      <c r="V193" s="51">
+      <c r="X193" s="48"/>
+      <c r="Y193" s="58">
+        <f t="shared" si="41"/>
+        <v>0</v>
+      </c>
+      <c r="Z193" s="49" t="str">
         <f t="shared" si="50"/>
-        <v>0</v>
-      </c>
-      <c r="W193" s="52">
-        <f t="shared" si="51"/>
-        <v>0</v>
-      </c>
-      <c r="X193" s="48"/>
-      <c r="Y193" s="51">
-        <f t="shared" si="52"/>
-        <v>0</v>
-      </c>
-      <c r="Z193" s="49" t="str">
-        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="AA193" s="64"/>
     </row>
     <row r="194" spans="1:27">
       <c r="A194" s="62" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="B194" s="44"/>
       <c r="C194" s="46"/>
       <c r="D194" s="46"/>
       <c r="E194" s="50">
-        <f t="shared" si="46"/>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="F194" s="48"/>
       <c r="G194" s="51">
-        <f t="shared" si="47"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="H194" s="44"/>
@@ -13810,47 +13811,47 @@
         <v>0</v>
       </c>
       <c r="T194" s="51">
+        <f t="shared" si="46"/>
+        <v>0</v>
+      </c>
+      <c r="U194" s="51">
+        <f t="shared" si="47"/>
+        <v>0</v>
+      </c>
+      <c r="V194" s="51">
         <f t="shared" si="48"/>
         <v>0</v>
       </c>
-      <c r="U194" s="51">
+      <c r="W194" s="52">
         <f t="shared" si="49"/>
         <v>0</v>
       </c>
-      <c r="V194" s="51">
+      <c r="X194" s="48"/>
+      <c r="Y194" s="58">
+        <f t="shared" si="41"/>
+        <v>0</v>
+      </c>
+      <c r="Z194" s="49" t="str">
         <f t="shared" si="50"/>
-        <v>0</v>
-      </c>
-      <c r="W194" s="52">
-        <f t="shared" si="51"/>
-        <v>0</v>
-      </c>
-      <c r="X194" s="48"/>
-      <c r="Y194" s="51">
-        <f t="shared" si="52"/>
-        <v>0</v>
-      </c>
-      <c r="Z194" s="49" t="str">
-        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="AA194" s="64"/>
     </row>
     <row r="195" spans="1:27">
       <c r="A195" s="62" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="B195" s="44"/>
       <c r="C195" s="46"/>
       <c r="D195" s="46"/>
       <c r="E195" s="50">
-        <f t="shared" si="46"/>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="F195" s="48"/>
       <c r="G195" s="51">
-        <f t="shared" si="47"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="H195" s="44"/>
@@ -13869,47 +13870,47 @@
         <v>0</v>
       </c>
       <c r="T195" s="51">
+        <f t="shared" si="46"/>
+        <v>0</v>
+      </c>
+      <c r="U195" s="51">
+        <f t="shared" si="47"/>
+        <v>0</v>
+      </c>
+      <c r="V195" s="51">
         <f t="shared" si="48"/>
         <v>0</v>
       </c>
-      <c r="U195" s="51">
+      <c r="W195" s="52">
         <f t="shared" si="49"/>
         <v>0</v>
       </c>
-      <c r="V195" s="51">
+      <c r="X195" s="48"/>
+      <c r="Y195" s="58">
+        <f t="shared" si="41"/>
+        <v>0</v>
+      </c>
+      <c r="Z195" s="49" t="str">
         <f t="shared" si="50"/>
-        <v>0</v>
-      </c>
-      <c r="W195" s="52">
-        <f t="shared" si="51"/>
-        <v>0</v>
-      </c>
-      <c r="X195" s="48"/>
-      <c r="Y195" s="51">
-        <f t="shared" si="52"/>
-        <v>0</v>
-      </c>
-      <c r="Z195" s="49" t="str">
-        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="AA195" s="64"/>
     </row>
     <row r="196" spans="1:27">
       <c r="A196" s="62" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="B196" s="44"/>
       <c r="C196" s="46"/>
       <c r="D196" s="46"/>
       <c r="E196" s="50">
-        <f t="shared" si="46"/>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="F196" s="48"/>
       <c r="G196" s="51">
-        <f t="shared" si="47"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="H196" s="44"/>
@@ -13928,47 +13929,47 @@
         <v>0</v>
       </c>
       <c r="T196" s="51">
+        <f t="shared" si="46"/>
+        <v>0</v>
+      </c>
+      <c r="U196" s="51">
+        <f t="shared" si="47"/>
+        <v>0</v>
+      </c>
+      <c r="V196" s="51">
         <f t="shared" si="48"/>
         <v>0</v>
       </c>
-      <c r="U196" s="51">
+      <c r="W196" s="52">
         <f t="shared" si="49"/>
         <v>0</v>
       </c>
-      <c r="V196" s="51">
+      <c r="X196" s="48"/>
+      <c r="Y196" s="58">
+        <f t="shared" si="41"/>
+        <v>0</v>
+      </c>
+      <c r="Z196" s="49" t="str">
         <f t="shared" si="50"/>
-        <v>0</v>
-      </c>
-      <c r="W196" s="52">
-        <f t="shared" si="51"/>
-        <v>0</v>
-      </c>
-      <c r="X196" s="48"/>
-      <c r="Y196" s="51">
-        <f t="shared" si="52"/>
-        <v>0</v>
-      </c>
-      <c r="Z196" s="49" t="str">
-        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="AA196" s="64"/>
     </row>
     <row r="197" spans="1:27">
       <c r="A197" s="62" t="str">
-        <f t="shared" ref="A197:A204" si="54">IF(B197="","","LOC-"&amp;TEXT(ROW()-5,"000"))</f>
+        <f t="shared" ref="A197:A204" si="51">IF(B197="","","LOC-"&amp;TEXT(ROW()-5,"000"))</f>
         <v/>
       </c>
       <c r="B197" s="44"/>
       <c r="C197" s="46"/>
       <c r="D197" s="46"/>
       <c r="E197" s="50">
-        <f t="shared" ref="E197:E204" si="55">IF(OR(B197="",C197="",D197=""),0,MAX(0,D197-C197))</f>
+        <f t="shared" ref="E197:E204" si="52">IF(OR(B197="",C197="",D197=""),0,MAX(0,D197-C197))</f>
         <v>0</v>
       </c>
       <c r="F197" s="48"/>
       <c r="G197" s="51">
-        <f t="shared" ref="G197:G204" si="56">IF(OR(B197="",E197=0,F197=""),0,E197*F197)</f>
+        <f t="shared" ref="G197:G204" si="53">IF(OR(B197="",E197=0,F197=""),0,E197*F197)</f>
         <v>0</v>
       </c>
       <c r="H197" s="44"/>
@@ -13987,47 +13988,47 @@
         <v>0</v>
       </c>
       <c r="T197" s="51">
-        <f t="shared" ref="T197:T204" si="57">IF(OR(B197="",E197=0),0,S197/E197)</f>
+        <f t="shared" ref="T197:T204" si="54">IF(OR(B197="",E197=0),0,S197/E197)</f>
         <v>0</v>
       </c>
       <c r="U197" s="51">
-        <f t="shared" ref="U197:U204" si="58">IF(B197="",0,G197-S197)</f>
+        <f t="shared" ref="U197:U204" si="55">IF(B197="",0,G197-S197)</f>
         <v>0</v>
       </c>
       <c r="V197" s="51">
-        <f t="shared" ref="V197:V204" si="59">IF(OR(B197="",E197=0),0,U197/E197)</f>
+        <f t="shared" ref="V197:V204" si="56">IF(OR(B197="",E197=0),0,U197/E197)</f>
         <v>0</v>
       </c>
       <c r="W197" s="52">
-        <f t="shared" ref="W197:W204" si="60">IF(OR(B197="",G197=0),0,U197/G197)</f>
+        <f t="shared" ref="W197:W204" si="57">IF(OR(B197="",G197=0),0,U197/G197)</f>
         <v>0</v>
       </c>
       <c r="X197" s="48"/>
-      <c r="Y197" s="51">
-        <f t="shared" ref="Y197:Y204" si="61">IF(B197="",0,IFERROR(MAX(0,G197-X197),G197))</f>
+      <c r="Y197" s="58">
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="Z197" s="49" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="AA197" s="64"/>
     </row>
     <row r="198" spans="1:27">
       <c r="A198" s="62" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="B198" s="44"/>
       <c r="C198" s="46"/>
       <c r="D198" s="46"/>
       <c r="E198" s="50">
-        <f t="shared" si="55"/>
+        <f t="shared" si="52"/>
         <v>0</v>
       </c>
       <c r="F198" s="48"/>
       <c r="G198" s="51">
-        <f t="shared" si="56"/>
+        <f t="shared" si="53"/>
         <v>0</v>
       </c>
       <c r="H198" s="44"/>
@@ -14046,47 +14047,47 @@
         <v>0</v>
       </c>
       <c r="T198" s="51">
+        <f t="shared" si="54"/>
+        <v>0</v>
+      </c>
+      <c r="U198" s="51">
+        <f t="shared" si="55"/>
+        <v>0</v>
+      </c>
+      <c r="V198" s="51">
+        <f t="shared" si="56"/>
+        <v>0</v>
+      </c>
+      <c r="W198" s="52">
         <f t="shared" si="57"/>
         <v>0</v>
       </c>
-      <c r="U198" s="51">
-        <f t="shared" si="58"/>
-        <v>0</v>
-      </c>
-      <c r="V198" s="51">
-        <f t="shared" si="59"/>
-        <v>0</v>
-      </c>
-      <c r="W198" s="52">
-        <f t="shared" si="60"/>
-        <v>0</v>
-      </c>
       <c r="X198" s="48"/>
-      <c r="Y198" s="51">
-        <f t="shared" si="61"/>
+      <c r="Y198" s="58">
+        <f t="shared" ref="Y198:Y204" si="58">IF(B198="",0,IFERROR(MAX(0,G198-X198),G198))</f>
         <v>0</v>
       </c>
       <c r="Z198" s="49" t="str">
-        <f t="shared" ref="Z198:Z204" si="62">IF(B198="","",IF(COUNTIFS($C$6:$C$204,"&lt;"&amp;D198,$D$6:$D$204,"&gt;"&amp;C198,$I$6:$I$204,"&lt;&gt;Cancelada",$I$6:$I$204,"&lt;&gt;Consulta")&gt;1,"CONFLITO","OK"))</f>
+        <f t="shared" ref="Z198:Z204" si="59">IF(B198="","",IF(COUNTIFS($C$6:$C$204,"&lt;"&amp;D198,$D$6:$D$204,"&gt;"&amp;C198,$I$6:$I$204,"&lt;&gt;Cancelada",$I$6:$I$204,"&lt;&gt;Consulta")&gt;1,"CONFLITO","OK"))</f>
         <v/>
       </c>
       <c r="AA198" s="64"/>
     </row>
     <row r="199" spans="1:27">
       <c r="A199" s="62" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="B199" s="44"/>
       <c r="C199" s="46"/>
       <c r="D199" s="46"/>
       <c r="E199" s="50">
-        <f t="shared" si="55"/>
+        <f t="shared" si="52"/>
         <v>0</v>
       </c>
       <c r="F199" s="48"/>
       <c r="G199" s="51">
-        <f t="shared" si="56"/>
+        <f t="shared" si="53"/>
         <v>0</v>
       </c>
       <c r="H199" s="44"/>
@@ -14105,47 +14106,47 @@
         <v>0</v>
       </c>
       <c r="T199" s="51">
+        <f t="shared" si="54"/>
+        <v>0</v>
+      </c>
+      <c r="U199" s="51">
+        <f t="shared" si="55"/>
+        <v>0</v>
+      </c>
+      <c r="V199" s="51">
+        <f t="shared" si="56"/>
+        <v>0</v>
+      </c>
+      <c r="W199" s="52">
         <f t="shared" si="57"/>
         <v>0</v>
       </c>
-      <c r="U199" s="51">
+      <c r="X199" s="48"/>
+      <c r="Y199" s="58">
         <f t="shared" si="58"/>
         <v>0</v>
       </c>
-      <c r="V199" s="51">
+      <c r="Z199" s="49" t="str">
         <f t="shared" si="59"/>
-        <v>0</v>
-      </c>
-      <c r="W199" s="52">
-        <f t="shared" si="60"/>
-        <v>0</v>
-      </c>
-      <c r="X199" s="48"/>
-      <c r="Y199" s="51">
-        <f t="shared" si="61"/>
-        <v>0</v>
-      </c>
-      <c r="Z199" s="49" t="str">
-        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="AA199" s="64"/>
     </row>
     <row r="200" spans="1:27">
       <c r="A200" s="62" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="B200" s="44"/>
       <c r="C200" s="46"/>
       <c r="D200" s="46"/>
       <c r="E200" s="50">
-        <f t="shared" si="55"/>
+        <f t="shared" si="52"/>
         <v>0</v>
       </c>
       <c r="F200" s="48"/>
       <c r="G200" s="51">
-        <f t="shared" si="56"/>
+        <f t="shared" si="53"/>
         <v>0</v>
       </c>
       <c r="H200" s="44"/>
@@ -14164,47 +14165,47 @@
         <v>0</v>
       </c>
       <c r="T200" s="51">
+        <f t="shared" si="54"/>
+        <v>0</v>
+      </c>
+      <c r="U200" s="51">
+        <f t="shared" si="55"/>
+        <v>0</v>
+      </c>
+      <c r="V200" s="51">
+        <f t="shared" si="56"/>
+        <v>0</v>
+      </c>
+      <c r="W200" s="52">
         <f t="shared" si="57"/>
         <v>0</v>
       </c>
-      <c r="U200" s="51">
+      <c r="X200" s="48"/>
+      <c r="Y200" s="58">
         <f t="shared" si="58"/>
         <v>0</v>
       </c>
-      <c r="V200" s="51">
+      <c r="Z200" s="49" t="str">
         <f t="shared" si="59"/>
-        <v>0</v>
-      </c>
-      <c r="W200" s="52">
-        <f t="shared" si="60"/>
-        <v>0</v>
-      </c>
-      <c r="X200" s="48"/>
-      <c r="Y200" s="51">
-        <f t="shared" si="61"/>
-        <v>0</v>
-      </c>
-      <c r="Z200" s="49" t="str">
-        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="AA200" s="64"/>
     </row>
     <row r="201" spans="1:27">
       <c r="A201" s="62" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="B201" s="44"/>
       <c r="C201" s="46"/>
       <c r="D201" s="46"/>
       <c r="E201" s="50">
-        <f t="shared" si="55"/>
+        <f t="shared" si="52"/>
         <v>0</v>
       </c>
       <c r="F201" s="48"/>
       <c r="G201" s="51">
-        <f t="shared" si="56"/>
+        <f t="shared" si="53"/>
         <v>0</v>
       </c>
       <c r="H201" s="44"/>
@@ -14223,47 +14224,47 @@
         <v>0</v>
       </c>
       <c r="T201" s="51">
+        <f t="shared" si="54"/>
+        <v>0</v>
+      </c>
+      <c r="U201" s="51">
+        <f t="shared" si="55"/>
+        <v>0</v>
+      </c>
+      <c r="V201" s="51">
+        <f t="shared" si="56"/>
+        <v>0</v>
+      </c>
+      <c r="W201" s="52">
         <f t="shared" si="57"/>
         <v>0</v>
       </c>
-      <c r="U201" s="51">
+      <c r="X201" s="48"/>
+      <c r="Y201" s="58">
         <f t="shared" si="58"/>
         <v>0</v>
       </c>
-      <c r="V201" s="51">
+      <c r="Z201" s="49" t="str">
         <f t="shared" si="59"/>
-        <v>0</v>
-      </c>
-      <c r="W201" s="52">
-        <f t="shared" si="60"/>
-        <v>0</v>
-      </c>
-      <c r="X201" s="48"/>
-      <c r="Y201" s="51">
-        <f t="shared" si="61"/>
-        <v>0</v>
-      </c>
-      <c r="Z201" s="49" t="str">
-        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="AA201" s="64"/>
     </row>
     <row r="202" spans="1:27">
       <c r="A202" s="62" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="B202" s="44"/>
       <c r="C202" s="46"/>
       <c r="D202" s="46"/>
       <c r="E202" s="50">
-        <f t="shared" si="55"/>
+        <f t="shared" si="52"/>
         <v>0</v>
       </c>
       <c r="F202" s="48"/>
       <c r="G202" s="51">
-        <f t="shared" si="56"/>
+        <f t="shared" si="53"/>
         <v>0</v>
       </c>
       <c r="H202" s="44"/>
@@ -14282,47 +14283,47 @@
         <v>0</v>
       </c>
       <c r="T202" s="51">
+        <f t="shared" si="54"/>
+        <v>0</v>
+      </c>
+      <c r="U202" s="51">
+        <f t="shared" si="55"/>
+        <v>0</v>
+      </c>
+      <c r="V202" s="51">
+        <f t="shared" si="56"/>
+        <v>0</v>
+      </c>
+      <c r="W202" s="52">
         <f t="shared" si="57"/>
         <v>0</v>
       </c>
-      <c r="U202" s="51">
+      <c r="X202" s="48"/>
+      <c r="Y202" s="58">
         <f t="shared" si="58"/>
         <v>0</v>
       </c>
-      <c r="V202" s="51">
+      <c r="Z202" s="49" t="str">
         <f t="shared" si="59"/>
-        <v>0</v>
-      </c>
-      <c r="W202" s="52">
-        <f t="shared" si="60"/>
-        <v>0</v>
-      </c>
-      <c r="X202" s="48"/>
-      <c r="Y202" s="51">
-        <f t="shared" si="61"/>
-        <v>0</v>
-      </c>
-      <c r="Z202" s="49" t="str">
-        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="AA202" s="64"/>
     </row>
     <row r="203" spans="1:27">
       <c r="A203" s="62" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="B203" s="44"/>
       <c r="C203" s="46"/>
       <c r="D203" s="46"/>
       <c r="E203" s="50">
-        <f t="shared" si="55"/>
+        <f t="shared" si="52"/>
         <v>0</v>
       </c>
       <c r="F203" s="48"/>
       <c r="G203" s="51">
-        <f t="shared" si="56"/>
+        <f t="shared" si="53"/>
         <v>0</v>
       </c>
       <c r="H203" s="44"/>
@@ -14341,47 +14342,47 @@
         <v>0</v>
       </c>
       <c r="T203" s="51">
+        <f t="shared" si="54"/>
+        <v>0</v>
+      </c>
+      <c r="U203" s="51">
+        <f t="shared" si="55"/>
+        <v>0</v>
+      </c>
+      <c r="V203" s="51">
+        <f t="shared" si="56"/>
+        <v>0</v>
+      </c>
+      <c r="W203" s="52">
         <f t="shared" si="57"/>
         <v>0</v>
       </c>
-      <c r="U203" s="51">
+      <c r="X203" s="48"/>
+      <c r="Y203" s="58">
         <f t="shared" si="58"/>
         <v>0</v>
       </c>
-      <c r="V203" s="51">
+      <c r="Z203" s="49" t="str">
         <f t="shared" si="59"/>
-        <v>0</v>
-      </c>
-      <c r="W203" s="52">
-        <f t="shared" si="60"/>
-        <v>0</v>
-      </c>
-      <c r="X203" s="48"/>
-      <c r="Y203" s="51">
-        <f t="shared" si="61"/>
-        <v>0</v>
-      </c>
-      <c r="Z203" s="49" t="str">
-        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="AA203" s="64"/>
     </row>
     <row r="204" spans="1:27">
       <c r="A204" s="65" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="B204" s="66"/>
       <c r="C204" s="67"/>
       <c r="D204" s="67"/>
       <c r="E204" s="68">
-        <f t="shared" si="55"/>
+        <f t="shared" si="52"/>
         <v>0</v>
       </c>
       <c r="F204" s="69"/>
       <c r="G204" s="70">
-        <f t="shared" si="56"/>
+        <f t="shared" si="53"/>
         <v>0</v>
       </c>
       <c r="H204" s="66"/>
@@ -14400,28 +14401,28 @@
         <v>0</v>
       </c>
       <c r="T204" s="70">
+        <f t="shared" si="54"/>
+        <v>0</v>
+      </c>
+      <c r="U204" s="70">
+        <f t="shared" si="55"/>
+        <v>0</v>
+      </c>
+      <c r="V204" s="70">
+        <f t="shared" si="56"/>
+        <v>0</v>
+      </c>
+      <c r="W204" s="71">
         <f t="shared" si="57"/>
         <v>0</v>
       </c>
-      <c r="U204" s="70">
+      <c r="X204" s="69"/>
+      <c r="Y204" s="58">
         <f t="shared" si="58"/>
         <v>0</v>
       </c>
-      <c r="V204" s="70">
+      <c r="Z204" s="72" t="str">
         <f t="shared" si="59"/>
-        <v>0</v>
-      </c>
-      <c r="W204" s="71">
-        <f t="shared" si="60"/>
-        <v>0</v>
-      </c>
-      <c r="X204" s="69"/>
-      <c r="Y204" s="70">
-        <f t="shared" si="61"/>
-        <v>0</v>
-      </c>
-      <c r="Z204" s="72" t="str">
-        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="AA204" s="73"/>
@@ -14436,7 +14437,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Y6:Y64">
+  <conditionalFormatting sqref="Y6:Y204">
     <cfRule type="expression" dxfId="3" priority="3">
       <formula>Y6&gt;0</formula>
     </cfRule>

--- a/Controle_Locacao.xlsx
+++ b/Controle_Locacao.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Renato.Neves\Documents\TRABALHOS 2025\LOCAÇÃO PRAIA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C32F49AB-3A53-44B1-AE48-DABD717F70D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57514459-33F0-4018-8AE4-100F7AC13664}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PAINEL" sheetId="1" r:id="rId1"/>
@@ -40,26 +40,14 @@
     <author>Renato.Neves</author>
   </authors>
   <commentList>
-    <comment ref="P6" authorId="0" shapeId="0" xr:uid="{F7B1BF18-3B4D-4722-A894-EF97CA9955C4}">
+    <comment ref="P6" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000001000000}">
       <text>
         <r>
           <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Segoe UI"/>
-            <family val="2"/>
+            <sz val="11"/>
+            <rFont val="Carlito"/>
           </rPr>
-          <t>Renato.Neves:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Segoe UI"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
+          <t>Renato.Neves:
 2 janelas da frente</t>
         </r>
       </text>
@@ -69,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="125">
   <si>
     <t>PAINEL FINANCEIRO E DE OCUPAÇÃO</t>
   </si>
@@ -239,9 +227,6 @@
     <t>RESERVAS — CONTROLE AUTOMÁTICO DE LOCAÇÃO</t>
   </si>
   <si>
-    <t>Preencha apenas as células amarelas. O restante é calculado automaticamente. A data de saída (check-out) não conta como diária. Datas já comprometidas ficam BLOQUEADAS para novos lançamentos, inclusive coincidência com entrada ou saída de outra reserva.</t>
-  </si>
-  <si>
     <t>ID</t>
   </si>
   <si>
@@ -314,6 +299,9 @@
     <t>Observações</t>
   </si>
   <si>
+    <t>Carlos - Natal/Ano Novo</t>
+  </si>
+  <si>
     <t>Natal / Réveillon</t>
   </si>
   <si>
@@ -324,6 +312,24 @@
   </si>
   <si>
     <t>25/12/2026 a 04/01/2027 = 10 diárias</t>
+  </si>
+  <si>
+    <t>Regina - 7 de Setembro</t>
+  </si>
+  <si>
+    <t>Feriado</t>
+  </si>
+  <si>
+    <t>Airbnb</t>
+  </si>
+  <si>
+    <t>Louis Renan - Férias</t>
+  </si>
+  <si>
+    <t>Normal</t>
+  </si>
+  <si>
+    <t>Cortesia</t>
   </si>
   <si>
     <t>DESPESAS GERAIS DA CASA</t>
@@ -347,6 +353,9 @@
     <t>Reserva relacionada (ID)</t>
   </si>
   <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
     <t>LOC-001</t>
   </si>
   <si>
@@ -356,22 +365,10 @@
     <t>Nº</t>
   </si>
   <si>
-    <t>Normal</t>
-  </si>
-  <si>
     <t>Consulta</t>
   </si>
   <si>
-    <t>Férias escolares</t>
-  </si>
-  <si>
     <t>Pré-reserva</t>
-  </si>
-  <si>
-    <t>Airbnb</t>
-  </si>
-  <si>
-    <t>Feriado</t>
   </si>
   <si>
     <t>Booking</t>
@@ -395,10 +392,10 @@
     <t>Indicação</t>
   </si>
   <si>
-    <t>Outro</t>
+    <t>Carnaval</t>
   </si>
   <si>
-    <t>Carnaval</t>
+    <t>Outro</t>
   </si>
   <si>
     <t>Páscoa</t>
@@ -413,19 +410,28 @@
     <t>Evento local</t>
   </si>
   <si>
-    <t>Carlos - Natal/Ano Novo</t>
+    <t>Preencha apenas as células amarelas. O restante é calculado automaticamente. A data de saída (check-out) não conta como diária. Datas já comprometidas ficam BLOQUEADAS para novos lançamentos, inclusive coincidência com entrada ou saída de outra reserva. Preencha também o campo Imóvel com Casa Cinza ou Casa Laranja.</t>
   </si>
   <si>
-    <t xml:space="preserve"> </t>
+    <t>Imóvel</t>
   </si>
   <si>
-    <t>Regina - 7 de Setembro</t>
+    <t>Casa Cinza</t>
   </si>
   <si>
-    <t>Cortesia</t>
+    <t>Casa Laranja</t>
   </si>
   <si>
-    <t>Louis Renan - Férias</t>
+    <t>Miguel - Ano Novo</t>
+  </si>
+  <si>
+    <t>Miguel - Férias</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Férias </t>
+  </si>
+  <si>
+    <t>Férias</t>
   </si>
 </sst>
 </file>
@@ -440,7 +446,7 @@
     <numFmt numFmtId="168" formatCode="\R\$\ #,##0.00;[Red]\-\R\$\ #,##0.00;;"/>
     <numFmt numFmtId="169" formatCode="0.0%;[Red]\-0.0%;;"/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -561,21 +567,8 @@
       <color rgb="FF166534"/>
       <name val="Carlito"/>
     </font>
-    <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Segoe UI"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Segoe UI"/>
-      <family val="2"/>
-    </font>
   </fonts>
-  <fills count="14">
+  <fills count="16">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -640,11 +633,20 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF0F766E"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF2CC"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="20">
+  <borders count="22">
     <border>
       <left/>
       <right/>
@@ -849,11 +851,41 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD1D5DB"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD1D5DB"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD1D5DB"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD1D5DB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD9E2F3"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD9E2F3"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD9E2F3"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD9E2F3"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="97">
+  <cellXfs count="100">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -971,11 +1003,15 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="15" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -983,21 +1019,14 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="9">
-    <dxf>
-      <font>
-        <color rgb="FFB91C1C"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFF8D7DA"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="8">
     <dxf>
       <font>
         <color rgb="FF166534"/>
@@ -1096,6 +1125,64 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>1676400</xdr:colOff>
+      <xdr:row>51</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1026" name="Text Box 2" hidden="1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C0B29B2F-E337-70A6-920F-E7F94C845311}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1">
+          <a:spLocks noSelect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="9525000" cy="9525000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:miter lim="800000"/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1311,22 +1398,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="24" customHeight="1">
-      <c r="A1" s="93" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="93"/>
-      <c r="C1" s="93"/>
-      <c r="D1" s="93"/>
-      <c r="E1" s="93"/>
-      <c r="F1" s="93"/>
-      <c r="G1" s="93"/>
-      <c r="H1" s="93"/>
-      <c r="I1" s="93"/>
-      <c r="J1" s="93"/>
-      <c r="K1" s="93"/>
-      <c r="L1" s="93"/>
-      <c r="M1" s="93"/>
-      <c r="N1" s="93"/>
+      <c r="A1" s="96" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="96"/>
+      <c r="C1" s="96"/>
+      <c r="D1" s="96"/>
+      <c r="E1" s="96"/>
+      <c r="F1" s="96"/>
+      <c r="G1" s="96"/>
+      <c r="H1" s="96"/>
+      <c r="I1" s="96"/>
+      <c r="J1" s="96"/>
+      <c r="K1" s="96"/>
+      <c r="L1" s="96"/>
+      <c r="M1" s="96"/>
+      <c r="N1" s="96"/>
     </row>
     <row r="3" spans="1:14" ht="23.25">
       <c r="A3" s="1" t="s">
@@ -1340,7 +1427,7 @@
       </c>
       <c r="N3" s="85">
         <f>SUMIFS(RESERVAS!$Y$6:$Y$204,RESERVAS!$I$6:$I$204,"&lt;&gt;Cancelada",RESERVAS!$I$6:$I$204,"&lt;&gt;Consulta")</f>
-        <v>11000</v>
+        <v>26700</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="20.25">
@@ -1349,7 +1436,7 @@
       </c>
       <c r="B5" s="9">
         <f>SUM(F13:F24)</f>
-        <v>10500</v>
+        <v>13800</v>
       </c>
       <c r="D5" s="8" t="s">
         <v>4</v>
@@ -1370,7 +1457,7 @@
       </c>
       <c r="K5" s="91">
         <f>SUM(I13:I24)</f>
-        <v>10467.950000000001</v>
+        <v>13767.95</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="15.75">
@@ -1379,7 +1466,7 @@
       </c>
       <c r="B8" s="12">
         <f>SUM(C13:C24)</f>
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C8" s="14"/>
       <c r="D8" s="74" t="s">
@@ -1387,21 +1474,21 @@
       </c>
       <c r="E8" s="12">
         <f>SUM(D13:D24)</f>
-        <v>350</v>
+        <v>711</v>
       </c>
       <c r="G8" s="8" t="s">
         <v>9</v>
       </c>
       <c r="H8" s="13">
         <f>IF(SUM(B13:B24)=0,0,SUM(C13:C24)/SUM(B13:B24))</f>
-        <v>4.1095890410958902E-2</v>
+        <v>2.6027397260273973E-2</v>
       </c>
       <c r="J8" s="8" t="s">
         <v>10</v>
       </c>
       <c r="K8" s="10">
         <f>IF(B8=0,0,B5/B8)</f>
-        <v>700</v>
+        <v>726.31578947368416</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="24" customHeight="1">
@@ -1435,19 +1522,19 @@
       <c r="J12" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="L12" s="95" t="s">
+      <c r="L12" s="97" t="s">
         <v>18</v>
       </c>
-      <c r="M12" s="95"/>
-      <c r="N12" s="95"/>
+      <c r="M12" s="97"/>
+      <c r="N12" s="97"/>
     </row>
     <row r="13" spans="1:14" ht="18">
       <c r="A13" s="15" t="s">
         <v>19</v>
       </c>
       <c r="B13" s="14">
-        <f>DAY(EOMONTH(DATE($B$3,1,1),0))</f>
-        <v>31</v>
+        <f>DAY(EOMONTH(DATE($B$3,1,1),0))*2</f>
+        <v>62</v>
       </c>
       <c r="C13" s="89">
         <f>SUMPRODUCT((RESERVAS!$C$6:$C$204&lt;DATE($B$3,2,1))*(RESERVAS!$D$6:$D$204&gt;DATE($B$3,1,1))*(RESERVAS!$I$6:$I$204&lt;&gt;"Cancelada")*(RESERVAS!$I$6:$I$204&lt;&gt;"Consulta")*(((RESERVAS!$D$6:$D$204&lt;DATE($B$3,2,1))*RESERVAS!$D$6:$D$204+(RESERVAS!$D$6:$D$204&gt;=DATE($B$3,2,1))*DATE($B$3,2,1))-((RESERVAS!$C$6:$C$204&gt;DATE($B$3,1,1))*RESERVAS!$C$6:$C$204+(RESERVAS!$C$6:$C$204&lt;=DATE($B$3,1,1))*DATE($B$3,1,1))))</f>
@@ -1455,7 +1542,7 @@
       </c>
       <c r="D13" s="89">
         <f t="shared" ref="D13:D24" si="0">MAX(0,B13-C13)</f>
-        <v>31</v>
+        <v>62</v>
       </c>
       <c r="E13" s="6">
         <f t="shared" ref="E13:E24" si="1">IF(B13=0,0,C13/B13)</f>
@@ -1494,8 +1581,8 @@
         <v>22</v>
       </c>
       <c r="B14" s="14">
-        <f>DAY(EOMONTH(DATE($B$3,2,1),0))</f>
-        <v>28</v>
+        <f>DAY(EOMONTH(DATE($B$3,2,1),0))*2</f>
+        <v>56</v>
       </c>
       <c r="C14" s="89">
         <f>SUMPRODUCT((RESERVAS!$C$6:$C$204&lt;DATE($B$3,3,1))*(RESERVAS!$D$6:$D$204&gt;DATE($B$3,2,1))*(RESERVAS!$I$6:$I$204&lt;&gt;"Cancelada")*(RESERVAS!$I$6:$I$204&lt;&gt;"Consulta")*(((RESERVAS!$D$6:$D$204&lt;DATE($B$3,3,1))*RESERVAS!$D$6:$D$204+(RESERVAS!$D$6:$D$204&gt;=DATE($B$3,3,1))*DATE($B$3,3,1))-((RESERVAS!$C$6:$C$204&gt;DATE($B$3,2,1))*RESERVAS!$C$6:$C$204+(RESERVAS!$C$6:$C$204&lt;=DATE($B$3,2,1))*DATE($B$3,2,1))))</f>
@@ -1503,7 +1590,7 @@
       </c>
       <c r="D14" s="89">
         <f t="shared" si="0"/>
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="E14" s="6">
         <f t="shared" si="1"/>
@@ -1542,8 +1629,8 @@
         <v>24</v>
       </c>
       <c r="B15" s="14">
-        <f>DAY(EOMONTH(DATE($B$3,3,1),0))</f>
-        <v>31</v>
+        <f>DAY(EOMONTH(DATE($B$3,3,1),0))*2</f>
+        <v>62</v>
       </c>
       <c r="C15" s="89">
         <f>SUMPRODUCT((RESERVAS!$C$6:$C$204&lt;DATE($B$3,4,1))*(RESERVAS!$D$6:$D$204&gt;DATE($B$3,3,1))*(RESERVAS!$I$6:$I$204&lt;&gt;"Cancelada")*(RESERVAS!$I$6:$I$204&lt;&gt;"Consulta")*(((RESERVAS!$D$6:$D$204&lt;DATE($B$3,4,1))*RESERVAS!$D$6:$D$204+(RESERVAS!$D$6:$D$204&gt;=DATE($B$3,4,1))*DATE($B$3,4,1))-((RESERVAS!$C$6:$C$204&gt;DATE($B$3,3,1))*RESERVAS!$C$6:$C$204+(RESERVAS!$C$6:$C$204&lt;=DATE($B$3,3,1))*DATE($B$3,3,1))))</f>
@@ -1551,7 +1638,7 @@
       </c>
       <c r="D15" s="89">
         <f t="shared" si="0"/>
-        <v>31</v>
+        <v>62</v>
       </c>
       <c r="E15" s="6">
         <f t="shared" si="1"/>
@@ -1590,8 +1677,8 @@
         <v>26</v>
       </c>
       <c r="B16" s="14">
-        <f>DAY(EOMONTH(DATE($B$3,4,1),0))</f>
-        <v>30</v>
+        <f>DAY(EOMONTH(DATE($B$3,4,1),0))*2</f>
+        <v>60</v>
       </c>
       <c r="C16" s="89">
         <f>SUMPRODUCT((RESERVAS!$C$6:$C$204&lt;DATE($B$3,5,1))*(RESERVAS!$D$6:$D$204&gt;DATE($B$3,4,1))*(RESERVAS!$I$6:$I$204&lt;&gt;"Cancelada")*(RESERVAS!$I$6:$I$204&lt;&gt;"Consulta")*(((RESERVAS!$D$6:$D$204&lt;DATE($B$3,5,1))*RESERVAS!$D$6:$D$204+(RESERVAS!$D$6:$D$204&gt;=DATE($B$3,5,1))*DATE($B$3,5,1))-((RESERVAS!$C$6:$C$204&gt;DATE($B$3,4,1))*RESERVAS!$C$6:$C$204+(RESERVAS!$C$6:$C$204&lt;=DATE($B$3,4,1))*DATE($B$3,4,1))))</f>
@@ -1599,7 +1686,7 @@
       </c>
       <c r="D16" s="89">
         <f t="shared" si="0"/>
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="E16" s="6">
         <f t="shared" si="1"/>
@@ -1638,8 +1725,8 @@
         <v>28</v>
       </c>
       <c r="B17" s="14">
-        <f>DAY(EOMONTH(DATE($B$3,5,1),0))</f>
-        <v>31</v>
+        <f>DAY(EOMONTH(DATE($B$3,5,1),0))*2</f>
+        <v>62</v>
       </c>
       <c r="C17" s="89">
         <f>SUMPRODUCT((RESERVAS!$C$6:$C$204&lt;DATE($B$3,6,1))*(RESERVAS!$D$6:$D$204&gt;DATE($B$3,5,1))*(RESERVAS!$I$6:$I$204&lt;&gt;"Cancelada")*(RESERVAS!$I$6:$I$204&lt;&gt;"Consulta")*(((RESERVAS!$D$6:$D$204&lt;DATE($B$3,6,1))*RESERVAS!$D$6:$D$204+(RESERVAS!$D$6:$D$204&gt;=DATE($B$3,6,1))*DATE($B$3,6,1))-((RESERVAS!$C$6:$C$204&gt;DATE($B$3,5,1))*RESERVAS!$C$6:$C$204+(RESERVAS!$C$6:$C$204&lt;=DATE($B$3,5,1))*DATE($B$3,5,1))))</f>
@@ -1647,7 +1734,7 @@
       </c>
       <c r="D17" s="89">
         <f t="shared" si="0"/>
-        <v>31</v>
+        <v>62</v>
       </c>
       <c r="E17" s="6">
         <f t="shared" si="1"/>
@@ -1686,8 +1773,8 @@
         <v>31</v>
       </c>
       <c r="B18" s="14">
-        <f>DAY(EOMONTH(DATE($B$3,6,1),0))</f>
-        <v>30</v>
+        <f>DAY(EOMONTH(DATE($B$3,6,1),0))*2</f>
+        <v>60</v>
       </c>
       <c r="C18" s="89">
         <f>SUMPRODUCT((RESERVAS!$C$6:$C$204&lt;DATE($B$3,7,1))*(RESERVAS!$D$6:$D$204&gt;DATE($B$3,6,1))*(RESERVAS!$I$6:$I$204&lt;&gt;"Cancelada")*(RESERVAS!$I$6:$I$204&lt;&gt;"Consulta")*(((RESERVAS!$D$6:$D$204&lt;DATE($B$3,7,1))*RESERVAS!$D$6:$D$204+(RESERVAS!$D$6:$D$204&gt;=DATE($B$3,7,1))*DATE($B$3,7,1))-((RESERVAS!$C$6:$C$204&gt;DATE($B$3,6,1))*RESERVAS!$C$6:$C$204+(RESERVAS!$C$6:$C$204&lt;=DATE($B$3,6,1))*DATE($B$3,6,1))))</f>
@@ -1695,7 +1782,7 @@
       </c>
       <c r="D18" s="89">
         <f t="shared" si="0"/>
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="E18" s="6">
         <f t="shared" si="1"/>
@@ -1727,8 +1814,8 @@
         <v>32</v>
       </c>
       <c r="B19" s="14">
-        <f>DAY(EOMONTH(DATE($B$3,7,1),0))</f>
-        <v>31</v>
+        <f>DAY(EOMONTH(DATE($B$3,7,1),0))*2</f>
+        <v>62</v>
       </c>
       <c r="C19" s="89">
         <f>SUMPRODUCT((RESERVAS!$C$6:$C$204&lt;DATE($B$3,8,1))*(RESERVAS!$D$6:$D$204&gt;DATE($B$3,7,1))*(RESERVAS!$I$6:$I$204&lt;&gt;"Cancelada")*(RESERVAS!$I$6:$I$204&lt;&gt;"Consulta")*(((RESERVAS!$D$6:$D$204&lt;DATE($B$3,8,1))*RESERVAS!$D$6:$D$204+(RESERVAS!$D$6:$D$204&gt;=DATE($B$3,8,1))*DATE($B$3,8,1))-((RESERVAS!$C$6:$C$204&gt;DATE($B$3,7,1))*RESERVAS!$C$6:$C$204+(RESERVAS!$C$6:$C$204&lt;=DATE($B$3,7,1))*DATE($B$3,7,1))))</f>
@@ -1736,7 +1823,7 @@
       </c>
       <c r="D19" s="89">
         <f t="shared" si="0"/>
-        <v>31</v>
+        <v>62</v>
       </c>
       <c r="E19" s="6">
         <f t="shared" si="1"/>
@@ -1768,8 +1855,8 @@
         <v>33</v>
       </c>
       <c r="B20" s="14">
-        <f>DAY(EOMONTH(DATE($B$3,8,1),0))</f>
-        <v>31</v>
+        <f>DAY(EOMONTH(DATE($B$3,8,1),0))*2</f>
+        <v>62</v>
       </c>
       <c r="C20" s="89">
         <f>SUMPRODUCT((RESERVAS!$C$6:$C$204&lt;DATE($B$3,9,1))*(RESERVAS!$D$6:$D$204&gt;DATE($B$3,8,1))*(RESERVAS!$I$6:$I$204&lt;&gt;"Cancelada")*(RESERVAS!$I$6:$I$204&lt;&gt;"Consulta")*(((RESERVAS!$D$6:$D$204&lt;DATE($B$3,9,1))*RESERVAS!$D$6:$D$204+(RESERVAS!$D$6:$D$204&gt;=DATE($B$3,9,1))*DATE($B$3,9,1))-((RESERVAS!$C$6:$C$204&gt;DATE($B$3,8,1))*RESERVAS!$C$6:$C$204+(RESERVAS!$C$6:$C$204&lt;=DATE($B$3,8,1))*DATE($B$3,8,1))))</f>
@@ -1777,7 +1864,7 @@
       </c>
       <c r="D20" s="89">
         <f t="shared" si="0"/>
-        <v>31</v>
+        <v>62</v>
       </c>
       <c r="E20" s="6">
         <f t="shared" si="1"/>
@@ -1809,8 +1896,8 @@
         <v>34</v>
       </c>
       <c r="B21" s="14">
-        <f>DAY(EOMONTH(DATE($B$3,9,1),0))</f>
-        <v>30</v>
+        <f>DAY(EOMONTH(DATE($B$3,9,1),0))*2</f>
+        <v>60</v>
       </c>
       <c r="C21" s="89">
         <f>SUMPRODUCT((RESERVAS!$C$6:$C$204&lt;DATE($B$3,10,1))*(RESERVAS!$D$6:$D$204&gt;DATE($B$3,9,1))*(RESERVAS!$I$6:$I$204&lt;&gt;"Cancelada")*(RESERVAS!$I$6:$I$204&lt;&gt;"Consulta")*(((RESERVAS!$D$6:$D$204&lt;DATE($B$3,10,1))*RESERVAS!$D$6:$D$204+(RESERVAS!$D$6:$D$204&gt;=DATE($B$3,10,1))*DATE($B$3,10,1))-((RESERVAS!$C$6:$C$204&gt;DATE($B$3,9,1))*RESERVAS!$C$6:$C$204+(RESERVAS!$C$6:$C$204&lt;=DATE($B$3,9,1))*DATE($B$3,9,1))))</f>
@@ -1818,11 +1905,11 @@
       </c>
       <c r="D21" s="89">
         <f t="shared" si="0"/>
-        <v>22</v>
+        <v>52</v>
       </c>
       <c r="E21" s="6">
         <f t="shared" si="1"/>
-        <v>0.26666666666666666</v>
+        <v>0.13333333333333333</v>
       </c>
       <c r="F21" s="5">
         <f>SUMPRODUCT((RESERVAS!$C$6:$C$204&lt;DATE($B$3,10,1))*(RESERVAS!$D$6:$D$204&gt;DATE($B$3,9,1))*(RESERVAS!$I$6:$I$204&lt;&gt;"Cancelada")*(RESERVAS!$I$6:$I$204&lt;&gt;"Consulta")*RESERVAS!$F$6:$F$204*(((RESERVAS!$D$6:$D$204&lt;DATE($B$3,10,1))*RESERVAS!$D$6:$D$204+(RESERVAS!$D$6:$D$204&gt;=DATE($B$3,10,1))*DATE($B$3,10,1))-((RESERVAS!$C$6:$C$204&gt;DATE($B$3,9,1))*RESERVAS!$C$6:$C$204+(RESERVAS!$C$6:$C$204&lt;=DATE($B$3,9,1))*DATE($B$3,9,1))))</f>
@@ -1850,8 +1937,8 @@
         <v>35</v>
       </c>
       <c r="B22" s="14">
-        <f>DAY(EOMONTH(DATE($B$3,10,1),0))</f>
-        <v>31</v>
+        <f>DAY(EOMONTH(DATE($B$3,10,1),0))*2</f>
+        <v>62</v>
       </c>
       <c r="C22" s="89">
         <f>SUMPRODUCT((RESERVAS!$C$6:$C$204&lt;DATE($B$3,11,1))*(RESERVAS!$D$6:$D$204&gt;DATE($B$3,10,1))*(RESERVAS!$I$6:$I$204&lt;&gt;"Cancelada")*(RESERVAS!$I$6:$I$204&lt;&gt;"Consulta")*(((RESERVAS!$D$6:$D$204&lt;DATE($B$3,11,1))*RESERVAS!$D$6:$D$204+(RESERVAS!$D$6:$D$204&gt;=DATE($B$3,11,1))*DATE($B$3,11,1))-((RESERVAS!$C$6:$C$204&gt;DATE($B$3,10,1))*RESERVAS!$C$6:$C$204+(RESERVAS!$C$6:$C$204&lt;=DATE($B$3,10,1))*DATE($B$3,10,1))))</f>
@@ -1859,7 +1946,7 @@
       </c>
       <c r="D22" s="89">
         <f t="shared" si="0"/>
-        <v>31</v>
+        <v>62</v>
       </c>
       <c r="E22" s="6">
         <f t="shared" si="1"/>
@@ -1891,8 +1978,8 @@
         <v>36</v>
       </c>
       <c r="B23" s="14">
-        <f>DAY(EOMONTH(DATE($B$3,11,1),0))</f>
-        <v>30</v>
+        <f>DAY(EOMONTH(DATE($B$3,11,1),0))*2</f>
+        <v>60</v>
       </c>
       <c r="C23" s="89">
         <f>SUMPRODUCT((RESERVAS!$C$6:$C$204&lt;DATE($B$3,12,1))*(RESERVAS!$D$6:$D$204&gt;DATE($B$3,11,1))*(RESERVAS!$I$6:$I$204&lt;&gt;"Cancelada")*(RESERVAS!$I$6:$I$204&lt;&gt;"Consulta")*(((RESERVAS!$D$6:$D$204&lt;DATE($B$3,12,1))*RESERVAS!$D$6:$D$204+(RESERVAS!$D$6:$D$204&gt;=DATE($B$3,12,1))*DATE($B$3,12,1))-((RESERVAS!$C$6:$C$204&gt;DATE($B$3,11,1))*RESERVAS!$C$6:$C$204+(RESERVAS!$C$6:$C$204&lt;=DATE($B$3,11,1))*DATE($B$3,11,1))))</f>
@@ -1900,7 +1987,7 @@
       </c>
       <c r="D23" s="89">
         <f t="shared" si="0"/>
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="E23" s="6">
         <f t="shared" si="1"/>
@@ -1932,24 +2019,24 @@
         <v>37</v>
       </c>
       <c r="B24" s="18">
-        <f>DAY(EOMONTH(DATE($B$3,12,1),0))</f>
-        <v>31</v>
+        <f>DAY(EOMONTH(DATE($B$3,12,1),0))*2</f>
+        <v>62</v>
       </c>
       <c r="C24" s="90">
         <f>SUMPRODUCT((RESERVAS!$C$6:$C$204&lt;DATE($B$3,13,1))*(RESERVAS!$D$6:$D$204&gt;DATE($B$3,12,1))*(RESERVAS!$I$6:$I$204&lt;&gt;"Cancelada")*(RESERVAS!$I$6:$I$204&lt;&gt;"Consulta")*(((RESERVAS!$D$6:$D$204&lt;DATE($B$3,13,1))*RESERVAS!$D$6:$D$204+(RESERVAS!$D$6:$D$204&gt;=DATE($B$3,13,1))*DATE($B$3,13,1))-((RESERVAS!$C$6:$C$204&gt;DATE($B$3,12,1))*RESERVAS!$C$6:$C$204+(RESERVAS!$C$6:$C$204&lt;=DATE($B$3,12,1))*DATE($B$3,12,1))))</f>
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D24" s="90">
         <f t="shared" si="0"/>
-        <v>24</v>
+        <v>51</v>
       </c>
       <c r="E24" s="19">
         <f t="shared" si="1"/>
-        <v>0.22580645161290322</v>
+        <v>0.17741935483870969</v>
       </c>
       <c r="F24" s="20">
         <f>SUMPRODUCT((RESERVAS!$C$6:$C$204&lt;DATE($B$3,13,1))*(RESERVAS!$D$6:$D$204&gt;DATE($B$3,12,1))*(RESERVAS!$I$6:$I$204&lt;&gt;"Cancelada")*(RESERVAS!$I$6:$I$204&lt;&gt;"Consulta")*RESERVAS!$F$6:$F$204*(((RESERVAS!$D$6:$D$204&lt;DATE($B$3,13,1))*RESERVAS!$D$6:$D$204+(RESERVAS!$D$6:$D$204&gt;=DATE($B$3,13,1))*DATE($B$3,13,1))-((RESERVAS!$C$6:$C$204&gt;DATE($B$3,12,1))*RESERVAS!$C$6:$C$204+(RESERVAS!$C$6:$C$204&lt;=DATE($B$3,12,1))*DATE($B$3,12,1))))</f>
-        <v>7700</v>
+        <v>11000</v>
       </c>
       <c r="G24" s="20">
         <f>SUMPRODUCT((RESERVAS!$C$6:$C$204&lt;DATE($B$3,13,1))*(RESERVAS!$D$6:$D$204&gt;DATE($B$3,12,1))*(RESERVAS!$I$6:$I$204&lt;&gt;"Cancelada")*(RESERVAS!$I$6:$I$204&lt;&gt;"Consulta")*RESERVAS!$T$6:$T$204*(((RESERVAS!$D$6:$D$204&lt;DATE($B$3,13,1))*RESERVAS!$D$6:$D$204+(RESERVAS!$D$6:$D$204&gt;=DATE($B$3,13,1))*DATE($B$3,13,1))-((RESERVAS!$C$6:$C$204&gt;DATE($B$3,12,1))*RESERVAS!$C$6:$C$204+(RESERVAS!$C$6:$C$204&lt;=DATE($B$3,12,1))*DATE($B$3,12,1))))</f>
@@ -1961,7 +2048,7 @@
       </c>
       <c r="I24" s="88">
         <f t="shared" si="2"/>
-        <v>7700</v>
+        <v>11000</v>
       </c>
       <c r="J24" s="21">
         <f t="shared" si="3"/>
@@ -1987,6 +2074,13 @@
         <cfvo type="max"/>
         <color rgb="FFA02B93"/>
       </dataBar>
+    </cfRule>
+    <cfRule type="dataBar" priority="4">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFA02B93"/>
+      </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
           <x14:id>{90F4BC7A-ABBD-72D5-E0CF-D59801F0A8DD}</x14:id>
@@ -1995,7 +2089,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I13:I24">
-    <cfRule type="cellIs" dxfId="8" priority="2" operator="lessThan">
+    <cfRule type="cellIs" dxfId="7" priority="2" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2037,20 +2131,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="24" customHeight="1">
-      <c r="A1" s="93" t="s">
+      <c r="A1" s="96" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="93"/>
-      <c r="C1" s="93"/>
-      <c r="D1" s="93"/>
-      <c r="E1" s="93"/>
-      <c r="F1" s="93"/>
-      <c r="G1" s="93"/>
-      <c r="H1" s="93"/>
-      <c r="I1" s="93"/>
-      <c r="J1" s="93"/>
-      <c r="K1" s="93"/>
-      <c r="L1" s="93"/>
+      <c r="B1" s="96"/>
+      <c r="C1" s="96"/>
+      <c r="D1" s="96"/>
+      <c r="E1" s="96"/>
+      <c r="F1" s="96"/>
+      <c r="G1" s="96"/>
+      <c r="H1" s="96"/>
+      <c r="I1" s="96"/>
+      <c r="J1" s="96"/>
+      <c r="K1" s="96"/>
+      <c r="L1" s="96"/>
     </row>
     <row r="2" spans="1:12" ht="15">
       <c r="A2" s="1" t="s">
@@ -2095,12 +2189,12 @@
       <c r="G4" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="I4" s="96" t="s">
+      <c r="I4" s="98" t="s">
         <v>47</v>
       </c>
-      <c r="J4" s="96"/>
-      <c r="K4" s="96"/>
-      <c r="L4" s="96"/>
+      <c r="J4" s="98"/>
+      <c r="K4" s="98"/>
+      <c r="L4" s="98"/>
     </row>
     <row r="5" spans="1:12" ht="60.75" customHeight="1">
       <c r="A5" s="29" t="str">
@@ -2370,12 +2464,12 @@
       <c r="E12" s="92"/>
       <c r="F12" s="92"/>
       <c r="G12" s="92"/>
-      <c r="I12" s="95" t="s">
+      <c r="I12" s="97" t="s">
         <v>48</v>
       </c>
-      <c r="J12" s="95"/>
-      <c r="K12" s="95"/>
-      <c r="L12" s="95"/>
+      <c r="J12" s="97"/>
+      <c r="K12" s="97"/>
+      <c r="L12" s="97"/>
     </row>
     <row r="13" spans="1:12" ht="15">
       <c r="A13" s="92"/>
@@ -2422,13 +2516,13 @@
     <mergeCell ref="I12:L12"/>
   </mergeCells>
   <conditionalFormatting sqref="A5:G10">
-    <cfRule type="expression" dxfId="7" priority="1">
+    <cfRule type="expression" dxfId="6" priority="1">
       <formula>ISNUMBER(SEARCH("DISPONÍVEL",A5))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="6" priority="2">
+    <cfRule type="expression" dxfId="5" priority="2">
       <formula>ISNUMBER(SEARCH("ALUGADA",A5))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="5" priority="3">
+    <cfRule type="expression" dxfId="4" priority="3">
       <formula>ISNUMBER(SEARCH("CONFLITO",A5))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2446,7 +2540,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:AA204"/>
+  <dimension ref="A1:AB204"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
@@ -2470,160 +2564,164 @@
     <col min="24" max="25" width="17" customWidth="1"/>
     <col min="26" max="26" width="12" customWidth="1"/>
     <col min="27" max="27" width="34" customWidth="1"/>
+    <col min="28" max="28" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" ht="24" customHeight="1">
-      <c r="A1" s="93" t="s">
+    <row r="1" spans="1:28" ht="24" customHeight="1">
+      <c r="A1" s="96" t="s">
         <v>55</v>
       </c>
-      <c r="B1" s="93"/>
-      <c r="C1" s="93"/>
-      <c r="D1" s="93"/>
-      <c r="E1" s="93"/>
-      <c r="F1" s="93"/>
-      <c r="G1" s="93"/>
-      <c r="H1" s="93"/>
-      <c r="I1" s="93"/>
-      <c r="J1" s="93"/>
-      <c r="K1" s="93"/>
-      <c r="L1" s="93"/>
-      <c r="M1" s="93"/>
-      <c r="N1" s="93"/>
-      <c r="O1" s="93"/>
-      <c r="P1" s="93"/>
-      <c r="Q1" s="93"/>
-      <c r="R1" s="93"/>
-      <c r="S1" s="93"/>
-      <c r="T1" s="93"/>
-      <c r="U1" s="93"/>
-      <c r="V1" s="93"/>
-      <c r="W1" s="93"/>
-      <c r="X1" s="93"/>
-      <c r="Y1" s="93"/>
-      <c r="Z1" s="93"/>
-      <c r="AA1" s="93"/>
-    </row>
-    <row r="3" spans="1:27">
-      <c r="A3" s="94" t="s">
+      <c r="B1" s="96"/>
+      <c r="C1" s="96"/>
+      <c r="D1" s="96"/>
+      <c r="E1" s="96"/>
+      <c r="F1" s="96"/>
+      <c r="G1" s="96"/>
+      <c r="H1" s="96"/>
+      <c r="I1" s="96"/>
+      <c r="J1" s="96"/>
+      <c r="K1" s="96"/>
+      <c r="L1" s="96"/>
+      <c r="M1" s="96"/>
+      <c r="N1" s="96"/>
+      <c r="O1" s="96"/>
+      <c r="P1" s="96"/>
+      <c r="Q1" s="96"/>
+      <c r="R1" s="96"/>
+      <c r="S1" s="96"/>
+      <c r="T1" s="96"/>
+      <c r="U1" s="96"/>
+      <c r="V1" s="96"/>
+      <c r="W1" s="96"/>
+      <c r="X1" s="96"/>
+      <c r="Y1" s="96"/>
+      <c r="Z1" s="96"/>
+      <c r="AA1" s="96"/>
+    </row>
+    <row r="3" spans="1:28">
+      <c r="A3" s="99" t="s">
+        <v>117</v>
+      </c>
+      <c r="B3" s="99"/>
+      <c r="C3" s="99"/>
+      <c r="D3" s="99"/>
+      <c r="E3" s="99"/>
+      <c r="F3" s="99"/>
+      <c r="G3" s="99"/>
+      <c r="H3" s="99"/>
+      <c r="I3" s="99"/>
+      <c r="J3" s="99"/>
+      <c r="K3" s="99"/>
+      <c r="L3" s="99"/>
+      <c r="M3" s="99"/>
+      <c r="N3" s="99"/>
+      <c r="O3" s="99"/>
+      <c r="P3" s="99"/>
+      <c r="Q3" s="99"/>
+      <c r="R3" s="99"/>
+      <c r="S3" s="99"/>
+      <c r="T3" s="99"/>
+      <c r="U3" s="99"/>
+      <c r="V3" s="99"/>
+      <c r="W3" s="99"/>
+      <c r="X3" s="99"/>
+      <c r="Y3" s="99"/>
+      <c r="Z3" s="99"/>
+      <c r="AA3" s="99"/>
+    </row>
+    <row r="5" spans="1:28" ht="24" customHeight="1">
+      <c r="A5" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="B3" s="94"/>
-      <c r="C3" s="94"/>
-      <c r="D3" s="94"/>
-      <c r="E3" s="94"/>
-      <c r="F3" s="94"/>
-      <c r="G3" s="94"/>
-      <c r="H3" s="94"/>
-      <c r="I3" s="94"/>
-      <c r="J3" s="94"/>
-      <c r="K3" s="94"/>
-      <c r="L3" s="94"/>
-      <c r="M3" s="94"/>
-      <c r="N3" s="94"/>
-      <c r="O3" s="94"/>
-      <c r="P3" s="94"/>
-      <c r="Q3" s="94"/>
-      <c r="R3" s="94"/>
-      <c r="S3" s="94"/>
-      <c r="T3" s="94"/>
-      <c r="U3" s="94"/>
-      <c r="V3" s="94"/>
-      <c r="W3" s="94"/>
-      <c r="X3" s="94"/>
-      <c r="Y3" s="94"/>
-      <c r="Z3" s="94"/>
-      <c r="AA3" s="94"/>
-    </row>
-    <row r="5" spans="1:27" ht="24" customHeight="1">
-      <c r="A5" s="2" t="s">
+      <c r="B5" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="C5" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="D5" s="4" t="s">
         <v>59</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>60</v>
       </c>
       <c r="E5" s="4" t="s">
         <v>23</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G5" s="4" t="s">
         <v>3</v>
       </c>
       <c r="H5" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="I5" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="I5" s="4" t="s">
+      <c r="J5" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="J5" s="4" t="s">
+      <c r="K5" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="K5" s="4" t="s">
+      <c r="L5" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="L5" s="4" t="s">
+      <c r="M5" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="M5" s="4" t="s">
+      <c r="N5" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="N5" s="4" t="s">
+      <c r="O5" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="O5" s="4" t="s">
+      <c r="P5" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="P5" s="4" t="s">
+      <c r="Q5" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="Q5" s="4" t="s">
+      <c r="R5" s="4" t="s">
         <v>71</v>
-      </c>
-      <c r="R5" s="4" t="s">
-        <v>72</v>
       </c>
       <c r="S5" s="4" t="s">
         <v>4</v>
       </c>
       <c r="T5" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="U5" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="U5" s="4" t="s">
+      <c r="V5" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="V5" s="4" t="s">
+      <c r="W5" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="W5" s="4" t="s">
+      <c r="X5" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="X5" s="4" t="s">
+      <c r="Y5" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="Y5" s="4" t="s">
+      <c r="Z5" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="Z5" s="4" t="s">
+      <c r="AA5" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="AA5" s="3" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="6" spans="1:27">
+      <c r="AB5" s="93" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="6" spans="1:28">
       <c r="A6" s="53" t="str">
         <f t="shared" ref="A6:A36" si="0">IF(B6="","","LOC-"&amp;TEXT(ROW()-5,"000"))</f>
         <v>LOC-001</v>
       </c>
       <c r="B6" s="54" t="s">
-        <v>114</v>
+        <v>80</v>
       </c>
       <c r="C6" s="55">
         <v>46381</v>
@@ -2704,20 +2802,23 @@
         <v>11000</v>
       </c>
       <c r="Z6" s="60" t="str">
-        <f t="shared" ref="Z6:Z37" si="8">IF(B6="","",IF(COUNTIFS($C$6:$C$204,"&lt;"&amp;D6,$D$6:$D$204,"&gt;"&amp;C6,$I$6:$I$204,"&lt;&gt;Cancelada",$I$6:$I$204,"&lt;&gt;Consulta")&gt;1,"CONFLITO","OK"))</f>
+        <f t="shared" ref="Z6:Z37" si="8">IF(B6="","",IF(COUNTIFS($C$6:$C$204,"&lt;"&amp;D6,$D$6:$D$204,"&gt;"&amp;C6,$I$6:$I$204,"&lt;&gt;Cancelada",$I$6:$I$204,"&lt;&gt;Consulta",$AB$6:$AB$204,$AB6)&gt;1,"CONFLITO","OK"))</f>
         <v>OK</v>
       </c>
       <c r="AA6" s="61" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="7" spans="1:27">
+      <c r="AB6" s="94" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="7" spans="1:28">
       <c r="A7" s="62" t="str">
         <f t="shared" si="0"/>
         <v>LOC-002</v>
       </c>
       <c r="B7" s="43" t="s">
-        <v>116</v>
+        <v>85</v>
       </c>
       <c r="C7" s="45">
         <v>46269</v>
@@ -2737,13 +2838,13 @@
         <v>2800</v>
       </c>
       <c r="H7" s="43" t="s">
-        <v>100</v>
+        <v>86</v>
       </c>
       <c r="I7" s="43" t="s">
         <v>82</v>
       </c>
       <c r="J7" s="54" t="s">
-        <v>99</v>
+        <v>87</v>
       </c>
       <c r="K7" s="47"/>
       <c r="L7" s="47"/>
@@ -2789,14 +2890,17 @@
         <v>OK</v>
       </c>
       <c r="AA7" s="63"/>
-    </row>
-    <row r="8" spans="1:27">
+      <c r="AB7" s="94" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="8" spans="1:28">
       <c r="A8" s="62" t="str">
         <f t="shared" si="0"/>
         <v>LOC-003</v>
       </c>
       <c r="B8" s="43" t="s">
-        <v>118</v>
+        <v>88</v>
       </c>
       <c r="C8" s="45">
         <v>46276</v>
@@ -2816,13 +2920,13 @@
         <v>0</v>
       </c>
       <c r="H8" s="43" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="I8" s="43" t="s">
         <v>82</v>
       </c>
       <c r="J8" s="54" t="s">
-        <v>117</v>
+        <v>90</v>
       </c>
       <c r="K8" s="47"/>
       <c r="L8" s="47"/>
@@ -2862,27 +2966,44 @@
         <v>OK</v>
       </c>
       <c r="AA8" s="63"/>
-    </row>
-    <row r="9" spans="1:27">
+      <c r="AB8" s="94" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="9" spans="1:28">
       <c r="A9" s="62" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="B9" s="43"/>
-      <c r="C9" s="45"/>
-      <c r="D9" s="45"/>
+        <v>LOC-004</v>
+      </c>
+      <c r="B9" s="43" t="s">
+        <v>121</v>
+      </c>
+      <c r="C9" s="45">
+        <v>46384</v>
+      </c>
+      <c r="D9" s="45">
+        <v>46385</v>
+      </c>
       <c r="E9" s="50">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="F9" s="47"/>
+        <v>1</v>
+      </c>
+      <c r="F9" s="47">
+        <v>0</v>
+      </c>
       <c r="G9" s="51">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="H9" s="43"/>
-      <c r="I9" s="43"/>
-      <c r="J9" s="54"/>
+      <c r="H9" s="43" t="s">
+        <v>108</v>
+      </c>
+      <c r="I9" s="43" t="s">
+        <v>82</v>
+      </c>
+      <c r="J9" s="54" t="s">
+        <v>90</v>
+      </c>
       <c r="K9" s="47"/>
       <c r="L9" s="47"/>
       <c r="M9" s="47"/>
@@ -2918,30 +3039,47 @@
       </c>
       <c r="Z9" s="49" t="str">
         <f t="shared" si="8"/>
-        <v/>
+        <v>OK</v>
       </c>
       <c r="AA9" s="63"/>
-    </row>
-    <row r="10" spans="1:27">
+      <c r="AB9" s="94" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="10" spans="1:28">
       <c r="A10" s="62" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="B10" s="43"/>
-      <c r="C10" s="45"/>
-      <c r="D10" s="45"/>
+        <v>LOC-005</v>
+      </c>
+      <c r="B10" s="43" t="s">
+        <v>122</v>
+      </c>
+      <c r="C10" s="45">
+        <v>46385</v>
+      </c>
+      <c r="D10" s="45">
+        <v>46391</v>
+      </c>
       <c r="E10" s="50">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="F10" s="47"/>
+        <v>6</v>
+      </c>
+      <c r="F10" s="47">
+        <v>1100</v>
+      </c>
       <c r="G10" s="51">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H10" s="43"/>
-      <c r="I10" s="43"/>
-      <c r="J10" s="54"/>
+        <v>6600</v>
+      </c>
+      <c r="H10" s="43" t="s">
+        <v>108</v>
+      </c>
+      <c r="I10" s="43" t="s">
+        <v>82</v>
+      </c>
+      <c r="J10" s="54" t="s">
+        <v>83</v>
+      </c>
       <c r="K10" s="47"/>
       <c r="L10" s="47"/>
       <c r="M10" s="47"/>
@@ -2960,47 +3098,64 @@
       </c>
       <c r="U10" s="51">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>6600</v>
       </c>
       <c r="V10" s="51">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1100</v>
       </c>
       <c r="W10" s="52">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X10" s="47"/>
       <c r="Y10" s="58">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>6600</v>
       </c>
       <c r="Z10" s="49" t="str">
         <f t="shared" si="8"/>
-        <v/>
+        <v>OK</v>
       </c>
       <c r="AA10" s="63"/>
-    </row>
-    <row r="11" spans="1:27">
+      <c r="AB10" s="94" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="11" spans="1:28">
       <c r="A11" s="62" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="B11" s="43"/>
-      <c r="C11" s="45"/>
-      <c r="D11" s="45"/>
+        <v>LOC-006</v>
+      </c>
+      <c r="B11" s="43" t="s">
+        <v>122</v>
+      </c>
+      <c r="C11" s="45">
+        <v>46391</v>
+      </c>
+      <c r="D11" s="45">
+        <v>46401</v>
+      </c>
       <c r="E11" s="50">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="F11" s="47"/>
+        <v>10</v>
+      </c>
+      <c r="F11" s="47">
+        <v>910</v>
+      </c>
       <c r="G11" s="51">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H11" s="43"/>
-      <c r="I11" s="43"/>
-      <c r="J11" s="54"/>
+        <v>9100</v>
+      </c>
+      <c r="H11" s="43" t="s">
+        <v>124</v>
+      </c>
+      <c r="I11" s="43" t="s">
+        <v>82</v>
+      </c>
+      <c r="J11" s="54" t="s">
+        <v>83</v>
+      </c>
       <c r="K11" s="47"/>
       <c r="L11" s="47"/>
       <c r="M11" s="47"/>
@@ -3019,28 +3174,31 @@
       </c>
       <c r="U11" s="51">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>9100</v>
       </c>
       <c r="V11" s="51">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>910</v>
       </c>
       <c r="W11" s="52">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X11" s="47"/>
       <c r="Y11" s="58">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>9100</v>
       </c>
       <c r="Z11" s="49" t="str">
         <f t="shared" si="8"/>
-        <v/>
+        <v>OK</v>
       </c>
       <c r="AA11" s="63"/>
-    </row>
-    <row r="12" spans="1:27">
+      <c r="AB11" s="94" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="12" spans="1:28">
       <c r="A12" s="62" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -3098,8 +3256,9 @@
         <v/>
       </c>
       <c r="AA12" s="63"/>
-    </row>
-    <row r="13" spans="1:27">
+      <c r="AB12" s="94"/>
+    </row>
+    <row r="13" spans="1:28">
       <c r="A13" s="62" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -3157,8 +3316,9 @@
         <v/>
       </c>
       <c r="AA13" s="63"/>
-    </row>
-    <row r="14" spans="1:27">
+      <c r="AB13" s="94"/>
+    </row>
+    <row r="14" spans="1:28">
       <c r="A14" s="62" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -3216,8 +3376,9 @@
         <v/>
       </c>
       <c r="AA14" s="63"/>
-    </row>
-    <row r="15" spans="1:27">
+      <c r="AB14" s="94"/>
+    </row>
+    <row r="15" spans="1:28">
       <c r="A15" s="62" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -3275,8 +3436,9 @@
         <v/>
       </c>
       <c r="AA15" s="63"/>
-    </row>
-    <row r="16" spans="1:27">
+      <c r="AB15" s="94"/>
+    </row>
+    <row r="16" spans="1:28">
       <c r="A16" s="62" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -3334,8 +3496,9 @@
         <v/>
       </c>
       <c r="AA16" s="63"/>
-    </row>
-    <row r="17" spans="1:27">
+      <c r="AB16" s="94"/>
+    </row>
+    <row r="17" spans="1:28">
       <c r="A17" s="62" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -3393,8 +3556,9 @@
         <v/>
       </c>
       <c r="AA17" s="63"/>
-    </row>
-    <row r="18" spans="1:27">
+      <c r="AB17" s="94"/>
+    </row>
+    <row r="18" spans="1:28">
       <c r="A18" s="62" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -3452,8 +3616,9 @@
         <v/>
       </c>
       <c r="AA18" s="63"/>
-    </row>
-    <row r="19" spans="1:27">
+      <c r="AB18" s="94"/>
+    </row>
+    <row r="19" spans="1:28">
       <c r="A19" s="62" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -3511,8 +3676,9 @@
         <v/>
       </c>
       <c r="AA19" s="63"/>
-    </row>
-    <row r="20" spans="1:27">
+      <c r="AB19" s="94"/>
+    </row>
+    <row r="20" spans="1:28">
       <c r="A20" s="62" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -3570,8 +3736,9 @@
         <v/>
       </c>
       <c r="AA20" s="63"/>
-    </row>
-    <row r="21" spans="1:27">
+      <c r="AB20" s="94"/>
+    </row>
+    <row r="21" spans="1:28">
       <c r="A21" s="62" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -3629,8 +3796,9 @@
         <v/>
       </c>
       <c r="AA21" s="63"/>
-    </row>
-    <row r="22" spans="1:27">
+      <c r="AB21" s="94"/>
+    </row>
+    <row r="22" spans="1:28">
       <c r="A22" s="62" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -3688,8 +3856,9 @@
         <v/>
       </c>
       <c r="AA22" s="63"/>
-    </row>
-    <row r="23" spans="1:27">
+      <c r="AB22" s="94"/>
+    </row>
+    <row r="23" spans="1:28">
       <c r="A23" s="62" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -3747,8 +3916,9 @@
         <v/>
       </c>
       <c r="AA23" s="63"/>
-    </row>
-    <row r="24" spans="1:27">
+      <c r="AB23" s="94"/>
+    </row>
+    <row r="24" spans="1:28">
       <c r="A24" s="62" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -3806,8 +3976,9 @@
         <v/>
       </c>
       <c r="AA24" s="63"/>
-    </row>
-    <row r="25" spans="1:27">
+      <c r="AB24" s="94"/>
+    </row>
+    <row r="25" spans="1:28">
       <c r="A25" s="62" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -3865,8 +4036,9 @@
         <v/>
       </c>
       <c r="AA25" s="63"/>
-    </row>
-    <row r="26" spans="1:27">
+      <c r="AB25" s="94"/>
+    </row>
+    <row r="26" spans="1:28">
       <c r="A26" s="62" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -3924,8 +4096,9 @@
         <v/>
       </c>
       <c r="AA26" s="63"/>
-    </row>
-    <row r="27" spans="1:27">
+      <c r="AB26" s="94"/>
+    </row>
+    <row r="27" spans="1:28">
       <c r="A27" s="62" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -3983,8 +4156,9 @@
         <v/>
       </c>
       <c r="AA27" s="63"/>
-    </row>
-    <row r="28" spans="1:27">
+      <c r="AB27" s="94"/>
+    </row>
+    <row r="28" spans="1:28">
       <c r="A28" s="62" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -4042,8 +4216,9 @@
         <v/>
       </c>
       <c r="AA28" s="63"/>
-    </row>
-    <row r="29" spans="1:27">
+      <c r="AB28" s="94"/>
+    </row>
+    <row r="29" spans="1:28">
       <c r="A29" s="62" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -4101,8 +4276,9 @@
         <v/>
       </c>
       <c r="AA29" s="63"/>
-    </row>
-    <row r="30" spans="1:27">
+      <c r="AB29" s="94"/>
+    </row>
+    <row r="30" spans="1:28">
       <c r="A30" s="62" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -4160,8 +4336,9 @@
         <v/>
       </c>
       <c r="AA30" s="63"/>
-    </row>
-    <row r="31" spans="1:27">
+      <c r="AB30" s="94"/>
+    </row>
+    <row r="31" spans="1:28">
       <c r="A31" s="62" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -4219,8 +4396,9 @@
         <v/>
       </c>
       <c r="AA31" s="63"/>
-    </row>
-    <row r="32" spans="1:27">
+      <c r="AB31" s="94"/>
+    </row>
+    <row r="32" spans="1:28">
       <c r="A32" s="62" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -4278,8 +4456,9 @@
         <v/>
       </c>
       <c r="AA32" s="63"/>
-    </row>
-    <row r="33" spans="1:27">
+      <c r="AB32" s="94"/>
+    </row>
+    <row r="33" spans="1:28">
       <c r="A33" s="62" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -4337,8 +4516,9 @@
         <v/>
       </c>
       <c r="AA33" s="63"/>
-    </row>
-    <row r="34" spans="1:27">
+      <c r="AB33" s="94"/>
+    </row>
+    <row r="34" spans="1:28">
       <c r="A34" s="62" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -4396,8 +4576,9 @@
         <v/>
       </c>
       <c r="AA34" s="63"/>
-    </row>
-    <row r="35" spans="1:27">
+      <c r="AB34" s="94"/>
+    </row>
+    <row r="35" spans="1:28">
       <c r="A35" s="62" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -4455,8 +4636,9 @@
         <v/>
       </c>
       <c r="AA35" s="63"/>
-    </row>
-    <row r="36" spans="1:27">
+      <c r="AB35" s="94"/>
+    </row>
+    <row r="36" spans="1:28">
       <c r="A36" s="62" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -4514,8 +4696,9 @@
         <v/>
       </c>
       <c r="AA36" s="63"/>
-    </row>
-    <row r="37" spans="1:27">
+      <c r="AB36" s="94"/>
+    </row>
+    <row r="37" spans="1:28">
       <c r="A37" s="62" t="str">
         <f t="shared" ref="A37:A68" si="9">IF(B37="","","LOC-"&amp;TEXT(ROW()-5,"000"))</f>
         <v/>
@@ -4573,8 +4756,9 @@
         <v/>
       </c>
       <c r="AA37" s="63"/>
-    </row>
-    <row r="38" spans="1:27">
+      <c r="AB37" s="94"/>
+    </row>
+    <row r="38" spans="1:28">
       <c r="A38" s="62" t="str">
         <f t="shared" si="9"/>
         <v/>
@@ -4628,12 +4812,13 @@
         <v>0</v>
       </c>
       <c r="Z38" s="49" t="str">
-        <f t="shared" ref="Z38:Z69" si="16">IF(B38="","",IF(COUNTIFS($C$6:$C$204,"&lt;"&amp;D38,$D$6:$D$204,"&gt;"&amp;C38,$I$6:$I$204,"&lt;&gt;Cancelada",$I$6:$I$204,"&lt;&gt;Consulta")&gt;1,"CONFLITO","OK"))</f>
+        <f t="shared" ref="Z38:Z69" si="16">IF(B38="","",IF(COUNTIFS($C$6:$C$204,"&lt;"&amp;D38,$D$6:$D$204,"&gt;"&amp;C38,$I$6:$I$204,"&lt;&gt;Cancelada",$I$6:$I$204,"&lt;&gt;Consulta",$AB$6:$AB$204,$AB38)&gt;1,"CONFLITO","OK"))</f>
         <v/>
       </c>
       <c r="AA38" s="63"/>
-    </row>
-    <row r="39" spans="1:27">
+      <c r="AB38" s="94"/>
+    </row>
+    <row r="39" spans="1:28">
       <c r="A39" s="62" t="str">
         <f t="shared" si="9"/>
         <v/>
@@ -4691,8 +4876,9 @@
         <v/>
       </c>
       <c r="AA39" s="63"/>
-    </row>
-    <row r="40" spans="1:27">
+      <c r="AB39" s="94"/>
+    </row>
+    <row r="40" spans="1:28">
       <c r="A40" s="62" t="str">
         <f t="shared" si="9"/>
         <v/>
@@ -4750,8 +4936,9 @@
         <v/>
       </c>
       <c r="AA40" s="63"/>
-    </row>
-    <row r="41" spans="1:27">
+      <c r="AB40" s="94"/>
+    </row>
+    <row r="41" spans="1:28">
       <c r="A41" s="62" t="str">
         <f t="shared" si="9"/>
         <v/>
@@ -4809,8 +4996,9 @@
         <v/>
       </c>
       <c r="AA41" s="63"/>
-    </row>
-    <row r="42" spans="1:27">
+      <c r="AB41" s="94"/>
+    </row>
+    <row r="42" spans="1:28">
       <c r="A42" s="62" t="str">
         <f t="shared" si="9"/>
         <v/>
@@ -4868,8 +5056,9 @@
         <v/>
       </c>
       <c r="AA42" s="63"/>
-    </row>
-    <row r="43" spans="1:27">
+      <c r="AB42" s="94"/>
+    </row>
+    <row r="43" spans="1:28">
       <c r="A43" s="62" t="str">
         <f t="shared" si="9"/>
         <v/>
@@ -4927,8 +5116,9 @@
         <v/>
       </c>
       <c r="AA43" s="63"/>
-    </row>
-    <row r="44" spans="1:27">
+      <c r="AB43" s="94"/>
+    </row>
+    <row r="44" spans="1:28">
       <c r="A44" s="62" t="str">
         <f t="shared" si="9"/>
         <v/>
@@ -4986,8 +5176,9 @@
         <v/>
       </c>
       <c r="AA44" s="63"/>
-    </row>
-    <row r="45" spans="1:27">
+      <c r="AB44" s="94"/>
+    </row>
+    <row r="45" spans="1:28">
       <c r="A45" s="62" t="str">
         <f t="shared" si="9"/>
         <v/>
@@ -5045,8 +5236,9 @@
         <v/>
       </c>
       <c r="AA45" s="63"/>
-    </row>
-    <row r="46" spans="1:27">
+      <c r="AB45" s="94"/>
+    </row>
+    <row r="46" spans="1:28">
       <c r="A46" s="62" t="str">
         <f t="shared" si="9"/>
         <v/>
@@ -5104,8 +5296,9 @@
         <v/>
       </c>
       <c r="AA46" s="63"/>
-    </row>
-    <row r="47" spans="1:27">
+      <c r="AB46" s="94"/>
+    </row>
+    <row r="47" spans="1:28">
       <c r="A47" s="62" t="str">
         <f t="shared" si="9"/>
         <v/>
@@ -5163,8 +5356,9 @@
         <v/>
       </c>
       <c r="AA47" s="63"/>
-    </row>
-    <row r="48" spans="1:27">
+      <c r="AB47" s="94"/>
+    </row>
+    <row r="48" spans="1:28">
       <c r="A48" s="62" t="str">
         <f t="shared" si="9"/>
         <v/>
@@ -5222,8 +5416,9 @@
         <v/>
       </c>
       <c r="AA48" s="63"/>
-    </row>
-    <row r="49" spans="1:27">
+      <c r="AB48" s="94"/>
+    </row>
+    <row r="49" spans="1:28">
       <c r="A49" s="62" t="str">
         <f t="shared" si="9"/>
         <v/>
@@ -5281,8 +5476,9 @@
         <v/>
       </c>
       <c r="AA49" s="63"/>
-    </row>
-    <row r="50" spans="1:27">
+      <c r="AB49" s="94"/>
+    </row>
+    <row r="50" spans="1:28">
       <c r="A50" s="62" t="str">
         <f t="shared" si="9"/>
         <v/>
@@ -5340,8 +5536,9 @@
         <v/>
       </c>
       <c r="AA50" s="63"/>
-    </row>
-    <row r="51" spans="1:27">
+      <c r="AB50" s="94"/>
+    </row>
+    <row r="51" spans="1:28">
       <c r="A51" s="62" t="str">
         <f t="shared" si="9"/>
         <v/>
@@ -5399,8 +5596,9 @@
         <v/>
       </c>
       <c r="AA51" s="63"/>
-    </row>
-    <row r="52" spans="1:27">
+      <c r="AB51" s="94"/>
+    </row>
+    <row r="52" spans="1:28">
       <c r="A52" s="62" t="str">
         <f t="shared" si="9"/>
         <v/>
@@ -5458,8 +5656,9 @@
         <v/>
       </c>
       <c r="AA52" s="63"/>
-    </row>
-    <row r="53" spans="1:27">
+      <c r="AB52" s="94"/>
+    </row>
+    <row r="53" spans="1:28">
       <c r="A53" s="62" t="str">
         <f t="shared" si="9"/>
         <v/>
@@ -5517,8 +5716,9 @@
         <v/>
       </c>
       <c r="AA53" s="63"/>
-    </row>
-    <row r="54" spans="1:27">
+      <c r="AB53" s="94"/>
+    </row>
+    <row r="54" spans="1:28">
       <c r="A54" s="62" t="str">
         <f t="shared" si="9"/>
         <v/>
@@ -5576,8 +5776,9 @@
         <v/>
       </c>
       <c r="AA54" s="63"/>
-    </row>
-    <row r="55" spans="1:27">
+      <c r="AB54" s="94"/>
+    </row>
+    <row r="55" spans="1:28">
       <c r="A55" s="62" t="str">
         <f t="shared" si="9"/>
         <v/>
@@ -5635,8 +5836,9 @@
         <v/>
       </c>
       <c r="AA55" s="63"/>
-    </row>
-    <row r="56" spans="1:27">
+      <c r="AB55" s="94"/>
+    </row>
+    <row r="56" spans="1:28">
       <c r="A56" s="62" t="str">
         <f t="shared" si="9"/>
         <v/>
@@ -5694,8 +5896,9 @@
         <v/>
       </c>
       <c r="AA56" s="63"/>
-    </row>
-    <row r="57" spans="1:27">
+      <c r="AB56" s="94"/>
+    </row>
+    <row r="57" spans="1:28">
       <c r="A57" s="62" t="str">
         <f t="shared" si="9"/>
         <v/>
@@ -5753,8 +5956,9 @@
         <v/>
       </c>
       <c r="AA57" s="63"/>
-    </row>
-    <row r="58" spans="1:27">
+      <c r="AB57" s="94"/>
+    </row>
+    <row r="58" spans="1:28">
       <c r="A58" s="62" t="str">
         <f t="shared" si="9"/>
         <v/>
@@ -5812,8 +6016,9 @@
         <v/>
       </c>
       <c r="AA58" s="63"/>
-    </row>
-    <row r="59" spans="1:27">
+      <c r="AB58" s="94"/>
+    </row>
+    <row r="59" spans="1:28">
       <c r="A59" s="62" t="str">
         <f t="shared" si="9"/>
         <v/>
@@ -5871,8 +6076,9 @@
         <v/>
       </c>
       <c r="AA59" s="63"/>
-    </row>
-    <row r="60" spans="1:27">
+      <c r="AB59" s="94"/>
+    </row>
+    <row r="60" spans="1:28">
       <c r="A60" s="62" t="str">
         <f t="shared" si="9"/>
         <v/>
@@ -5930,8 +6136,9 @@
         <v/>
       </c>
       <c r="AA60" s="63"/>
-    </row>
-    <row r="61" spans="1:27">
+      <c r="AB60" s="94"/>
+    </row>
+    <row r="61" spans="1:28">
       <c r="A61" s="62" t="str">
         <f t="shared" si="9"/>
         <v/>
@@ -5989,8 +6196,9 @@
         <v/>
       </c>
       <c r="AA61" s="63"/>
-    </row>
-    <row r="62" spans="1:27">
+      <c r="AB61" s="94"/>
+    </row>
+    <row r="62" spans="1:28">
       <c r="A62" s="62" t="str">
         <f t="shared" si="9"/>
         <v/>
@@ -6048,8 +6256,9 @@
         <v/>
       </c>
       <c r="AA62" s="63"/>
-    </row>
-    <row r="63" spans="1:27">
+      <c r="AB62" s="94"/>
+    </row>
+    <row r="63" spans="1:28">
       <c r="A63" s="62" t="str">
         <f t="shared" si="9"/>
         <v/>
@@ -6107,8 +6316,9 @@
         <v/>
       </c>
       <c r="AA63" s="63"/>
-    </row>
-    <row r="64" spans="1:27">
+      <c r="AB63" s="94"/>
+    </row>
+    <row r="64" spans="1:28">
       <c r="A64" s="62" t="str">
         <f t="shared" si="9"/>
         <v/>
@@ -6166,8 +6376,9 @@
         <v/>
       </c>
       <c r="AA64" s="63"/>
-    </row>
-    <row r="65" spans="1:27">
+      <c r="AB64" s="94"/>
+    </row>
+    <row r="65" spans="1:28">
       <c r="A65" s="62" t="str">
         <f t="shared" si="9"/>
         <v/>
@@ -6184,7 +6395,7 @@
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="H65" s="44"/>
+      <c r="H65" s="43"/>
       <c r="I65" s="44"/>
       <c r="J65" s="54"/>
       <c r="K65" s="48"/>
@@ -6225,8 +6436,9 @@
         <v/>
       </c>
       <c r="AA65" s="64"/>
-    </row>
-    <row r="66" spans="1:27">
+      <c r="AB65" s="94"/>
+    </row>
+    <row r="66" spans="1:28">
       <c r="A66" s="62" t="str">
         <f t="shared" si="9"/>
         <v/>
@@ -6243,7 +6455,7 @@
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="H66" s="44"/>
+      <c r="H66" s="43"/>
       <c r="I66" s="44"/>
       <c r="J66" s="54"/>
       <c r="K66" s="48"/>
@@ -6284,8 +6496,9 @@
         <v/>
       </c>
       <c r="AA66" s="64"/>
-    </row>
-    <row r="67" spans="1:27">
+      <c r="AB66" s="94"/>
+    </row>
+    <row r="67" spans="1:28">
       <c r="A67" s="62" t="str">
         <f t="shared" si="9"/>
         <v/>
@@ -6302,7 +6515,7 @@
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="H67" s="44"/>
+      <c r="H67" s="43"/>
       <c r="I67" s="44"/>
       <c r="J67" s="54"/>
       <c r="K67" s="48"/>
@@ -6343,8 +6556,9 @@
         <v/>
       </c>
       <c r="AA67" s="64"/>
-    </row>
-    <row r="68" spans="1:27">
+      <c r="AB67" s="94"/>
+    </row>
+    <row r="68" spans="1:28">
       <c r="A68" s="62" t="str">
         <f t="shared" si="9"/>
         <v/>
@@ -6361,7 +6575,7 @@
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="H68" s="44"/>
+      <c r="H68" s="43"/>
       <c r="I68" s="44"/>
       <c r="J68" s="54"/>
       <c r="K68" s="48"/>
@@ -6402,8 +6616,9 @@
         <v/>
       </c>
       <c r="AA68" s="64"/>
-    </row>
-    <row r="69" spans="1:27">
+      <c r="AB68" s="94"/>
+    </row>
+    <row r="69" spans="1:28">
       <c r="A69" s="62" t="str">
         <f t="shared" ref="A69:A100" si="17">IF(B69="","","LOC-"&amp;TEXT(ROW()-5,"000"))</f>
         <v/>
@@ -6420,7 +6635,7 @@
         <f t="shared" ref="G69:G100" si="19">IF(OR(B69="",E69=0,F69=""),0,E69*F69)</f>
         <v>0</v>
       </c>
-      <c r="H69" s="44"/>
+      <c r="H69" s="43"/>
       <c r="I69" s="44"/>
       <c r="J69" s="54"/>
       <c r="K69" s="48"/>
@@ -6461,8 +6676,9 @@
         <v/>
       </c>
       <c r="AA69" s="64"/>
-    </row>
-    <row r="70" spans="1:27">
+      <c r="AB69" s="94"/>
+    </row>
+    <row r="70" spans="1:28">
       <c r="A70" s="62" t="str">
         <f t="shared" si="17"/>
         <v/>
@@ -6479,7 +6695,7 @@
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="H70" s="44"/>
+      <c r="H70" s="43"/>
       <c r="I70" s="44"/>
       <c r="J70" s="54"/>
       <c r="K70" s="48"/>
@@ -6516,12 +6732,13 @@
         <v>0</v>
       </c>
       <c r="Z70" s="49" t="str">
-        <f t="shared" ref="Z70:Z101" si="25">IF(B70="","",IF(COUNTIFS($C$6:$C$204,"&lt;"&amp;D70,$D$6:$D$204,"&gt;"&amp;C70,$I$6:$I$204,"&lt;&gt;Cancelada",$I$6:$I$204,"&lt;&gt;Consulta")&gt;1,"CONFLITO","OK"))</f>
+        <f t="shared" ref="Z70:Z101" si="25">IF(B70="","",IF(COUNTIFS($C$6:$C$204,"&lt;"&amp;D70,$D$6:$D$204,"&gt;"&amp;C70,$I$6:$I$204,"&lt;&gt;Cancelada",$I$6:$I$204,"&lt;&gt;Consulta",$AB$6:$AB$204,$AB70)&gt;1,"CONFLITO","OK"))</f>
         <v/>
       </c>
       <c r="AA70" s="64"/>
-    </row>
-    <row r="71" spans="1:27">
+      <c r="AB70" s="94"/>
+    </row>
+    <row r="71" spans="1:28">
       <c r="A71" s="62" t="str">
         <f t="shared" si="17"/>
         <v/>
@@ -6538,7 +6755,7 @@
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="H71" s="44"/>
+      <c r="H71" s="43"/>
       <c r="I71" s="44"/>
       <c r="J71" s="54"/>
       <c r="K71" s="48"/>
@@ -6579,8 +6796,9 @@
         <v/>
       </c>
       <c r="AA71" s="64"/>
-    </row>
-    <row r="72" spans="1:27">
+      <c r="AB71" s="94"/>
+    </row>
+    <row r="72" spans="1:28">
       <c r="A72" s="62" t="str">
         <f t="shared" si="17"/>
         <v/>
@@ -6597,7 +6815,7 @@
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="H72" s="44"/>
+      <c r="H72" s="43"/>
       <c r="I72" s="44"/>
       <c r="J72" s="54"/>
       <c r="K72" s="48"/>
@@ -6638,8 +6856,9 @@
         <v/>
       </c>
       <c r="AA72" s="64"/>
-    </row>
-    <row r="73" spans="1:27">
+      <c r="AB72" s="94"/>
+    </row>
+    <row r="73" spans="1:28">
       <c r="A73" s="62" t="str">
         <f t="shared" si="17"/>
         <v/>
@@ -6656,7 +6875,7 @@
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="H73" s="44"/>
+      <c r="H73" s="43"/>
       <c r="I73" s="44"/>
       <c r="J73" s="54"/>
       <c r="K73" s="48"/>
@@ -6697,8 +6916,9 @@
         <v/>
       </c>
       <c r="AA73" s="64"/>
-    </row>
-    <row r="74" spans="1:27">
+      <c r="AB73" s="94"/>
+    </row>
+    <row r="74" spans="1:28">
       <c r="A74" s="62" t="str">
         <f t="shared" si="17"/>
         <v/>
@@ -6715,7 +6935,7 @@
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="H74" s="44"/>
+      <c r="H74" s="43"/>
       <c r="I74" s="44"/>
       <c r="J74" s="54"/>
       <c r="K74" s="48"/>
@@ -6756,8 +6976,9 @@
         <v/>
       </c>
       <c r="AA74" s="64"/>
-    </row>
-    <row r="75" spans="1:27">
+      <c r="AB74" s="94"/>
+    </row>
+    <row r="75" spans="1:28">
       <c r="A75" s="62" t="str">
         <f t="shared" si="17"/>
         <v/>
@@ -6774,7 +6995,7 @@
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="H75" s="44"/>
+      <c r="H75" s="43"/>
       <c r="I75" s="44"/>
       <c r="J75" s="54"/>
       <c r="K75" s="48"/>
@@ -6815,8 +7036,9 @@
         <v/>
       </c>
       <c r="AA75" s="64"/>
-    </row>
-    <row r="76" spans="1:27">
+      <c r="AB75" s="94"/>
+    </row>
+    <row r="76" spans="1:28">
       <c r="A76" s="62" t="str">
         <f t="shared" si="17"/>
         <v/>
@@ -6833,7 +7055,7 @@
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="H76" s="44"/>
+      <c r="H76" s="43"/>
       <c r="I76" s="44"/>
       <c r="J76" s="54"/>
       <c r="K76" s="48"/>
@@ -6874,8 +7096,9 @@
         <v/>
       </c>
       <c r="AA76" s="64"/>
-    </row>
-    <row r="77" spans="1:27">
+      <c r="AB76" s="94"/>
+    </row>
+    <row r="77" spans="1:28">
       <c r="A77" s="62" t="str">
         <f t="shared" si="17"/>
         <v/>
@@ -6892,7 +7115,7 @@
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="H77" s="44"/>
+      <c r="H77" s="43"/>
       <c r="I77" s="44"/>
       <c r="J77" s="54"/>
       <c r="K77" s="48"/>
@@ -6933,8 +7156,9 @@
         <v/>
       </c>
       <c r="AA77" s="64"/>
-    </row>
-    <row r="78" spans="1:27">
+      <c r="AB77" s="94"/>
+    </row>
+    <row r="78" spans="1:28">
       <c r="A78" s="62" t="str">
         <f t="shared" si="17"/>
         <v/>
@@ -6951,7 +7175,7 @@
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="H78" s="44"/>
+      <c r="H78" s="43"/>
       <c r="I78" s="44"/>
       <c r="J78" s="54"/>
       <c r="K78" s="48"/>
@@ -6992,8 +7216,9 @@
         <v/>
       </c>
       <c r="AA78" s="64"/>
-    </row>
-    <row r="79" spans="1:27">
+      <c r="AB78" s="94"/>
+    </row>
+    <row r="79" spans="1:28">
       <c r="A79" s="62" t="str">
         <f t="shared" si="17"/>
         <v/>
@@ -7010,7 +7235,7 @@
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="H79" s="44"/>
+      <c r="H79" s="43"/>
       <c r="I79" s="44"/>
       <c r="J79" s="54"/>
       <c r="K79" s="48"/>
@@ -7051,8 +7276,9 @@
         <v/>
       </c>
       <c r="AA79" s="64"/>
-    </row>
-    <row r="80" spans="1:27">
+      <c r="AB79" s="94"/>
+    </row>
+    <row r="80" spans="1:28">
       <c r="A80" s="62" t="str">
         <f t="shared" si="17"/>
         <v/>
@@ -7069,7 +7295,7 @@
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="H80" s="44"/>
+      <c r="H80" s="43"/>
       <c r="I80" s="44"/>
       <c r="J80" s="54"/>
       <c r="K80" s="48"/>
@@ -7110,8 +7336,9 @@
         <v/>
       </c>
       <c r="AA80" s="64"/>
-    </row>
-    <row r="81" spans="1:27">
+      <c r="AB80" s="94"/>
+    </row>
+    <row r="81" spans="1:28">
       <c r="A81" s="62" t="str">
         <f t="shared" si="17"/>
         <v/>
@@ -7128,7 +7355,7 @@
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="H81" s="44"/>
+      <c r="H81" s="43"/>
       <c r="I81" s="44"/>
       <c r="J81" s="54"/>
       <c r="K81" s="48"/>
@@ -7169,8 +7396,9 @@
         <v/>
       </c>
       <c r="AA81" s="64"/>
-    </row>
-    <row r="82" spans="1:27">
+      <c r="AB81" s="94"/>
+    </row>
+    <row r="82" spans="1:28">
       <c r="A82" s="62" t="str">
         <f t="shared" si="17"/>
         <v/>
@@ -7187,7 +7415,7 @@
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="H82" s="44"/>
+      <c r="H82" s="43"/>
       <c r="I82" s="44"/>
       <c r="J82" s="54"/>
       <c r="K82" s="48"/>
@@ -7228,8 +7456,9 @@
         <v/>
       </c>
       <c r="AA82" s="64"/>
-    </row>
-    <row r="83" spans="1:27">
+      <c r="AB82" s="94"/>
+    </row>
+    <row r="83" spans="1:28">
       <c r="A83" s="62" t="str">
         <f t="shared" si="17"/>
         <v/>
@@ -7246,7 +7475,7 @@
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="H83" s="44"/>
+      <c r="H83" s="43"/>
       <c r="I83" s="44"/>
       <c r="J83" s="54"/>
       <c r="K83" s="48"/>
@@ -7287,8 +7516,9 @@
         <v/>
       </c>
       <c r="AA83" s="64"/>
-    </row>
-    <row r="84" spans="1:27">
+      <c r="AB83" s="94"/>
+    </row>
+    <row r="84" spans="1:28">
       <c r="A84" s="62" t="str">
         <f t="shared" si="17"/>
         <v/>
@@ -7305,7 +7535,7 @@
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="H84" s="44"/>
+      <c r="H84" s="43"/>
       <c r="I84" s="44"/>
       <c r="J84" s="54"/>
       <c r="K84" s="48"/>
@@ -7346,8 +7576,9 @@
         <v/>
       </c>
       <c r="AA84" s="64"/>
-    </row>
-    <row r="85" spans="1:27">
+      <c r="AB84" s="94"/>
+    </row>
+    <row r="85" spans="1:28">
       <c r="A85" s="62" t="str">
         <f t="shared" si="17"/>
         <v/>
@@ -7364,7 +7595,7 @@
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="H85" s="44"/>
+      <c r="H85" s="43"/>
       <c r="I85" s="44"/>
       <c r="J85" s="54"/>
       <c r="K85" s="48"/>
@@ -7405,8 +7636,9 @@
         <v/>
       </c>
       <c r="AA85" s="64"/>
-    </row>
-    <row r="86" spans="1:27">
+      <c r="AB85" s="94"/>
+    </row>
+    <row r="86" spans="1:28">
       <c r="A86" s="62" t="str">
         <f t="shared" si="17"/>
         <v/>
@@ -7423,7 +7655,7 @@
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="H86" s="44"/>
+      <c r="H86" s="43"/>
       <c r="I86" s="44"/>
       <c r="J86" s="54"/>
       <c r="K86" s="48"/>
@@ -7464,8 +7696,9 @@
         <v/>
       </c>
       <c r="AA86" s="64"/>
-    </row>
-    <row r="87" spans="1:27">
+      <c r="AB86" s="94"/>
+    </row>
+    <row r="87" spans="1:28">
       <c r="A87" s="62" t="str">
         <f t="shared" si="17"/>
         <v/>
@@ -7482,7 +7715,7 @@
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="H87" s="44"/>
+      <c r="H87" s="43"/>
       <c r="I87" s="44"/>
       <c r="J87" s="54"/>
       <c r="K87" s="48"/>
@@ -7523,8 +7756,9 @@
         <v/>
       </c>
       <c r="AA87" s="64"/>
-    </row>
-    <row r="88" spans="1:27">
+      <c r="AB87" s="94"/>
+    </row>
+    <row r="88" spans="1:28">
       <c r="A88" s="62" t="str">
         <f t="shared" si="17"/>
         <v/>
@@ -7541,7 +7775,7 @@
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="H88" s="44"/>
+      <c r="H88" s="43"/>
       <c r="I88" s="44"/>
       <c r="J88" s="54"/>
       <c r="K88" s="48"/>
@@ -7582,8 +7816,9 @@
         <v/>
       </c>
       <c r="AA88" s="64"/>
-    </row>
-    <row r="89" spans="1:27">
+      <c r="AB88" s="94"/>
+    </row>
+    <row r="89" spans="1:28">
       <c r="A89" s="62" t="str">
         <f t="shared" si="17"/>
         <v/>
@@ -7600,7 +7835,7 @@
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="H89" s="44"/>
+      <c r="H89" s="43"/>
       <c r="I89" s="44"/>
       <c r="J89" s="54"/>
       <c r="K89" s="48"/>
@@ -7641,8 +7876,9 @@
         <v/>
       </c>
       <c r="AA89" s="64"/>
-    </row>
-    <row r="90" spans="1:27">
+      <c r="AB89" s="94"/>
+    </row>
+    <row r="90" spans="1:28">
       <c r="A90" s="62" t="str">
         <f t="shared" si="17"/>
         <v/>
@@ -7659,7 +7895,7 @@
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="H90" s="44"/>
+      <c r="H90" s="43"/>
       <c r="I90" s="44"/>
       <c r="J90" s="54"/>
       <c r="K90" s="48"/>
@@ -7700,8 +7936,9 @@
         <v/>
       </c>
       <c r="AA90" s="64"/>
-    </row>
-    <row r="91" spans="1:27">
+      <c r="AB90" s="94"/>
+    </row>
+    <row r="91" spans="1:28">
       <c r="A91" s="62" t="str">
         <f t="shared" si="17"/>
         <v/>
@@ -7718,7 +7955,7 @@
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="H91" s="44"/>
+      <c r="H91" s="43"/>
       <c r="I91" s="44"/>
       <c r="J91" s="54"/>
       <c r="K91" s="48"/>
@@ -7759,8 +7996,9 @@
         <v/>
       </c>
       <c r="AA91" s="64"/>
-    </row>
-    <row r="92" spans="1:27">
+      <c r="AB91" s="94"/>
+    </row>
+    <row r="92" spans="1:28">
       <c r="A92" s="62" t="str">
         <f t="shared" si="17"/>
         <v/>
@@ -7777,7 +8015,7 @@
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="H92" s="44"/>
+      <c r="H92" s="43"/>
       <c r="I92" s="44"/>
       <c r="J92" s="54"/>
       <c r="K92" s="48"/>
@@ -7818,8 +8056,9 @@
         <v/>
       </c>
       <c r="AA92" s="64"/>
-    </row>
-    <row r="93" spans="1:27">
+      <c r="AB92" s="94"/>
+    </row>
+    <row r="93" spans="1:28">
       <c r="A93" s="62" t="str">
         <f t="shared" si="17"/>
         <v/>
@@ -7836,7 +8075,7 @@
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="H93" s="44"/>
+      <c r="H93" s="43"/>
       <c r="I93" s="44"/>
       <c r="J93" s="54"/>
       <c r="K93" s="48"/>
@@ -7877,8 +8116,9 @@
         <v/>
       </c>
       <c r="AA93" s="64"/>
-    </row>
-    <row r="94" spans="1:27">
+      <c r="AB93" s="94"/>
+    </row>
+    <row r="94" spans="1:28">
       <c r="A94" s="62" t="str">
         <f t="shared" si="17"/>
         <v/>
@@ -7895,7 +8135,7 @@
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="H94" s="44"/>
+      <c r="H94" s="43"/>
       <c r="I94" s="44"/>
       <c r="J94" s="54"/>
       <c r="K94" s="48"/>
@@ -7936,8 +8176,9 @@
         <v/>
       </c>
       <c r="AA94" s="64"/>
-    </row>
-    <row r="95" spans="1:27">
+      <c r="AB94" s="94"/>
+    </row>
+    <row r="95" spans="1:28">
       <c r="A95" s="62" t="str">
         <f t="shared" si="17"/>
         <v/>
@@ -7954,7 +8195,7 @@
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="H95" s="44"/>
+      <c r="H95" s="43"/>
       <c r="I95" s="44"/>
       <c r="J95" s="54"/>
       <c r="K95" s="48"/>
@@ -7995,8 +8236,9 @@
         <v/>
       </c>
       <c r="AA95" s="64"/>
-    </row>
-    <row r="96" spans="1:27">
+      <c r="AB95" s="94"/>
+    </row>
+    <row r="96" spans="1:28">
       <c r="A96" s="62" t="str">
         <f t="shared" si="17"/>
         <v/>
@@ -8013,7 +8255,7 @@
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="H96" s="44"/>
+      <c r="H96" s="43"/>
       <c r="I96" s="44"/>
       <c r="J96" s="54"/>
       <c r="K96" s="48"/>
@@ -8054,8 +8296,9 @@
         <v/>
       </c>
       <c r="AA96" s="64"/>
-    </row>
-    <row r="97" spans="1:27">
+      <c r="AB96" s="94"/>
+    </row>
+    <row r="97" spans="1:28">
       <c r="A97" s="62" t="str">
         <f t="shared" si="17"/>
         <v/>
@@ -8072,7 +8315,7 @@
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="H97" s="44"/>
+      <c r="H97" s="43"/>
       <c r="I97" s="44"/>
       <c r="J97" s="54"/>
       <c r="K97" s="48"/>
@@ -8113,8 +8356,9 @@
         <v/>
       </c>
       <c r="AA97" s="64"/>
-    </row>
-    <row r="98" spans="1:27">
+      <c r="AB97" s="94"/>
+    </row>
+    <row r="98" spans="1:28">
       <c r="A98" s="62" t="str">
         <f t="shared" si="17"/>
         <v/>
@@ -8131,7 +8375,7 @@
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="H98" s="44"/>
+      <c r="H98" s="43"/>
       <c r="I98" s="44"/>
       <c r="J98" s="54"/>
       <c r="K98" s="48"/>
@@ -8172,8 +8416,9 @@
         <v/>
       </c>
       <c r="AA98" s="64"/>
-    </row>
-    <row r="99" spans="1:27">
+      <c r="AB98" s="94"/>
+    </row>
+    <row r="99" spans="1:28">
       <c r="A99" s="62" t="str">
         <f t="shared" si="17"/>
         <v/>
@@ -8190,7 +8435,7 @@
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="H99" s="44"/>
+      <c r="H99" s="43"/>
       <c r="I99" s="44"/>
       <c r="J99" s="54"/>
       <c r="K99" s="48"/>
@@ -8231,8 +8476,9 @@
         <v/>
       </c>
       <c r="AA99" s="64"/>
-    </row>
-    <row r="100" spans="1:27">
+      <c r="AB99" s="94"/>
+    </row>
+    <row r="100" spans="1:28">
       <c r="A100" s="62" t="str">
         <f t="shared" si="17"/>
         <v/>
@@ -8249,7 +8495,7 @@
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="H100" s="44"/>
+      <c r="H100" s="43"/>
       <c r="I100" s="44"/>
       <c r="J100" s="54"/>
       <c r="K100" s="48"/>
@@ -8290,8 +8536,9 @@
         <v/>
       </c>
       <c r="AA100" s="64"/>
-    </row>
-    <row r="101" spans="1:27">
+      <c r="AB100" s="94"/>
+    </row>
+    <row r="101" spans="1:28">
       <c r="A101" s="62" t="str">
         <f t="shared" ref="A101:A132" si="26">IF(B101="","","LOC-"&amp;TEXT(ROW()-5,"000"))</f>
         <v/>
@@ -8308,7 +8555,7 @@
         <f t="shared" ref="G101:G132" si="28">IF(OR(B101="",E101=0,F101=""),0,E101*F101)</f>
         <v>0</v>
       </c>
-      <c r="H101" s="44"/>
+      <c r="H101" s="43"/>
       <c r="I101" s="44"/>
       <c r="J101" s="54"/>
       <c r="K101" s="48"/>
@@ -8349,8 +8596,9 @@
         <v/>
       </c>
       <c r="AA101" s="64"/>
-    </row>
-    <row r="102" spans="1:27">
+      <c r="AB101" s="94"/>
+    </row>
+    <row r="102" spans="1:28">
       <c r="A102" s="62" t="str">
         <f t="shared" si="26"/>
         <v/>
@@ -8367,7 +8615,7 @@
         <f t="shared" si="28"/>
         <v>0</v>
       </c>
-      <c r="H102" s="44"/>
+      <c r="H102" s="43"/>
       <c r="I102" s="44"/>
       <c r="J102" s="54"/>
       <c r="K102" s="48"/>
@@ -8404,12 +8652,13 @@
         <v>0</v>
       </c>
       <c r="Z102" s="49" t="str">
-        <f t="shared" ref="Z102:Z133" si="33">IF(B102="","",IF(COUNTIFS($C$6:$C$204,"&lt;"&amp;D102,$D$6:$D$204,"&gt;"&amp;C102,$I$6:$I$204,"&lt;&gt;Cancelada",$I$6:$I$204,"&lt;&gt;Consulta")&gt;1,"CONFLITO","OK"))</f>
+        <f t="shared" ref="Z102:Z133" si="33">IF(B102="","",IF(COUNTIFS($C$6:$C$204,"&lt;"&amp;D102,$D$6:$D$204,"&gt;"&amp;C102,$I$6:$I$204,"&lt;&gt;Cancelada",$I$6:$I$204,"&lt;&gt;Consulta",$AB$6:$AB$204,$AB102)&gt;1,"CONFLITO","OK"))</f>
         <v/>
       </c>
       <c r="AA102" s="64"/>
-    </row>
-    <row r="103" spans="1:27">
+      <c r="AB102" s="94"/>
+    </row>
+    <row r="103" spans="1:28">
       <c r="A103" s="62" t="str">
         <f t="shared" si="26"/>
         <v/>
@@ -8426,7 +8675,7 @@
         <f t="shared" si="28"/>
         <v>0</v>
       </c>
-      <c r="H103" s="44"/>
+      <c r="H103" s="43"/>
       <c r="I103" s="44"/>
       <c r="J103" s="54"/>
       <c r="K103" s="48"/>
@@ -8467,8 +8716,9 @@
         <v/>
       </c>
       <c r="AA103" s="64"/>
-    </row>
-    <row r="104" spans="1:27">
+      <c r="AB103" s="94"/>
+    </row>
+    <row r="104" spans="1:28">
       <c r="A104" s="62" t="str">
         <f t="shared" si="26"/>
         <v/>
@@ -8485,7 +8735,7 @@
         <f t="shared" si="28"/>
         <v>0</v>
       </c>
-      <c r="H104" s="44"/>
+      <c r="H104" s="43"/>
       <c r="I104" s="44"/>
       <c r="J104" s="54"/>
       <c r="K104" s="48"/>
@@ -8526,8 +8776,9 @@
         <v/>
       </c>
       <c r="AA104" s="64"/>
-    </row>
-    <row r="105" spans="1:27">
+      <c r="AB104" s="94"/>
+    </row>
+    <row r="105" spans="1:28">
       <c r="A105" s="62" t="str">
         <f t="shared" si="26"/>
         <v/>
@@ -8544,7 +8795,7 @@
         <f t="shared" si="28"/>
         <v>0</v>
       </c>
-      <c r="H105" s="44"/>
+      <c r="H105" s="43"/>
       <c r="I105" s="44"/>
       <c r="J105" s="54"/>
       <c r="K105" s="48"/>
@@ -8585,8 +8836,9 @@
         <v/>
       </c>
       <c r="AA105" s="64"/>
-    </row>
-    <row r="106" spans="1:27">
+      <c r="AB105" s="94"/>
+    </row>
+    <row r="106" spans="1:28">
       <c r="A106" s="62" t="str">
         <f t="shared" si="26"/>
         <v/>
@@ -8603,7 +8855,7 @@
         <f t="shared" si="28"/>
         <v>0</v>
       </c>
-      <c r="H106" s="44"/>
+      <c r="H106" s="43"/>
       <c r="I106" s="44"/>
       <c r="J106" s="54"/>
       <c r="K106" s="48"/>
@@ -8644,8 +8896,9 @@
         <v/>
       </c>
       <c r="AA106" s="64"/>
-    </row>
-    <row r="107" spans="1:27">
+      <c r="AB106" s="94"/>
+    </row>
+    <row r="107" spans="1:28">
       <c r="A107" s="62" t="str">
         <f t="shared" si="26"/>
         <v/>
@@ -8662,7 +8915,7 @@
         <f t="shared" si="28"/>
         <v>0</v>
       </c>
-      <c r="H107" s="44"/>
+      <c r="H107" s="43"/>
       <c r="I107" s="44"/>
       <c r="J107" s="54"/>
       <c r="K107" s="48"/>
@@ -8703,8 +8956,9 @@
         <v/>
       </c>
       <c r="AA107" s="64"/>
-    </row>
-    <row r="108" spans="1:27">
+      <c r="AB107" s="94"/>
+    </row>
+    <row r="108" spans="1:28">
       <c r="A108" s="62" t="str">
         <f t="shared" si="26"/>
         <v/>
@@ -8721,7 +8975,7 @@
         <f t="shared" si="28"/>
         <v>0</v>
       </c>
-      <c r="H108" s="44"/>
+      <c r="H108" s="43"/>
       <c r="I108" s="44"/>
       <c r="J108" s="54"/>
       <c r="K108" s="48"/>
@@ -8762,8 +9016,9 @@
         <v/>
       </c>
       <c r="AA108" s="64"/>
-    </row>
-    <row r="109" spans="1:27">
+      <c r="AB108" s="94"/>
+    </row>
+    <row r="109" spans="1:28">
       <c r="A109" s="62" t="str">
         <f t="shared" si="26"/>
         <v/>
@@ -8780,7 +9035,7 @@
         <f t="shared" si="28"/>
         <v>0</v>
       </c>
-      <c r="H109" s="44"/>
+      <c r="H109" s="43"/>
       <c r="I109" s="44"/>
       <c r="J109" s="54"/>
       <c r="K109" s="48"/>
@@ -8821,8 +9076,9 @@
         <v/>
       </c>
       <c r="AA109" s="64"/>
-    </row>
-    <row r="110" spans="1:27">
+      <c r="AB109" s="94"/>
+    </row>
+    <row r="110" spans="1:28">
       <c r="A110" s="62" t="str">
         <f t="shared" si="26"/>
         <v/>
@@ -8839,7 +9095,7 @@
         <f t="shared" si="28"/>
         <v>0</v>
       </c>
-      <c r="H110" s="44"/>
+      <c r="H110" s="43"/>
       <c r="I110" s="44"/>
       <c r="J110" s="54"/>
       <c r="K110" s="48"/>
@@ -8880,8 +9136,9 @@
         <v/>
       </c>
       <c r="AA110" s="64"/>
-    </row>
-    <row r="111" spans="1:27">
+      <c r="AB110" s="94"/>
+    </row>
+    <row r="111" spans="1:28">
       <c r="A111" s="62" t="str">
         <f t="shared" si="26"/>
         <v/>
@@ -8898,7 +9155,7 @@
         <f t="shared" si="28"/>
         <v>0</v>
       </c>
-      <c r="H111" s="44"/>
+      <c r="H111" s="43"/>
       <c r="I111" s="44"/>
       <c r="J111" s="54"/>
       <c r="K111" s="48"/>
@@ -8939,8 +9196,9 @@
         <v/>
       </c>
       <c r="AA111" s="64"/>
-    </row>
-    <row r="112" spans="1:27">
+      <c r="AB111" s="94"/>
+    </row>
+    <row r="112" spans="1:28">
       <c r="A112" s="62" t="str">
         <f t="shared" si="26"/>
         <v/>
@@ -8957,7 +9215,7 @@
         <f t="shared" si="28"/>
         <v>0</v>
       </c>
-      <c r="H112" s="44"/>
+      <c r="H112" s="43"/>
       <c r="I112" s="44"/>
       <c r="J112" s="54"/>
       <c r="K112" s="48"/>
@@ -8998,8 +9256,9 @@
         <v/>
       </c>
       <c r="AA112" s="64"/>
-    </row>
-    <row r="113" spans="1:27">
+      <c r="AB112" s="94"/>
+    </row>
+    <row r="113" spans="1:28">
       <c r="A113" s="62" t="str">
         <f t="shared" si="26"/>
         <v/>
@@ -9016,7 +9275,7 @@
         <f t="shared" si="28"/>
         <v>0</v>
       </c>
-      <c r="H113" s="44"/>
+      <c r="H113" s="43"/>
       <c r="I113" s="44"/>
       <c r="J113" s="54"/>
       <c r="K113" s="48"/>
@@ -9057,8 +9316,9 @@
         <v/>
       </c>
       <c r="AA113" s="64"/>
-    </row>
-    <row r="114" spans="1:27">
+      <c r="AB113" s="94"/>
+    </row>
+    <row r="114" spans="1:28">
       <c r="A114" s="62" t="str">
         <f t="shared" si="26"/>
         <v/>
@@ -9075,7 +9335,7 @@
         <f t="shared" si="28"/>
         <v>0</v>
       </c>
-      <c r="H114" s="44"/>
+      <c r="H114" s="43"/>
       <c r="I114" s="44"/>
       <c r="J114" s="54"/>
       <c r="K114" s="48"/>
@@ -9116,8 +9376,9 @@
         <v/>
       </c>
       <c r="AA114" s="64"/>
-    </row>
-    <row r="115" spans="1:27">
+      <c r="AB114" s="94"/>
+    </row>
+    <row r="115" spans="1:28">
       <c r="A115" s="62" t="str">
         <f t="shared" si="26"/>
         <v/>
@@ -9134,7 +9395,7 @@
         <f t="shared" si="28"/>
         <v>0</v>
       </c>
-      <c r="H115" s="44"/>
+      <c r="H115" s="43"/>
       <c r="I115" s="44"/>
       <c r="J115" s="54"/>
       <c r="K115" s="48"/>
@@ -9175,8 +9436,9 @@
         <v/>
       </c>
       <c r="AA115" s="64"/>
-    </row>
-    <row r="116" spans="1:27">
+      <c r="AB115" s="94"/>
+    </row>
+    <row r="116" spans="1:28">
       <c r="A116" s="62" t="str">
         <f t="shared" si="26"/>
         <v/>
@@ -9193,7 +9455,7 @@
         <f t="shared" si="28"/>
         <v>0</v>
       </c>
-      <c r="H116" s="44"/>
+      <c r="H116" s="43"/>
       <c r="I116" s="44"/>
       <c r="J116" s="54"/>
       <c r="K116" s="48"/>
@@ -9234,8 +9496,9 @@
         <v/>
       </c>
       <c r="AA116" s="64"/>
-    </row>
-    <row r="117" spans="1:27">
+      <c r="AB116" s="94"/>
+    </row>
+    <row r="117" spans="1:28">
       <c r="A117" s="62" t="str">
         <f t="shared" si="26"/>
         <v/>
@@ -9252,7 +9515,7 @@
         <f t="shared" si="28"/>
         <v>0</v>
       </c>
-      <c r="H117" s="44"/>
+      <c r="H117" s="43"/>
       <c r="I117" s="44"/>
       <c r="J117" s="54"/>
       <c r="K117" s="48"/>
@@ -9293,8 +9556,9 @@
         <v/>
       </c>
       <c r="AA117" s="64"/>
-    </row>
-    <row r="118" spans="1:27">
+      <c r="AB117" s="94"/>
+    </row>
+    <row r="118" spans="1:28">
       <c r="A118" s="62" t="str">
         <f t="shared" si="26"/>
         <v/>
@@ -9311,7 +9575,7 @@
         <f t="shared" si="28"/>
         <v>0</v>
       </c>
-      <c r="H118" s="44"/>
+      <c r="H118" s="43"/>
       <c r="I118" s="44"/>
       <c r="J118" s="54"/>
       <c r="K118" s="48"/>
@@ -9352,8 +9616,9 @@
         <v/>
       </c>
       <c r="AA118" s="64"/>
-    </row>
-    <row r="119" spans="1:27">
+      <c r="AB118" s="94"/>
+    </row>
+    <row r="119" spans="1:28">
       <c r="A119" s="62" t="str">
         <f t="shared" si="26"/>
         <v/>
@@ -9370,7 +9635,7 @@
         <f t="shared" si="28"/>
         <v>0</v>
       </c>
-      <c r="H119" s="44"/>
+      <c r="H119" s="43"/>
       <c r="I119" s="44"/>
       <c r="J119" s="54"/>
       <c r="K119" s="48"/>
@@ -9411,8 +9676,9 @@
         <v/>
       </c>
       <c r="AA119" s="64"/>
-    </row>
-    <row r="120" spans="1:27">
+      <c r="AB119" s="94"/>
+    </row>
+    <row r="120" spans="1:28">
       <c r="A120" s="62" t="str">
         <f t="shared" si="26"/>
         <v/>
@@ -9429,7 +9695,7 @@
         <f t="shared" si="28"/>
         <v>0</v>
       </c>
-      <c r="H120" s="44"/>
+      <c r="H120" s="43"/>
       <c r="I120" s="44"/>
       <c r="J120" s="54"/>
       <c r="K120" s="48"/>
@@ -9470,8 +9736,9 @@
         <v/>
       </c>
       <c r="AA120" s="64"/>
-    </row>
-    <row r="121" spans="1:27">
+      <c r="AB120" s="94"/>
+    </row>
+    <row r="121" spans="1:28">
       <c r="A121" s="62" t="str">
         <f t="shared" si="26"/>
         <v/>
@@ -9488,7 +9755,7 @@
         <f t="shared" si="28"/>
         <v>0</v>
       </c>
-      <c r="H121" s="44"/>
+      <c r="H121" s="43"/>
       <c r="I121" s="44"/>
       <c r="J121" s="54"/>
       <c r="K121" s="48"/>
@@ -9529,8 +9796,9 @@
         <v/>
       </c>
       <c r="AA121" s="64"/>
-    </row>
-    <row r="122" spans="1:27">
+      <c r="AB121" s="94"/>
+    </row>
+    <row r="122" spans="1:28">
       <c r="A122" s="62" t="str">
         <f t="shared" si="26"/>
         <v/>
@@ -9547,7 +9815,7 @@
         <f t="shared" si="28"/>
         <v>0</v>
       </c>
-      <c r="H122" s="44"/>
+      <c r="H122" s="43"/>
       <c r="I122" s="44"/>
       <c r="J122" s="54"/>
       <c r="K122" s="48"/>
@@ -9588,8 +9856,9 @@
         <v/>
       </c>
       <c r="AA122" s="64"/>
-    </row>
-    <row r="123" spans="1:27">
+      <c r="AB122" s="94"/>
+    </row>
+    <row r="123" spans="1:28">
       <c r="A123" s="62" t="str">
         <f t="shared" si="26"/>
         <v/>
@@ -9606,7 +9875,7 @@
         <f t="shared" si="28"/>
         <v>0</v>
       </c>
-      <c r="H123" s="44"/>
+      <c r="H123" s="43"/>
       <c r="I123" s="44"/>
       <c r="J123" s="54"/>
       <c r="K123" s="48"/>
@@ -9647,8 +9916,9 @@
         <v/>
       </c>
       <c r="AA123" s="64"/>
-    </row>
-    <row r="124" spans="1:27">
+      <c r="AB123" s="94"/>
+    </row>
+    <row r="124" spans="1:28">
       <c r="A124" s="62" t="str">
         <f t="shared" si="26"/>
         <v/>
@@ -9665,7 +9935,7 @@
         <f t="shared" si="28"/>
         <v>0</v>
       </c>
-      <c r="H124" s="44"/>
+      <c r="H124" s="43"/>
       <c r="I124" s="44"/>
       <c r="J124" s="54"/>
       <c r="K124" s="48"/>
@@ -9706,8 +9976,9 @@
         <v/>
       </c>
       <c r="AA124" s="64"/>
-    </row>
-    <row r="125" spans="1:27">
+      <c r="AB124" s="94"/>
+    </row>
+    <row r="125" spans="1:28">
       <c r="A125" s="62" t="str">
         <f t="shared" si="26"/>
         <v/>
@@ -9724,7 +9995,7 @@
         <f t="shared" si="28"/>
         <v>0</v>
       </c>
-      <c r="H125" s="44"/>
+      <c r="H125" s="43"/>
       <c r="I125" s="44"/>
       <c r="J125" s="54"/>
       <c r="K125" s="48"/>
@@ -9765,8 +10036,9 @@
         <v/>
       </c>
       <c r="AA125" s="64"/>
-    </row>
-    <row r="126" spans="1:27">
+      <c r="AB125" s="94"/>
+    </row>
+    <row r="126" spans="1:28">
       <c r="A126" s="62" t="str">
         <f t="shared" si="26"/>
         <v/>
@@ -9783,7 +10055,7 @@
         <f t="shared" si="28"/>
         <v>0</v>
       </c>
-      <c r="H126" s="44"/>
+      <c r="H126" s="43"/>
       <c r="I126" s="44"/>
       <c r="J126" s="54"/>
       <c r="K126" s="48"/>
@@ -9824,8 +10096,9 @@
         <v/>
       </c>
       <c r="AA126" s="64"/>
-    </row>
-    <row r="127" spans="1:27">
+      <c r="AB126" s="94"/>
+    </row>
+    <row r="127" spans="1:28">
       <c r="A127" s="62" t="str">
         <f t="shared" si="26"/>
         <v/>
@@ -9842,7 +10115,7 @@
         <f t="shared" si="28"/>
         <v>0</v>
       </c>
-      <c r="H127" s="44"/>
+      <c r="H127" s="43"/>
       <c r="I127" s="44"/>
       <c r="J127" s="54"/>
       <c r="K127" s="48"/>
@@ -9883,8 +10156,9 @@
         <v/>
       </c>
       <c r="AA127" s="64"/>
-    </row>
-    <row r="128" spans="1:27">
+      <c r="AB127" s="94"/>
+    </row>
+    <row r="128" spans="1:28">
       <c r="A128" s="62" t="str">
         <f t="shared" si="26"/>
         <v/>
@@ -9901,7 +10175,7 @@
         <f t="shared" si="28"/>
         <v>0</v>
       </c>
-      <c r="H128" s="44"/>
+      <c r="H128" s="43"/>
       <c r="I128" s="44"/>
       <c r="J128" s="54"/>
       <c r="K128" s="48"/>
@@ -9942,8 +10216,9 @@
         <v/>
       </c>
       <c r="AA128" s="64"/>
-    </row>
-    <row r="129" spans="1:27">
+      <c r="AB128" s="94"/>
+    </row>
+    <row r="129" spans="1:28">
       <c r="A129" s="62" t="str">
         <f t="shared" si="26"/>
         <v/>
@@ -9960,7 +10235,7 @@
         <f t="shared" si="28"/>
         <v>0</v>
       </c>
-      <c r="H129" s="44"/>
+      <c r="H129" s="43"/>
       <c r="I129" s="44"/>
       <c r="J129" s="54"/>
       <c r="K129" s="48"/>
@@ -10001,8 +10276,9 @@
         <v/>
       </c>
       <c r="AA129" s="64"/>
-    </row>
-    <row r="130" spans="1:27">
+      <c r="AB129" s="94"/>
+    </row>
+    <row r="130" spans="1:28">
       <c r="A130" s="62" t="str">
         <f t="shared" si="26"/>
         <v/>
@@ -10019,7 +10295,7 @@
         <f t="shared" si="28"/>
         <v>0</v>
       </c>
-      <c r="H130" s="44"/>
+      <c r="H130" s="43"/>
       <c r="I130" s="44"/>
       <c r="J130" s="54"/>
       <c r="K130" s="48"/>
@@ -10060,8 +10336,9 @@
         <v/>
       </c>
       <c r="AA130" s="64"/>
-    </row>
-    <row r="131" spans="1:27">
+      <c r="AB130" s="94"/>
+    </row>
+    <row r="131" spans="1:28">
       <c r="A131" s="62" t="str">
         <f t="shared" si="26"/>
         <v/>
@@ -10078,7 +10355,7 @@
         <f t="shared" si="28"/>
         <v>0</v>
       </c>
-      <c r="H131" s="44"/>
+      <c r="H131" s="43"/>
       <c r="I131" s="44"/>
       <c r="J131" s="54"/>
       <c r="K131" s="48"/>
@@ -10119,8 +10396,9 @@
         <v/>
       </c>
       <c r="AA131" s="64"/>
-    </row>
-    <row r="132" spans="1:27">
+      <c r="AB131" s="94"/>
+    </row>
+    <row r="132" spans="1:28">
       <c r="A132" s="62" t="str">
         <f t="shared" si="26"/>
         <v/>
@@ -10137,7 +10415,7 @@
         <f t="shared" si="28"/>
         <v>0</v>
       </c>
-      <c r="H132" s="44"/>
+      <c r="H132" s="43"/>
       <c r="I132" s="44"/>
       <c r="J132" s="54"/>
       <c r="K132" s="48"/>
@@ -10178,8 +10456,9 @@
         <v/>
       </c>
       <c r="AA132" s="64"/>
-    </row>
-    <row r="133" spans="1:27">
+      <c r="AB132" s="94"/>
+    </row>
+    <row r="133" spans="1:28">
       <c r="A133" s="62" t="str">
         <f t="shared" ref="A133:A164" si="34">IF(B133="","","LOC-"&amp;TEXT(ROW()-5,"000"))</f>
         <v/>
@@ -10196,7 +10475,7 @@
         <f t="shared" ref="G133:G164" si="36">IF(OR(B133="",E133=0,F133=""),0,E133*F133)</f>
         <v>0</v>
       </c>
-      <c r="H133" s="44"/>
+      <c r="H133" s="43"/>
       <c r="I133" s="44"/>
       <c r="J133" s="54"/>
       <c r="K133" s="48"/>
@@ -10237,8 +10516,9 @@
         <v/>
       </c>
       <c r="AA133" s="64"/>
-    </row>
-    <row r="134" spans="1:27">
+      <c r="AB133" s="94"/>
+    </row>
+    <row r="134" spans="1:28">
       <c r="A134" s="62" t="str">
         <f t="shared" si="34"/>
         <v/>
@@ -10255,7 +10535,7 @@
         <f t="shared" si="36"/>
         <v>0</v>
       </c>
-      <c r="H134" s="44"/>
+      <c r="H134" s="43"/>
       <c r="I134" s="44"/>
       <c r="J134" s="54"/>
       <c r="K134" s="48"/>
@@ -10292,12 +10572,13 @@
         <v>0</v>
       </c>
       <c r="Z134" s="49" t="str">
-        <f t="shared" ref="Z134:Z165" si="42">IF(B134="","",IF(COUNTIFS($C$6:$C$204,"&lt;"&amp;D134,$D$6:$D$204,"&gt;"&amp;C134,$I$6:$I$204,"&lt;&gt;Cancelada",$I$6:$I$204,"&lt;&gt;Consulta")&gt;1,"CONFLITO","OK"))</f>
+        <f t="shared" ref="Z134:Z165" si="42">IF(B134="","",IF(COUNTIFS($C$6:$C$204,"&lt;"&amp;D134,$D$6:$D$204,"&gt;"&amp;C134,$I$6:$I$204,"&lt;&gt;Cancelada",$I$6:$I$204,"&lt;&gt;Consulta",$AB$6:$AB$204,$AB134)&gt;1,"CONFLITO","OK"))</f>
         <v/>
       </c>
       <c r="AA134" s="64"/>
-    </row>
-    <row r="135" spans="1:27">
+      <c r="AB134" s="94"/>
+    </row>
+    <row r="135" spans="1:28">
       <c r="A135" s="62" t="str">
         <f t="shared" si="34"/>
         <v/>
@@ -10314,7 +10595,7 @@
         <f t="shared" si="36"/>
         <v>0</v>
       </c>
-      <c r="H135" s="44"/>
+      <c r="H135" s="43"/>
       <c r="I135" s="44"/>
       <c r="J135" s="54"/>
       <c r="K135" s="48"/>
@@ -10355,8 +10636,9 @@
         <v/>
       </c>
       <c r="AA135" s="64"/>
-    </row>
-    <row r="136" spans="1:27">
+      <c r="AB135" s="94"/>
+    </row>
+    <row r="136" spans="1:28">
       <c r="A136" s="62" t="str">
         <f t="shared" si="34"/>
         <v/>
@@ -10373,7 +10655,7 @@
         <f t="shared" si="36"/>
         <v>0</v>
       </c>
-      <c r="H136" s="44"/>
+      <c r="H136" s="43"/>
       <c r="I136" s="44"/>
       <c r="J136" s="54"/>
       <c r="K136" s="48"/>
@@ -10414,8 +10696,9 @@
         <v/>
       </c>
       <c r="AA136" s="64"/>
-    </row>
-    <row r="137" spans="1:27">
+      <c r="AB136" s="94"/>
+    </row>
+    <row r="137" spans="1:28">
       <c r="A137" s="62" t="str">
         <f t="shared" si="34"/>
         <v/>
@@ -10432,7 +10715,7 @@
         <f t="shared" si="36"/>
         <v>0</v>
       </c>
-      <c r="H137" s="44"/>
+      <c r="H137" s="43"/>
       <c r="I137" s="44"/>
       <c r="J137" s="54"/>
       <c r="K137" s="48"/>
@@ -10473,8 +10756,9 @@
         <v/>
       </c>
       <c r="AA137" s="64"/>
-    </row>
-    <row r="138" spans="1:27">
+      <c r="AB137" s="94"/>
+    </row>
+    <row r="138" spans="1:28">
       <c r="A138" s="62" t="str">
         <f t="shared" si="34"/>
         <v/>
@@ -10491,7 +10775,7 @@
         <f t="shared" si="36"/>
         <v>0</v>
       </c>
-      <c r="H138" s="44"/>
+      <c r="H138" s="43"/>
       <c r="I138" s="44"/>
       <c r="J138" s="54"/>
       <c r="K138" s="48"/>
@@ -10532,8 +10816,9 @@
         <v/>
       </c>
       <c r="AA138" s="64"/>
-    </row>
-    <row r="139" spans="1:27">
+      <c r="AB138" s="94"/>
+    </row>
+    <row r="139" spans="1:28">
       <c r="A139" s="62" t="str">
         <f t="shared" si="34"/>
         <v/>
@@ -10550,7 +10835,7 @@
         <f t="shared" si="36"/>
         <v>0</v>
       </c>
-      <c r="H139" s="44"/>
+      <c r="H139" s="43"/>
       <c r="I139" s="44"/>
       <c r="J139" s="54"/>
       <c r="K139" s="48"/>
@@ -10591,8 +10876,9 @@
         <v/>
       </c>
       <c r="AA139" s="64"/>
-    </row>
-    <row r="140" spans="1:27">
+      <c r="AB139" s="94"/>
+    </row>
+    <row r="140" spans="1:28">
       <c r="A140" s="62" t="str">
         <f t="shared" si="34"/>
         <v/>
@@ -10609,7 +10895,7 @@
         <f t="shared" si="36"/>
         <v>0</v>
       </c>
-      <c r="H140" s="44"/>
+      <c r="H140" s="43"/>
       <c r="I140" s="44"/>
       <c r="J140" s="54"/>
       <c r="K140" s="48"/>
@@ -10650,8 +10936,9 @@
         <v/>
       </c>
       <c r="AA140" s="64"/>
-    </row>
-    <row r="141" spans="1:27">
+      <c r="AB140" s="94"/>
+    </row>
+    <row r="141" spans="1:28">
       <c r="A141" s="62" t="str">
         <f t="shared" si="34"/>
         <v/>
@@ -10668,7 +10955,7 @@
         <f t="shared" si="36"/>
         <v>0</v>
       </c>
-      <c r="H141" s="44"/>
+      <c r="H141" s="43"/>
       <c r="I141" s="44"/>
       <c r="J141" s="54"/>
       <c r="K141" s="48"/>
@@ -10709,8 +10996,9 @@
         <v/>
       </c>
       <c r="AA141" s="64"/>
-    </row>
-    <row r="142" spans="1:27">
+      <c r="AB141" s="94"/>
+    </row>
+    <row r="142" spans="1:28">
       <c r="A142" s="62" t="str">
         <f t="shared" si="34"/>
         <v/>
@@ -10727,7 +11015,7 @@
         <f t="shared" si="36"/>
         <v>0</v>
       </c>
-      <c r="H142" s="44"/>
+      <c r="H142" s="43"/>
       <c r="I142" s="44"/>
       <c r="J142" s="54"/>
       <c r="K142" s="48"/>
@@ -10768,8 +11056,9 @@
         <v/>
       </c>
       <c r="AA142" s="64"/>
-    </row>
-    <row r="143" spans="1:27">
+      <c r="AB142" s="94"/>
+    </row>
+    <row r="143" spans="1:28">
       <c r="A143" s="62" t="str">
         <f t="shared" si="34"/>
         <v/>
@@ -10786,7 +11075,7 @@
         <f t="shared" si="36"/>
         <v>0</v>
       </c>
-      <c r="H143" s="44"/>
+      <c r="H143" s="43"/>
       <c r="I143" s="44"/>
       <c r="J143" s="54"/>
       <c r="K143" s="48"/>
@@ -10827,8 +11116,9 @@
         <v/>
       </c>
       <c r="AA143" s="64"/>
-    </row>
-    <row r="144" spans="1:27">
+      <c r="AB143" s="94"/>
+    </row>
+    <row r="144" spans="1:28">
       <c r="A144" s="62" t="str">
         <f t="shared" si="34"/>
         <v/>
@@ -10845,7 +11135,7 @@
         <f t="shared" si="36"/>
         <v>0</v>
       </c>
-      <c r="H144" s="44"/>
+      <c r="H144" s="43"/>
       <c r="I144" s="44"/>
       <c r="J144" s="54"/>
       <c r="K144" s="48"/>
@@ -10886,8 +11176,9 @@
         <v/>
       </c>
       <c r="AA144" s="64"/>
-    </row>
-    <row r="145" spans="1:27">
+      <c r="AB144" s="94"/>
+    </row>
+    <row r="145" spans="1:28">
       <c r="A145" s="62" t="str">
         <f t="shared" si="34"/>
         <v/>
@@ -10904,7 +11195,7 @@
         <f t="shared" si="36"/>
         <v>0</v>
       </c>
-      <c r="H145" s="44"/>
+      <c r="H145" s="43"/>
       <c r="I145" s="44"/>
       <c r="J145" s="54"/>
       <c r="K145" s="48"/>
@@ -10945,8 +11236,9 @@
         <v/>
       </c>
       <c r="AA145" s="64"/>
-    </row>
-    <row r="146" spans="1:27">
+      <c r="AB145" s="94"/>
+    </row>
+    <row r="146" spans="1:28">
       <c r="A146" s="62" t="str">
         <f t="shared" si="34"/>
         <v/>
@@ -10963,7 +11255,7 @@
         <f t="shared" si="36"/>
         <v>0</v>
       </c>
-      <c r="H146" s="44"/>
+      <c r="H146" s="43"/>
       <c r="I146" s="44"/>
       <c r="J146" s="54"/>
       <c r="K146" s="48"/>
@@ -11004,8 +11296,9 @@
         <v/>
       </c>
       <c r="AA146" s="64"/>
-    </row>
-    <row r="147" spans="1:27">
+      <c r="AB146" s="94"/>
+    </row>
+    <row r="147" spans="1:28">
       <c r="A147" s="62" t="str">
         <f t="shared" si="34"/>
         <v/>
@@ -11022,7 +11315,7 @@
         <f t="shared" si="36"/>
         <v>0</v>
       </c>
-      <c r="H147" s="44"/>
+      <c r="H147" s="43"/>
       <c r="I147" s="44"/>
       <c r="J147" s="54"/>
       <c r="K147" s="48"/>
@@ -11063,8 +11356,9 @@
         <v/>
       </c>
       <c r="AA147" s="64"/>
-    </row>
-    <row r="148" spans="1:27">
+      <c r="AB147" s="94"/>
+    </row>
+    <row r="148" spans="1:28">
       <c r="A148" s="62" t="str">
         <f t="shared" si="34"/>
         <v/>
@@ -11081,7 +11375,7 @@
         <f t="shared" si="36"/>
         <v>0</v>
       </c>
-      <c r="H148" s="44"/>
+      <c r="H148" s="43"/>
       <c r="I148" s="44"/>
       <c r="J148" s="54"/>
       <c r="K148" s="48"/>
@@ -11122,8 +11416,9 @@
         <v/>
       </c>
       <c r="AA148" s="64"/>
-    </row>
-    <row r="149" spans="1:27">
+      <c r="AB148" s="94"/>
+    </row>
+    <row r="149" spans="1:28">
       <c r="A149" s="62" t="str">
         <f t="shared" si="34"/>
         <v/>
@@ -11140,7 +11435,7 @@
         <f t="shared" si="36"/>
         <v>0</v>
       </c>
-      <c r="H149" s="44"/>
+      <c r="H149" s="43"/>
       <c r="I149" s="44"/>
       <c r="J149" s="54"/>
       <c r="K149" s="48"/>
@@ -11181,8 +11476,9 @@
         <v/>
       </c>
       <c r="AA149" s="64"/>
-    </row>
-    <row r="150" spans="1:27">
+      <c r="AB149" s="94"/>
+    </row>
+    <row r="150" spans="1:28">
       <c r="A150" s="62" t="str">
         <f t="shared" si="34"/>
         <v/>
@@ -11199,7 +11495,7 @@
         <f t="shared" si="36"/>
         <v>0</v>
       </c>
-      <c r="H150" s="44"/>
+      <c r="H150" s="43"/>
       <c r="I150" s="44"/>
       <c r="J150" s="54"/>
       <c r="K150" s="48"/>
@@ -11240,8 +11536,9 @@
         <v/>
       </c>
       <c r="AA150" s="64"/>
-    </row>
-    <row r="151" spans="1:27">
+      <c r="AB150" s="94"/>
+    </row>
+    <row r="151" spans="1:28">
       <c r="A151" s="62" t="str">
         <f t="shared" si="34"/>
         <v/>
@@ -11258,7 +11555,7 @@
         <f t="shared" si="36"/>
         <v>0</v>
       </c>
-      <c r="H151" s="44"/>
+      <c r="H151" s="43"/>
       <c r="I151" s="44"/>
       <c r="J151" s="54"/>
       <c r="K151" s="48"/>
@@ -11299,8 +11596,9 @@
         <v/>
       </c>
       <c r="AA151" s="64"/>
-    </row>
-    <row r="152" spans="1:27">
+      <c r="AB151" s="94"/>
+    </row>
+    <row r="152" spans="1:28">
       <c r="A152" s="62" t="str">
         <f t="shared" si="34"/>
         <v/>
@@ -11317,7 +11615,7 @@
         <f t="shared" si="36"/>
         <v>0</v>
       </c>
-      <c r="H152" s="44"/>
+      <c r="H152" s="43"/>
       <c r="I152" s="44"/>
       <c r="J152" s="54"/>
       <c r="K152" s="48"/>
@@ -11358,8 +11656,9 @@
         <v/>
       </c>
       <c r="AA152" s="64"/>
-    </row>
-    <row r="153" spans="1:27">
+      <c r="AB152" s="94"/>
+    </row>
+    <row r="153" spans="1:28">
       <c r="A153" s="62" t="str">
         <f t="shared" si="34"/>
         <v/>
@@ -11376,7 +11675,7 @@
         <f t="shared" si="36"/>
         <v>0</v>
       </c>
-      <c r="H153" s="44"/>
+      <c r="H153" s="43"/>
       <c r="I153" s="44"/>
       <c r="J153" s="54"/>
       <c r="K153" s="48"/>
@@ -11417,8 +11716,9 @@
         <v/>
       </c>
       <c r="AA153" s="64"/>
-    </row>
-    <row r="154" spans="1:27">
+      <c r="AB153" s="94"/>
+    </row>
+    <row r="154" spans="1:28">
       <c r="A154" s="62" t="str">
         <f t="shared" si="34"/>
         <v/>
@@ -11435,7 +11735,7 @@
         <f t="shared" si="36"/>
         <v>0</v>
       </c>
-      <c r="H154" s="44"/>
+      <c r="H154" s="43"/>
       <c r="I154" s="44"/>
       <c r="J154" s="54"/>
       <c r="K154" s="48"/>
@@ -11476,8 +11776,9 @@
         <v/>
       </c>
       <c r="AA154" s="64"/>
-    </row>
-    <row r="155" spans="1:27">
+      <c r="AB154" s="94"/>
+    </row>
+    <row r="155" spans="1:28">
       <c r="A155" s="62" t="str">
         <f t="shared" si="34"/>
         <v/>
@@ -11494,7 +11795,7 @@
         <f t="shared" si="36"/>
         <v>0</v>
       </c>
-      <c r="H155" s="44"/>
+      <c r="H155" s="43"/>
       <c r="I155" s="44"/>
       <c r="J155" s="54"/>
       <c r="K155" s="48"/>
@@ -11535,8 +11836,9 @@
         <v/>
       </c>
       <c r="AA155" s="64"/>
-    </row>
-    <row r="156" spans="1:27">
+      <c r="AB155" s="94"/>
+    </row>
+    <row r="156" spans="1:28">
       <c r="A156" s="62" t="str">
         <f t="shared" si="34"/>
         <v/>
@@ -11553,7 +11855,7 @@
         <f t="shared" si="36"/>
         <v>0</v>
       </c>
-      <c r="H156" s="44"/>
+      <c r="H156" s="43"/>
       <c r="I156" s="44"/>
       <c r="J156" s="54"/>
       <c r="K156" s="48"/>
@@ -11594,8 +11896,9 @@
         <v/>
       </c>
       <c r="AA156" s="64"/>
-    </row>
-    <row r="157" spans="1:27">
+      <c r="AB156" s="94"/>
+    </row>
+    <row r="157" spans="1:28">
       <c r="A157" s="62" t="str">
         <f t="shared" si="34"/>
         <v/>
@@ -11612,7 +11915,7 @@
         <f t="shared" si="36"/>
         <v>0</v>
       </c>
-      <c r="H157" s="44"/>
+      <c r="H157" s="43"/>
       <c r="I157" s="44"/>
       <c r="J157" s="54"/>
       <c r="K157" s="48"/>
@@ -11653,8 +11956,9 @@
         <v/>
       </c>
       <c r="AA157" s="64"/>
-    </row>
-    <row r="158" spans="1:27">
+      <c r="AB157" s="94"/>
+    </row>
+    <row r="158" spans="1:28">
       <c r="A158" s="62" t="str">
         <f t="shared" si="34"/>
         <v/>
@@ -11671,7 +11975,7 @@
         <f t="shared" si="36"/>
         <v>0</v>
       </c>
-      <c r="H158" s="44"/>
+      <c r="H158" s="43"/>
       <c r="I158" s="44"/>
       <c r="J158" s="54"/>
       <c r="K158" s="48"/>
@@ -11712,8 +12016,9 @@
         <v/>
       </c>
       <c r="AA158" s="64"/>
-    </row>
-    <row r="159" spans="1:27">
+      <c r="AB158" s="94"/>
+    </row>
+    <row r="159" spans="1:28">
       <c r="A159" s="62" t="str">
         <f t="shared" si="34"/>
         <v/>
@@ -11730,7 +12035,7 @@
         <f t="shared" si="36"/>
         <v>0</v>
       </c>
-      <c r="H159" s="44"/>
+      <c r="H159" s="43"/>
       <c r="I159" s="44"/>
       <c r="J159" s="54"/>
       <c r="K159" s="48"/>
@@ -11771,8 +12076,9 @@
         <v/>
       </c>
       <c r="AA159" s="64"/>
-    </row>
-    <row r="160" spans="1:27">
+      <c r="AB159" s="94"/>
+    </row>
+    <row r="160" spans="1:28">
       <c r="A160" s="62" t="str">
         <f t="shared" si="34"/>
         <v/>
@@ -11789,7 +12095,7 @@
         <f t="shared" si="36"/>
         <v>0</v>
       </c>
-      <c r="H160" s="44"/>
+      <c r="H160" s="43"/>
       <c r="I160" s="44"/>
       <c r="J160" s="54"/>
       <c r="K160" s="48"/>
@@ -11830,8 +12136,9 @@
         <v/>
       </c>
       <c r="AA160" s="64"/>
-    </row>
-    <row r="161" spans="1:27">
+      <c r="AB160" s="94"/>
+    </row>
+    <row r="161" spans="1:28">
       <c r="A161" s="62" t="str">
         <f t="shared" si="34"/>
         <v/>
@@ -11848,7 +12155,7 @@
         <f t="shared" si="36"/>
         <v>0</v>
       </c>
-      <c r="H161" s="44"/>
+      <c r="H161" s="43"/>
       <c r="I161" s="44"/>
       <c r="J161" s="54"/>
       <c r="K161" s="48"/>
@@ -11889,8 +12196,9 @@
         <v/>
       </c>
       <c r="AA161" s="64"/>
-    </row>
-    <row r="162" spans="1:27">
+      <c r="AB161" s="94"/>
+    </row>
+    <row r="162" spans="1:28">
       <c r="A162" s="62" t="str">
         <f t="shared" si="34"/>
         <v/>
@@ -11907,7 +12215,7 @@
         <f t="shared" si="36"/>
         <v>0</v>
       </c>
-      <c r="H162" s="44"/>
+      <c r="H162" s="43"/>
       <c r="I162" s="44"/>
       <c r="J162" s="54"/>
       <c r="K162" s="48"/>
@@ -11948,8 +12256,9 @@
         <v/>
       </c>
       <c r="AA162" s="64"/>
-    </row>
-    <row r="163" spans="1:27">
+      <c r="AB162" s="94"/>
+    </row>
+    <row r="163" spans="1:28">
       <c r="A163" s="62" t="str">
         <f t="shared" si="34"/>
         <v/>
@@ -11966,7 +12275,7 @@
         <f t="shared" si="36"/>
         <v>0</v>
       </c>
-      <c r="H163" s="44"/>
+      <c r="H163" s="43"/>
       <c r="I163" s="44"/>
       <c r="J163" s="54"/>
       <c r="K163" s="48"/>
@@ -12007,8 +12316,9 @@
         <v/>
       </c>
       <c r="AA163" s="64"/>
-    </row>
-    <row r="164" spans="1:27">
+      <c r="AB163" s="94"/>
+    </row>
+    <row r="164" spans="1:28">
       <c r="A164" s="62" t="str">
         <f t="shared" si="34"/>
         <v/>
@@ -12025,7 +12335,7 @@
         <f t="shared" si="36"/>
         <v>0</v>
       </c>
-      <c r="H164" s="44"/>
+      <c r="H164" s="43"/>
       <c r="I164" s="44"/>
       <c r="J164" s="54"/>
       <c r="K164" s="48"/>
@@ -12066,8 +12376,9 @@
         <v/>
       </c>
       <c r="AA164" s="64"/>
-    </row>
-    <row r="165" spans="1:27">
+      <c r="AB164" s="94"/>
+    </row>
+    <row r="165" spans="1:28">
       <c r="A165" s="62" t="str">
         <f t="shared" ref="A165:A196" si="43">IF(B165="","","LOC-"&amp;TEXT(ROW()-5,"000"))</f>
         <v/>
@@ -12084,7 +12395,7 @@
         <f t="shared" ref="G165:G196" si="45">IF(OR(B165="",E165=0,F165=""),0,E165*F165)</f>
         <v>0</v>
       </c>
-      <c r="H165" s="44"/>
+      <c r="H165" s="43"/>
       <c r="I165" s="44"/>
       <c r="J165" s="54"/>
       <c r="K165" s="48"/>
@@ -12125,8 +12436,9 @@
         <v/>
       </c>
       <c r="AA165" s="64"/>
-    </row>
-    <row r="166" spans="1:27">
+      <c r="AB165" s="94"/>
+    </row>
+    <row r="166" spans="1:28">
       <c r="A166" s="62" t="str">
         <f t="shared" si="43"/>
         <v/>
@@ -12143,7 +12455,7 @@
         <f t="shared" si="45"/>
         <v>0</v>
       </c>
-      <c r="H166" s="44"/>
+      <c r="H166" s="43"/>
       <c r="I166" s="44"/>
       <c r="J166" s="54"/>
       <c r="K166" s="48"/>
@@ -12180,12 +12492,13 @@
         <v>0</v>
       </c>
       <c r="Z166" s="49" t="str">
-        <f t="shared" ref="Z166:Z197" si="50">IF(B166="","",IF(COUNTIFS($C$6:$C$204,"&lt;"&amp;D166,$D$6:$D$204,"&gt;"&amp;C166,$I$6:$I$204,"&lt;&gt;Cancelada",$I$6:$I$204,"&lt;&gt;Consulta")&gt;1,"CONFLITO","OK"))</f>
+        <f t="shared" ref="Z166:Z197" si="50">IF(B166="","",IF(COUNTIFS($C$6:$C$204,"&lt;"&amp;D166,$D$6:$D$204,"&gt;"&amp;C166,$I$6:$I$204,"&lt;&gt;Cancelada",$I$6:$I$204,"&lt;&gt;Consulta",$AB$6:$AB$204,$AB166)&gt;1,"CONFLITO","OK"))</f>
         <v/>
       </c>
       <c r="AA166" s="64"/>
-    </row>
-    <row r="167" spans="1:27">
+      <c r="AB166" s="94"/>
+    </row>
+    <row r="167" spans="1:28">
       <c r="A167" s="62" t="str">
         <f t="shared" si="43"/>
         <v/>
@@ -12202,7 +12515,7 @@
         <f t="shared" si="45"/>
         <v>0</v>
       </c>
-      <c r="H167" s="44"/>
+      <c r="H167" s="43"/>
       <c r="I167" s="44"/>
       <c r="J167" s="54"/>
       <c r="K167" s="48"/>
@@ -12243,8 +12556,9 @@
         <v/>
       </c>
       <c r="AA167" s="64"/>
-    </row>
-    <row r="168" spans="1:27">
+      <c r="AB167" s="94"/>
+    </row>
+    <row r="168" spans="1:28">
       <c r="A168" s="62" t="str">
         <f t="shared" si="43"/>
         <v/>
@@ -12261,7 +12575,7 @@
         <f t="shared" si="45"/>
         <v>0</v>
       </c>
-      <c r="H168" s="44"/>
+      <c r="H168" s="43"/>
       <c r="I168" s="44"/>
       <c r="J168" s="54"/>
       <c r="K168" s="48"/>
@@ -12302,8 +12616,9 @@
         <v/>
       </c>
       <c r="AA168" s="64"/>
-    </row>
-    <row r="169" spans="1:27">
+      <c r="AB168" s="94"/>
+    </row>
+    <row r="169" spans="1:28">
       <c r="A169" s="62" t="str">
         <f t="shared" si="43"/>
         <v/>
@@ -12320,7 +12635,7 @@
         <f t="shared" si="45"/>
         <v>0</v>
       </c>
-      <c r="H169" s="44"/>
+      <c r="H169" s="43"/>
       <c r="I169" s="44"/>
       <c r="J169" s="54"/>
       <c r="K169" s="48"/>
@@ -12361,8 +12676,9 @@
         <v/>
       </c>
       <c r="AA169" s="64"/>
-    </row>
-    <row r="170" spans="1:27">
+      <c r="AB169" s="94"/>
+    </row>
+    <row r="170" spans="1:28">
       <c r="A170" s="62" t="str">
         <f t="shared" si="43"/>
         <v/>
@@ -12379,7 +12695,7 @@
         <f t="shared" si="45"/>
         <v>0</v>
       </c>
-      <c r="H170" s="44"/>
+      <c r="H170" s="43"/>
       <c r="I170" s="44"/>
       <c r="J170" s="54"/>
       <c r="K170" s="48"/>
@@ -12420,8 +12736,9 @@
         <v/>
       </c>
       <c r="AA170" s="64"/>
-    </row>
-    <row r="171" spans="1:27">
+      <c r="AB170" s="94"/>
+    </row>
+    <row r="171" spans="1:28">
       <c r="A171" s="62" t="str">
         <f t="shared" si="43"/>
         <v/>
@@ -12438,7 +12755,7 @@
         <f t="shared" si="45"/>
         <v>0</v>
       </c>
-      <c r="H171" s="44"/>
+      <c r="H171" s="43"/>
       <c r="I171" s="44"/>
       <c r="J171" s="54"/>
       <c r="K171" s="48"/>
@@ -12479,8 +12796,9 @@
         <v/>
       </c>
       <c r="AA171" s="64"/>
-    </row>
-    <row r="172" spans="1:27">
+      <c r="AB171" s="94"/>
+    </row>
+    <row r="172" spans="1:28">
       <c r="A172" s="62" t="str">
         <f t="shared" si="43"/>
         <v/>
@@ -12497,7 +12815,7 @@
         <f t="shared" si="45"/>
         <v>0</v>
       </c>
-      <c r="H172" s="44"/>
+      <c r="H172" s="43"/>
       <c r="I172" s="44"/>
       <c r="J172" s="54"/>
       <c r="K172" s="48"/>
@@ -12538,8 +12856,9 @@
         <v/>
       </c>
       <c r="AA172" s="64"/>
-    </row>
-    <row r="173" spans="1:27">
+      <c r="AB172" s="94"/>
+    </row>
+    <row r="173" spans="1:28">
       <c r="A173" s="62" t="str">
         <f t="shared" si="43"/>
         <v/>
@@ -12556,7 +12875,7 @@
         <f t="shared" si="45"/>
         <v>0</v>
       </c>
-      <c r="H173" s="44"/>
+      <c r="H173" s="43"/>
       <c r="I173" s="44"/>
       <c r="J173" s="54"/>
       <c r="K173" s="48"/>
@@ -12597,8 +12916,9 @@
         <v/>
       </c>
       <c r="AA173" s="64"/>
-    </row>
-    <row r="174" spans="1:27">
+      <c r="AB173" s="94"/>
+    </row>
+    <row r="174" spans="1:28">
       <c r="A174" s="62" t="str">
         <f t="shared" si="43"/>
         <v/>
@@ -12615,7 +12935,7 @@
         <f t="shared" si="45"/>
         <v>0</v>
       </c>
-      <c r="H174" s="44"/>
+      <c r="H174" s="43"/>
       <c r="I174" s="44"/>
       <c r="J174" s="54"/>
       <c r="K174" s="48"/>
@@ -12656,8 +12976,9 @@
         <v/>
       </c>
       <c r="AA174" s="64"/>
-    </row>
-    <row r="175" spans="1:27">
+      <c r="AB174" s="94"/>
+    </row>
+    <row r="175" spans="1:28">
       <c r="A175" s="62" t="str">
         <f t="shared" si="43"/>
         <v/>
@@ -12674,7 +12995,7 @@
         <f t="shared" si="45"/>
         <v>0</v>
       </c>
-      <c r="H175" s="44"/>
+      <c r="H175" s="43"/>
       <c r="I175" s="44"/>
       <c r="J175" s="54"/>
       <c r="K175" s="48"/>
@@ -12715,8 +13036,9 @@
         <v/>
       </c>
       <c r="AA175" s="64"/>
-    </row>
-    <row r="176" spans="1:27">
+      <c r="AB175" s="94"/>
+    </row>
+    <row r="176" spans="1:28">
       <c r="A176" s="62" t="str">
         <f t="shared" si="43"/>
         <v/>
@@ -12733,7 +13055,7 @@
         <f t="shared" si="45"/>
         <v>0</v>
       </c>
-      <c r="H176" s="44"/>
+      <c r="H176" s="43"/>
       <c r="I176" s="44"/>
       <c r="J176" s="54"/>
       <c r="K176" s="48"/>
@@ -12774,8 +13096,9 @@
         <v/>
       </c>
       <c r="AA176" s="64"/>
-    </row>
-    <row r="177" spans="1:27">
+      <c r="AB176" s="94"/>
+    </row>
+    <row r="177" spans="1:28">
       <c r="A177" s="62" t="str">
         <f t="shared" si="43"/>
         <v/>
@@ -12792,7 +13115,7 @@
         <f t="shared" si="45"/>
         <v>0</v>
       </c>
-      <c r="H177" s="44"/>
+      <c r="H177" s="43"/>
       <c r="I177" s="44"/>
       <c r="J177" s="54"/>
       <c r="K177" s="48"/>
@@ -12833,8 +13156,9 @@
         <v/>
       </c>
       <c r="AA177" s="64"/>
-    </row>
-    <row r="178" spans="1:27">
+      <c r="AB177" s="94"/>
+    </row>
+    <row r="178" spans="1:28">
       <c r="A178" s="62" t="str">
         <f t="shared" si="43"/>
         <v/>
@@ -12851,7 +13175,7 @@
         <f t="shared" si="45"/>
         <v>0</v>
       </c>
-      <c r="H178" s="44"/>
+      <c r="H178" s="43"/>
       <c r="I178" s="44"/>
       <c r="J178" s="54"/>
       <c r="K178" s="48"/>
@@ -12892,8 +13216,9 @@
         <v/>
       </c>
       <c r="AA178" s="64"/>
-    </row>
-    <row r="179" spans="1:27">
+      <c r="AB178" s="94"/>
+    </row>
+    <row r="179" spans="1:28">
       <c r="A179" s="62" t="str">
         <f t="shared" si="43"/>
         <v/>
@@ -12910,7 +13235,7 @@
         <f t="shared" si="45"/>
         <v>0</v>
       </c>
-      <c r="H179" s="44"/>
+      <c r="H179" s="43"/>
       <c r="I179" s="44"/>
       <c r="J179" s="54"/>
       <c r="K179" s="48"/>
@@ -12951,8 +13276,9 @@
         <v/>
       </c>
       <c r="AA179" s="64"/>
-    </row>
-    <row r="180" spans="1:27">
+      <c r="AB179" s="94"/>
+    </row>
+    <row r="180" spans="1:28">
       <c r="A180" s="62" t="str">
         <f t="shared" si="43"/>
         <v/>
@@ -12969,7 +13295,7 @@
         <f t="shared" si="45"/>
         <v>0</v>
       </c>
-      <c r="H180" s="44"/>
+      <c r="H180" s="43"/>
       <c r="I180" s="44"/>
       <c r="J180" s="54"/>
       <c r="K180" s="48"/>
@@ -13010,8 +13336,9 @@
         <v/>
       </c>
       <c r="AA180" s="64"/>
-    </row>
-    <row r="181" spans="1:27">
+      <c r="AB180" s="94"/>
+    </row>
+    <row r="181" spans="1:28">
       <c r="A181" s="62" t="str">
         <f t="shared" si="43"/>
         <v/>
@@ -13028,7 +13355,7 @@
         <f t="shared" si="45"/>
         <v>0</v>
       </c>
-      <c r="H181" s="44"/>
+      <c r="H181" s="43"/>
       <c r="I181" s="44"/>
       <c r="J181" s="54"/>
       <c r="K181" s="48"/>
@@ -13069,8 +13396,9 @@
         <v/>
       </c>
       <c r="AA181" s="64"/>
-    </row>
-    <row r="182" spans="1:27">
+      <c r="AB181" s="94"/>
+    </row>
+    <row r="182" spans="1:28">
       <c r="A182" s="62" t="str">
         <f t="shared" si="43"/>
         <v/>
@@ -13087,7 +13415,7 @@
         <f t="shared" si="45"/>
         <v>0</v>
       </c>
-      <c r="H182" s="44"/>
+      <c r="H182" s="43"/>
       <c r="I182" s="44"/>
       <c r="J182" s="54"/>
       <c r="K182" s="48"/>
@@ -13128,8 +13456,9 @@
         <v/>
       </c>
       <c r="AA182" s="64"/>
-    </row>
-    <row r="183" spans="1:27">
+      <c r="AB182" s="94"/>
+    </row>
+    <row r="183" spans="1:28">
       <c r="A183" s="62" t="str">
         <f t="shared" si="43"/>
         <v/>
@@ -13146,7 +13475,7 @@
         <f t="shared" si="45"/>
         <v>0</v>
       </c>
-      <c r="H183" s="44"/>
+      <c r="H183" s="43"/>
       <c r="I183" s="44"/>
       <c r="J183" s="54"/>
       <c r="K183" s="48"/>
@@ -13187,8 +13516,9 @@
         <v/>
       </c>
       <c r="AA183" s="64"/>
-    </row>
-    <row r="184" spans="1:27">
+      <c r="AB183" s="94"/>
+    </row>
+    <row r="184" spans="1:28">
       <c r="A184" s="62" t="str">
         <f t="shared" si="43"/>
         <v/>
@@ -13205,7 +13535,7 @@
         <f t="shared" si="45"/>
         <v>0</v>
       </c>
-      <c r="H184" s="44"/>
+      <c r="H184" s="43"/>
       <c r="I184" s="44"/>
       <c r="J184" s="54"/>
       <c r="K184" s="48"/>
@@ -13246,8 +13576,9 @@
         <v/>
       </c>
       <c r="AA184" s="64"/>
-    </row>
-    <row r="185" spans="1:27">
+      <c r="AB184" s="94"/>
+    </row>
+    <row r="185" spans="1:28">
       <c r="A185" s="62" t="str">
         <f t="shared" si="43"/>
         <v/>
@@ -13264,7 +13595,7 @@
         <f t="shared" si="45"/>
         <v>0</v>
       </c>
-      <c r="H185" s="44"/>
+      <c r="H185" s="43"/>
       <c r="I185" s="44"/>
       <c r="J185" s="54"/>
       <c r="K185" s="48"/>
@@ -13305,8 +13636,9 @@
         <v/>
       </c>
       <c r="AA185" s="64"/>
-    </row>
-    <row r="186" spans="1:27">
+      <c r="AB185" s="94"/>
+    </row>
+    <row r="186" spans="1:28">
       <c r="A186" s="62" t="str">
         <f t="shared" si="43"/>
         <v/>
@@ -13323,7 +13655,7 @@
         <f t="shared" si="45"/>
         <v>0</v>
       </c>
-      <c r="H186" s="44"/>
+      <c r="H186" s="43"/>
       <c r="I186" s="44"/>
       <c r="J186" s="54"/>
       <c r="K186" s="48"/>
@@ -13364,8 +13696,9 @@
         <v/>
       </c>
       <c r="AA186" s="64"/>
-    </row>
-    <row r="187" spans="1:27">
+      <c r="AB186" s="94"/>
+    </row>
+    <row r="187" spans="1:28">
       <c r="A187" s="62" t="str">
         <f t="shared" si="43"/>
         <v/>
@@ -13382,7 +13715,7 @@
         <f t="shared" si="45"/>
         <v>0</v>
       </c>
-      <c r="H187" s="44"/>
+      <c r="H187" s="43"/>
       <c r="I187" s="44"/>
       <c r="J187" s="54"/>
       <c r="K187" s="48"/>
@@ -13423,8 +13756,9 @@
         <v/>
       </c>
       <c r="AA187" s="64"/>
-    </row>
-    <row r="188" spans="1:27">
+      <c r="AB187" s="94"/>
+    </row>
+    <row r="188" spans="1:28">
       <c r="A188" s="62" t="str">
         <f t="shared" si="43"/>
         <v/>
@@ -13441,7 +13775,7 @@
         <f t="shared" si="45"/>
         <v>0</v>
       </c>
-      <c r="H188" s="44"/>
+      <c r="H188" s="43"/>
       <c r="I188" s="44"/>
       <c r="J188" s="54"/>
       <c r="K188" s="48"/>
@@ -13482,8 +13816,9 @@
         <v/>
       </c>
       <c r="AA188" s="64"/>
-    </row>
-    <row r="189" spans="1:27">
+      <c r="AB188" s="94"/>
+    </row>
+    <row r="189" spans="1:28">
       <c r="A189" s="62" t="str">
         <f t="shared" si="43"/>
         <v/>
@@ -13500,7 +13835,7 @@
         <f t="shared" si="45"/>
         <v>0</v>
       </c>
-      <c r="H189" s="44"/>
+      <c r="H189" s="43"/>
       <c r="I189" s="44"/>
       <c r="J189" s="54"/>
       <c r="K189" s="48"/>
@@ -13541,8 +13876,9 @@
         <v/>
       </c>
       <c r="AA189" s="64"/>
-    </row>
-    <row r="190" spans="1:27">
+      <c r="AB189" s="94"/>
+    </row>
+    <row r="190" spans="1:28">
       <c r="A190" s="62" t="str">
         <f t="shared" si="43"/>
         <v/>
@@ -13559,7 +13895,7 @@
         <f t="shared" si="45"/>
         <v>0</v>
       </c>
-      <c r="H190" s="44"/>
+      <c r="H190" s="43"/>
       <c r="I190" s="44"/>
       <c r="J190" s="54"/>
       <c r="K190" s="48"/>
@@ -13600,8 +13936,9 @@
         <v/>
       </c>
       <c r="AA190" s="64"/>
-    </row>
-    <row r="191" spans="1:27">
+      <c r="AB190" s="94"/>
+    </row>
+    <row r="191" spans="1:28">
       <c r="A191" s="62" t="str">
         <f t="shared" si="43"/>
         <v/>
@@ -13618,7 +13955,7 @@
         <f t="shared" si="45"/>
         <v>0</v>
       </c>
-      <c r="H191" s="44"/>
+      <c r="H191" s="43"/>
       <c r="I191" s="44"/>
       <c r="J191" s="54"/>
       <c r="K191" s="48"/>
@@ -13659,8 +13996,9 @@
         <v/>
       </c>
       <c r="AA191" s="64"/>
-    </row>
-    <row r="192" spans="1:27">
+      <c r="AB191" s="94"/>
+    </row>
+    <row r="192" spans="1:28">
       <c r="A192" s="62" t="str">
         <f t="shared" si="43"/>
         <v/>
@@ -13677,7 +14015,7 @@
         <f t="shared" si="45"/>
         <v>0</v>
       </c>
-      <c r="H192" s="44"/>
+      <c r="H192" s="43"/>
       <c r="I192" s="44"/>
       <c r="J192" s="54"/>
       <c r="K192" s="48"/>
@@ -13718,8 +14056,9 @@
         <v/>
       </c>
       <c r="AA192" s="64"/>
-    </row>
-    <row r="193" spans="1:27">
+      <c r="AB192" s="94"/>
+    </row>
+    <row r="193" spans="1:28">
       <c r="A193" s="62" t="str">
         <f t="shared" si="43"/>
         <v/>
@@ -13736,7 +14075,7 @@
         <f t="shared" si="45"/>
         <v>0</v>
       </c>
-      <c r="H193" s="44"/>
+      <c r="H193" s="43"/>
       <c r="I193" s="44"/>
       <c r="J193" s="54"/>
       <c r="K193" s="48"/>
@@ -13777,8 +14116,9 @@
         <v/>
       </c>
       <c r="AA193" s="64"/>
-    </row>
-    <row r="194" spans="1:27">
+      <c r="AB193" s="94"/>
+    </row>
+    <row r="194" spans="1:28">
       <c r="A194" s="62" t="str">
         <f t="shared" si="43"/>
         <v/>
@@ -13795,7 +14135,7 @@
         <f t="shared" si="45"/>
         <v>0</v>
       </c>
-      <c r="H194" s="44"/>
+      <c r="H194" s="43"/>
       <c r="I194" s="44"/>
       <c r="J194" s="54"/>
       <c r="K194" s="48"/>
@@ -13836,8 +14176,9 @@
         <v/>
       </c>
       <c r="AA194" s="64"/>
-    </row>
-    <row r="195" spans="1:27">
+      <c r="AB194" s="94"/>
+    </row>
+    <row r="195" spans="1:28">
       <c r="A195" s="62" t="str">
         <f t="shared" si="43"/>
         <v/>
@@ -13854,7 +14195,7 @@
         <f t="shared" si="45"/>
         <v>0</v>
       </c>
-      <c r="H195" s="44"/>
+      <c r="H195" s="43"/>
       <c r="I195" s="44"/>
       <c r="J195" s="54"/>
       <c r="K195" s="48"/>
@@ -13895,8 +14236,9 @@
         <v/>
       </c>
       <c r="AA195" s="64"/>
-    </row>
-    <row r="196" spans="1:27">
+      <c r="AB195" s="94"/>
+    </row>
+    <row r="196" spans="1:28">
       <c r="A196" s="62" t="str">
         <f t="shared" si="43"/>
         <v/>
@@ -13913,7 +14255,7 @@
         <f t="shared" si="45"/>
         <v>0</v>
       </c>
-      <c r="H196" s="44"/>
+      <c r="H196" s="43"/>
       <c r="I196" s="44"/>
       <c r="J196" s="54"/>
       <c r="K196" s="48"/>
@@ -13954,8 +14296,9 @@
         <v/>
       </c>
       <c r="AA196" s="64"/>
-    </row>
-    <row r="197" spans="1:27">
+      <c r="AB196" s="94"/>
+    </row>
+    <row r="197" spans="1:28">
       <c r="A197" s="62" t="str">
         <f t="shared" ref="A197:A204" si="51">IF(B197="","","LOC-"&amp;TEXT(ROW()-5,"000"))</f>
         <v/>
@@ -13972,7 +14315,7 @@
         <f t="shared" ref="G197:G204" si="53">IF(OR(B197="",E197=0,F197=""),0,E197*F197)</f>
         <v>0</v>
       </c>
-      <c r="H197" s="44"/>
+      <c r="H197" s="43"/>
       <c r="I197" s="44"/>
       <c r="J197" s="54"/>
       <c r="K197" s="48"/>
@@ -14013,8 +14356,9 @@
         <v/>
       </c>
       <c r="AA197" s="64"/>
-    </row>
-    <row r="198" spans="1:27">
+      <c r="AB197" s="94"/>
+    </row>
+    <row r="198" spans="1:28">
       <c r="A198" s="62" t="str">
         <f t="shared" si="51"/>
         <v/>
@@ -14031,7 +14375,7 @@
         <f t="shared" si="53"/>
         <v>0</v>
       </c>
-      <c r="H198" s="44"/>
+      <c r="H198" s="43"/>
       <c r="I198" s="44"/>
       <c r="J198" s="54"/>
       <c r="K198" s="48"/>
@@ -14068,12 +14412,13 @@
         <v>0</v>
       </c>
       <c r="Z198" s="49" t="str">
-        <f t="shared" ref="Z198:Z204" si="59">IF(B198="","",IF(COUNTIFS($C$6:$C$204,"&lt;"&amp;D198,$D$6:$D$204,"&gt;"&amp;C198,$I$6:$I$204,"&lt;&gt;Cancelada",$I$6:$I$204,"&lt;&gt;Consulta")&gt;1,"CONFLITO","OK"))</f>
+        <f t="shared" ref="Z198:Z204" si="59">IF(B198="","",IF(COUNTIFS($C$6:$C$204,"&lt;"&amp;D198,$D$6:$D$204,"&gt;"&amp;C198,$I$6:$I$204,"&lt;&gt;Cancelada",$I$6:$I$204,"&lt;&gt;Consulta",$AB$6:$AB$204,$AB198)&gt;1,"CONFLITO","OK"))</f>
         <v/>
       </c>
       <c r="AA198" s="64"/>
-    </row>
-    <row r="199" spans="1:27">
+      <c r="AB198" s="94"/>
+    </row>
+    <row r="199" spans="1:28">
       <c r="A199" s="62" t="str">
         <f t="shared" si="51"/>
         <v/>
@@ -14090,7 +14435,7 @@
         <f t="shared" si="53"/>
         <v>0</v>
       </c>
-      <c r="H199" s="44"/>
+      <c r="H199" s="43"/>
       <c r="I199" s="44"/>
       <c r="J199" s="54"/>
       <c r="K199" s="48"/>
@@ -14131,8 +14476,9 @@
         <v/>
       </c>
       <c r="AA199" s="64"/>
-    </row>
-    <row r="200" spans="1:27">
+      <c r="AB199" s="94"/>
+    </row>
+    <row r="200" spans="1:28">
       <c r="A200" s="62" t="str">
         <f t="shared" si="51"/>
         <v/>
@@ -14149,7 +14495,7 @@
         <f t="shared" si="53"/>
         <v>0</v>
       </c>
-      <c r="H200" s="44"/>
+      <c r="H200" s="43"/>
       <c r="I200" s="44"/>
       <c r="J200" s="54"/>
       <c r="K200" s="48"/>
@@ -14190,8 +14536,9 @@
         <v/>
       </c>
       <c r="AA200" s="64"/>
-    </row>
-    <row r="201" spans="1:27">
+      <c r="AB200" s="94"/>
+    </row>
+    <row r="201" spans="1:28">
       <c r="A201" s="62" t="str">
         <f t="shared" si="51"/>
         <v/>
@@ -14208,7 +14555,7 @@
         <f t="shared" si="53"/>
         <v>0</v>
       </c>
-      <c r="H201" s="44"/>
+      <c r="H201" s="43"/>
       <c r="I201" s="44"/>
       <c r="J201" s="54"/>
       <c r="K201" s="48"/>
@@ -14249,8 +14596,9 @@
         <v/>
       </c>
       <c r="AA201" s="64"/>
-    </row>
-    <row r="202" spans="1:27">
+      <c r="AB201" s="94"/>
+    </row>
+    <row r="202" spans="1:28">
       <c r="A202" s="62" t="str">
         <f t="shared" si="51"/>
         <v/>
@@ -14267,7 +14615,7 @@
         <f t="shared" si="53"/>
         <v>0</v>
       </c>
-      <c r="H202" s="44"/>
+      <c r="H202" s="43"/>
       <c r="I202" s="44"/>
       <c r="J202" s="54"/>
       <c r="K202" s="48"/>
@@ -14308,8 +14656,9 @@
         <v/>
       </c>
       <c r="AA202" s="64"/>
-    </row>
-    <row r="203" spans="1:27">
+      <c r="AB202" s="94"/>
+    </row>
+    <row r="203" spans="1:28">
       <c r="A203" s="62" t="str">
         <f t="shared" si="51"/>
         <v/>
@@ -14326,7 +14675,7 @@
         <f t="shared" si="53"/>
         <v>0</v>
       </c>
-      <c r="H203" s="44"/>
+      <c r="H203" s="43"/>
       <c r="I203" s="44"/>
       <c r="J203" s="54"/>
       <c r="K203" s="48"/>
@@ -14367,8 +14716,9 @@
         <v/>
       </c>
       <c r="AA203" s="64"/>
-    </row>
-    <row r="204" spans="1:27">
+      <c r="AB203" s="94"/>
+    </row>
+    <row r="204" spans="1:28">
       <c r="A204" s="65" t="str">
         <f t="shared" si="51"/>
         <v/>
@@ -14385,7 +14735,7 @@
         <f t="shared" si="53"/>
         <v>0</v>
       </c>
-      <c r="H204" s="66"/>
+      <c r="H204" s="43"/>
       <c r="I204" s="66"/>
       <c r="J204" s="54"/>
       <c r="K204" s="69"/>
@@ -14426,6 +14776,7 @@
         <v/>
       </c>
       <c r="AA204" s="73"/>
+      <c r="AB204" s="94"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -14433,48 +14784,55 @@
     <mergeCell ref="A3:AA3"/>
   </mergeCells>
   <conditionalFormatting sqref="U6:U64">
-    <cfRule type="cellIs" dxfId="4" priority="4" operator="lessThan">
+    <cfRule type="cellIs" dxfId="3" priority="4" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y6:Y204">
-    <cfRule type="expression" dxfId="3" priority="3">
+    <cfRule type="expression" dxfId="2" priority="3">
       <formula>Y6&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Z6:Z64">
-    <cfRule type="expression" dxfId="2" priority="1">
+    <cfRule type="expression" dxfId="1" priority="1">
       <formula>Z6="CONFLITO"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="1" priority="2">
+    <cfRule type="expression" dxfId="0" priority="2">
       <formula>Z6="OK"</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="5">
-    <dataValidation type="list" sqref="H6:H204" xr:uid="{00000000-0002-0000-0200-000000000000}">
+  <dataValidations count="7">
+    <dataValidation type="list" sqref="H6:H9" xr:uid="{00000000-0002-0000-0200-000000000000}">
       <formula1>"Normal,Férias escolares,Feriado,Natal,Réveillon,Natal / Réveillon,Carnaval,Páscoa,Temporada de verão,Final de semana prolongado,Evento local,Outro"</formula1>
     </dataValidation>
     <dataValidation type="list" sqref="I6:I204" xr:uid="{00000000-0002-0000-0200-000001000000}">
       <formula1>"Consulta,Pré-reserva,Confirmada,Concluída,Cancelada"</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="DATA DE ENTRADA INDISPONÍVEL" error="Esta data coincide ou está dentro de outra reserva, inclusive no dia de saída. Escolha outra data." promptTitle="Entrada da reserva" prompt="Escolha uma data livre. Dias já comprometidos, inclusive check-out de outra reserva, são bloqueados." sqref="C6:C204" xr:uid="{00000000-0002-0000-0200-000006000000}">
-      <formula1>OR(C6="",SUMPRODUCT(($C$6:$C$204&lt;=C6)*($D$6:$D$204&gt;=C6)*($I$6:$I$204&lt;&gt;"Cancelada")*($I$6:$I$204&lt;&gt;"Consulta")*(ROW($C$6:$C$204)&lt;&gt;ROW()))=0)</formula1>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Conflito de agenda" error="Esta data coincide com outra reserva do mesmo imóvel. Escolha outra data ou selecione o imóvel correto." promptTitle="Entrada da reserva" prompt="Escolha uma data livre. Dias já comprometidos, inclusive check-out de outra reserva, são bloqueados." sqref="C6:C204" xr:uid="{00000000-0002-0000-0200-000002000000}">
+      <formula1>OR(C6="",SUMPRODUCT(($C$6:$C$204&lt;=C6)*($D$6:$D$204&gt;=C6)*($I$6:$I$204&lt;&gt;"Cancelada")*($I$6:$I$204&lt;&gt;"Consulta")*(IF($AB$6:$AB$204="","Casa Cinza",$AB$6:$AB$204)=IF($AB6="","Casa Cinza",$AB6))*(ROW($C$6:$C$204)&lt;&gt;ROW()))=0)</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="PERÍODO INDISPONÍVEL" error="A saída deve ser posterior à entrada e o período inteiro precisa estar livre, sem coincidir com outra reserva." promptTitle="Saída da reserva" prompt="Informe uma saída posterior à entrada. O período não pode sobrepor nenhuma reserva existente." sqref="D6:D204" xr:uid="{00000000-0002-0000-0200-000007000000}">
-      <formula1>OR(D6="",AND(C6&lt;&gt;"",D6&gt;C6,SUMPRODUCT(($C$6:$C$204&lt;=D6)*($D$6:$D$204&gt;=C6)*($I$6:$I$204&lt;&gt;"Cancelada")*($I$6:$I$204&lt;&gt;"Consulta")*(ROW($C$6:$C$204)&lt;&gt;ROW()))=0))</formula1>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Conflito de agenda" error="Esta data coincide com outra reserva do mesmo imóvel. Escolha outra data ou selecione o imóvel correto." promptTitle="Saída da reserva" prompt="Informe uma saída posterior à entrada. O período não pode sobrepor nenhuma reserva existente." sqref="D6:D204" xr:uid="{00000000-0002-0000-0200-000003000000}">
+      <formula1>OR(D6="",AND(C6&lt;&gt;"",D6&gt;C6,SUMPRODUCT(($C$6:$C$204&lt;=D6)*($D$6:$D$204&gt;=C6)*($I$6:$I$204&lt;&gt;"Cancelada")*($I$6:$I$204&lt;&gt;"Consulta")*(IF($AB$6:$AB$204="","Casa Cinza",$AB$6:$AB$204)=IF($AB6="","Casa Cinza",$AB6))*(ROW($C$6:$C$204)&lt;&gt;ROW()))=0))</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="J6:J204" xr:uid="{B22C96CE-7948-45F7-BCA7-CAA02DD8F23B}">
+    <dataValidation type="list" sqref="J6:J204" xr:uid="{00000000-0002-0000-0200-000004000000}">
       <formula1>"Direto,Airbnb,Booking,Imobiliária,Indicação,Cortesia,Outro"</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="AB6:AB204" xr:uid="{00000000-0002-0000-0200-000005000000}">
+      <formula1>"Casa Cinza,Casa Laranja"</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="H10:H204" xr:uid="{315E0772-C836-474B-A702-0BAA8E4361DE}">
+      <formula1>"Normal,Férias,Feriado,Natal,Réveillon,Natal / Réveillon,Carnaval,Páscoa,Temporada de verão,Final de semana prolongado,Evento local,Outro"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId1"/>
+  <drawing r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:F305"/>
+  <dimension ref="A1:G305"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
@@ -14483,2528 +14841,2818 @@
     <col min="4" max="4" width="15" customWidth="1"/>
     <col min="5" max="5" width="21" customWidth="1"/>
     <col min="6" max="6" width="34" customWidth="1"/>
+    <col min="7" max="7" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="24" customHeight="1">
-      <c r="A1" s="93" t="s">
-        <v>85</v>
-      </c>
-      <c r="B1" s="93"/>
-      <c r="C1" s="93"/>
-      <c r="D1" s="93"/>
-      <c r="E1" s="93"/>
-      <c r="F1" s="93"/>
-    </row>
-    <row r="3" spans="1:6" ht="27.2" customHeight="1">
-      <c r="A3" s="94" t="s">
-        <v>86</v>
-      </c>
-      <c r="B3" s="94"/>
-      <c r="C3" s="94"/>
-      <c r="D3" s="94"/>
-      <c r="E3" s="94"/>
-      <c r="F3" s="94"/>
-    </row>
-    <row r="5" spans="1:6" ht="24" customHeight="1">
+    <row r="1" spans="1:7" ht="24" customHeight="1">
+      <c r="A1" s="96" t="s">
+        <v>91</v>
+      </c>
+      <c r="B1" s="96"/>
+      <c r="C1" s="96"/>
+      <c r="D1" s="96"/>
+      <c r="E1" s="96"/>
+      <c r="F1" s="96"/>
+    </row>
+    <row r="3" spans="1:7" ht="27.2" customHeight="1">
+      <c r="A3" s="99" t="s">
+        <v>92</v>
+      </c>
+      <c r="B3" s="99"/>
+      <c r="C3" s="99"/>
+      <c r="D3" s="99"/>
+      <c r="E3" s="99"/>
+      <c r="F3" s="99"/>
+    </row>
+    <row r="5" spans="1:7" ht="24" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
+        <v>79</v>
+      </c>
+      <c r="G5" s="93" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
       <c r="A6" s="75"/>
       <c r="B6" s="54" t="s">
-        <v>115</v>
+        <v>98</v>
       </c>
       <c r="C6" s="54"/>
       <c r="D6" s="81"/>
       <c r="E6" s="54" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="F6" s="76"/>
-    </row>
-    <row r="7" spans="1:6">
+      <c r="G6" s="94" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
       <c r="A7" s="77"/>
       <c r="B7" s="43"/>
       <c r="C7" s="43"/>
       <c r="D7" s="82"/>
       <c r="E7" s="43"/>
       <c r="F7" s="78"/>
-    </row>
-    <row r="8" spans="1:6">
+      <c r="G7" s="94"/>
+    </row>
+    <row r="8" spans="1:7">
       <c r="A8" s="77"/>
       <c r="B8" s="43"/>
       <c r="C8" s="43"/>
       <c r="D8" s="82"/>
       <c r="E8" s="43"/>
       <c r="F8" s="78"/>
-    </row>
-    <row r="9" spans="1:6">
+      <c r="G8" s="94"/>
+    </row>
+    <row r="9" spans="1:7">
       <c r="A9" s="77"/>
       <c r="B9" s="43"/>
       <c r="C9" s="43"/>
       <c r="D9" s="82"/>
       <c r="E9" s="43"/>
       <c r="F9" s="78"/>
-    </row>
-    <row r="10" spans="1:6">
+      <c r="G9" s="94"/>
+    </row>
+    <row r="10" spans="1:7">
       <c r="A10" s="77"/>
       <c r="B10" s="43"/>
       <c r="C10" s="43"/>
       <c r="D10" s="82"/>
       <c r="E10" s="43"/>
       <c r="F10" s="78"/>
-    </row>
-    <row r="11" spans="1:6">
+      <c r="G10" s="94"/>
+    </row>
+    <row r="11" spans="1:7">
       <c r="A11" s="77"/>
       <c r="B11" s="43"/>
       <c r="C11" s="43"/>
       <c r="D11" s="82"/>
       <c r="E11" s="43"/>
       <c r="F11" s="78"/>
-    </row>
-    <row r="12" spans="1:6">
+      <c r="G11" s="94"/>
+    </row>
+    <row r="12" spans="1:7">
       <c r="A12" s="77"/>
       <c r="B12" s="43"/>
       <c r="C12" s="43"/>
       <c r="D12" s="82"/>
       <c r="E12" s="43"/>
       <c r="F12" s="78"/>
-    </row>
-    <row r="13" spans="1:6">
+      <c r="G12" s="94"/>
+    </row>
+    <row r="13" spans="1:7">
       <c r="A13" s="77"/>
       <c r="B13" s="43"/>
       <c r="C13" s="43"/>
       <c r="D13" s="82"/>
       <c r="E13" s="43"/>
       <c r="F13" s="78"/>
-    </row>
-    <row r="14" spans="1:6">
+      <c r="G13" s="94"/>
+    </row>
+    <row r="14" spans="1:7">
       <c r="A14" s="77"/>
       <c r="B14" s="43"/>
       <c r="C14" s="43"/>
       <c r="D14" s="82"/>
       <c r="E14" s="43"/>
       <c r="F14" s="78"/>
-    </row>
-    <row r="15" spans="1:6">
+      <c r="G14" s="94"/>
+    </row>
+    <row r="15" spans="1:7">
       <c r="A15" s="77"/>
       <c r="B15" s="43"/>
       <c r="C15" s="43"/>
       <c r="D15" s="82"/>
       <c r="E15" s="43"/>
       <c r="F15" s="78"/>
-    </row>
-    <row r="16" spans="1:6">
+      <c r="G15" s="94"/>
+    </row>
+    <row r="16" spans="1:7">
       <c r="A16" s="77"/>
       <c r="B16" s="43"/>
       <c r="C16" s="43"/>
       <c r="D16" s="82"/>
       <c r="E16" s="43"/>
       <c r="F16" s="78"/>
-    </row>
-    <row r="17" spans="1:6">
+      <c r="G16" s="94"/>
+    </row>
+    <row r="17" spans="1:7">
       <c r="A17" s="77"/>
       <c r="B17" s="43"/>
       <c r="C17" s="43"/>
       <c r="D17" s="82"/>
       <c r="E17" s="43"/>
       <c r="F17" s="78"/>
-    </row>
-    <row r="18" spans="1:6">
+      <c r="G17" s="94"/>
+    </row>
+    <row r="18" spans="1:7">
       <c r="A18" s="77"/>
       <c r="B18" s="43"/>
       <c r="C18" s="43"/>
       <c r="D18" s="82"/>
       <c r="E18" s="43"/>
       <c r="F18" s="78"/>
-    </row>
-    <row r="19" spans="1:6">
+      <c r="G18" s="94"/>
+    </row>
+    <row r="19" spans="1:7">
       <c r="A19" s="77"/>
       <c r="B19" s="43"/>
       <c r="C19" s="43"/>
       <c r="D19" s="82"/>
       <c r="E19" s="43"/>
       <c r="F19" s="78"/>
-    </row>
-    <row r="20" spans="1:6">
+      <c r="G19" s="94"/>
+    </row>
+    <row r="20" spans="1:7">
       <c r="A20" s="77"/>
       <c r="B20" s="43"/>
       <c r="C20" s="43"/>
       <c r="D20" s="82"/>
       <c r="E20" s="43"/>
       <c r="F20" s="78"/>
-    </row>
-    <row r="21" spans="1:6">
+      <c r="G20" s="94"/>
+    </row>
+    <row r="21" spans="1:7">
       <c r="A21" s="77"/>
       <c r="B21" s="43"/>
       <c r="C21" s="43"/>
       <c r="D21" s="82"/>
       <c r="E21" s="43"/>
       <c r="F21" s="78"/>
-    </row>
-    <row r="22" spans="1:6">
+      <c r="G21" s="94"/>
+    </row>
+    <row r="22" spans="1:7">
       <c r="A22" s="77"/>
       <c r="B22" s="43"/>
       <c r="C22" s="43"/>
       <c r="D22" s="82"/>
       <c r="E22" s="43"/>
       <c r="F22" s="78"/>
-    </row>
-    <row r="23" spans="1:6">
+      <c r="G22" s="94"/>
+    </row>
+    <row r="23" spans="1:7">
       <c r="A23" s="77"/>
       <c r="B23" s="43"/>
       <c r="C23" s="43"/>
       <c r="D23" s="82"/>
       <c r="E23" s="43"/>
       <c r="F23" s="78"/>
-    </row>
-    <row r="24" spans="1:6">
+      <c r="G23" s="94"/>
+    </row>
+    <row r="24" spans="1:7">
       <c r="A24" s="77"/>
       <c r="B24" s="43"/>
       <c r="C24" s="43"/>
       <c r="D24" s="82"/>
       <c r="E24" s="43"/>
       <c r="F24" s="78"/>
-    </row>
-    <row r="25" spans="1:6">
+      <c r="G24" s="94"/>
+    </row>
+    <row r="25" spans="1:7">
       <c r="A25" s="77"/>
       <c r="B25" s="43"/>
       <c r="C25" s="43"/>
       <c r="D25" s="82"/>
       <c r="E25" s="43"/>
       <c r="F25" s="78"/>
-    </row>
-    <row r="26" spans="1:6">
+      <c r="G25" s="94"/>
+    </row>
+    <row r="26" spans="1:7">
       <c r="A26" s="77"/>
       <c r="B26" s="43"/>
       <c r="C26" s="43"/>
       <c r="D26" s="82"/>
       <c r="E26" s="43"/>
       <c r="F26" s="78"/>
-    </row>
-    <row r="27" spans="1:6">
+      <c r="G26" s="94"/>
+    </row>
+    <row r="27" spans="1:7">
       <c r="A27" s="77"/>
       <c r="B27" s="43"/>
       <c r="C27" s="43"/>
       <c r="D27" s="82"/>
       <c r="E27" s="43"/>
       <c r="F27" s="78"/>
-    </row>
-    <row r="28" spans="1:6">
+      <c r="G27" s="94"/>
+    </row>
+    <row r="28" spans="1:7">
       <c r="A28" s="77"/>
       <c r="B28" s="43"/>
       <c r="C28" s="43"/>
       <c r="D28" s="82"/>
       <c r="E28" s="43"/>
       <c r="F28" s="78"/>
-    </row>
-    <row r="29" spans="1:6">
+      <c r="G28" s="94"/>
+    </row>
+    <row r="29" spans="1:7">
       <c r="A29" s="77"/>
       <c r="B29" s="43"/>
       <c r="C29" s="43"/>
       <c r="D29" s="82"/>
       <c r="E29" s="43"/>
       <c r="F29" s="78"/>
-    </row>
-    <row r="30" spans="1:6">
+      <c r="G29" s="94"/>
+    </row>
+    <row r="30" spans="1:7">
       <c r="A30" s="77"/>
       <c r="B30" s="43"/>
       <c r="C30" s="43"/>
       <c r="D30" s="82"/>
       <c r="E30" s="43"/>
       <c r="F30" s="78"/>
-    </row>
-    <row r="31" spans="1:6">
+      <c r="G30" s="94"/>
+    </row>
+    <row r="31" spans="1:7">
       <c r="A31" s="77"/>
       <c r="B31" s="43"/>
       <c r="C31" s="43"/>
       <c r="D31" s="82"/>
       <c r="E31" s="43"/>
       <c r="F31" s="78"/>
-    </row>
-    <row r="32" spans="1:6">
+      <c r="G31" s="94"/>
+    </row>
+    <row r="32" spans="1:7">
       <c r="A32" s="77"/>
       <c r="B32" s="43"/>
       <c r="C32" s="43"/>
       <c r="D32" s="82"/>
       <c r="E32" s="43"/>
       <c r="F32" s="78"/>
-    </row>
-    <row r="33" spans="1:6">
+      <c r="G32" s="94"/>
+    </row>
+    <row r="33" spans="1:7">
       <c r="A33" s="77"/>
       <c r="B33" s="43"/>
       <c r="C33" s="43"/>
       <c r="D33" s="82"/>
       <c r="E33" s="43"/>
       <c r="F33" s="78"/>
-    </row>
-    <row r="34" spans="1:6">
+      <c r="G33" s="94"/>
+    </row>
+    <row r="34" spans="1:7">
       <c r="A34" s="77"/>
       <c r="B34" s="43"/>
       <c r="C34" s="43"/>
       <c r="D34" s="82"/>
       <c r="E34" s="43"/>
       <c r="F34" s="78"/>
-    </row>
-    <row r="35" spans="1:6">
+      <c r="G34" s="94"/>
+    </row>
+    <row r="35" spans="1:7">
       <c r="A35" s="77"/>
       <c r="B35" s="43"/>
       <c r="C35" s="43"/>
       <c r="D35" s="82"/>
       <c r="E35" s="43"/>
       <c r="F35" s="78"/>
-    </row>
-    <row r="36" spans="1:6">
+      <c r="G35" s="94"/>
+    </row>
+    <row r="36" spans="1:7">
       <c r="A36" s="77"/>
       <c r="B36" s="43"/>
       <c r="C36" s="43"/>
       <c r="D36" s="82"/>
       <c r="E36" s="43"/>
       <c r="F36" s="78"/>
-    </row>
-    <row r="37" spans="1:6">
+      <c r="G36" s="94"/>
+    </row>
+    <row r="37" spans="1:7">
       <c r="A37" s="77"/>
       <c r="B37" s="43"/>
       <c r="C37" s="43"/>
       <c r="D37" s="82"/>
       <c r="E37" s="43"/>
       <c r="F37" s="78"/>
-    </row>
-    <row r="38" spans="1:6">
+      <c r="G37" s="94"/>
+    </row>
+    <row r="38" spans="1:7">
       <c r="A38" s="77"/>
       <c r="B38" s="43"/>
       <c r="C38" s="43"/>
       <c r="D38" s="82"/>
       <c r="E38" s="43"/>
       <c r="F38" s="78"/>
-    </row>
-    <row r="39" spans="1:6">
+      <c r="G38" s="94"/>
+    </row>
+    <row r="39" spans="1:7">
       <c r="A39" s="77"/>
       <c r="B39" s="43"/>
       <c r="C39" s="43"/>
       <c r="D39" s="82"/>
       <c r="E39" s="43"/>
       <c r="F39" s="78"/>
-    </row>
-    <row r="40" spans="1:6">
+      <c r="G39" s="94"/>
+    </row>
+    <row r="40" spans="1:7">
       <c r="A40" s="77"/>
       <c r="B40" s="43"/>
       <c r="C40" s="43"/>
       <c r="D40" s="82"/>
       <c r="E40" s="43"/>
       <c r="F40" s="78"/>
-    </row>
-    <row r="41" spans="1:6">
+      <c r="G40" s="94"/>
+    </row>
+    <row r="41" spans="1:7">
       <c r="A41" s="77"/>
       <c r="B41" s="43"/>
       <c r="C41" s="43"/>
       <c r="D41" s="82"/>
       <c r="E41" s="43"/>
       <c r="F41" s="78"/>
-    </row>
-    <row r="42" spans="1:6">
+      <c r="G41" s="94"/>
+    </row>
+    <row r="42" spans="1:7">
       <c r="A42" s="77"/>
       <c r="B42" s="43"/>
       <c r="C42" s="43"/>
       <c r="D42" s="82"/>
       <c r="E42" s="43"/>
       <c r="F42" s="78"/>
-    </row>
-    <row r="43" spans="1:6">
+      <c r="G42" s="94"/>
+    </row>
+    <row r="43" spans="1:7">
       <c r="A43" s="77"/>
       <c r="B43" s="43"/>
       <c r="C43" s="43"/>
       <c r="D43" s="82"/>
       <c r="E43" s="43"/>
       <c r="F43" s="78"/>
-    </row>
-    <row r="44" spans="1:6">
+      <c r="G43" s="94"/>
+    </row>
+    <row r="44" spans="1:7">
       <c r="A44" s="77"/>
       <c r="B44" s="43"/>
       <c r="C44" s="43"/>
       <c r="D44" s="82"/>
       <c r="E44" s="43"/>
       <c r="F44" s="78"/>
-    </row>
-    <row r="45" spans="1:6">
+      <c r="G44" s="94"/>
+    </row>
+    <row r="45" spans="1:7">
       <c r="A45" s="77"/>
       <c r="B45" s="43"/>
       <c r="C45" s="43"/>
       <c r="D45" s="82"/>
       <c r="E45" s="43"/>
       <c r="F45" s="78"/>
-    </row>
-    <row r="46" spans="1:6">
+      <c r="G45" s="94"/>
+    </row>
+    <row r="46" spans="1:7">
       <c r="A46" s="77"/>
       <c r="B46" s="43"/>
       <c r="C46" s="43"/>
       <c r="D46" s="82"/>
       <c r="E46" s="43"/>
       <c r="F46" s="78"/>
-    </row>
-    <row r="47" spans="1:6">
+      <c r="G46" s="94"/>
+    </row>
+    <row r="47" spans="1:7">
       <c r="A47" s="77"/>
       <c r="B47" s="43"/>
       <c r="C47" s="43"/>
       <c r="D47" s="82"/>
       <c r="E47" s="43"/>
       <c r="F47" s="78"/>
-    </row>
-    <row r="48" spans="1:6">
+      <c r="G47" s="94"/>
+    </row>
+    <row r="48" spans="1:7">
       <c r="A48" s="77"/>
       <c r="B48" s="43"/>
       <c r="C48" s="43"/>
       <c r="D48" s="82"/>
       <c r="E48" s="43"/>
       <c r="F48" s="78"/>
-    </row>
-    <row r="49" spans="1:6">
+      <c r="G48" s="94"/>
+    </row>
+    <row r="49" spans="1:7">
       <c r="A49" s="77"/>
       <c r="B49" s="43"/>
       <c r="C49" s="43"/>
       <c r="D49" s="82"/>
       <c r="E49" s="43"/>
       <c r="F49" s="78"/>
-    </row>
-    <row r="50" spans="1:6">
+      <c r="G49" s="94"/>
+    </row>
+    <row r="50" spans="1:7">
       <c r="A50" s="77"/>
       <c r="B50" s="43"/>
       <c r="C50" s="43"/>
       <c r="D50" s="82"/>
       <c r="E50" s="43"/>
       <c r="F50" s="78"/>
-    </row>
-    <row r="51" spans="1:6">
+      <c r="G50" s="94"/>
+    </row>
+    <row r="51" spans="1:7">
       <c r="A51" s="77"/>
       <c r="B51" s="43"/>
       <c r="C51" s="43"/>
       <c r="D51" s="82"/>
       <c r="E51" s="43"/>
       <c r="F51" s="78"/>
-    </row>
-    <row r="52" spans="1:6">
+      <c r="G51" s="94"/>
+    </row>
+    <row r="52" spans="1:7">
       <c r="A52" s="77"/>
       <c r="B52" s="43"/>
       <c r="C52" s="43"/>
       <c r="D52" s="82"/>
       <c r="E52" s="43"/>
       <c r="F52" s="78"/>
-    </row>
-    <row r="53" spans="1:6">
+      <c r="G52" s="94"/>
+    </row>
+    <row r="53" spans="1:7">
       <c r="A53" s="77"/>
       <c r="B53" s="43"/>
       <c r="C53" s="43"/>
       <c r="D53" s="82"/>
       <c r="E53" s="43"/>
       <c r="F53" s="78"/>
-    </row>
-    <row r="54" spans="1:6">
+      <c r="G53" s="94"/>
+    </row>
+    <row r="54" spans="1:7">
       <c r="A54" s="77"/>
       <c r="B54" s="43"/>
       <c r="C54" s="43"/>
       <c r="D54" s="82"/>
       <c r="E54" s="43"/>
       <c r="F54" s="78"/>
-    </row>
-    <row r="55" spans="1:6">
+      <c r="G54" s="94"/>
+    </row>
+    <row r="55" spans="1:7">
       <c r="A55" s="77"/>
       <c r="B55" s="43"/>
       <c r="C55" s="43"/>
       <c r="D55" s="82"/>
       <c r="E55" s="43"/>
       <c r="F55" s="78"/>
-    </row>
-    <row r="56" spans="1:6">
+      <c r="G55" s="94"/>
+    </row>
+    <row r="56" spans="1:7">
       <c r="A56" s="77"/>
       <c r="B56" s="43"/>
       <c r="C56" s="43"/>
       <c r="D56" s="82"/>
       <c r="E56" s="43"/>
       <c r="F56" s="78"/>
-    </row>
-    <row r="57" spans="1:6">
+      <c r="G56" s="94"/>
+    </row>
+    <row r="57" spans="1:7">
       <c r="A57" s="77"/>
       <c r="B57" s="43"/>
       <c r="C57" s="43"/>
       <c r="D57" s="82"/>
       <c r="E57" s="43"/>
       <c r="F57" s="78"/>
-    </row>
-    <row r="58" spans="1:6">
+      <c r="G57" s="94"/>
+    </row>
+    <row r="58" spans="1:7">
       <c r="A58" s="77"/>
       <c r="B58" s="43"/>
       <c r="C58" s="43"/>
       <c r="D58" s="82"/>
       <c r="E58" s="43"/>
       <c r="F58" s="78"/>
-    </row>
-    <row r="59" spans="1:6">
+      <c r="G58" s="94"/>
+    </row>
+    <row r="59" spans="1:7">
       <c r="A59" s="77"/>
       <c r="B59" s="43"/>
       <c r="C59" s="43"/>
       <c r="D59" s="82"/>
       <c r="E59" s="43"/>
       <c r="F59" s="78"/>
-    </row>
-    <row r="60" spans="1:6">
+      <c r="G59" s="94"/>
+    </row>
+    <row r="60" spans="1:7">
       <c r="A60" s="77"/>
       <c r="B60" s="43"/>
       <c r="C60" s="43"/>
       <c r="D60" s="82"/>
       <c r="E60" s="43"/>
       <c r="F60" s="78"/>
-    </row>
-    <row r="61" spans="1:6">
+      <c r="G60" s="94"/>
+    </row>
+    <row r="61" spans="1:7">
       <c r="A61" s="77"/>
       <c r="B61" s="43"/>
       <c r="C61" s="43"/>
       <c r="D61" s="82"/>
       <c r="E61" s="43"/>
       <c r="F61" s="78"/>
-    </row>
-    <row r="62" spans="1:6">
+      <c r="G61" s="94"/>
+    </row>
+    <row r="62" spans="1:7">
       <c r="A62" s="77"/>
       <c r="B62" s="43"/>
       <c r="C62" s="43"/>
       <c r="D62" s="82"/>
       <c r="E62" s="43"/>
       <c r="F62" s="78"/>
-    </row>
-    <row r="63" spans="1:6">
+      <c r="G62" s="94"/>
+    </row>
+    <row r="63" spans="1:7">
       <c r="A63" s="77"/>
       <c r="B63" s="43"/>
       <c r="C63" s="43"/>
       <c r="D63" s="82"/>
       <c r="E63" s="43"/>
       <c r="F63" s="78"/>
-    </row>
-    <row r="64" spans="1:6">
+      <c r="G63" s="94"/>
+    </row>
+    <row r="64" spans="1:7">
       <c r="A64" s="77"/>
       <c r="B64" s="43"/>
       <c r="C64" s="43"/>
       <c r="D64" s="82"/>
       <c r="E64" s="43"/>
       <c r="F64" s="78"/>
-    </row>
-    <row r="65" spans="1:6">
+      <c r="G64" s="94"/>
+    </row>
+    <row r="65" spans="1:7">
       <c r="A65" s="77"/>
       <c r="B65" s="43"/>
       <c r="C65" s="43"/>
       <c r="D65" s="82"/>
       <c r="E65" s="43"/>
       <c r="F65" s="78"/>
-    </row>
-    <row r="66" spans="1:6">
+      <c r="G65" s="94"/>
+    </row>
+    <row r="66" spans="1:7">
       <c r="A66" s="77"/>
       <c r="B66" s="43"/>
       <c r="C66" s="43"/>
       <c r="D66" s="82"/>
       <c r="E66" s="43"/>
       <c r="F66" s="78"/>
-    </row>
-    <row r="67" spans="1:6">
+      <c r="G66" s="94"/>
+    </row>
+    <row r="67" spans="1:7">
       <c r="A67" s="77"/>
       <c r="B67" s="43"/>
       <c r="C67" s="43"/>
       <c r="D67" s="82"/>
       <c r="E67" s="43"/>
       <c r="F67" s="78"/>
-    </row>
-    <row r="68" spans="1:6">
+      <c r="G67" s="94"/>
+    </row>
+    <row r="68" spans="1:7">
       <c r="A68" s="77"/>
       <c r="B68" s="43"/>
       <c r="C68" s="43"/>
       <c r="D68" s="82"/>
       <c r="E68" s="43"/>
       <c r="F68" s="78"/>
-    </row>
-    <row r="69" spans="1:6">
+      <c r="G68" s="94"/>
+    </row>
+    <row r="69" spans="1:7">
       <c r="A69" s="77"/>
       <c r="B69" s="43"/>
       <c r="C69" s="43"/>
       <c r="D69" s="82"/>
       <c r="E69" s="43"/>
       <c r="F69" s="78"/>
-    </row>
-    <row r="70" spans="1:6">
+      <c r="G69" s="94"/>
+    </row>
+    <row r="70" spans="1:7">
       <c r="A70" s="77"/>
       <c r="B70" s="43"/>
       <c r="C70" s="43"/>
       <c r="D70" s="82"/>
       <c r="E70" s="43"/>
       <c r="F70" s="78"/>
-    </row>
-    <row r="71" spans="1:6">
+      <c r="G70" s="94"/>
+    </row>
+    <row r="71" spans="1:7">
       <c r="A71" s="77"/>
       <c r="B71" s="43"/>
       <c r="C71" s="43"/>
       <c r="D71" s="82"/>
       <c r="E71" s="43"/>
       <c r="F71" s="78"/>
-    </row>
-    <row r="72" spans="1:6">
+      <c r="G71" s="94"/>
+    </row>
+    <row r="72" spans="1:7">
       <c r="A72" s="77"/>
       <c r="B72" s="43"/>
       <c r="C72" s="43"/>
       <c r="D72" s="82"/>
       <c r="E72" s="43"/>
       <c r="F72" s="78"/>
-    </row>
-    <row r="73" spans="1:6">
+      <c r="G72" s="94"/>
+    </row>
+    <row r="73" spans="1:7">
       <c r="A73" s="77"/>
       <c r="B73" s="43"/>
       <c r="C73" s="43"/>
       <c r="D73" s="82"/>
       <c r="E73" s="43"/>
       <c r="F73" s="78"/>
-    </row>
-    <row r="74" spans="1:6">
+      <c r="G73" s="94"/>
+    </row>
+    <row r="74" spans="1:7">
       <c r="A74" s="77"/>
       <c r="B74" s="43"/>
       <c r="C74" s="43"/>
       <c r="D74" s="82"/>
       <c r="E74" s="43"/>
       <c r="F74" s="78"/>
-    </row>
-    <row r="75" spans="1:6">
+      <c r="G74" s="94"/>
+    </row>
+    <row r="75" spans="1:7">
       <c r="A75" s="77"/>
       <c r="B75" s="43"/>
       <c r="C75" s="43"/>
       <c r="D75" s="82"/>
       <c r="E75" s="43"/>
       <c r="F75" s="78"/>
-    </row>
-    <row r="76" spans="1:6">
+      <c r="G75" s="94"/>
+    </row>
+    <row r="76" spans="1:7">
       <c r="A76" s="77"/>
       <c r="B76" s="43"/>
       <c r="C76" s="43"/>
       <c r="D76" s="82"/>
       <c r="E76" s="43"/>
       <c r="F76" s="78"/>
-    </row>
-    <row r="77" spans="1:6">
+      <c r="G76" s="94"/>
+    </row>
+    <row r="77" spans="1:7">
       <c r="A77" s="77"/>
       <c r="B77" s="43"/>
       <c r="C77" s="43"/>
       <c r="D77" s="82"/>
       <c r="E77" s="43"/>
       <c r="F77" s="78"/>
-    </row>
-    <row r="78" spans="1:6">
+      <c r="G77" s="94"/>
+    </row>
+    <row r="78" spans="1:7">
       <c r="A78" s="77"/>
       <c r="B78" s="43"/>
       <c r="C78" s="43"/>
       <c r="D78" s="82"/>
       <c r="E78" s="43"/>
       <c r="F78" s="78"/>
-    </row>
-    <row r="79" spans="1:6">
+      <c r="G78" s="94"/>
+    </row>
+    <row r="79" spans="1:7">
       <c r="A79" s="77"/>
       <c r="B79" s="43"/>
       <c r="C79" s="43"/>
       <c r="D79" s="82"/>
       <c r="E79" s="43"/>
       <c r="F79" s="78"/>
-    </row>
-    <row r="80" spans="1:6">
+      <c r="G79" s="94"/>
+    </row>
+    <row r="80" spans="1:7">
       <c r="A80" s="77"/>
       <c r="B80" s="43"/>
       <c r="C80" s="43"/>
       <c r="D80" s="82"/>
       <c r="E80" s="43"/>
       <c r="F80" s="78"/>
-    </row>
-    <row r="81" spans="1:6">
+      <c r="G80" s="94"/>
+    </row>
+    <row r="81" spans="1:7">
       <c r="A81" s="77"/>
       <c r="B81" s="43"/>
       <c r="C81" s="43"/>
       <c r="D81" s="82"/>
       <c r="E81" s="43"/>
       <c r="F81" s="78"/>
-    </row>
-    <row r="82" spans="1:6">
+      <c r="G81" s="94"/>
+    </row>
+    <row r="82" spans="1:7">
       <c r="A82" s="77"/>
       <c r="B82" s="43"/>
       <c r="C82" s="43"/>
       <c r="D82" s="82"/>
       <c r="E82" s="43"/>
       <c r="F82" s="78"/>
-    </row>
-    <row r="83" spans="1:6">
+      <c r="G82" s="94"/>
+    </row>
+    <row r="83" spans="1:7">
       <c r="A83" s="77"/>
       <c r="B83" s="43"/>
       <c r="C83" s="43"/>
       <c r="D83" s="82"/>
       <c r="E83" s="43"/>
       <c r="F83" s="78"/>
-    </row>
-    <row r="84" spans="1:6">
+      <c r="G83" s="94"/>
+    </row>
+    <row r="84" spans="1:7">
       <c r="A84" s="77"/>
       <c r="B84" s="43"/>
       <c r="C84" s="43"/>
       <c r="D84" s="82"/>
       <c r="E84" s="43"/>
       <c r="F84" s="78"/>
-    </row>
-    <row r="85" spans="1:6">
+      <c r="G84" s="94"/>
+    </row>
+    <row r="85" spans="1:7">
       <c r="A85" s="77"/>
       <c r="B85" s="43"/>
       <c r="C85" s="43"/>
       <c r="D85" s="82"/>
       <c r="E85" s="43"/>
       <c r="F85" s="78"/>
-    </row>
-    <row r="86" spans="1:6">
+      <c r="G85" s="94"/>
+    </row>
+    <row r="86" spans="1:7">
       <c r="A86" s="77"/>
       <c r="B86" s="43"/>
       <c r="C86" s="43"/>
       <c r="D86" s="82"/>
       <c r="E86" s="43"/>
       <c r="F86" s="78"/>
-    </row>
-    <row r="87" spans="1:6">
+      <c r="G86" s="94"/>
+    </row>
+    <row r="87" spans="1:7">
       <c r="A87" s="77"/>
       <c r="B87" s="43"/>
       <c r="C87" s="43"/>
       <c r="D87" s="82"/>
       <c r="E87" s="43"/>
       <c r="F87" s="78"/>
-    </row>
-    <row r="88" spans="1:6">
+      <c r="G87" s="94"/>
+    </row>
+    <row r="88" spans="1:7">
       <c r="A88" s="77"/>
       <c r="B88" s="43"/>
       <c r="C88" s="43"/>
       <c r="D88" s="82"/>
       <c r="E88" s="43"/>
       <c r="F88" s="78"/>
-    </row>
-    <row r="89" spans="1:6">
+      <c r="G88" s="94"/>
+    </row>
+    <row r="89" spans="1:7">
       <c r="A89" s="77"/>
       <c r="B89" s="43"/>
       <c r="C89" s="43"/>
       <c r="D89" s="82"/>
       <c r="E89" s="43"/>
       <c r="F89" s="78"/>
-    </row>
-    <row r="90" spans="1:6">
+      <c r="G89" s="94"/>
+    </row>
+    <row r="90" spans="1:7">
       <c r="A90" s="77"/>
       <c r="B90" s="43"/>
       <c r="C90" s="43"/>
       <c r="D90" s="82"/>
       <c r="E90" s="43"/>
       <c r="F90" s="78"/>
-    </row>
-    <row r="91" spans="1:6">
+      <c r="G90" s="94"/>
+    </row>
+    <row r="91" spans="1:7">
       <c r="A91" s="77"/>
       <c r="B91" s="43"/>
       <c r="C91" s="43"/>
       <c r="D91" s="82"/>
       <c r="E91" s="43"/>
       <c r="F91" s="78"/>
-    </row>
-    <row r="92" spans="1:6">
+      <c r="G91" s="94"/>
+    </row>
+    <row r="92" spans="1:7">
       <c r="A92" s="77"/>
       <c r="B92" s="43"/>
       <c r="C92" s="43"/>
       <c r="D92" s="82"/>
       <c r="E92" s="43"/>
       <c r="F92" s="78"/>
-    </row>
-    <row r="93" spans="1:6">
+      <c r="G92" s="94"/>
+    </row>
+    <row r="93" spans="1:7">
       <c r="A93" s="77"/>
       <c r="B93" s="43"/>
       <c r="C93" s="43"/>
       <c r="D93" s="82"/>
       <c r="E93" s="43"/>
       <c r="F93" s="78"/>
-    </row>
-    <row r="94" spans="1:6">
+      <c r="G93" s="94"/>
+    </row>
+    <row r="94" spans="1:7">
       <c r="A94" s="77"/>
       <c r="B94" s="43"/>
       <c r="C94" s="43"/>
       <c r="D94" s="82"/>
       <c r="E94" s="43"/>
       <c r="F94" s="78"/>
-    </row>
-    <row r="95" spans="1:6">
+      <c r="G94" s="94"/>
+    </row>
+    <row r="95" spans="1:7">
       <c r="A95" s="77"/>
       <c r="B95" s="43"/>
       <c r="C95" s="43"/>
       <c r="D95" s="82"/>
       <c r="E95" s="43"/>
       <c r="F95" s="78"/>
-    </row>
-    <row r="96" spans="1:6">
+      <c r="G95" s="94"/>
+    </row>
+    <row r="96" spans="1:7">
       <c r="A96" s="77"/>
       <c r="B96" s="43"/>
       <c r="C96" s="43"/>
       <c r="D96" s="82"/>
       <c r="E96" s="43"/>
       <c r="F96" s="78"/>
-    </row>
-    <row r="97" spans="1:6">
+      <c r="G96" s="94"/>
+    </row>
+    <row r="97" spans="1:7">
       <c r="A97" s="77"/>
       <c r="B97" s="43"/>
       <c r="C97" s="43"/>
       <c r="D97" s="82"/>
       <c r="E97" s="43"/>
       <c r="F97" s="78"/>
-    </row>
-    <row r="98" spans="1:6">
+      <c r="G97" s="94"/>
+    </row>
+    <row r="98" spans="1:7">
       <c r="A98" s="77"/>
       <c r="B98" s="43"/>
       <c r="C98" s="43"/>
       <c r="D98" s="82"/>
       <c r="E98" s="43"/>
       <c r="F98" s="78"/>
-    </row>
-    <row r="99" spans="1:6">
+      <c r="G98" s="94"/>
+    </row>
+    <row r="99" spans="1:7">
       <c r="A99" s="77"/>
       <c r="B99" s="43"/>
       <c r="C99" s="43"/>
       <c r="D99" s="82"/>
       <c r="E99" s="43"/>
       <c r="F99" s="78"/>
-    </row>
-    <row r="100" spans="1:6">
+      <c r="G99" s="94"/>
+    </row>
+    <row r="100" spans="1:7">
       <c r="A100" s="77"/>
       <c r="B100" s="43"/>
       <c r="C100" s="43"/>
       <c r="D100" s="82"/>
       <c r="E100" s="43"/>
       <c r="F100" s="78"/>
-    </row>
-    <row r="101" spans="1:6">
+      <c r="G100" s="94"/>
+    </row>
+    <row r="101" spans="1:7">
       <c r="A101" s="77"/>
       <c r="B101" s="43"/>
       <c r="C101" s="43"/>
       <c r="D101" s="82"/>
       <c r="E101" s="43"/>
       <c r="F101" s="78"/>
-    </row>
-    <row r="102" spans="1:6">
+      <c r="G101" s="94"/>
+    </row>
+    <row r="102" spans="1:7">
       <c r="A102" s="77"/>
       <c r="B102" s="43"/>
       <c r="C102" s="43"/>
       <c r="D102" s="82"/>
       <c r="E102" s="43"/>
       <c r="F102" s="78"/>
-    </row>
-    <row r="103" spans="1:6">
+      <c r="G102" s="94"/>
+    </row>
+    <row r="103" spans="1:7">
       <c r="A103" s="77"/>
       <c r="B103" s="43"/>
       <c r="C103" s="43"/>
       <c r="D103" s="82"/>
       <c r="E103" s="43"/>
       <c r="F103" s="78"/>
-    </row>
-    <row r="104" spans="1:6">
+      <c r="G103" s="94"/>
+    </row>
+    <row r="104" spans="1:7">
       <c r="A104" s="77"/>
       <c r="B104" s="43"/>
       <c r="C104" s="43"/>
       <c r="D104" s="82"/>
       <c r="E104" s="43"/>
       <c r="F104" s="78"/>
-    </row>
-    <row r="105" spans="1:6">
+      <c r="G104" s="94"/>
+    </row>
+    <row r="105" spans="1:7">
       <c r="A105" s="77"/>
       <c r="B105" s="43"/>
       <c r="C105" s="43"/>
       <c r="D105" s="82"/>
       <c r="E105" s="43"/>
       <c r="F105" s="78"/>
-    </row>
-    <row r="106" spans="1:6">
+      <c r="G105" s="94"/>
+    </row>
+    <row r="106" spans="1:7">
       <c r="A106" s="79"/>
       <c r="B106" s="44"/>
       <c r="C106" s="44"/>
       <c r="D106" s="83"/>
       <c r="E106" s="44"/>
       <c r="F106" s="64"/>
-    </row>
-    <row r="107" spans="1:6">
+      <c r="G106" s="94"/>
+    </row>
+    <row r="107" spans="1:7">
       <c r="A107" s="79"/>
       <c r="B107" s="44"/>
       <c r="C107" s="44"/>
       <c r="D107" s="83"/>
       <c r="E107" s="44"/>
       <c r="F107" s="64"/>
-    </row>
-    <row r="108" spans="1:6">
+      <c r="G107" s="94"/>
+    </row>
+    <row r="108" spans="1:7">
       <c r="A108" s="79"/>
       <c r="B108" s="44"/>
       <c r="C108" s="44"/>
       <c r="D108" s="83"/>
       <c r="E108" s="44"/>
       <c r="F108" s="64"/>
-    </row>
-    <row r="109" spans="1:6">
+      <c r="G108" s="94"/>
+    </row>
+    <row r="109" spans="1:7">
       <c r="A109" s="79"/>
       <c r="B109" s="44"/>
       <c r="C109" s="44"/>
       <c r="D109" s="83"/>
       <c r="E109" s="44"/>
       <c r="F109" s="64"/>
-    </row>
-    <row r="110" spans="1:6">
+      <c r="G109" s="94"/>
+    </row>
+    <row r="110" spans="1:7">
       <c r="A110" s="79"/>
       <c r="B110" s="44"/>
       <c r="C110" s="44"/>
       <c r="D110" s="83"/>
       <c r="E110" s="44"/>
       <c r="F110" s="64"/>
-    </row>
-    <row r="111" spans="1:6">
+      <c r="G110" s="94"/>
+    </row>
+    <row r="111" spans="1:7">
       <c r="A111" s="79"/>
       <c r="B111" s="44"/>
       <c r="C111" s="44"/>
       <c r="D111" s="83"/>
       <c r="E111" s="44"/>
       <c r="F111" s="64"/>
-    </row>
-    <row r="112" spans="1:6">
+      <c r="G111" s="94"/>
+    </row>
+    <row r="112" spans="1:7">
       <c r="A112" s="79"/>
       <c r="B112" s="44"/>
       <c r="C112" s="44"/>
       <c r="D112" s="83"/>
       <c r="E112" s="44"/>
       <c r="F112" s="64"/>
-    </row>
-    <row r="113" spans="1:6">
+      <c r="G112" s="94"/>
+    </row>
+    <row r="113" spans="1:7">
       <c r="A113" s="79"/>
       <c r="B113" s="44"/>
       <c r="C113" s="44"/>
       <c r="D113" s="83"/>
       <c r="E113" s="44"/>
       <c r="F113" s="64"/>
-    </row>
-    <row r="114" spans="1:6">
+      <c r="G113" s="94"/>
+    </row>
+    <row r="114" spans="1:7">
       <c r="A114" s="79"/>
       <c r="B114" s="44"/>
       <c r="C114" s="44"/>
       <c r="D114" s="83"/>
       <c r="E114" s="44"/>
       <c r="F114" s="64"/>
-    </row>
-    <row r="115" spans="1:6">
+      <c r="G114" s="94"/>
+    </row>
+    <row r="115" spans="1:7">
       <c r="A115" s="79"/>
       <c r="B115" s="44"/>
       <c r="C115" s="44"/>
       <c r="D115" s="83"/>
       <c r="E115" s="44"/>
       <c r="F115" s="64"/>
-    </row>
-    <row r="116" spans="1:6">
+      <c r="G115" s="94"/>
+    </row>
+    <row r="116" spans="1:7">
       <c r="A116" s="79"/>
       <c r="B116" s="44"/>
       <c r="C116" s="44"/>
       <c r="D116" s="83"/>
       <c r="E116" s="44"/>
       <c r="F116" s="64"/>
-    </row>
-    <row r="117" spans="1:6">
+      <c r="G116" s="94"/>
+    </row>
+    <row r="117" spans="1:7">
       <c r="A117" s="79"/>
       <c r="B117" s="44"/>
       <c r="C117" s="44"/>
       <c r="D117" s="83"/>
       <c r="E117" s="44"/>
       <c r="F117" s="64"/>
-    </row>
-    <row r="118" spans="1:6">
+      <c r="G117" s="94"/>
+    </row>
+    <row r="118" spans="1:7">
       <c r="A118" s="79"/>
       <c r="B118" s="44"/>
       <c r="C118" s="44"/>
       <c r="D118" s="83"/>
       <c r="E118" s="44"/>
       <c r="F118" s="64"/>
-    </row>
-    <row r="119" spans="1:6">
+      <c r="G118" s="94"/>
+    </row>
+    <row r="119" spans="1:7">
       <c r="A119" s="79"/>
       <c r="B119" s="44"/>
       <c r="C119" s="44"/>
       <c r="D119" s="83"/>
       <c r="E119" s="44"/>
       <c r="F119" s="64"/>
-    </row>
-    <row r="120" spans="1:6">
+      <c r="G119" s="94"/>
+    </row>
+    <row r="120" spans="1:7">
       <c r="A120" s="79"/>
       <c r="B120" s="44"/>
       <c r="C120" s="44"/>
       <c r="D120" s="83"/>
       <c r="E120" s="44"/>
       <c r="F120" s="64"/>
-    </row>
-    <row r="121" spans="1:6">
+      <c r="G120" s="94"/>
+    </row>
+    <row r="121" spans="1:7">
       <c r="A121" s="79"/>
       <c r="B121" s="44"/>
       <c r="C121" s="44"/>
       <c r="D121" s="83"/>
       <c r="E121" s="44"/>
       <c r="F121" s="64"/>
-    </row>
-    <row r="122" spans="1:6">
+      <c r="G121" s="94"/>
+    </row>
+    <row r="122" spans="1:7">
       <c r="A122" s="79"/>
       <c r="B122" s="44"/>
       <c r="C122" s="44"/>
       <c r="D122" s="83"/>
       <c r="E122" s="44"/>
       <c r="F122" s="64"/>
-    </row>
-    <row r="123" spans="1:6">
+      <c r="G122" s="94"/>
+    </row>
+    <row r="123" spans="1:7">
       <c r="A123" s="79"/>
       <c r="B123" s="44"/>
       <c r="C123" s="44"/>
       <c r="D123" s="83"/>
       <c r="E123" s="44"/>
       <c r="F123" s="64"/>
-    </row>
-    <row r="124" spans="1:6">
+      <c r="G123" s="94"/>
+    </row>
+    <row r="124" spans="1:7">
       <c r="A124" s="79"/>
       <c r="B124" s="44"/>
       <c r="C124" s="44"/>
       <c r="D124" s="83"/>
       <c r="E124" s="44"/>
       <c r="F124" s="64"/>
-    </row>
-    <row r="125" spans="1:6">
+      <c r="G124" s="94"/>
+    </row>
+    <row r="125" spans="1:7">
       <c r="A125" s="79"/>
       <c r="B125" s="44"/>
       <c r="C125" s="44"/>
       <c r="D125" s="83"/>
       <c r="E125" s="44"/>
       <c r="F125" s="64"/>
-    </row>
-    <row r="126" spans="1:6">
+      <c r="G125" s="94"/>
+    </row>
+    <row r="126" spans="1:7">
       <c r="A126" s="79"/>
       <c r="B126" s="44"/>
       <c r="C126" s="44"/>
       <c r="D126" s="83"/>
       <c r="E126" s="44"/>
       <c r="F126" s="64"/>
-    </row>
-    <row r="127" spans="1:6">
+      <c r="G126" s="94"/>
+    </row>
+    <row r="127" spans="1:7">
       <c r="A127" s="79"/>
       <c r="B127" s="44"/>
       <c r="C127" s="44"/>
       <c r="D127" s="83"/>
       <c r="E127" s="44"/>
       <c r="F127" s="64"/>
-    </row>
-    <row r="128" spans="1:6">
+      <c r="G127" s="94"/>
+    </row>
+    <row r="128" spans="1:7">
       <c r="A128" s="79"/>
       <c r="B128" s="44"/>
       <c r="C128" s="44"/>
       <c r="D128" s="83"/>
       <c r="E128" s="44"/>
       <c r="F128" s="64"/>
-    </row>
-    <row r="129" spans="1:6">
+      <c r="G128" s="94"/>
+    </row>
+    <row r="129" spans="1:7">
       <c r="A129" s="79"/>
       <c r="B129" s="44"/>
       <c r="C129" s="44"/>
       <c r="D129" s="83"/>
       <c r="E129" s="44"/>
       <c r="F129" s="64"/>
-    </row>
-    <row r="130" spans="1:6">
+      <c r="G129" s="94"/>
+    </row>
+    <row r="130" spans="1:7">
       <c r="A130" s="79"/>
       <c r="B130" s="44"/>
       <c r="C130" s="44"/>
       <c r="D130" s="83"/>
       <c r="E130" s="44"/>
       <c r="F130" s="64"/>
-    </row>
-    <row r="131" spans="1:6">
+      <c r="G130" s="94"/>
+    </row>
+    <row r="131" spans="1:7">
       <c r="A131" s="79"/>
       <c r="B131" s="44"/>
       <c r="C131" s="44"/>
       <c r="D131" s="83"/>
       <c r="E131" s="44"/>
       <c r="F131" s="64"/>
-    </row>
-    <row r="132" spans="1:6">
+      <c r="G131" s="94"/>
+    </row>
+    <row r="132" spans="1:7">
       <c r="A132" s="79"/>
       <c r="B132" s="44"/>
       <c r="C132" s="44"/>
       <c r="D132" s="83"/>
       <c r="E132" s="44"/>
       <c r="F132" s="64"/>
-    </row>
-    <row r="133" spans="1:6">
+      <c r="G132" s="94"/>
+    </row>
+    <row r="133" spans="1:7">
       <c r="A133" s="79"/>
       <c r="B133" s="44"/>
       <c r="C133" s="44"/>
       <c r="D133" s="83"/>
       <c r="E133" s="44"/>
       <c r="F133" s="64"/>
-    </row>
-    <row r="134" spans="1:6">
+      <c r="G133" s="94"/>
+    </row>
+    <row r="134" spans="1:7">
       <c r="A134" s="79"/>
       <c r="B134" s="44"/>
       <c r="C134" s="44"/>
       <c r="D134" s="83"/>
       <c r="E134" s="44"/>
       <c r="F134" s="64"/>
-    </row>
-    <row r="135" spans="1:6">
+      <c r="G134" s="94"/>
+    </row>
+    <row r="135" spans="1:7">
       <c r="A135" s="79"/>
       <c r="B135" s="44"/>
       <c r="C135" s="44"/>
       <c r="D135" s="83"/>
       <c r="E135" s="44"/>
       <c r="F135" s="64"/>
-    </row>
-    <row r="136" spans="1:6">
+      <c r="G135" s="94"/>
+    </row>
+    <row r="136" spans="1:7">
       <c r="A136" s="79"/>
       <c r="B136" s="44"/>
       <c r="C136" s="44"/>
       <c r="D136" s="83"/>
       <c r="E136" s="44"/>
       <c r="F136" s="64"/>
-    </row>
-    <row r="137" spans="1:6">
+      <c r="G136" s="94"/>
+    </row>
+    <row r="137" spans="1:7">
       <c r="A137" s="79"/>
       <c r="B137" s="44"/>
       <c r="C137" s="44"/>
       <c r="D137" s="83"/>
       <c r="E137" s="44"/>
       <c r="F137" s="64"/>
-    </row>
-    <row r="138" spans="1:6">
+      <c r="G137" s="94"/>
+    </row>
+    <row r="138" spans="1:7">
       <c r="A138" s="79"/>
       <c r="B138" s="44"/>
       <c r="C138" s="44"/>
       <c r="D138" s="83"/>
       <c r="E138" s="44"/>
       <c r="F138" s="64"/>
-    </row>
-    <row r="139" spans="1:6">
+      <c r="G138" s="94"/>
+    </row>
+    <row r="139" spans="1:7">
       <c r="A139" s="79"/>
       <c r="B139" s="44"/>
       <c r="C139" s="44"/>
       <c r="D139" s="83"/>
       <c r="E139" s="44"/>
       <c r="F139" s="64"/>
-    </row>
-    <row r="140" spans="1:6">
+      <c r="G139" s="94"/>
+    </row>
+    <row r="140" spans="1:7">
       <c r="A140" s="79"/>
       <c r="B140" s="44"/>
       <c r="C140" s="44"/>
       <c r="D140" s="83"/>
       <c r="E140" s="44"/>
       <c r="F140" s="64"/>
-    </row>
-    <row r="141" spans="1:6">
+      <c r="G140" s="94"/>
+    </row>
+    <row r="141" spans="1:7">
       <c r="A141" s="79"/>
       <c r="B141" s="44"/>
       <c r="C141" s="44"/>
       <c r="D141" s="83"/>
       <c r="E141" s="44"/>
       <c r="F141" s="64"/>
-    </row>
-    <row r="142" spans="1:6">
+      <c r="G141" s="94"/>
+    </row>
+    <row r="142" spans="1:7">
       <c r="A142" s="79"/>
       <c r="B142" s="44"/>
       <c r="C142" s="44"/>
       <c r="D142" s="83"/>
       <c r="E142" s="44"/>
       <c r="F142" s="64"/>
-    </row>
-    <row r="143" spans="1:6">
+      <c r="G142" s="94"/>
+    </row>
+    <row r="143" spans="1:7">
       <c r="A143" s="79"/>
       <c r="B143" s="44"/>
       <c r="C143" s="44"/>
       <c r="D143" s="83"/>
       <c r="E143" s="44"/>
       <c r="F143" s="64"/>
-    </row>
-    <row r="144" spans="1:6">
+      <c r="G143" s="94"/>
+    </row>
+    <row r="144" spans="1:7">
       <c r="A144" s="79"/>
       <c r="B144" s="44"/>
       <c r="C144" s="44"/>
       <c r="D144" s="83"/>
       <c r="E144" s="44"/>
       <c r="F144" s="64"/>
-    </row>
-    <row r="145" spans="1:6">
+      <c r="G144" s="94"/>
+    </row>
+    <row r="145" spans="1:7">
       <c r="A145" s="79"/>
       <c r="B145" s="44"/>
       <c r="C145" s="44"/>
       <c r="D145" s="83"/>
       <c r="E145" s="44"/>
       <c r="F145" s="64"/>
-    </row>
-    <row r="146" spans="1:6">
+      <c r="G145" s="94"/>
+    </row>
+    <row r="146" spans="1:7">
       <c r="A146" s="79"/>
       <c r="B146" s="44"/>
       <c r="C146" s="44"/>
       <c r="D146" s="83"/>
       <c r="E146" s="44"/>
       <c r="F146" s="64"/>
-    </row>
-    <row r="147" spans="1:6">
+      <c r="G146" s="94"/>
+    </row>
+    <row r="147" spans="1:7">
       <c r="A147" s="79"/>
       <c r="B147" s="44"/>
       <c r="C147" s="44"/>
       <c r="D147" s="83"/>
       <c r="E147" s="44"/>
       <c r="F147" s="64"/>
-    </row>
-    <row r="148" spans="1:6">
+      <c r="G147" s="94"/>
+    </row>
+    <row r="148" spans="1:7">
       <c r="A148" s="79"/>
       <c r="B148" s="44"/>
       <c r="C148" s="44"/>
       <c r="D148" s="83"/>
       <c r="E148" s="44"/>
       <c r="F148" s="64"/>
-    </row>
-    <row r="149" spans="1:6">
+      <c r="G148" s="94"/>
+    </row>
+    <row r="149" spans="1:7">
       <c r="A149" s="79"/>
       <c r="B149" s="44"/>
       <c r="C149" s="44"/>
       <c r="D149" s="83"/>
       <c r="E149" s="44"/>
       <c r="F149" s="64"/>
-    </row>
-    <row r="150" spans="1:6">
+      <c r="G149" s="94"/>
+    </row>
+    <row r="150" spans="1:7">
       <c r="A150" s="79"/>
       <c r="B150" s="44"/>
       <c r="C150" s="44"/>
       <c r="D150" s="83"/>
       <c r="E150" s="44"/>
       <c r="F150" s="64"/>
-    </row>
-    <row r="151" spans="1:6">
+      <c r="G150" s="94"/>
+    </row>
+    <row r="151" spans="1:7">
       <c r="A151" s="79"/>
       <c r="B151" s="44"/>
       <c r="C151" s="44"/>
       <c r="D151" s="83"/>
       <c r="E151" s="44"/>
       <c r="F151" s="64"/>
-    </row>
-    <row r="152" spans="1:6">
+      <c r="G151" s="94"/>
+    </row>
+    <row r="152" spans="1:7">
       <c r="A152" s="79"/>
       <c r="B152" s="44"/>
       <c r="C152" s="44"/>
       <c r="D152" s="83"/>
       <c r="E152" s="44"/>
       <c r="F152" s="64"/>
-    </row>
-    <row r="153" spans="1:6">
+      <c r="G152" s="94"/>
+    </row>
+    <row r="153" spans="1:7">
       <c r="A153" s="79"/>
       <c r="B153" s="44"/>
       <c r="C153" s="44"/>
       <c r="D153" s="83"/>
       <c r="E153" s="44"/>
       <c r="F153" s="64"/>
-    </row>
-    <row r="154" spans="1:6">
+      <c r="G153" s="94"/>
+    </row>
+    <row r="154" spans="1:7">
       <c r="A154" s="79"/>
       <c r="B154" s="44"/>
       <c r="C154" s="44"/>
       <c r="D154" s="83"/>
       <c r="E154" s="44"/>
       <c r="F154" s="64"/>
-    </row>
-    <row r="155" spans="1:6">
+      <c r="G154" s="94"/>
+    </row>
+    <row r="155" spans="1:7">
       <c r="A155" s="79"/>
       <c r="B155" s="44"/>
       <c r="C155" s="44"/>
       <c r="D155" s="83"/>
       <c r="E155" s="44"/>
       <c r="F155" s="64"/>
-    </row>
-    <row r="156" spans="1:6">
+      <c r="G155" s="94"/>
+    </row>
+    <row r="156" spans="1:7">
       <c r="A156" s="79"/>
       <c r="B156" s="44"/>
       <c r="C156" s="44"/>
       <c r="D156" s="83"/>
       <c r="E156" s="44"/>
       <c r="F156" s="64"/>
-    </row>
-    <row r="157" spans="1:6">
+      <c r="G156" s="94"/>
+    </row>
+    <row r="157" spans="1:7">
       <c r="A157" s="79"/>
       <c r="B157" s="44"/>
       <c r="C157" s="44"/>
       <c r="D157" s="83"/>
       <c r="E157" s="44"/>
       <c r="F157" s="64"/>
-    </row>
-    <row r="158" spans="1:6">
+      <c r="G157" s="94"/>
+    </row>
+    <row r="158" spans="1:7">
       <c r="A158" s="79"/>
       <c r="B158" s="44"/>
       <c r="C158" s="44"/>
       <c r="D158" s="83"/>
       <c r="E158" s="44"/>
       <c r="F158" s="64"/>
-    </row>
-    <row r="159" spans="1:6">
+      <c r="G158" s="94"/>
+    </row>
+    <row r="159" spans="1:7">
       <c r="A159" s="79"/>
       <c r="B159" s="44"/>
       <c r="C159" s="44"/>
       <c r="D159" s="83"/>
       <c r="E159" s="44"/>
       <c r="F159" s="64"/>
-    </row>
-    <row r="160" spans="1:6">
+      <c r="G159" s="94"/>
+    </row>
+    <row r="160" spans="1:7">
       <c r="A160" s="79"/>
       <c r="B160" s="44"/>
       <c r="C160" s="44"/>
       <c r="D160" s="83"/>
       <c r="E160" s="44"/>
       <c r="F160" s="64"/>
-    </row>
-    <row r="161" spans="1:6">
+      <c r="G160" s="94"/>
+    </row>
+    <row r="161" spans="1:7">
       <c r="A161" s="79"/>
       <c r="B161" s="44"/>
       <c r="C161" s="44"/>
       <c r="D161" s="83"/>
       <c r="E161" s="44"/>
       <c r="F161" s="64"/>
-    </row>
-    <row r="162" spans="1:6">
+      <c r="G161" s="94"/>
+    </row>
+    <row r="162" spans="1:7">
       <c r="A162" s="79"/>
       <c r="B162" s="44"/>
       <c r="C162" s="44"/>
       <c r="D162" s="83"/>
       <c r="E162" s="44"/>
       <c r="F162" s="64"/>
-    </row>
-    <row r="163" spans="1:6">
+      <c r="G162" s="94"/>
+    </row>
+    <row r="163" spans="1:7">
       <c r="A163" s="79"/>
       <c r="B163" s="44"/>
       <c r="C163" s="44"/>
       <c r="D163" s="83"/>
       <c r="E163" s="44"/>
       <c r="F163" s="64"/>
-    </row>
-    <row r="164" spans="1:6">
+      <c r="G163" s="94"/>
+    </row>
+    <row r="164" spans="1:7">
       <c r="A164" s="79"/>
       <c r="B164" s="44"/>
       <c r="C164" s="44"/>
       <c r="D164" s="83"/>
       <c r="E164" s="44"/>
       <c r="F164" s="64"/>
-    </row>
-    <row r="165" spans="1:6">
+      <c r="G164" s="94"/>
+    </row>
+    <row r="165" spans="1:7">
       <c r="A165" s="79"/>
       <c r="B165" s="44"/>
       <c r="C165" s="44"/>
       <c r="D165" s="83"/>
       <c r="E165" s="44"/>
       <c r="F165" s="64"/>
-    </row>
-    <row r="166" spans="1:6">
+      <c r="G165" s="94"/>
+    </row>
+    <row r="166" spans="1:7">
       <c r="A166" s="79"/>
       <c r="B166" s="44"/>
       <c r="C166" s="44"/>
       <c r="D166" s="83"/>
       <c r="E166" s="44"/>
       <c r="F166" s="64"/>
-    </row>
-    <row r="167" spans="1:6">
+      <c r="G166" s="94"/>
+    </row>
+    <row r="167" spans="1:7">
       <c r="A167" s="79"/>
       <c r="B167" s="44"/>
       <c r="C167" s="44"/>
       <c r="D167" s="83"/>
       <c r="E167" s="44"/>
       <c r="F167" s="64"/>
-    </row>
-    <row r="168" spans="1:6">
+      <c r="G167" s="94"/>
+    </row>
+    <row r="168" spans="1:7">
       <c r="A168" s="79"/>
       <c r="B168" s="44"/>
       <c r="C168" s="44"/>
       <c r="D168" s="83"/>
       <c r="E168" s="44"/>
       <c r="F168" s="64"/>
-    </row>
-    <row r="169" spans="1:6">
+      <c r="G168" s="94"/>
+    </row>
+    <row r="169" spans="1:7">
       <c r="A169" s="79"/>
       <c r="B169" s="44"/>
       <c r="C169" s="44"/>
       <c r="D169" s="83"/>
       <c r="E169" s="44"/>
       <c r="F169" s="64"/>
-    </row>
-    <row r="170" spans="1:6">
+      <c r="G169" s="94"/>
+    </row>
+    <row r="170" spans="1:7">
       <c r="A170" s="79"/>
       <c r="B170" s="44"/>
       <c r="C170" s="44"/>
       <c r="D170" s="83"/>
       <c r="E170" s="44"/>
       <c r="F170" s="64"/>
-    </row>
-    <row r="171" spans="1:6">
+      <c r="G170" s="94"/>
+    </row>
+    <row r="171" spans="1:7">
       <c r="A171" s="79"/>
       <c r="B171" s="44"/>
       <c r="C171" s="44"/>
       <c r="D171" s="83"/>
       <c r="E171" s="44"/>
       <c r="F171" s="64"/>
-    </row>
-    <row r="172" spans="1:6">
+      <c r="G171" s="94"/>
+    </row>
+    <row r="172" spans="1:7">
       <c r="A172" s="79"/>
       <c r="B172" s="44"/>
       <c r="C172" s="44"/>
       <c r="D172" s="83"/>
       <c r="E172" s="44"/>
       <c r="F172" s="64"/>
-    </row>
-    <row r="173" spans="1:6">
+      <c r="G172" s="94"/>
+    </row>
+    <row r="173" spans="1:7">
       <c r="A173" s="79"/>
       <c r="B173" s="44"/>
       <c r="C173" s="44"/>
       <c r="D173" s="83"/>
       <c r="E173" s="44"/>
       <c r="F173" s="64"/>
-    </row>
-    <row r="174" spans="1:6">
+      <c r="G173" s="94"/>
+    </row>
+    <row r="174" spans="1:7">
       <c r="A174" s="79"/>
       <c r="B174" s="44"/>
       <c r="C174" s="44"/>
       <c r="D174" s="83"/>
       <c r="E174" s="44"/>
       <c r="F174" s="64"/>
-    </row>
-    <row r="175" spans="1:6">
+      <c r="G174" s="94"/>
+    </row>
+    <row r="175" spans="1:7">
       <c r="A175" s="79"/>
       <c r="B175" s="44"/>
       <c r="C175" s="44"/>
       <c r="D175" s="83"/>
       <c r="E175" s="44"/>
       <c r="F175" s="64"/>
-    </row>
-    <row r="176" spans="1:6">
+      <c r="G175" s="94"/>
+    </row>
+    <row r="176" spans="1:7">
       <c r="A176" s="79"/>
       <c r="B176" s="44"/>
       <c r="C176" s="44"/>
       <c r="D176" s="83"/>
       <c r="E176" s="44"/>
       <c r="F176" s="64"/>
-    </row>
-    <row r="177" spans="1:6">
+      <c r="G176" s="94"/>
+    </row>
+    <row r="177" spans="1:7">
       <c r="A177" s="79"/>
       <c r="B177" s="44"/>
       <c r="C177" s="44"/>
       <c r="D177" s="83"/>
       <c r="E177" s="44"/>
       <c r="F177" s="64"/>
-    </row>
-    <row r="178" spans="1:6">
+      <c r="G177" s="94"/>
+    </row>
+    <row r="178" spans="1:7">
       <c r="A178" s="79"/>
       <c r="B178" s="44"/>
       <c r="C178" s="44"/>
       <c r="D178" s="83"/>
       <c r="E178" s="44"/>
       <c r="F178" s="64"/>
-    </row>
-    <row r="179" spans="1:6">
+      <c r="G178" s="94"/>
+    </row>
+    <row r="179" spans="1:7">
       <c r="A179" s="79"/>
       <c r="B179" s="44"/>
       <c r="C179" s="44"/>
       <c r="D179" s="83"/>
       <c r="E179" s="44"/>
       <c r="F179" s="64"/>
-    </row>
-    <row r="180" spans="1:6">
+      <c r="G179" s="94"/>
+    </row>
+    <row r="180" spans="1:7">
       <c r="A180" s="79"/>
       <c r="B180" s="44"/>
       <c r="C180" s="44"/>
       <c r="D180" s="83"/>
       <c r="E180" s="44"/>
       <c r="F180" s="64"/>
-    </row>
-    <row r="181" spans="1:6">
+      <c r="G180" s="94"/>
+    </row>
+    <row r="181" spans="1:7">
       <c r="A181" s="79"/>
       <c r="B181" s="44"/>
       <c r="C181" s="44"/>
       <c r="D181" s="83"/>
       <c r="E181" s="44"/>
       <c r="F181" s="64"/>
-    </row>
-    <row r="182" spans="1:6">
+      <c r="G181" s="94"/>
+    </row>
+    <row r="182" spans="1:7">
       <c r="A182" s="79"/>
       <c r="B182" s="44"/>
       <c r="C182" s="44"/>
       <c r="D182" s="83"/>
       <c r="E182" s="44"/>
       <c r="F182" s="64"/>
-    </row>
-    <row r="183" spans="1:6">
+      <c r="G182" s="94"/>
+    </row>
+    <row r="183" spans="1:7">
       <c r="A183" s="79"/>
       <c r="B183" s="44"/>
       <c r="C183" s="44"/>
       <c r="D183" s="83"/>
       <c r="E183" s="44"/>
       <c r="F183" s="64"/>
-    </row>
-    <row r="184" spans="1:6">
+      <c r="G183" s="94"/>
+    </row>
+    <row r="184" spans="1:7">
       <c r="A184" s="79"/>
       <c r="B184" s="44"/>
       <c r="C184" s="44"/>
       <c r="D184" s="83"/>
       <c r="E184" s="44"/>
       <c r="F184" s="64"/>
-    </row>
-    <row r="185" spans="1:6">
+      <c r="G184" s="94"/>
+    </row>
+    <row r="185" spans="1:7">
       <c r="A185" s="79"/>
       <c r="B185" s="44"/>
       <c r="C185" s="44"/>
       <c r="D185" s="83"/>
       <c r="E185" s="44"/>
       <c r="F185" s="64"/>
-    </row>
-    <row r="186" spans="1:6">
+      <c r="G185" s="94"/>
+    </row>
+    <row r="186" spans="1:7">
       <c r="A186" s="79"/>
       <c r="B186" s="44"/>
       <c r="C186" s="44"/>
       <c r="D186" s="83"/>
       <c r="E186" s="44"/>
       <c r="F186" s="64"/>
-    </row>
-    <row r="187" spans="1:6">
+      <c r="G186" s="94"/>
+    </row>
+    <row r="187" spans="1:7">
       <c r="A187" s="79"/>
       <c r="B187" s="44"/>
       <c r="C187" s="44"/>
       <c r="D187" s="83"/>
       <c r="E187" s="44"/>
       <c r="F187" s="64"/>
-    </row>
-    <row r="188" spans="1:6">
+      <c r="G187" s="94"/>
+    </row>
+    <row r="188" spans="1:7">
       <c r="A188" s="79"/>
       <c r="B188" s="44"/>
       <c r="C188" s="44"/>
       <c r="D188" s="83"/>
       <c r="E188" s="44"/>
       <c r="F188" s="64"/>
-    </row>
-    <row r="189" spans="1:6">
+      <c r="G188" s="94"/>
+    </row>
+    <row r="189" spans="1:7">
       <c r="A189" s="79"/>
       <c r="B189" s="44"/>
       <c r="C189" s="44"/>
       <c r="D189" s="83"/>
       <c r="E189" s="44"/>
       <c r="F189" s="64"/>
-    </row>
-    <row r="190" spans="1:6">
+      <c r="G189" s="94"/>
+    </row>
+    <row r="190" spans="1:7">
       <c r="A190" s="79"/>
       <c r="B190" s="44"/>
       <c r="C190" s="44"/>
       <c r="D190" s="83"/>
       <c r="E190" s="44"/>
       <c r="F190" s="64"/>
-    </row>
-    <row r="191" spans="1:6">
+      <c r="G190" s="94"/>
+    </row>
+    <row r="191" spans="1:7">
       <c r="A191" s="79"/>
       <c r="B191" s="44"/>
       <c r="C191" s="44"/>
       <c r="D191" s="83"/>
       <c r="E191" s="44"/>
       <c r="F191" s="64"/>
-    </row>
-    <row r="192" spans="1:6">
+      <c r="G191" s="94"/>
+    </row>
+    <row r="192" spans="1:7">
       <c r="A192" s="79"/>
       <c r="B192" s="44"/>
       <c r="C192" s="44"/>
       <c r="D192" s="83"/>
       <c r="E192" s="44"/>
       <c r="F192" s="64"/>
-    </row>
-    <row r="193" spans="1:6">
+      <c r="G192" s="94"/>
+    </row>
+    <row r="193" spans="1:7">
       <c r="A193" s="79"/>
       <c r="B193" s="44"/>
       <c r="C193" s="44"/>
       <c r="D193" s="83"/>
       <c r="E193" s="44"/>
       <c r="F193" s="64"/>
-    </row>
-    <row r="194" spans="1:6">
+      <c r="G193" s="94"/>
+    </row>
+    <row r="194" spans="1:7">
       <c r="A194" s="79"/>
       <c r="B194" s="44"/>
       <c r="C194" s="44"/>
       <c r="D194" s="83"/>
       <c r="E194" s="44"/>
       <c r="F194" s="64"/>
-    </row>
-    <row r="195" spans="1:6">
+      <c r="G194" s="94"/>
+    </row>
+    <row r="195" spans="1:7">
       <c r="A195" s="79"/>
       <c r="B195" s="44"/>
       <c r="C195" s="44"/>
       <c r="D195" s="83"/>
       <c r="E195" s="44"/>
       <c r="F195" s="64"/>
-    </row>
-    <row r="196" spans="1:6">
+      <c r="G195" s="94"/>
+    </row>
+    <row r="196" spans="1:7">
       <c r="A196" s="79"/>
       <c r="B196" s="44"/>
       <c r="C196" s="44"/>
       <c r="D196" s="83"/>
       <c r="E196" s="44"/>
       <c r="F196" s="64"/>
-    </row>
-    <row r="197" spans="1:6">
+      <c r="G196" s="94"/>
+    </row>
+    <row r="197" spans="1:7">
       <c r="A197" s="79"/>
       <c r="B197" s="44"/>
       <c r="C197" s="44"/>
       <c r="D197" s="83"/>
       <c r="E197" s="44"/>
       <c r="F197" s="64"/>
-    </row>
-    <row r="198" spans="1:6">
+      <c r="G197" s="94"/>
+    </row>
+    <row r="198" spans="1:7">
       <c r="A198" s="79"/>
       <c r="B198" s="44"/>
       <c r="C198" s="44"/>
       <c r="D198" s="83"/>
       <c r="E198" s="44"/>
       <c r="F198" s="64"/>
-    </row>
-    <row r="199" spans="1:6">
+      <c r="G198" s="94"/>
+    </row>
+    <row r="199" spans="1:7">
       <c r="A199" s="79"/>
       <c r="B199" s="44"/>
       <c r="C199" s="44"/>
       <c r="D199" s="83"/>
       <c r="E199" s="44"/>
       <c r="F199" s="64"/>
-    </row>
-    <row r="200" spans="1:6">
+      <c r="G199" s="94"/>
+    </row>
+    <row r="200" spans="1:7">
       <c r="A200" s="79"/>
       <c r="B200" s="44"/>
       <c r="C200" s="44"/>
       <c r="D200" s="83"/>
       <c r="E200" s="44"/>
       <c r="F200" s="64"/>
-    </row>
-    <row r="201" spans="1:6">
+      <c r="G200" s="94"/>
+    </row>
+    <row r="201" spans="1:7">
       <c r="A201" s="79"/>
       <c r="B201" s="44"/>
       <c r="C201" s="44"/>
       <c r="D201" s="83"/>
       <c r="E201" s="44"/>
       <c r="F201" s="64"/>
-    </row>
-    <row r="202" spans="1:6">
+      <c r="G201" s="94"/>
+    </row>
+    <row r="202" spans="1:7">
       <c r="A202" s="79"/>
       <c r="B202" s="44"/>
       <c r="C202" s="44"/>
       <c r="D202" s="83"/>
       <c r="E202" s="44"/>
       <c r="F202" s="64"/>
-    </row>
-    <row r="203" spans="1:6">
+      <c r="G202" s="94"/>
+    </row>
+    <row r="203" spans="1:7">
       <c r="A203" s="79"/>
       <c r="B203" s="44"/>
       <c r="C203" s="44"/>
       <c r="D203" s="83"/>
       <c r="E203" s="44"/>
       <c r="F203" s="64"/>
-    </row>
-    <row r="204" spans="1:6">
+      <c r="G203" s="94"/>
+    </row>
+    <row r="204" spans="1:7">
       <c r="A204" s="79"/>
       <c r="B204" s="44"/>
       <c r="C204" s="44"/>
       <c r="D204" s="83"/>
       <c r="E204" s="44"/>
       <c r="F204" s="64"/>
-    </row>
-    <row r="205" spans="1:6">
+      <c r="G204" s="94"/>
+    </row>
+    <row r="205" spans="1:7">
       <c r="A205" s="79"/>
       <c r="B205" s="44"/>
       <c r="C205" s="44"/>
       <c r="D205" s="83"/>
       <c r="E205" s="44"/>
       <c r="F205" s="64"/>
-    </row>
-    <row r="206" spans="1:6">
+      <c r="G205" s="94"/>
+    </row>
+    <row r="206" spans="1:7">
       <c r="A206" s="79"/>
       <c r="B206" s="44"/>
       <c r="C206" s="44"/>
       <c r="D206" s="83"/>
       <c r="E206" s="44"/>
       <c r="F206" s="64"/>
-    </row>
-    <row r="207" spans="1:6">
+      <c r="G206" s="94"/>
+    </row>
+    <row r="207" spans="1:7">
       <c r="A207" s="79"/>
       <c r="B207" s="44"/>
       <c r="C207" s="44"/>
       <c r="D207" s="83"/>
       <c r="E207" s="44"/>
       <c r="F207" s="64"/>
-    </row>
-    <row r="208" spans="1:6">
+      <c r="G207" s="94"/>
+    </row>
+    <row r="208" spans="1:7">
       <c r="A208" s="79"/>
       <c r="B208" s="44"/>
       <c r="C208" s="44"/>
       <c r="D208" s="83"/>
       <c r="E208" s="44"/>
       <c r="F208" s="64"/>
-    </row>
-    <row r="209" spans="1:6">
+      <c r="G208" s="94"/>
+    </row>
+    <row r="209" spans="1:7">
       <c r="A209" s="79"/>
       <c r="B209" s="44"/>
       <c r="C209" s="44"/>
       <c r="D209" s="83"/>
       <c r="E209" s="44"/>
       <c r="F209" s="64"/>
-    </row>
-    <row r="210" spans="1:6">
+      <c r="G209" s="94"/>
+    </row>
+    <row r="210" spans="1:7">
       <c r="A210" s="79"/>
       <c r="B210" s="44"/>
       <c r="C210" s="44"/>
       <c r="D210" s="83"/>
       <c r="E210" s="44"/>
       <c r="F210" s="64"/>
-    </row>
-    <row r="211" spans="1:6">
+      <c r="G210" s="94"/>
+    </row>
+    <row r="211" spans="1:7">
       <c r="A211" s="79"/>
       <c r="B211" s="44"/>
       <c r="C211" s="44"/>
       <c r="D211" s="83"/>
       <c r="E211" s="44"/>
       <c r="F211" s="64"/>
-    </row>
-    <row r="212" spans="1:6">
+      <c r="G211" s="94"/>
+    </row>
+    <row r="212" spans="1:7">
       <c r="A212" s="79"/>
       <c r="B212" s="44"/>
       <c r="C212" s="44"/>
       <c r="D212" s="83"/>
       <c r="E212" s="44"/>
       <c r="F212" s="64"/>
-    </row>
-    <row r="213" spans="1:6">
+      <c r="G212" s="94"/>
+    </row>
+    <row r="213" spans="1:7">
       <c r="A213" s="79"/>
       <c r="B213" s="44"/>
       <c r="C213" s="44"/>
       <c r="D213" s="83"/>
       <c r="E213" s="44"/>
       <c r="F213" s="64"/>
-    </row>
-    <row r="214" spans="1:6">
+      <c r="G213" s="94"/>
+    </row>
+    <row r="214" spans="1:7">
       <c r="A214" s="79"/>
       <c r="B214" s="44"/>
       <c r="C214" s="44"/>
       <c r="D214" s="83"/>
       <c r="E214" s="44"/>
       <c r="F214" s="64"/>
-    </row>
-    <row r="215" spans="1:6">
+      <c r="G214" s="94"/>
+    </row>
+    <row r="215" spans="1:7">
       <c r="A215" s="79"/>
       <c r="B215" s="44"/>
       <c r="C215" s="44"/>
       <c r="D215" s="83"/>
       <c r="E215" s="44"/>
       <c r="F215" s="64"/>
-    </row>
-    <row r="216" spans="1:6">
+      <c r="G215" s="94"/>
+    </row>
+    <row r="216" spans="1:7">
       <c r="A216" s="79"/>
       <c r="B216" s="44"/>
       <c r="C216" s="44"/>
       <c r="D216" s="83"/>
       <c r="E216" s="44"/>
       <c r="F216" s="64"/>
-    </row>
-    <row r="217" spans="1:6">
+      <c r="G216" s="94"/>
+    </row>
+    <row r="217" spans="1:7">
       <c r="A217" s="79"/>
       <c r="B217" s="44"/>
       <c r="C217" s="44"/>
       <c r="D217" s="83"/>
       <c r="E217" s="44"/>
       <c r="F217" s="64"/>
-    </row>
-    <row r="218" spans="1:6">
+      <c r="G217" s="94"/>
+    </row>
+    <row r="218" spans="1:7">
       <c r="A218" s="79"/>
       <c r="B218" s="44"/>
       <c r="C218" s="44"/>
       <c r="D218" s="83"/>
       <c r="E218" s="44"/>
       <c r="F218" s="64"/>
-    </row>
-    <row r="219" spans="1:6">
+      <c r="G218" s="94"/>
+    </row>
+    <row r="219" spans="1:7">
       <c r="A219" s="79"/>
       <c r="B219" s="44"/>
       <c r="C219" s="44"/>
       <c r="D219" s="83"/>
       <c r="E219" s="44"/>
       <c r="F219" s="64"/>
-    </row>
-    <row r="220" spans="1:6">
+      <c r="G219" s="94"/>
+    </row>
+    <row r="220" spans="1:7">
       <c r="A220" s="79"/>
       <c r="B220" s="44"/>
       <c r="C220" s="44"/>
       <c r="D220" s="83"/>
       <c r="E220" s="44"/>
       <c r="F220" s="64"/>
-    </row>
-    <row r="221" spans="1:6">
+      <c r="G220" s="94"/>
+    </row>
+    <row r="221" spans="1:7">
       <c r="A221" s="79"/>
       <c r="B221" s="44"/>
       <c r="C221" s="44"/>
       <c r="D221" s="83"/>
       <c r="E221" s="44"/>
       <c r="F221" s="64"/>
-    </row>
-    <row r="222" spans="1:6">
+      <c r="G221" s="94"/>
+    </row>
+    <row r="222" spans="1:7">
       <c r="A222" s="79"/>
       <c r="B222" s="44"/>
       <c r="C222" s="44"/>
       <c r="D222" s="83"/>
       <c r="E222" s="44"/>
       <c r="F222" s="64"/>
-    </row>
-    <row r="223" spans="1:6">
+      <c r="G222" s="94"/>
+    </row>
+    <row r="223" spans="1:7">
       <c r="A223" s="79"/>
       <c r="B223" s="44"/>
       <c r="C223" s="44"/>
       <c r="D223" s="83"/>
       <c r="E223" s="44"/>
       <c r="F223" s="64"/>
-    </row>
-    <row r="224" spans="1:6">
+      <c r="G223" s="94"/>
+    </row>
+    <row r="224" spans="1:7">
       <c r="A224" s="79"/>
       <c r="B224" s="44"/>
       <c r="C224" s="44"/>
       <c r="D224" s="83"/>
       <c r="E224" s="44"/>
       <c r="F224" s="64"/>
-    </row>
-    <row r="225" spans="1:6">
+      <c r="G224" s="94"/>
+    </row>
+    <row r="225" spans="1:7">
       <c r="A225" s="79"/>
       <c r="B225" s="44"/>
       <c r="C225" s="44"/>
       <c r="D225" s="83"/>
       <c r="E225" s="44"/>
       <c r="F225" s="64"/>
-    </row>
-    <row r="226" spans="1:6">
+      <c r="G225" s="94"/>
+    </row>
+    <row r="226" spans="1:7">
       <c r="A226" s="79"/>
       <c r="B226" s="44"/>
       <c r="C226" s="44"/>
       <c r="D226" s="83"/>
       <c r="E226" s="44"/>
       <c r="F226" s="64"/>
-    </row>
-    <row r="227" spans="1:6">
+      <c r="G226" s="94"/>
+    </row>
+    <row r="227" spans="1:7">
       <c r="A227" s="79"/>
       <c r="B227" s="44"/>
       <c r="C227" s="44"/>
       <c r="D227" s="83"/>
       <c r="E227" s="44"/>
       <c r="F227" s="64"/>
-    </row>
-    <row r="228" spans="1:6">
+      <c r="G227" s="94"/>
+    </row>
+    <row r="228" spans="1:7">
       <c r="A228" s="79"/>
       <c r="B228" s="44"/>
       <c r="C228" s="44"/>
       <c r="D228" s="83"/>
       <c r="E228" s="44"/>
       <c r="F228" s="64"/>
-    </row>
-    <row r="229" spans="1:6">
+      <c r="G228" s="94"/>
+    </row>
+    <row r="229" spans="1:7">
       <c r="A229" s="79"/>
       <c r="B229" s="44"/>
       <c r="C229" s="44"/>
       <c r="D229" s="83"/>
       <c r="E229" s="44"/>
       <c r="F229" s="64"/>
-    </row>
-    <row r="230" spans="1:6">
+      <c r="G229" s="94"/>
+    </row>
+    <row r="230" spans="1:7">
       <c r="A230" s="79"/>
       <c r="B230" s="44"/>
       <c r="C230" s="44"/>
       <c r="D230" s="83"/>
       <c r="E230" s="44"/>
       <c r="F230" s="64"/>
-    </row>
-    <row r="231" spans="1:6">
+      <c r="G230" s="94"/>
+    </row>
+    <row r="231" spans="1:7">
       <c r="A231" s="79"/>
       <c r="B231" s="44"/>
       <c r="C231" s="44"/>
       <c r="D231" s="83"/>
       <c r="E231" s="44"/>
       <c r="F231" s="64"/>
-    </row>
-    <row r="232" spans="1:6">
+      <c r="G231" s="94"/>
+    </row>
+    <row r="232" spans="1:7">
       <c r="A232" s="79"/>
       <c r="B232" s="44"/>
       <c r="C232" s="44"/>
       <c r="D232" s="83"/>
       <c r="E232" s="44"/>
       <c r="F232" s="64"/>
-    </row>
-    <row r="233" spans="1:6">
+      <c r="G232" s="94"/>
+    </row>
+    <row r="233" spans="1:7">
       <c r="A233" s="79"/>
       <c r="B233" s="44"/>
       <c r="C233" s="44"/>
       <c r="D233" s="83"/>
       <c r="E233" s="44"/>
       <c r="F233" s="64"/>
-    </row>
-    <row r="234" spans="1:6">
+      <c r="G233" s="94"/>
+    </row>
+    <row r="234" spans="1:7">
       <c r="A234" s="79"/>
       <c r="B234" s="44"/>
       <c r="C234" s="44"/>
       <c r="D234" s="83"/>
       <c r="E234" s="44"/>
       <c r="F234" s="64"/>
-    </row>
-    <row r="235" spans="1:6">
+      <c r="G234" s="94"/>
+    </row>
+    <row r="235" spans="1:7">
       <c r="A235" s="79"/>
       <c r="B235" s="44"/>
       <c r="C235" s="44"/>
       <c r="D235" s="83"/>
       <c r="E235" s="44"/>
       <c r="F235" s="64"/>
-    </row>
-    <row r="236" spans="1:6">
+      <c r="G235" s="94"/>
+    </row>
+    <row r="236" spans="1:7">
       <c r="A236" s="79"/>
       <c r="B236" s="44"/>
       <c r="C236" s="44"/>
       <c r="D236" s="83"/>
       <c r="E236" s="44"/>
       <c r="F236" s="64"/>
-    </row>
-    <row r="237" spans="1:6">
+      <c r="G236" s="94"/>
+    </row>
+    <row r="237" spans="1:7">
       <c r="A237" s="79"/>
       <c r="B237" s="44"/>
       <c r="C237" s="44"/>
       <c r="D237" s="83"/>
       <c r="E237" s="44"/>
       <c r="F237" s="64"/>
-    </row>
-    <row r="238" spans="1:6">
+      <c r="G237" s="94"/>
+    </row>
+    <row r="238" spans="1:7">
       <c r="A238" s="79"/>
       <c r="B238" s="44"/>
       <c r="C238" s="44"/>
       <c r="D238" s="83"/>
       <c r="E238" s="44"/>
       <c r="F238" s="64"/>
-    </row>
-    <row r="239" spans="1:6">
+      <c r="G238" s="94"/>
+    </row>
+    <row r="239" spans="1:7">
       <c r="A239" s="79"/>
       <c r="B239" s="44"/>
       <c r="C239" s="44"/>
       <c r="D239" s="83"/>
       <c r="E239" s="44"/>
       <c r="F239" s="64"/>
-    </row>
-    <row r="240" spans="1:6">
+      <c r="G239" s="94"/>
+    </row>
+    <row r="240" spans="1:7">
       <c r="A240" s="79"/>
       <c r="B240" s="44"/>
       <c r="C240" s="44"/>
       <c r="D240" s="83"/>
       <c r="E240" s="44"/>
       <c r="F240" s="64"/>
-    </row>
-    <row r="241" spans="1:6">
+      <c r="G240" s="94"/>
+    </row>
+    <row r="241" spans="1:7">
       <c r="A241" s="79"/>
       <c r="B241" s="44"/>
       <c r="C241" s="44"/>
       <c r="D241" s="83"/>
       <c r="E241" s="44"/>
       <c r="F241" s="64"/>
-    </row>
-    <row r="242" spans="1:6">
+      <c r="G241" s="94"/>
+    </row>
+    <row r="242" spans="1:7">
       <c r="A242" s="79"/>
       <c r="B242" s="44"/>
       <c r="C242" s="44"/>
       <c r="D242" s="83"/>
       <c r="E242" s="44"/>
       <c r="F242" s="64"/>
-    </row>
-    <row r="243" spans="1:6">
+      <c r="G242" s="94"/>
+    </row>
+    <row r="243" spans="1:7">
       <c r="A243" s="79"/>
       <c r="B243" s="44"/>
       <c r="C243" s="44"/>
       <c r="D243" s="83"/>
       <c r="E243" s="44"/>
       <c r="F243" s="64"/>
-    </row>
-    <row r="244" spans="1:6">
+      <c r="G243" s="94"/>
+    </row>
+    <row r="244" spans="1:7">
       <c r="A244" s="79"/>
       <c r="B244" s="44"/>
       <c r="C244" s="44"/>
       <c r="D244" s="83"/>
       <c r="E244" s="44"/>
       <c r="F244" s="64"/>
-    </row>
-    <row r="245" spans="1:6">
+      <c r="G244" s="94"/>
+    </row>
+    <row r="245" spans="1:7">
       <c r="A245" s="79"/>
       <c r="B245" s="44"/>
       <c r="C245" s="44"/>
       <c r="D245" s="83"/>
       <c r="E245" s="44"/>
       <c r="F245" s="64"/>
-    </row>
-    <row r="246" spans="1:6">
+      <c r="G245" s="94"/>
+    </row>
+    <row r="246" spans="1:7">
       <c r="A246" s="79"/>
       <c r="B246" s="44"/>
       <c r="C246" s="44"/>
       <c r="D246" s="83"/>
       <c r="E246" s="44"/>
       <c r="F246" s="64"/>
-    </row>
-    <row r="247" spans="1:6">
+      <c r="G246" s="94"/>
+    </row>
+    <row r="247" spans="1:7">
       <c r="A247" s="79"/>
       <c r="B247" s="44"/>
       <c r="C247" s="44"/>
       <c r="D247" s="83"/>
       <c r="E247" s="44"/>
       <c r="F247" s="64"/>
-    </row>
-    <row r="248" spans="1:6">
+      <c r="G247" s="94"/>
+    </row>
+    <row r="248" spans="1:7">
       <c r="A248" s="79"/>
       <c r="B248" s="44"/>
       <c r="C248" s="44"/>
       <c r="D248" s="83"/>
       <c r="E248" s="44"/>
       <c r="F248" s="64"/>
-    </row>
-    <row r="249" spans="1:6">
+      <c r="G248" s="94"/>
+    </row>
+    <row r="249" spans="1:7">
       <c r="A249" s="79"/>
       <c r="B249" s="44"/>
       <c r="C249" s="44"/>
       <c r="D249" s="83"/>
       <c r="E249" s="44"/>
       <c r="F249" s="64"/>
-    </row>
-    <row r="250" spans="1:6">
+      <c r="G249" s="94"/>
+    </row>
+    <row r="250" spans="1:7">
       <c r="A250" s="79"/>
       <c r="B250" s="44"/>
       <c r="C250" s="44"/>
       <c r="D250" s="83"/>
       <c r="E250" s="44"/>
       <c r="F250" s="64"/>
-    </row>
-    <row r="251" spans="1:6">
+      <c r="G250" s="94"/>
+    </row>
+    <row r="251" spans="1:7">
       <c r="A251" s="79"/>
       <c r="B251" s="44"/>
       <c r="C251" s="44"/>
       <c r="D251" s="83"/>
       <c r="E251" s="44"/>
       <c r="F251" s="64"/>
-    </row>
-    <row r="252" spans="1:6">
+      <c r="G251" s="94"/>
+    </row>
+    <row r="252" spans="1:7">
       <c r="A252" s="79"/>
       <c r="B252" s="44"/>
       <c r="C252" s="44"/>
       <c r="D252" s="83"/>
       <c r="E252" s="44"/>
       <c r="F252" s="64"/>
-    </row>
-    <row r="253" spans="1:6">
+      <c r="G252" s="94"/>
+    </row>
+    <row r="253" spans="1:7">
       <c r="A253" s="79"/>
       <c r="B253" s="44"/>
       <c r="C253" s="44"/>
       <c r="D253" s="83"/>
       <c r="E253" s="44"/>
       <c r="F253" s="64"/>
-    </row>
-    <row r="254" spans="1:6">
+      <c r="G253" s="94"/>
+    </row>
+    <row r="254" spans="1:7">
       <c r="A254" s="79"/>
       <c r="B254" s="44"/>
       <c r="C254" s="44"/>
       <c r="D254" s="83"/>
       <c r="E254" s="44"/>
       <c r="F254" s="64"/>
-    </row>
-    <row r="255" spans="1:6">
+      <c r="G254" s="94"/>
+    </row>
+    <row r="255" spans="1:7">
       <c r="A255" s="79"/>
       <c r="B255" s="44"/>
       <c r="C255" s="44"/>
       <c r="D255" s="83"/>
       <c r="E255" s="44"/>
       <c r="F255" s="64"/>
-    </row>
-    <row r="256" spans="1:6">
+      <c r="G255" s="94"/>
+    </row>
+    <row r="256" spans="1:7">
       <c r="A256" s="79"/>
       <c r="B256" s="44"/>
       <c r="C256" s="44"/>
       <c r="D256" s="83"/>
       <c r="E256" s="44"/>
       <c r="F256" s="64"/>
-    </row>
-    <row r="257" spans="1:6">
+      <c r="G256" s="94"/>
+    </row>
+    <row r="257" spans="1:7">
       <c r="A257" s="79"/>
       <c r="B257" s="44"/>
       <c r="C257" s="44"/>
       <c r="D257" s="83"/>
       <c r="E257" s="44"/>
       <c r="F257" s="64"/>
-    </row>
-    <row r="258" spans="1:6">
+      <c r="G257" s="94"/>
+    </row>
+    <row r="258" spans="1:7">
       <c r="A258" s="79"/>
       <c r="B258" s="44"/>
       <c r="C258" s="44"/>
       <c r="D258" s="83"/>
       <c r="E258" s="44"/>
       <c r="F258" s="64"/>
-    </row>
-    <row r="259" spans="1:6">
+      <c r="G258" s="94"/>
+    </row>
+    <row r="259" spans="1:7">
       <c r="A259" s="79"/>
       <c r="B259" s="44"/>
       <c r="C259" s="44"/>
       <c r="D259" s="83"/>
       <c r="E259" s="44"/>
       <c r="F259" s="64"/>
-    </row>
-    <row r="260" spans="1:6">
+      <c r="G259" s="94"/>
+    </row>
+    <row r="260" spans="1:7">
       <c r="A260" s="79"/>
       <c r="B260" s="44"/>
       <c r="C260" s="44"/>
       <c r="D260" s="83"/>
       <c r="E260" s="44"/>
       <c r="F260" s="64"/>
-    </row>
-    <row r="261" spans="1:6">
+      <c r="G260" s="94"/>
+    </row>
+    <row r="261" spans="1:7">
       <c r="A261" s="79"/>
       <c r="B261" s="44"/>
       <c r="C261" s="44"/>
       <c r="D261" s="83"/>
       <c r="E261" s="44"/>
       <c r="F261" s="64"/>
-    </row>
-    <row r="262" spans="1:6">
+      <c r="G261" s="94"/>
+    </row>
+    <row r="262" spans="1:7">
       <c r="A262" s="79"/>
       <c r="B262" s="44"/>
       <c r="C262" s="44"/>
       <c r="D262" s="83"/>
       <c r="E262" s="44"/>
       <c r="F262" s="64"/>
-    </row>
-    <row r="263" spans="1:6">
+      <c r="G262" s="94"/>
+    </row>
+    <row r="263" spans="1:7">
       <c r="A263" s="79"/>
       <c r="B263" s="44"/>
       <c r="C263" s="44"/>
       <c r="D263" s="83"/>
       <c r="E263" s="44"/>
       <c r="F263" s="64"/>
-    </row>
-    <row r="264" spans="1:6">
+      <c r="G263" s="94"/>
+    </row>
+    <row r="264" spans="1:7">
       <c r="A264" s="79"/>
       <c r="B264" s="44"/>
       <c r="C264" s="44"/>
       <c r="D264" s="83"/>
       <c r="E264" s="44"/>
       <c r="F264" s="64"/>
-    </row>
-    <row r="265" spans="1:6">
+      <c r="G264" s="94"/>
+    </row>
+    <row r="265" spans="1:7">
       <c r="A265" s="79"/>
       <c r="B265" s="44"/>
       <c r="C265" s="44"/>
       <c r="D265" s="83"/>
       <c r="E265" s="44"/>
       <c r="F265" s="64"/>
-    </row>
-    <row r="266" spans="1:6">
+      <c r="G265" s="94"/>
+    </row>
+    <row r="266" spans="1:7">
       <c r="A266" s="79"/>
       <c r="B266" s="44"/>
       <c r="C266" s="44"/>
       <c r="D266" s="83"/>
       <c r="E266" s="44"/>
       <c r="F266" s="64"/>
-    </row>
-    <row r="267" spans="1:6">
+      <c r="G266" s="94"/>
+    </row>
+    <row r="267" spans="1:7">
       <c r="A267" s="79"/>
       <c r="B267" s="44"/>
       <c r="C267" s="44"/>
       <c r="D267" s="83"/>
       <c r="E267" s="44"/>
       <c r="F267" s="64"/>
-    </row>
-    <row r="268" spans="1:6">
+      <c r="G267" s="94"/>
+    </row>
+    <row r="268" spans="1:7">
       <c r="A268" s="79"/>
       <c r="B268" s="44"/>
       <c r="C268" s="44"/>
       <c r="D268" s="83"/>
       <c r="E268" s="44"/>
       <c r="F268" s="64"/>
-    </row>
-    <row r="269" spans="1:6">
+      <c r="G268" s="94"/>
+    </row>
+    <row r="269" spans="1:7">
       <c r="A269" s="79"/>
       <c r="B269" s="44"/>
       <c r="C269" s="44"/>
       <c r="D269" s="83"/>
       <c r="E269" s="44"/>
       <c r="F269" s="64"/>
-    </row>
-    <row r="270" spans="1:6">
+      <c r="G269" s="94"/>
+    </row>
+    <row r="270" spans="1:7">
       <c r="A270" s="79"/>
       <c r="B270" s="44"/>
       <c r="C270" s="44"/>
       <c r="D270" s="83"/>
       <c r="E270" s="44"/>
       <c r="F270" s="64"/>
-    </row>
-    <row r="271" spans="1:6">
+      <c r="G270" s="94"/>
+    </row>
+    <row r="271" spans="1:7">
       <c r="A271" s="79"/>
       <c r="B271" s="44"/>
       <c r="C271" s="44"/>
       <c r="D271" s="83"/>
       <c r="E271" s="44"/>
       <c r="F271" s="64"/>
-    </row>
-    <row r="272" spans="1:6">
+      <c r="G271" s="94"/>
+    </row>
+    <row r="272" spans="1:7">
       <c r="A272" s="79"/>
       <c r="B272" s="44"/>
       <c r="C272" s="44"/>
       <c r="D272" s="83"/>
       <c r="E272" s="44"/>
       <c r="F272" s="64"/>
-    </row>
-    <row r="273" spans="1:6">
+      <c r="G272" s="94"/>
+    </row>
+    <row r="273" spans="1:7">
       <c r="A273" s="79"/>
       <c r="B273" s="44"/>
       <c r="C273" s="44"/>
       <c r="D273" s="83"/>
       <c r="E273" s="44"/>
       <c r="F273" s="64"/>
-    </row>
-    <row r="274" spans="1:6">
+      <c r="G273" s="94"/>
+    </row>
+    <row r="274" spans="1:7">
       <c r="A274" s="79"/>
       <c r="B274" s="44"/>
       <c r="C274" s="44"/>
       <c r="D274" s="83"/>
       <c r="E274" s="44"/>
       <c r="F274" s="64"/>
-    </row>
-    <row r="275" spans="1:6">
+      <c r="G274" s="94"/>
+    </row>
+    <row r="275" spans="1:7">
       <c r="A275" s="79"/>
       <c r="B275" s="44"/>
       <c r="C275" s="44"/>
       <c r="D275" s="83"/>
       <c r="E275" s="44"/>
       <c r="F275" s="64"/>
-    </row>
-    <row r="276" spans="1:6">
+      <c r="G275" s="94"/>
+    </row>
+    <row r="276" spans="1:7">
       <c r="A276" s="79"/>
       <c r="B276" s="44"/>
       <c r="C276" s="44"/>
       <c r="D276" s="83"/>
       <c r="E276" s="44"/>
       <c r="F276" s="64"/>
-    </row>
-    <row r="277" spans="1:6">
+      <c r="G276" s="94"/>
+    </row>
+    <row r="277" spans="1:7">
       <c r="A277" s="79"/>
       <c r="B277" s="44"/>
       <c r="C277" s="44"/>
       <c r="D277" s="83"/>
       <c r="E277" s="44"/>
       <c r="F277" s="64"/>
-    </row>
-    <row r="278" spans="1:6">
+      <c r="G277" s="94"/>
+    </row>
+    <row r="278" spans="1:7">
       <c r="A278" s="79"/>
       <c r="B278" s="44"/>
       <c r="C278" s="44"/>
       <c r="D278" s="83"/>
       <c r="E278" s="44"/>
       <c r="F278" s="64"/>
-    </row>
-    <row r="279" spans="1:6">
+      <c r="G278" s="94"/>
+    </row>
+    <row r="279" spans="1:7">
       <c r="A279" s="79"/>
       <c r="B279" s="44"/>
       <c r="C279" s="44"/>
       <c r="D279" s="83"/>
       <c r="E279" s="44"/>
       <c r="F279" s="64"/>
-    </row>
-    <row r="280" spans="1:6">
+      <c r="G279" s="94"/>
+    </row>
+    <row r="280" spans="1:7">
       <c r="A280" s="79"/>
       <c r="B280" s="44"/>
       <c r="C280" s="44"/>
       <c r="D280" s="83"/>
       <c r="E280" s="44"/>
       <c r="F280" s="64"/>
-    </row>
-    <row r="281" spans="1:6">
+      <c r="G280" s="94"/>
+    </row>
+    <row r="281" spans="1:7">
       <c r="A281" s="79"/>
       <c r="B281" s="44"/>
       <c r="C281" s="44"/>
       <c r="D281" s="83"/>
       <c r="E281" s="44"/>
       <c r="F281" s="64"/>
-    </row>
-    <row r="282" spans="1:6">
+      <c r="G281" s="94"/>
+    </row>
+    <row r="282" spans="1:7">
       <c r="A282" s="79"/>
       <c r="B282" s="44"/>
       <c r="C282" s="44"/>
       <c r="D282" s="83"/>
       <c r="E282" s="44"/>
       <c r="F282" s="64"/>
-    </row>
-    <row r="283" spans="1:6">
+      <c r="G282" s="94"/>
+    </row>
+    <row r="283" spans="1:7">
       <c r="A283" s="79"/>
       <c r="B283" s="44"/>
       <c r="C283" s="44"/>
       <c r="D283" s="83"/>
       <c r="E283" s="44"/>
       <c r="F283" s="64"/>
-    </row>
-    <row r="284" spans="1:6">
+      <c r="G283" s="94"/>
+    </row>
+    <row r="284" spans="1:7">
       <c r="A284" s="79"/>
       <c r="B284" s="44"/>
       <c r="C284" s="44"/>
       <c r="D284" s="83"/>
       <c r="E284" s="44"/>
       <c r="F284" s="64"/>
-    </row>
-    <row r="285" spans="1:6">
+      <c r="G284" s="94"/>
+    </row>
+    <row r="285" spans="1:7">
       <c r="A285" s="79"/>
       <c r="B285" s="44"/>
       <c r="C285" s="44"/>
       <c r="D285" s="83"/>
       <c r="E285" s="44"/>
       <c r="F285" s="64"/>
-    </row>
-    <row r="286" spans="1:6">
+      <c r="G285" s="94"/>
+    </row>
+    <row r="286" spans="1:7">
       <c r="A286" s="79"/>
       <c r="B286" s="44"/>
       <c r="C286" s="44"/>
       <c r="D286" s="83"/>
       <c r="E286" s="44"/>
       <c r="F286" s="64"/>
-    </row>
-    <row r="287" spans="1:6">
+      <c r="G286" s="94"/>
+    </row>
+    <row r="287" spans="1:7">
       <c r="A287" s="79"/>
       <c r="B287" s="44"/>
       <c r="C287" s="44"/>
       <c r="D287" s="83"/>
       <c r="E287" s="44"/>
       <c r="F287" s="64"/>
-    </row>
-    <row r="288" spans="1:6">
+      <c r="G287" s="94"/>
+    </row>
+    <row r="288" spans="1:7">
       <c r="A288" s="79"/>
       <c r="B288" s="44"/>
       <c r="C288" s="44"/>
       <c r="D288" s="83"/>
       <c r="E288" s="44"/>
       <c r="F288" s="64"/>
-    </row>
-    <row r="289" spans="1:6">
+      <c r="G288" s="94"/>
+    </row>
+    <row r="289" spans="1:7">
       <c r="A289" s="79"/>
       <c r="B289" s="44"/>
       <c r="C289" s="44"/>
       <c r="D289" s="83"/>
       <c r="E289" s="44"/>
       <c r="F289" s="64"/>
-    </row>
-    <row r="290" spans="1:6">
+      <c r="G289" s="94"/>
+    </row>
+    <row r="290" spans="1:7">
       <c r="A290" s="79"/>
       <c r="B290" s="44"/>
       <c r="C290" s="44"/>
       <c r="D290" s="83"/>
       <c r="E290" s="44"/>
       <c r="F290" s="64"/>
-    </row>
-    <row r="291" spans="1:6">
+      <c r="G290" s="94"/>
+    </row>
+    <row r="291" spans="1:7">
       <c r="A291" s="79"/>
       <c r="B291" s="44"/>
       <c r="C291" s="44"/>
       <c r="D291" s="83"/>
       <c r="E291" s="44"/>
       <c r="F291" s="64"/>
-    </row>
-    <row r="292" spans="1:6">
+      <c r="G291" s="94"/>
+    </row>
+    <row r="292" spans="1:7">
       <c r="A292" s="79"/>
       <c r="B292" s="44"/>
       <c r="C292" s="44"/>
       <c r="D292" s="83"/>
       <c r="E292" s="44"/>
       <c r="F292" s="64"/>
-    </row>
-    <row r="293" spans="1:6">
+      <c r="G292" s="94"/>
+    </row>
+    <row r="293" spans="1:7">
       <c r="A293" s="79"/>
       <c r="B293" s="44"/>
       <c r="C293" s="44"/>
       <c r="D293" s="83"/>
       <c r="E293" s="44"/>
       <c r="F293" s="64"/>
-    </row>
-    <row r="294" spans="1:6">
+      <c r="G293" s="94"/>
+    </row>
+    <row r="294" spans="1:7">
       <c r="A294" s="79"/>
       <c r="B294" s="44"/>
       <c r="C294" s="44"/>
       <c r="D294" s="83"/>
       <c r="E294" s="44"/>
       <c r="F294" s="64"/>
-    </row>
-    <row r="295" spans="1:6">
+      <c r="G294" s="94"/>
+    </row>
+    <row r="295" spans="1:7">
       <c r="A295" s="79"/>
       <c r="B295" s="44"/>
       <c r="C295" s="44"/>
       <c r="D295" s="83"/>
       <c r="E295" s="44"/>
       <c r="F295" s="64"/>
-    </row>
-    <row r="296" spans="1:6">
+      <c r="G295" s="94"/>
+    </row>
+    <row r="296" spans="1:7">
       <c r="A296" s="79"/>
       <c r="B296" s="44"/>
       <c r="C296" s="44"/>
       <c r="D296" s="83"/>
       <c r="E296" s="44"/>
       <c r="F296" s="64"/>
-    </row>
-    <row r="297" spans="1:6">
+      <c r="G296" s="94"/>
+    </row>
+    <row r="297" spans="1:7">
       <c r="A297" s="79"/>
       <c r="B297" s="44"/>
       <c r="C297" s="44"/>
       <c r="D297" s="83"/>
       <c r="E297" s="44"/>
       <c r="F297" s="64"/>
-    </row>
-    <row r="298" spans="1:6">
+      <c r="G297" s="94"/>
+    </row>
+    <row r="298" spans="1:7">
       <c r="A298" s="79"/>
       <c r="B298" s="44"/>
       <c r="C298" s="44"/>
       <c r="D298" s="83"/>
       <c r="E298" s="44"/>
       <c r="F298" s="64"/>
-    </row>
-    <row r="299" spans="1:6">
+      <c r="G298" s="94"/>
+    </row>
+    <row r="299" spans="1:7">
       <c r="A299" s="79"/>
       <c r="B299" s="44"/>
       <c r="C299" s="44"/>
       <c r="D299" s="83"/>
       <c r="E299" s="44"/>
       <c r="F299" s="64"/>
-    </row>
-    <row r="300" spans="1:6">
+      <c r="G299" s="94"/>
+    </row>
+    <row r="300" spans="1:7">
       <c r="A300" s="79"/>
       <c r="B300" s="44"/>
       <c r="C300" s="44"/>
       <c r="D300" s="83"/>
       <c r="E300" s="44"/>
       <c r="F300" s="64"/>
-    </row>
-    <row r="301" spans="1:6">
+      <c r="G300" s="94"/>
+    </row>
+    <row r="301" spans="1:7">
       <c r="A301" s="79"/>
       <c r="B301" s="44"/>
       <c r="C301" s="44"/>
       <c r="D301" s="83"/>
       <c r="E301" s="44"/>
       <c r="F301" s="64"/>
-    </row>
-    <row r="302" spans="1:6">
+      <c r="G301" s="94"/>
+    </row>
+    <row r="302" spans="1:7">
       <c r="A302" s="79"/>
       <c r="B302" s="44"/>
       <c r="C302" s="44"/>
       <c r="D302" s="83"/>
       <c r="E302" s="44"/>
       <c r="F302" s="64"/>
-    </row>
-    <row r="303" spans="1:6">
+      <c r="G302" s="94"/>
+    </row>
+    <row r="303" spans="1:7">
       <c r="A303" s="79"/>
       <c r="B303" s="44"/>
       <c r="C303" s="44"/>
       <c r="D303" s="83"/>
       <c r="E303" s="44"/>
       <c r="F303" s="64"/>
-    </row>
-    <row r="304" spans="1:6">
+      <c r="G303" s="94"/>
+    </row>
+    <row r="304" spans="1:7">
       <c r="A304" s="79"/>
       <c r="B304" s="44"/>
       <c r="C304" s="44"/>
       <c r="D304" s="83"/>
       <c r="E304" s="44"/>
       <c r="F304" s="64"/>
-    </row>
-    <row r="305" spans="1:6">
+      <c r="G304" s="94"/>
+    </row>
+    <row r="305" spans="1:7">
       <c r="A305" s="80"/>
       <c r="B305" s="66"/>
       <c r="C305" s="66"/>
       <c r="D305" s="84"/>
       <c r="E305" s="66"/>
       <c r="F305" s="73"/>
+      <c r="G305" s="94"/>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A3:F3"/>
   </mergeCells>
-  <dataValidations count="2">
+  <dataValidations count="3">
     <dataValidation type="list" sqref="B6:B105" xr:uid="{00000000-0002-0000-0300-000000000000}">
       <formula1>"Água,Luz,IPTU,Condomínio,Seguro,Internet,Piscina,Jardinagem,Manutenção geral,Investimento,Reposição,Taxas,Outro"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="ID inválido" error="Selecione um ID existente na lista de reservas." promptTitle="Vincular à locação" prompt="Selecione o ID da reserva quando esta despesa pertencer a uma locação. Em branco = despesa geral." sqref="E6:E305" xr:uid="{00000000-0002-0000-0300-000001000000}">
       <formula1>OFFSET(INDIRECT("RESERVAS!$A$6"),0,0,MAX(1,COUNTA(INDIRECT("RESERVAS!$B$6:$B$205"))),1)</formula1>
     </dataValidation>
+    <dataValidation type="list" sqref="G6:G305" xr:uid="{00000000-0002-0000-0300-000002000000}">
+      <formula1>"Casa Cinza,Casa Laranja"</formula1>
+    </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
-      <x14:conditionalFormattings>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="expression" priority="1" id="{00000000-000E-0000-0300-000001000000}">
-            <xm:f>AND(E6&lt;&gt;"",COUNTIF(RESERVAS!$A$6:$A$204,E6)=0)</xm:f>
-            <x14:dxf>
-              <font>
-                <color rgb="FFB91C1C"/>
-              </font>
-              <fill>
-                <patternFill patternType="solid">
-                  <bgColor rgb="FFF8D7DA"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>E6:E305</xm:sqref>
-        </x14:conditionalFormatting>
-      </x14:conditionalFormattings>
-    </ext>
-  </extLst>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
     <col min="2" max="2" width="8" customWidth="1"/>
     <col min="4" max="4" width="28" customWidth="1"/>
-    <col min="5" max="6" width="18" customWidth="1"/>
+    <col min="5" max="7" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="24" customHeight="1">
-      <c r="A1" s="93" t="s">
-        <v>93</v>
-      </c>
-      <c r="B1" s="93"/>
-      <c r="C1" s="93"/>
-      <c r="D1" s="93"/>
-    </row>
-    <row r="3" spans="1:6" ht="24" customHeight="1">
+    <row r="1" spans="1:7" ht="24" customHeight="1">
+      <c r="A1" s="96" t="s">
+        <v>100</v>
+      </c>
+      <c r="B1" s="96"/>
+      <c r="C1" s="96"/>
+      <c r="D1" s="96"/>
+    </row>
+    <row r="3" spans="1:7" ht="24" customHeight="1">
       <c r="A3" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="D3" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="E3" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="F3" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="F3" s="3" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
+      <c r="G3" s="93" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
       <c r="A4" t="s">
         <v>19</v>
       </c>
@@ -17012,16 +17660,19 @@
         <v>1</v>
       </c>
       <c r="D4" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="E4" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="F4" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="5" spans="1:6">
+      <c r="G4" s="95" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
       <c r="A5" t="s">
         <v>22</v>
       </c>
@@ -17029,16 +17680,19 @@
         <v>2</v>
       </c>
       <c r="D5" t="s">
-        <v>97</v>
+        <v>123</v>
       </c>
       <c r="E5" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="F5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
+        <v>87</v>
+      </c>
+      <c r="G5" s="95" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
       <c r="A6" t="s">
         <v>24</v>
       </c>
@@ -17046,16 +17700,17 @@
         <v>3</v>
       </c>
       <c r="D6" t="s">
-        <v>100</v>
+        <v>86</v>
       </c>
       <c r="E6" t="s">
         <v>82</v>
       </c>
       <c r="F6" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
+        <v>104</v>
+      </c>
+      <c r="G6" s="95"/>
+    </row>
+    <row r="7" spans="1:7">
       <c r="A7" t="s">
         <v>26</v>
       </c>
@@ -17063,16 +17718,17 @@
         <v>4</v>
       </c>
       <c r="D7" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="E7" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="F7" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
+        <v>107</v>
+      </c>
+      <c r="G7" s="95"/>
+    </row>
+    <row r="8" spans="1:7">
       <c r="A8" t="s">
         <v>28</v>
       </c>
@@ -17080,16 +17736,17 @@
         <v>5</v>
       </c>
       <c r="D8" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="E8" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="F8" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
+        <v>110</v>
+      </c>
+      <c r="G8" s="95"/>
+    </row>
+    <row r="9" spans="1:7">
       <c r="A9" t="s">
         <v>31</v>
       </c>
@@ -17100,10 +17757,10 @@
         <v>81</v>
       </c>
       <c r="F9" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
       <c r="A10" t="s">
         <v>32</v>
       </c>
@@ -17111,13 +17768,13 @@
         <v>7</v>
       </c>
       <c r="D10" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="F10" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
       <c r="A11" t="s">
         <v>33</v>
       </c>
@@ -17125,10 +17782,10 @@
         <v>8</v>
       </c>
       <c r="D11" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
       <c r="A12" t="s">
         <v>34</v>
       </c>
@@ -17136,10 +17793,10 @@
         <v>9</v>
       </c>
       <c r="D12" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
       <c r="A13" t="s">
         <v>35</v>
       </c>
@@ -17147,10 +17804,10 @@
         <v>10</v>
       </c>
       <c r="D13" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
       <c r="A14" t="s">
         <v>36</v>
       </c>
@@ -17158,10 +17815,10 @@
         <v>11</v>
       </c>
       <c r="D14" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
       <c r="A15" t="s">
         <v>37</v>
       </c>
@@ -17169,13 +17826,18 @@
         <v>12</v>
       </c>
       <c r="D15" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:D1"/>
   </mergeCells>
+  <dataValidations count="1">
+    <dataValidation type="list" sqref="G3:G5" xr:uid="{00000000-0002-0000-0400-000000000000}">
+      <formula1>"Casa Cinza,Casa Laranja"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Controle_Locacao.xlsx
+++ b/Controle_Locacao.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Renato.Neves\Documents\TRABALHOS 2025\LOCAÇÃO PRAIA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57514459-33F0-4018-8AE4-100F7AC13664}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C5F6A92-B94A-4C3E-82FF-023EDECBFCD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PAINEL" sheetId="1" r:id="rId1"/>
@@ -57,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="127">
   <si>
     <t>PAINEL FINANCEIRO E DE OCUPAÇÃO</t>
   </si>
@@ -432,6 +432,12 @@
   </si>
   <si>
     <t>Férias</t>
+  </si>
+  <si>
+    <t>Sogro Felipe</t>
+  </si>
+  <si>
+    <t>Luiz Moran</t>
   </si>
 </sst>
 </file>
@@ -1178,11 +1184,61 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>1676400</xdr:colOff>
+      <xdr:row>51</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="AutoShape 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{94528648-935B-33C3-FAD1-BB3E49C9A0E7}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="9525000" cy="9525000"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst/>
+          <a:ahLst/>
+          <a:cxnLst/>
+          <a:rect l="0" t="0" r="0" b="0"/>
+          <a:pathLst/>
+        </a:custGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:round/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1427,7 +1483,7 @@
       </c>
       <c r="N3" s="85">
         <f>SUMIFS(RESERVAS!$Y$6:$Y$204,RESERVAS!$I$6:$I$204,"&lt;&gt;Cancelada",RESERVAS!$I$6:$I$204,"&lt;&gt;Consulta")</f>
-        <v>26700</v>
+        <v>30574.25</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="20.25">
@@ -1436,7 +1492,7 @@
       </c>
       <c r="B5" s="9">
         <f>SUM(F13:F24)</f>
-        <v>13800</v>
+        <v>17674.25</v>
       </c>
       <c r="D5" s="8" t="s">
         <v>4</v>
@@ -1457,7 +1513,7 @@
       </c>
       <c r="K5" s="91">
         <f>SUM(I13:I24)</f>
-        <v>13767.95</v>
+        <v>17642.2</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="15.75">
@@ -1466,7 +1522,7 @@
       </c>
       <c r="B8" s="12">
         <f>SUM(C13:C24)</f>
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="C8" s="14"/>
       <c r="D8" s="74" t="s">
@@ -1474,21 +1530,21 @@
       </c>
       <c r="E8" s="12">
         <f>SUM(D13:D24)</f>
-        <v>711</v>
+        <v>700</v>
       </c>
       <c r="G8" s="8" t="s">
         <v>9</v>
       </c>
       <c r="H8" s="13">
         <f>IF(SUM(B13:B24)=0,0,SUM(C13:C24)/SUM(B13:B24))</f>
-        <v>2.6027397260273973E-2</v>
+        <v>4.1095890410958902E-2</v>
       </c>
       <c r="J8" s="8" t="s">
         <v>10</v>
       </c>
       <c r="K8" s="10">
         <f>IF(B8=0,0,B5/B8)</f>
-        <v>726.31578947368416</v>
+        <v>589.14166666666665</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="24" customHeight="1">
@@ -1901,15 +1957,15 @@
       </c>
       <c r="C21" s="89">
         <f>SUMPRODUCT((RESERVAS!$C$6:$C$204&lt;DATE($B$3,10,1))*(RESERVAS!$D$6:$D$204&gt;DATE($B$3,9,1))*(RESERVAS!$I$6:$I$204&lt;&gt;"Cancelada")*(RESERVAS!$I$6:$I$204&lt;&gt;"Consulta")*(((RESERVAS!$D$6:$D$204&lt;DATE($B$3,10,1))*RESERVAS!$D$6:$D$204+(RESERVAS!$D$6:$D$204&gt;=DATE($B$3,10,1))*DATE($B$3,10,1))-((RESERVAS!$C$6:$C$204&gt;DATE($B$3,9,1))*RESERVAS!$C$6:$C$204+(RESERVAS!$C$6:$C$204&lt;=DATE($B$3,9,1))*DATE($B$3,9,1))))</f>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D21" s="89">
         <f t="shared" si="0"/>
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E21" s="6">
         <f t="shared" si="1"/>
-        <v>0.13333333333333333</v>
+        <v>0.16666666666666666</v>
       </c>
       <c r="F21" s="5">
         <f>SUMPRODUCT((RESERVAS!$C$6:$C$204&lt;DATE($B$3,10,1))*(RESERVAS!$D$6:$D$204&gt;DATE($B$3,9,1))*(RESERVAS!$I$6:$I$204&lt;&gt;"Cancelada")*(RESERVAS!$I$6:$I$204&lt;&gt;"Consulta")*RESERVAS!$F$6:$F$204*(((RESERVAS!$D$6:$D$204&lt;DATE($B$3,10,1))*RESERVAS!$D$6:$D$204+(RESERVAS!$D$6:$D$204&gt;=DATE($B$3,10,1))*DATE($B$3,10,1))-((RESERVAS!$C$6:$C$204&gt;DATE($B$3,9,1))*RESERVAS!$C$6:$C$204+(RESERVAS!$C$6:$C$204&lt;=DATE($B$3,9,1))*DATE($B$3,9,1))))</f>
@@ -1942,19 +1998,19 @@
       </c>
       <c r="C22" s="89">
         <f>SUMPRODUCT((RESERVAS!$C$6:$C$204&lt;DATE($B$3,11,1))*(RESERVAS!$D$6:$D$204&gt;DATE($B$3,10,1))*(RESERVAS!$I$6:$I$204&lt;&gt;"Cancelada")*(RESERVAS!$I$6:$I$204&lt;&gt;"Consulta")*(((RESERVAS!$D$6:$D$204&lt;DATE($B$3,11,1))*RESERVAS!$D$6:$D$204+(RESERVAS!$D$6:$D$204&gt;=DATE($B$3,11,1))*DATE($B$3,11,1))-((RESERVAS!$C$6:$C$204&gt;DATE($B$3,10,1))*RESERVAS!$C$6:$C$204+(RESERVAS!$C$6:$C$204&lt;=DATE($B$3,10,1))*DATE($B$3,10,1))))</f>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D22" s="89">
         <f t="shared" si="0"/>
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="E22" s="6">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.14516129032258066</v>
       </c>
       <c r="F22" s="5">
         <f>SUMPRODUCT((RESERVAS!$C$6:$C$204&lt;DATE($B$3,11,1))*(RESERVAS!$D$6:$D$204&gt;DATE($B$3,10,1))*(RESERVAS!$I$6:$I$204&lt;&gt;"Cancelada")*(RESERVAS!$I$6:$I$204&lt;&gt;"Consulta")*RESERVAS!$F$6:$F$204*(((RESERVAS!$D$6:$D$204&lt;DATE($B$3,11,1))*RESERVAS!$D$6:$D$204+(RESERVAS!$D$6:$D$204&gt;=DATE($B$3,11,1))*DATE($B$3,11,1))-((RESERVAS!$C$6:$C$204&gt;DATE($B$3,10,1))*RESERVAS!$C$6:$C$204+(RESERVAS!$C$6:$C$204&lt;=DATE($B$3,10,1))*DATE($B$3,10,1))))</f>
-        <v>0</v>
+        <v>3874.25</v>
       </c>
       <c r="G22" s="5">
         <f>SUMPRODUCT((RESERVAS!$C$6:$C$204&lt;DATE($B$3,11,1))*(RESERVAS!$D$6:$D$204&gt;DATE($B$3,10,1))*(RESERVAS!$I$6:$I$204&lt;&gt;"Cancelada")*(RESERVAS!$I$6:$I$204&lt;&gt;"Consulta")*RESERVAS!$T$6:$T$204*(((RESERVAS!$D$6:$D$204&lt;DATE($B$3,11,1))*RESERVAS!$D$6:$D$204+(RESERVAS!$D$6:$D$204&gt;=DATE($B$3,11,1))*DATE($B$3,11,1))-((RESERVAS!$C$6:$C$204&gt;DATE($B$3,10,1))*RESERVAS!$C$6:$C$204+(RESERVAS!$C$6:$C$204&lt;=DATE($B$3,10,1))*DATE($B$3,10,1))))</f>
@@ -1966,11 +2022,11 @@
       </c>
       <c r="I22" s="87">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>3874.25</v>
       </c>
       <c r="J22" s="16">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:14" ht="18">
@@ -2364,12 +2420,14 @@
       <c r="F8" s="33" t="str">
         <f>IF(MONTH((DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+26))&lt;&gt;$K$2,"",TEXT((DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+26),"dd")&amp;CHAR(10)&amp;IF(COUNTIFS(RESERVAS!$C$6:$C$204,"&lt;="&amp;(DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+26),RESERVAS!$D$6:$D$204,"&gt;"&amp;(DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+26),RESERVAS!$I$6:$I$204,"&lt;&gt;Cancelada",RESERVAS!$I$6:$I$204,"&lt;&gt;Consulta")=0,"DISPONÍVEL",IF(COUNTIFS(RESERVAS!$C$6:$C$204,"&lt;="&amp;(DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+26),RESERVAS!$D$6:$D$204,"&gt;"&amp;(DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+26),RESERVAS!$I$6:$I$204,"&lt;&gt;Cancelada",RESERVAS!$I$6:$I$204,"&lt;&gt;Consulta")=1,"ALUGADA","CONFLITO"))&amp;IF(COUNTIFS(RESERVAS!$C$6:$C$204,"&lt;="&amp;(DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+26),RESERVAS!$D$6:$D$204,"&gt;"&amp;(DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+26),RESERVAS!$I$6:$I$204,"&lt;&gt;Cancelada",RESERVAS!$I$6:$I$204,"&lt;&gt;Consulta")=0,"",CHAR(10)&amp;IFERROR(LOOKUP(2,1/((RESERVAS!$C$6:$C$204&lt;=(DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+26))*(RESERVAS!$D$6:$D$204&gt;(DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+26))*(RESERVAS!$I$6:$I$204&lt;&gt;"Cancelada")*(RESERVAS!$I$6:$I$204&lt;&gt;"Consulta")),RESERVAS!$B$6:$B$204),"")))</f>
         <v>26
-DISPONÍVEL</v>
+ALUGADA
+Sogro Felipe</v>
       </c>
       <c r="G8" s="34" t="str">
         <f>IF(MONTH((DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+27))&lt;&gt;$K$2,"",TEXT((DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+27),"dd")&amp;CHAR(10)&amp;IF(COUNTIFS(RESERVAS!$C$6:$C$204,"&lt;="&amp;(DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+27),RESERVAS!$D$6:$D$204,"&gt;"&amp;(DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+27),RESERVAS!$I$6:$I$204,"&lt;&gt;Cancelada",RESERVAS!$I$6:$I$204,"&lt;&gt;Consulta")=0,"DISPONÍVEL",IF(COUNTIFS(RESERVAS!$C$6:$C$204,"&lt;="&amp;(DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+27),RESERVAS!$D$6:$D$204,"&gt;"&amp;(DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+27),RESERVAS!$I$6:$I$204,"&lt;&gt;Cancelada",RESERVAS!$I$6:$I$204,"&lt;&gt;Consulta")=1,"ALUGADA","CONFLITO"))&amp;IF(COUNTIFS(RESERVAS!$C$6:$C$204,"&lt;="&amp;(DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+27),RESERVAS!$D$6:$D$204,"&gt;"&amp;(DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+27),RESERVAS!$I$6:$I$204,"&lt;&gt;Cancelada",RESERVAS!$I$6:$I$204,"&lt;&gt;Consulta")=0,"",CHAR(10)&amp;IFERROR(LOOKUP(2,1/((RESERVAS!$C$6:$C$204&lt;=(DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+27))*(RESERVAS!$D$6:$D$204&gt;(DATE($E$2,$K$2,1)-WEEKDAY(DATE($E$2,$K$2,1),2)+1+27))*(RESERVAS!$I$6:$I$204&lt;&gt;"Cancelada")*(RESERVAS!$I$6:$I$204&lt;&gt;"Consulta")),RESERVAS!$B$6:$B$204),"")))</f>
         <v>27
-DISPONÍVEL</v>
+ALUGADA
+Sogro Felipe</v>
       </c>
       <c r="I8" s="35" t="s">
         <v>6</v>
@@ -2416,7 +2474,7 @@
       </c>
       <c r="J9" s="37">
         <f>SUMPRODUCT((RESERVAS!$C$6:$C$204&lt;DATE($E$2,$K$2+1,1))*(RESERVAS!$D$6:$D$204&gt;DATE($E$2,$K$2,1))*(RESERVAS!$I$6:$I$204&lt;&gt;"Cancelada")*(RESERVAS!$I$6:$I$204&lt;&gt;"Consulta")*(((RESERVAS!$D$6:$D$204&lt;DATE($E$2,$K$2+1,1))*RESERVAS!$D$6:$D$204+(RESERVAS!$D$6:$D$204&gt;=DATE($E$2,$K$2+1,1))*DATE($E$2,$K$2+1,1))-((RESERVAS!$C$6:$C$204&gt;DATE($E$2,$K$2,1))*RESERVAS!$C$6:$C$204+(RESERVAS!$C$6:$C$204&lt;=DATE($E$2,$K$2,1))*DATE($E$2,$K$2,1))))</f>
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:12" ht="60.75" customHeight="1">
@@ -2453,7 +2511,7 @@
       </c>
       <c r="J10" s="38">
         <f>IF(DAY(EOMONTH(DATE($E$2,$K$2,1),0))=0,0,J9/DAY(EOMONTH(DATE($E$2,$K$2,1),0)))</f>
-        <v>0.26666666666666666</v>
+        <v>0.33333333333333331</v>
       </c>
     </row>
     <row r="12" spans="1:12" ht="15">
@@ -3201,23 +3259,35 @@
     <row r="12" spans="1:28">
       <c r="A12" s="62" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="B12" s="43"/>
-      <c r="C12" s="45"/>
-      <c r="D12" s="45"/>
+        <v>LOC-007</v>
+      </c>
+      <c r="B12" s="43" t="s">
+        <v>125</v>
+      </c>
+      <c r="C12" s="45">
+        <v>46291</v>
+      </c>
+      <c r="D12" s="45">
+        <v>46293</v>
+      </c>
       <c r="E12" s="50">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F12" s="47"/>
       <c r="G12" s="51">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="H12" s="43"/>
-      <c r="I12" s="43"/>
-      <c r="J12" s="54"/>
+      <c r="H12" s="43" t="s">
+        <v>89</v>
+      </c>
+      <c r="I12" s="43" t="s">
+        <v>82</v>
+      </c>
+      <c r="J12" s="54" t="s">
+        <v>83</v>
+      </c>
       <c r="K12" s="47"/>
       <c r="L12" s="47"/>
       <c r="M12" s="47"/>
@@ -3253,31 +3323,48 @@
       </c>
       <c r="Z12" s="49" t="str">
         <f t="shared" si="8"/>
-        <v/>
+        <v>OK</v>
       </c>
       <c r="AA12" s="63"/>
-      <c r="AB12" s="94"/>
+      <c r="AB12" s="94" t="s">
+        <v>119</v>
+      </c>
     </row>
     <row r="13" spans="1:28">
       <c r="A13" s="62" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="B13" s="43"/>
-      <c r="C13" s="45"/>
-      <c r="D13" s="45"/>
+        <v>LOC-008</v>
+      </c>
+      <c r="B13" s="43" t="s">
+        <v>126</v>
+      </c>
+      <c r="C13" s="45">
+        <v>46305</v>
+      </c>
+      <c r="D13" s="45">
+        <v>46314</v>
+      </c>
       <c r="E13" s="50">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="F13" s="47"/>
+        <v>9</v>
+      </c>
+      <c r="F13" s="47">
+        <f>3874.25/9</f>
+        <v>430.47222222222223</v>
+      </c>
       <c r="G13" s="51">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H13" s="43"/>
-      <c r="I13" s="43"/>
-      <c r="J13" s="54"/>
+        <v>3874.25</v>
+      </c>
+      <c r="H13" s="43" t="s">
+        <v>89</v>
+      </c>
+      <c r="I13" s="43" t="s">
+        <v>82</v>
+      </c>
+      <c r="J13" s="54" t="s">
+        <v>83</v>
+      </c>
       <c r="K13" s="47"/>
       <c r="L13" s="47"/>
       <c r="M13" s="47"/>
@@ -3296,27 +3383,29 @@
       </c>
       <c r="U13" s="51">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>3874.25</v>
       </c>
       <c r="V13" s="51">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>430.47222222222223</v>
       </c>
       <c r="W13" s="52">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X13" s="47"/>
       <c r="Y13" s="58">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>3874.25</v>
       </c>
       <c r="Z13" s="49" t="str">
         <f t="shared" si="8"/>
-        <v/>
+        <v>OK</v>
       </c>
       <c r="AA13" s="63"/>
-      <c r="AB13" s="94"/>
+      <c r="AB13" s="94" t="s">
+        <v>119</v>
+      </c>
     </row>
     <row r="14" spans="1:28">
       <c r="A14" s="62" t="str">

--- a/Controle_Locacao.xlsx
+++ b/Controle_Locacao.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Renato.Neves\Documents\TRABALHOS 2025\LOCAÇÃO PRAIA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C5F6A92-B94A-4C3E-82FF-023EDECBFCD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E0141B7-2BC0-4101-A5B9-D983EF609DDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1019,14 +1019,14 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1203,6 +1203,60 @@
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{94528648-935B-33C3-FAD1-BB3E49C9A0E7}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="9525000" cy="9525000"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst/>
+          <a:ahLst/>
+          <a:cxnLst/>
+          <a:rect l="0" t="0" r="0" b="0"/>
+          <a:pathLst/>
+        </a:custGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:round/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>1676400</xdr:colOff>
+      <xdr:row>51</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="AutoShape 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EBB5BD9A-1AF1-D6AD-C283-F10B0EA3155C}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1578,11 +1632,11 @@
       <c r="J12" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="L12" s="97" t="s">
+      <c r="L12" s="98" t="s">
         <v>18</v>
       </c>
-      <c r="M12" s="97"/>
-      <c r="N12" s="97"/>
+      <c r="M12" s="98"/>
+      <c r="N12" s="98"/>
     </row>
     <row r="13" spans="1:14" ht="18">
       <c r="A13" s="15" t="s">
@@ -2245,12 +2299,12 @@
       <c r="G4" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="I4" s="98" t="s">
+      <c r="I4" s="99" t="s">
         <v>47</v>
       </c>
-      <c r="J4" s="98"/>
-      <c r="K4" s="98"/>
-      <c r="L4" s="98"/>
+      <c r="J4" s="99"/>
+      <c r="K4" s="99"/>
+      <c r="L4" s="99"/>
     </row>
     <row r="5" spans="1:12" ht="60.75" customHeight="1">
       <c r="A5" s="29" t="str">
@@ -2522,12 +2576,12 @@
       <c r="E12" s="92"/>
       <c r="F12" s="92"/>
       <c r="G12" s="92"/>
-      <c r="I12" s="97" t="s">
+      <c r="I12" s="98" t="s">
         <v>48</v>
       </c>
-      <c r="J12" s="97"/>
-      <c r="K12" s="97"/>
-      <c r="L12" s="97"/>
+      <c r="J12" s="98"/>
+      <c r="K12" s="98"/>
+      <c r="L12" s="98"/>
     </row>
     <row r="13" spans="1:12" ht="15">
       <c r="A13" s="92"/>
@@ -2657,35 +2711,35 @@
       <c r="AA1" s="96"/>
     </row>
     <row r="3" spans="1:28">
-      <c r="A3" s="99" t="s">
+      <c r="A3" s="97" t="s">
         <v>117</v>
       </c>
-      <c r="B3" s="99"/>
-      <c r="C3" s="99"/>
-      <c r="D3" s="99"/>
-      <c r="E3" s="99"/>
-      <c r="F3" s="99"/>
-      <c r="G3" s="99"/>
-      <c r="H3" s="99"/>
-      <c r="I3" s="99"/>
-      <c r="J3" s="99"/>
-      <c r="K3" s="99"/>
-      <c r="L3" s="99"/>
-      <c r="M3" s="99"/>
-      <c r="N3" s="99"/>
-      <c r="O3" s="99"/>
-      <c r="P3" s="99"/>
-      <c r="Q3" s="99"/>
-      <c r="R3" s="99"/>
-      <c r="S3" s="99"/>
-      <c r="T3" s="99"/>
-      <c r="U3" s="99"/>
-      <c r="V3" s="99"/>
-      <c r="W3" s="99"/>
-      <c r="X3" s="99"/>
-      <c r="Y3" s="99"/>
-      <c r="Z3" s="99"/>
-      <c r="AA3" s="99"/>
+      <c r="B3" s="97"/>
+      <c r="C3" s="97"/>
+      <c r="D3" s="97"/>
+      <c r="E3" s="97"/>
+      <c r="F3" s="97"/>
+      <c r="G3" s="97"/>
+      <c r="H3" s="97"/>
+      <c r="I3" s="97"/>
+      <c r="J3" s="97"/>
+      <c r="K3" s="97"/>
+      <c r="L3" s="97"/>
+      <c r="M3" s="97"/>
+      <c r="N3" s="97"/>
+      <c r="O3" s="97"/>
+      <c r="P3" s="97"/>
+      <c r="Q3" s="97"/>
+      <c r="R3" s="97"/>
+      <c r="S3" s="97"/>
+      <c r="T3" s="97"/>
+      <c r="U3" s="97"/>
+      <c r="V3" s="97"/>
+      <c r="W3" s="97"/>
+      <c r="X3" s="97"/>
+      <c r="Y3" s="97"/>
+      <c r="Z3" s="97"/>
+      <c r="AA3" s="97"/>
     </row>
     <row r="5" spans="1:28" ht="24" customHeight="1">
       <c r="A5" s="2" t="s">
@@ -3286,7 +3340,7 @@
         <v>82</v>
       </c>
       <c r="J12" s="54" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="K12" s="47"/>
       <c r="L12" s="47"/>
@@ -14944,14 +14998,14 @@
       <c r="F1" s="96"/>
     </row>
     <row r="3" spans="1:7" ht="27.2" customHeight="1">
-      <c r="A3" s="99" t="s">
+      <c r="A3" s="97" t="s">
         <v>92</v>
       </c>
-      <c r="B3" s="99"/>
-      <c r="C3" s="99"/>
-      <c r="D3" s="99"/>
-      <c r="E3" s="99"/>
-      <c r="F3" s="99"/>
+      <c r="B3" s="97"/>
+      <c r="C3" s="97"/>
+      <c r="D3" s="97"/>
+      <c r="E3" s="97"/>
+      <c r="F3" s="97"/>
     </row>
     <row r="5" spans="1:7" ht="24" customHeight="1">
       <c r="A5" s="2" t="s">

--- a/Controle_Locacao.xlsx
+++ b/Controle_Locacao.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Renato.Neves\Documents\TRABALHOS 2025\LOCAÇÃO PRAIA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4979B0F7-9AB6-4A39-B245-FD821628CD5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96554C20-B748-44EA-A023-30CCBC7ED24B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PAINEL" sheetId="1" r:id="rId1"/>
@@ -18,6 +18,7 @@
     <sheet name="RESERVAS" sheetId="3" r:id="rId3"/>
     <sheet name="DESPESAS CASA" sheetId="4" r:id="rId4"/>
     <sheet name="LISTAS" sheetId="5" r:id="rId5"/>
+    <sheet name="PGTOS" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -56,8 +57,64 @@
 </comments>
 </file>
 
+<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Renato.Neves</author>
+  </authors>
+  <commentList>
+    <comment ref="E3" authorId="0" shapeId="0" xr:uid="{62588A23-1D47-4B24-B09E-D6BA54470A05}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Segoe UI"/>
+            <family val="2"/>
+          </rPr>
+          <t>Renato.Neves:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Segoe UI"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Novas locações do canal Direto aparecem automaticamente. Quando surgir 'Configurar pagamento', informe as condições de pagamento na área de parâmetros azuis.</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="156">
   <si>
     <t>PAINEL FINANCEIRO E DE OCUPAÇÃO</t>
   </si>
@@ -460,20 +517,87 @@
   <si>
     <t>Média de pessoas</t>
   </si>
+  <si>
+    <t>ID da locação</t>
+  </si>
+  <si>
+    <t>Valor (R$)</t>
+  </si>
+  <si>
+    <t>Hóspede</t>
+  </si>
+  <si>
+    <t>CONTROLE DE PAGAMENTOS</t>
+  </si>
+  <si>
+    <t>Total contrato</t>
+  </si>
+  <si>
+    <t>Parcela</t>
+  </si>
+  <si>
+    <t>Vencimento</t>
+  </si>
+  <si>
+    <t>Valor previsto</t>
+  </si>
+  <si>
+    <t>Valor pago</t>
+  </si>
+  <si>
+    <t>Data pagamento</t>
+  </si>
+  <si>
+    <t>Saldo em aberto</t>
+  </si>
+  <si>
+    <t>PARÂMETROS EDITÁVEIS</t>
+  </si>
+  <si>
+    <t>CARLOS</t>
+  </si>
+  <si>
+    <t>Valor / Data</t>
+  </si>
+  <si>
+    <t>Primeiro vencimento</t>
+  </si>
+  <si>
+    <t>Parcela mensal</t>
+  </si>
+  <si>
+    <t>Quantidade parcelas</t>
+  </si>
+  <si>
+    <t>MIGUEL</t>
+  </si>
+  <si>
+    <t>LOC-005</t>
+  </si>
+  <si>
+    <t>LOC-006</t>
+  </si>
+  <si>
+    <t>Situação do controle</t>
+  </si>
+  <si>
+    <t>Alerta prazo</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="6">
+  <numFmts count="7">
     <numFmt numFmtId="164" formatCode="\R\$\ #,##0.00;[Red]\-\R\$\ #,##0.00;\R\$\ 0.00"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
     <numFmt numFmtId="166" formatCode="\R\$\ #,##0.00"/>
     <numFmt numFmtId="167" formatCode="0;[Red]\-0;;"/>
     <numFmt numFmtId="168" formatCode="\R\$\ #,##0.00;[Red]\-\R\$\ #,##0.00;;"/>
     <numFmt numFmtId="169" formatCode="0.0%;[Red]\-0.0%;;"/>
+    <numFmt numFmtId="170" formatCode="[$R$-416]\ #,##0.00;[Red]\-[$R$-416]\ #,##0.00;;"/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="30">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -605,8 +729,48 @@
       <color rgb="FFFFFFFF"/>
       <name val="Carlito"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Carlito"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Carlito"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Carlito"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF008000"/>
+      <name val="Carlito"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF0070C0"/>
+      <name val="Carlito"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="17">
+  <fills count="20">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -689,8 +853,26 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D2330"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE2E3E5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="22">
+  <borders count="24">
     <border>
       <left/>
       <right/>
@@ -925,11 +1107,29 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color rgb="FF1D2330"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="105">
+  <cellXfs count="128">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1054,6 +1254,51 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="19" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="170" fontId="23" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="12" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="25" fillId="19" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="170" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="170" fontId="27" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="14" fontId="27" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="170" fontId="23" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="16" fontId="23" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="23" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="23" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="170" fontId="23" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1066,30 +1311,87 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="1" fontId="19" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="170" fontId="27" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="14" fontId="27" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="35">
+  <dxfs count="20">
     <dxf>
       <font>
-        <color rgb="FF9C0006"/>
+        <b/>
+        <i val="0"/>
+        <color rgb="FF7F6000"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFF2CC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color theme="0"/>
       </font>
       <fill>
         <patternFill patternType="solid">
           <fgColor indexed="64"/>
           <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1109,23 +1411,12 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF006100"/>
+        <color rgb="FF9C0006"/>
       </font>
       <fill>
         <patternFill patternType="solid">
           <fgColor indexed="64"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFFF0000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1174,150 +1465,6 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF000000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="8" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FF0BFDA1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF166534"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFDCFCE7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF991B1B"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFEE2E2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF92400E"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFEF3C7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF991B1B"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFEE2E2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF000000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="8" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <color rgb="FF006100"/>
       </font>
       <fill>
@@ -1334,50 +1481,7 @@
       <fill>
         <patternFill patternType="solid">
           <fgColor indexed="64"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF166534"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFDCFCE7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF991B1B"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFEE2E2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF92400E"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFEF3C7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF991B1B"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFEE2E2"/>
+          <bgColor rgb="FF0BFDA1"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1775,6 +1879,114 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>1676400</xdr:colOff>
+      <xdr:row>51</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="7" name="AutoShape 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B232ABAB-947D-EC12-B6CE-E29549540822}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="9525000" cy="10439400"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst/>
+          <a:ahLst/>
+          <a:cxnLst/>
+          <a:rect l="0" t="0" r="0" b="0"/>
+          <a:pathLst/>
+        </a:custGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:round/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>1676400</xdr:colOff>
+      <xdr:row>51</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="8" name="AutoShape 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F4D54CCB-B758-D879-3A00-9D4BAAD367D4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="9525000" cy="10439400"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst/>
+          <a:ahLst/>
+          <a:cxnLst/>
+          <a:rect l="0" t="0" r="0" b="0"/>
+          <a:pathLst/>
+        </a:custGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:round/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -2013,22 +2225,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="24" customHeight="1">
-      <c r="A1" s="96" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="96"/>
-      <c r="C1" s="96"/>
-      <c r="D1" s="96"/>
-      <c r="E1" s="96"/>
-      <c r="F1" s="96"/>
-      <c r="G1" s="96"/>
-      <c r="H1" s="96"/>
-      <c r="I1" s="96"/>
-      <c r="J1" s="96"/>
-      <c r="K1" s="96"/>
-      <c r="L1" s="96"/>
-      <c r="M1" s="96"/>
-      <c r="N1" s="96"/>
+      <c r="A1" s="119" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="119"/>
+      <c r="C1" s="119"/>
+      <c r="D1" s="119"/>
+      <c r="E1" s="119"/>
+      <c r="F1" s="119"/>
+      <c r="G1" s="119"/>
+      <c r="H1" s="119"/>
+      <c r="I1" s="119"/>
+      <c r="J1" s="119"/>
+      <c r="K1" s="119"/>
+      <c r="L1" s="119"/>
+      <c r="M1" s="119"/>
+      <c r="N1" s="119"/>
     </row>
     <row r="3" spans="1:14" ht="23.25">
       <c r="A3" s="1" t="s">
@@ -2137,11 +2349,11 @@
       <c r="J12" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="L12" s="97" t="s">
+      <c r="L12" s="120" t="s">
         <v>18</v>
       </c>
-      <c r="M12" s="97"/>
-      <c r="N12" s="97"/>
+      <c r="M12" s="120"/>
+      <c r="N12" s="120"/>
     </row>
     <row r="13" spans="1:14" ht="18">
       <c r="A13" s="15" t="s">
@@ -2704,7 +2916,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I13:I24">
-    <cfRule type="cellIs" dxfId="34" priority="2" operator="lessThan">
+    <cfRule type="cellIs" dxfId="19" priority="2" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2746,20 +2958,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="24" customHeight="1">
-      <c r="A1" s="96" t="s">
+      <c r="A1" s="119" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="96"/>
-      <c r="C1" s="96"/>
-      <c r="D1" s="96"/>
-      <c r="E1" s="96"/>
-      <c r="F1" s="96"/>
-      <c r="G1" s="96"/>
-      <c r="H1" s="96"/>
-      <c r="I1" s="96"/>
-      <c r="J1" s="96"/>
-      <c r="K1" s="96"/>
-      <c r="L1" s="96"/>
+      <c r="B1" s="119"/>
+      <c r="C1" s="119"/>
+      <c r="D1" s="119"/>
+      <c r="E1" s="119"/>
+      <c r="F1" s="119"/>
+      <c r="G1" s="119"/>
+      <c r="H1" s="119"/>
+      <c r="I1" s="119"/>
+      <c r="J1" s="119"/>
+      <c r="K1" s="119"/>
+      <c r="L1" s="119"/>
     </row>
     <row r="2" spans="1:12" ht="15">
       <c r="A2" s="1" t="s">
@@ -2804,12 +3016,12 @@
       <c r="G4" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="I4" s="98" t="s">
+      <c r="I4" s="121" t="s">
         <v>47</v>
       </c>
-      <c r="J4" s="98"/>
-      <c r="K4" s="98"/>
-      <c r="L4" s="98"/>
+      <c r="J4" s="121"/>
+      <c r="K4" s="121"/>
+      <c r="L4" s="121"/>
     </row>
     <row r="5" spans="1:12" ht="60.75" customHeight="1">
       <c r="A5" s="29" t="str">
@@ -3079,12 +3291,12 @@
       <c r="E12" s="92"/>
       <c r="F12" s="92"/>
       <c r="G12" s="92"/>
-      <c r="I12" s="97" t="s">
+      <c r="I12" s="120" t="s">
         <v>48</v>
       </c>
-      <c r="J12" s="97"/>
-      <c r="K12" s="97"/>
-      <c r="L12" s="97"/>
+      <c r="J12" s="120"/>
+      <c r="K12" s="120"/>
+      <c r="L12" s="120"/>
     </row>
     <row r="13" spans="1:12" ht="15">
       <c r="A13" s="92"/>
@@ -3131,13 +3343,13 @@
     <mergeCell ref="I12:L12"/>
   </mergeCells>
   <conditionalFormatting sqref="A5:G10">
-    <cfRule type="expression" dxfId="33" priority="1">
+    <cfRule type="expression" dxfId="18" priority="1">
       <formula>ISNUMBER(SEARCH("DISPONÍVEL",A5))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="32" priority="2">
+    <cfRule type="expression" dxfId="17" priority="2">
       <formula>ISNUMBER(SEARCH("ALUGADA",A5))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="31" priority="3">
+    <cfRule type="expression" dxfId="16" priority="3">
       <formula>ISNUMBER(SEARCH("CONFLITO",A5))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3185,72 +3397,72 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:34" ht="24" customHeight="1">
-      <c r="A1" s="96" t="s">
+      <c r="A1" s="119" t="s">
         <v>55</v>
       </c>
-      <c r="B1" s="96"/>
-      <c r="C1" s="96"/>
-      <c r="D1" s="96"/>
-      <c r="E1" s="96"/>
-      <c r="F1" s="96"/>
-      <c r="G1" s="96"/>
-      <c r="H1" s="96"/>
-      <c r="I1" s="96"/>
-      <c r="J1" s="96"/>
-      <c r="K1" s="96"/>
-      <c r="L1" s="96"/>
-      <c r="M1" s="96"/>
-      <c r="N1" s="96"/>
-      <c r="O1" s="96"/>
-      <c r="P1" s="96"/>
-      <c r="Q1" s="96"/>
-      <c r="R1" s="96"/>
-      <c r="S1" s="96"/>
-      <c r="T1" s="96"/>
-      <c r="U1" s="96"/>
-      <c r="V1" s="96"/>
-      <c r="W1" s="96"/>
-      <c r="X1" s="96"/>
-      <c r="Y1" s="96"/>
-      <c r="Z1" s="96"/>
-      <c r="AA1" s="96"/>
+      <c r="B1" s="119"/>
+      <c r="C1" s="119"/>
+      <c r="D1" s="119"/>
+      <c r="E1" s="119"/>
+      <c r="F1" s="119"/>
+      <c r="G1" s="119"/>
+      <c r="H1" s="119"/>
+      <c r="I1" s="119"/>
+      <c r="J1" s="119"/>
+      <c r="K1" s="119"/>
+      <c r="L1" s="119"/>
+      <c r="M1" s="119"/>
+      <c r="N1" s="119"/>
+      <c r="O1" s="119"/>
+      <c r="P1" s="119"/>
+      <c r="Q1" s="119"/>
+      <c r="R1" s="119"/>
+      <c r="S1" s="119"/>
+      <c r="T1" s="119"/>
+      <c r="U1" s="119"/>
+      <c r="V1" s="119"/>
+      <c r="W1" s="119"/>
+      <c r="X1" s="119"/>
+      <c r="Y1" s="119"/>
+      <c r="Z1" s="119"/>
+      <c r="AA1" s="119"/>
     </row>
     <row r="3" spans="1:34">
-      <c r="A3" s="99" t="s">
+      <c r="A3" s="122" t="s">
         <v>117</v>
       </c>
-      <c r="B3" s="99"/>
-      <c r="C3" s="99"/>
-      <c r="D3" s="99"/>
-      <c r="E3" s="99"/>
-      <c r="F3" s="99"/>
-      <c r="G3" s="99"/>
-      <c r="H3" s="99"/>
-      <c r="I3" s="99"/>
-      <c r="J3" s="99"/>
-      <c r="K3" s="99"/>
-      <c r="L3" s="99"/>
-      <c r="M3" s="99"/>
-      <c r="N3" s="99"/>
-      <c r="O3" s="99"/>
-      <c r="P3" s="99"/>
-      <c r="Q3" s="99"/>
-      <c r="R3" s="99"/>
-      <c r="S3" s="99"/>
-      <c r="T3" s="99"/>
-      <c r="U3" s="99"/>
-      <c r="V3" s="99"/>
-      <c r="W3" s="99"/>
-      <c r="X3" s="99"/>
-      <c r="Y3" s="99"/>
-      <c r="Z3" s="99"/>
-      <c r="AA3" s="99"/>
+      <c r="B3" s="122"/>
+      <c r="C3" s="122"/>
+      <c r="D3" s="122"/>
+      <c r="E3" s="122"/>
+      <c r="F3" s="122"/>
+      <c r="G3" s="122"/>
+      <c r="H3" s="122"/>
+      <c r="I3" s="122"/>
+      <c r="J3" s="122"/>
+      <c r="K3" s="122"/>
+      <c r="L3" s="122"/>
+      <c r="M3" s="122"/>
+      <c r="N3" s="122"/>
+      <c r="O3" s="122"/>
+      <c r="P3" s="122"/>
+      <c r="Q3" s="122"/>
+      <c r="R3" s="122"/>
+      <c r="S3" s="122"/>
+      <c r="T3" s="122"/>
+      <c r="U3" s="122"/>
+      <c r="V3" s="122"/>
+      <c r="W3" s="122"/>
+      <c r="X3" s="122"/>
+      <c r="Y3" s="122"/>
+      <c r="Z3" s="122"/>
+      <c r="AA3" s="122"/>
     </row>
     <row r="4" spans="1:34" ht="15">
-      <c r="AG4" s="103" t="s">
+      <c r="AG4" s="123" t="s">
         <v>133</v>
       </c>
-      <c r="AH4" s="103"/>
+      <c r="AH4" s="123"/>
     </row>
     <row r="5" spans="1:34" ht="24" customHeight="1">
       <c r="A5" s="2" t="s">
@@ -3337,19 +3549,19 @@
       <c r="AB5" s="93" t="s">
         <v>118</v>
       </c>
-      <c r="AC5" s="100" t="s">
+      <c r="AC5" s="96" t="s">
         <v>130</v>
       </c>
-      <c r="AD5" s="100" t="s">
+      <c r="AD5" s="96" t="s">
         <v>131</v>
       </c>
-      <c r="AE5" s="102" t="s">
+      <c r="AE5" s="98" t="s">
         <v>132</v>
       </c>
-      <c r="AG5" s="100" t="s">
+      <c r="AG5" s="96" t="s">
         <v>119</v>
       </c>
-      <c r="AH5" s="100" t="s">
+      <c r="AH5" s="96" t="s">
         <v>120</v>
       </c>
     </row>
@@ -3433,11 +3645,12 @@
         <v>1</v>
       </c>
       <c r="X6" s="57">
-        <v>0</v>
+        <f>2200*2</f>
+        <v>4400</v>
       </c>
       <c r="Y6" s="58">
         <f t="shared" ref="Y6:Y68" si="7">IF(B6="",0,IFERROR(MAX(0,G6-X6),G6))</f>
-        <v>11000</v>
+        <v>6600</v>
       </c>
       <c r="Z6" s="60" t="str">
         <f t="shared" ref="Z6:Z37" si="8">IF(B6="","",IF(COUNTIFS($C$6:$C$203,"&lt;"&amp;D6,$D$6:$D$203,"&gt;"&amp;C6,$I$6:$I$203,"&lt;&gt;Cancelada",$I$6:$I$203,"&lt;&gt;Consulta",$AB$6:$AB$203,$AB6)&gt;1,"CONFLITO","OK"))</f>
@@ -3455,15 +3668,15 @@
       <c r="AD6">
         <v>0</v>
       </c>
-      <c r="AE6" s="101" t="str">
+      <c r="AE6" s="97" t="str">
         <f>IF((AC6+AD6)=0,"",AC6+AD6)</f>
         <v/>
       </c>
-      <c r="AG6" s="104">
+      <c r="AG6" s="99">
         <f>IFERROR(SUMIF($AB$6:$AB$1000,AG$5,$AE$6:$AE$1000)/COUNTIFS($AB$6:$AB$1000,AG$5,$AE$6:$AE$1000,"&gt;0"),"")</f>
         <v>4.166666666666667</v>
       </c>
-      <c r="AH6" s="104">
+      <c r="AH6" s="99">
         <f>IFERROR(SUMIF($AB$6:$AB$1000,AH$5,$AE$6:$AE$1000)/COUNTIFS($AB$6:$AB$1000,AH$5,$AE$6:$AE$1000,"&gt;0"),"")</f>
         <v>5</v>
       </c>
@@ -3549,7 +3762,7 @@
       <c r="AB7" s="94" t="s">
         <v>119</v>
       </c>
-      <c r="AE7" s="101" t="str">
+      <c r="AE7" s="97" t="str">
         <f t="shared" ref="AE7:AE70" si="9">IF((AC7+AD7)=0,"",AC7+AD7)</f>
         <v/>
       </c>
@@ -3580,7 +3793,7 @@
         <v>0</v>
       </c>
       <c r="H8" s="43" t="s">
-        <v>89</v>
+        <v>124</v>
       </c>
       <c r="I8" s="43" t="s">
         <v>106</v>
@@ -3635,7 +3848,7 @@
       <c r="AD8">
         <v>0</v>
       </c>
-      <c r="AE8" s="101">
+      <c r="AE8" s="97">
         <f t="shared" si="9"/>
         <v>4</v>
       </c>
@@ -3718,7 +3931,7 @@
       <c r="AC9">
         <v>5</v>
       </c>
-      <c r="AE9" s="101">
+      <c r="AE9" s="97">
         <f t="shared" si="9"/>
         <v>5</v>
       </c>
@@ -3785,10 +3998,12 @@
         <f t="shared" si="6"/>
         <v>1</v>
       </c>
-      <c r="X10" s="47"/>
+      <c r="X10" s="47">
+        <v>3925</v>
+      </c>
       <c r="Y10" s="58">
         <f t="shared" si="7"/>
-        <v>6600</v>
+        <v>2675</v>
       </c>
       <c r="Z10" s="49" t="str">
         <f t="shared" si="8"/>
@@ -3801,7 +4016,7 @@
       <c r="AC10">
         <v>5</v>
       </c>
-      <c r="AE10" s="101">
+      <c r="AE10" s="97">
         <f t="shared" si="9"/>
         <v>5</v>
       </c>
@@ -3884,7 +4099,7 @@
       <c r="AC11">
         <v>5</v>
       </c>
-      <c r="AE11" s="101">
+      <c r="AE11" s="97">
         <f t="shared" si="9"/>
         <v>5</v>
       </c>
@@ -3916,7 +4131,7 @@
         <v>3874.25</v>
       </c>
       <c r="H12" s="43" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="I12" s="43" t="s">
         <v>82</v>
@@ -3965,7 +4180,7 @@
       <c r="AB12" s="94" t="s">
         <v>119</v>
       </c>
-      <c r="AE12" s="101" t="str">
+      <c r="AE12" s="97" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
@@ -3997,7 +4212,7 @@
         <v>6396.57</v>
       </c>
       <c r="H13" s="43" t="s">
-        <v>89</v>
+        <v>124</v>
       </c>
       <c r="I13" s="43" t="s">
         <v>82</v>
@@ -4052,7 +4267,7 @@
       <c r="AD13">
         <v>1</v>
       </c>
-      <c r="AE13" s="101">
+      <c r="AE13" s="97">
         <f t="shared" si="9"/>
         <v>2</v>
       </c>
@@ -4084,7 +4299,7 @@
         <v>2070.85</v>
       </c>
       <c r="H14" s="43" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="I14" s="43" t="s">
         <v>82</v>
@@ -4139,7 +4354,7 @@
       <c r="AD14">
         <v>2</v>
       </c>
-      <c r="AE14" s="101">
+      <c r="AE14" s="97">
         <f t="shared" si="9"/>
         <v>5</v>
       </c>
@@ -4222,7 +4437,7 @@
       <c r="AC15">
         <v>4</v>
       </c>
-      <c r="AE15" s="101">
+      <c r="AE15" s="97">
         <f t="shared" si="9"/>
         <v>4</v>
       </c>
@@ -4306,7 +4521,7 @@
       <c r="AC16">
         <v>5</v>
       </c>
-      <c r="AE16" s="101">
+      <c r="AE16" s="97">
         <f t="shared" si="9"/>
         <v>5</v>
       </c>
@@ -4370,7 +4585,7 @@
       </c>
       <c r="AA17" s="63"/>
       <c r="AB17" s="94"/>
-      <c r="AE17" s="101" t="str">
+      <c r="AE17" s="97" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
@@ -4434,7 +4649,7 @@
       </c>
       <c r="AA18" s="63"/>
       <c r="AB18" s="94"/>
-      <c r="AE18" s="101" t="str">
+      <c r="AE18" s="97" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
@@ -4498,7 +4713,7 @@
       </c>
       <c r="AA19" s="63"/>
       <c r="AB19" s="94"/>
-      <c r="AE19" s="101" t="str">
+      <c r="AE19" s="97" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
@@ -4562,7 +4777,7 @@
       </c>
       <c r="AA20" s="63"/>
       <c r="AB20" s="94"/>
-      <c r="AE20" s="101" t="str">
+      <c r="AE20" s="97" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
@@ -4626,7 +4841,7 @@
       </c>
       <c r="AA21" s="63"/>
       <c r="AB21" s="94"/>
-      <c r="AE21" s="101" t="str">
+      <c r="AE21" s="97" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
@@ -4690,7 +4905,7 @@
       </c>
       <c r="AA22" s="63"/>
       <c r="AB22" s="94"/>
-      <c r="AE22" s="101" t="str">
+      <c r="AE22" s="97" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
@@ -4754,7 +4969,7 @@
       </c>
       <c r="AA23" s="63"/>
       <c r="AB23" s="94"/>
-      <c r="AE23" s="101" t="str">
+      <c r="AE23" s="97" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
@@ -4818,7 +5033,7 @@
       </c>
       <c r="AA24" s="63"/>
       <c r="AB24" s="94"/>
-      <c r="AE24" s="101" t="str">
+      <c r="AE24" s="97" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
@@ -4882,7 +5097,7 @@
       </c>
       <c r="AA25" s="63"/>
       <c r="AB25" s="94"/>
-      <c r="AE25" s="101" t="str">
+      <c r="AE25" s="97" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
@@ -4946,7 +5161,7 @@
       </c>
       <c r="AA26" s="63"/>
       <c r="AB26" s="94"/>
-      <c r="AE26" s="101" t="str">
+      <c r="AE26" s="97" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
@@ -5010,7 +5225,7 @@
       </c>
       <c r="AA27" s="63"/>
       <c r="AB27" s="94"/>
-      <c r="AE27" s="101" t="str">
+      <c r="AE27" s="97" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
@@ -5074,7 +5289,7 @@
       </c>
       <c r="AA28" s="63"/>
       <c r="AB28" s="94"/>
-      <c r="AE28" s="101" t="str">
+      <c r="AE28" s="97" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
@@ -5138,7 +5353,7 @@
       </c>
       <c r="AA29" s="63"/>
       <c r="AB29" s="94"/>
-      <c r="AE29" s="101" t="str">
+      <c r="AE29" s="97" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
@@ -5202,7 +5417,7 @@
       </c>
       <c r="AA30" s="63"/>
       <c r="AB30" s="94"/>
-      <c r="AE30" s="101" t="str">
+      <c r="AE30" s="97" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
@@ -5266,7 +5481,7 @@
       </c>
       <c r="AA31" s="63"/>
       <c r="AB31" s="94"/>
-      <c r="AE31" s="101" t="str">
+      <c r="AE31" s="97" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
@@ -5330,7 +5545,7 @@
       </c>
       <c r="AA32" s="63"/>
       <c r="AB32" s="94"/>
-      <c r="AE32" s="101" t="str">
+      <c r="AE32" s="97" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
@@ -5394,7 +5609,7 @@
       </c>
       <c r="AA33" s="63"/>
       <c r="AB33" s="94"/>
-      <c r="AE33" s="101" t="str">
+      <c r="AE33" s="97" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
@@ -5458,7 +5673,7 @@
       </c>
       <c r="AA34" s="63"/>
       <c r="AB34" s="94"/>
-      <c r="AE34" s="101" t="str">
+      <c r="AE34" s="97" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
@@ -5522,7 +5737,7 @@
       </c>
       <c r="AA35" s="63"/>
       <c r="AB35" s="94"/>
-      <c r="AE35" s="101" t="str">
+      <c r="AE35" s="97" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
@@ -5586,7 +5801,7 @@
       </c>
       <c r="AA36" s="63"/>
       <c r="AB36" s="94"/>
-      <c r="AE36" s="101" t="str">
+      <c r="AE36" s="97" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
@@ -5650,7 +5865,7 @@
       </c>
       <c r="AA37" s="63"/>
       <c r="AB37" s="94"/>
-      <c r="AE37" s="101" t="str">
+      <c r="AE37" s="97" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
@@ -5714,7 +5929,7 @@
       </c>
       <c r="AA38" s="63"/>
       <c r="AB38" s="94"/>
-      <c r="AE38" s="101" t="str">
+      <c r="AE38" s="97" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
@@ -5778,7 +5993,7 @@
       </c>
       <c r="AA39" s="63"/>
       <c r="AB39" s="94"/>
-      <c r="AE39" s="101" t="str">
+      <c r="AE39" s="97" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
@@ -5842,7 +6057,7 @@
       </c>
       <c r="AA40" s="63"/>
       <c r="AB40" s="94"/>
-      <c r="AE40" s="101" t="str">
+      <c r="AE40" s="97" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
@@ -5906,7 +6121,7 @@
       </c>
       <c r="AA41" s="63"/>
       <c r="AB41" s="94"/>
-      <c r="AE41" s="101" t="str">
+      <c r="AE41" s="97" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
@@ -5970,7 +6185,7 @@
       </c>
       <c r="AA42" s="63"/>
       <c r="AB42" s="94"/>
-      <c r="AE42" s="101" t="str">
+      <c r="AE42" s="97" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
@@ -6034,7 +6249,7 @@
       </c>
       <c r="AA43" s="63"/>
       <c r="AB43" s="94"/>
-      <c r="AE43" s="101" t="str">
+      <c r="AE43" s="97" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
@@ -6098,7 +6313,7 @@
       </c>
       <c r="AA44" s="63"/>
       <c r="AB44" s="94"/>
-      <c r="AE44" s="101" t="str">
+      <c r="AE44" s="97" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
@@ -6162,7 +6377,7 @@
       </c>
       <c r="AA45" s="63"/>
       <c r="AB45" s="94"/>
-      <c r="AE45" s="101" t="str">
+      <c r="AE45" s="97" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
@@ -6226,7 +6441,7 @@
       </c>
       <c r="AA46" s="63"/>
       <c r="AB46" s="94"/>
-      <c r="AE46" s="101" t="str">
+      <c r="AE46" s="97" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
@@ -6290,7 +6505,7 @@
       </c>
       <c r="AA47" s="63"/>
       <c r="AB47" s="94"/>
-      <c r="AE47" s="101" t="str">
+      <c r="AE47" s="97" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
@@ -6354,7 +6569,7 @@
       </c>
       <c r="AA48" s="63"/>
       <c r="AB48" s="94"/>
-      <c r="AE48" s="101" t="str">
+      <c r="AE48" s="97" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
@@ -6418,7 +6633,7 @@
       </c>
       <c r="AA49" s="63"/>
       <c r="AB49" s="94"/>
-      <c r="AE49" s="101" t="str">
+      <c r="AE49" s="97" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
@@ -6482,7 +6697,7 @@
       </c>
       <c r="AA50" s="63"/>
       <c r="AB50" s="94"/>
-      <c r="AE50" s="101" t="str">
+      <c r="AE50" s="97" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
@@ -6546,7 +6761,7 @@
       </c>
       <c r="AA51" s="63"/>
       <c r="AB51" s="94"/>
-      <c r="AE51" s="101" t="str">
+      <c r="AE51" s="97" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
@@ -6610,7 +6825,7 @@
       </c>
       <c r="AA52" s="63"/>
       <c r="AB52" s="94"/>
-      <c r="AE52" s="101" t="str">
+      <c r="AE52" s="97" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
@@ -6674,7 +6889,7 @@
       </c>
       <c r="AA53" s="63"/>
       <c r="AB53" s="94"/>
-      <c r="AE53" s="101" t="str">
+      <c r="AE53" s="97" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
@@ -6738,7 +6953,7 @@
       </c>
       <c r="AA54" s="63"/>
       <c r="AB54" s="94"/>
-      <c r="AE54" s="101" t="str">
+      <c r="AE54" s="97" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
@@ -6802,7 +7017,7 @@
       </c>
       <c r="AA55" s="63"/>
       <c r="AB55" s="94"/>
-      <c r="AE55" s="101" t="str">
+      <c r="AE55" s="97" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
@@ -6866,7 +7081,7 @@
       </c>
       <c r="AA56" s="63"/>
       <c r="AB56" s="94"/>
-      <c r="AE56" s="101" t="str">
+      <c r="AE56" s="97" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
@@ -6930,7 +7145,7 @@
       </c>
       <c r="AA57" s="63"/>
       <c r="AB57" s="94"/>
-      <c r="AE57" s="101" t="str">
+      <c r="AE57" s="97" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
@@ -6994,7 +7209,7 @@
       </c>
       <c r="AA58" s="63"/>
       <c r="AB58" s="94"/>
-      <c r="AE58" s="101" t="str">
+      <c r="AE58" s="97" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
@@ -7058,7 +7273,7 @@
       </c>
       <c r="AA59" s="63"/>
       <c r="AB59" s="94"/>
-      <c r="AE59" s="101" t="str">
+      <c r="AE59" s="97" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
@@ -7122,7 +7337,7 @@
       </c>
       <c r="AA60" s="63"/>
       <c r="AB60" s="94"/>
-      <c r="AE60" s="101" t="str">
+      <c r="AE60" s="97" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
@@ -7186,7 +7401,7 @@
       </c>
       <c r="AA61" s="63"/>
       <c r="AB61" s="94"/>
-      <c r="AE61" s="101" t="str">
+      <c r="AE61" s="97" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
@@ -7250,7 +7465,7 @@
       </c>
       <c r="AA62" s="63"/>
       <c r="AB62" s="94"/>
-      <c r="AE62" s="101" t="str">
+      <c r="AE62" s="97" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
@@ -7314,7 +7529,7 @@
       </c>
       <c r="AA63" s="63"/>
       <c r="AB63" s="94"/>
-      <c r="AE63" s="101" t="str">
+      <c r="AE63" s="97" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
@@ -7378,7 +7593,7 @@
       </c>
       <c r="AA64" s="64"/>
       <c r="AB64" s="94"/>
-      <c r="AE64" s="101" t="str">
+      <c r="AE64" s="97" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
@@ -7442,7 +7657,7 @@
       </c>
       <c r="AA65" s="64"/>
       <c r="AB65" s="94"/>
-      <c r="AE65" s="101" t="str">
+      <c r="AE65" s="97" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
@@ -7506,7 +7721,7 @@
       </c>
       <c r="AA66" s="64"/>
       <c r="AB66" s="94"/>
-      <c r="AE66" s="101" t="str">
+      <c r="AE66" s="97" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
@@ -7570,7 +7785,7 @@
       </c>
       <c r="AA67" s="64"/>
       <c r="AB67" s="94"/>
-      <c r="AE67" s="101" t="str">
+      <c r="AE67" s="97" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
@@ -7634,7 +7849,7 @@
       </c>
       <c r="AA68" s="64"/>
       <c r="AB68" s="94"/>
-      <c r="AE68" s="101" t="str">
+      <c r="AE68" s="97" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
@@ -7698,7 +7913,7 @@
       </c>
       <c r="AA69" s="64"/>
       <c r="AB69" s="94"/>
-      <c r="AE69" s="101" t="str">
+      <c r="AE69" s="97" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
@@ -7762,7 +7977,7 @@
       </c>
       <c r="AA70" s="64"/>
       <c r="AB70" s="94"/>
-      <c r="AE70" s="101" t="str">
+      <c r="AE70" s="97" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
@@ -7826,7 +8041,7 @@
       </c>
       <c r="AA71" s="64"/>
       <c r="AB71" s="94"/>
-      <c r="AE71" s="101" t="str">
+      <c r="AE71" s="97" t="str">
         <f t="shared" ref="AE71:AE134" si="27">IF((AC71+AD71)=0,"",AC71+AD71)</f>
         <v/>
       </c>
@@ -7890,7 +8105,7 @@
       </c>
       <c r="AA72" s="64"/>
       <c r="AB72" s="94"/>
-      <c r="AE72" s="101" t="str">
+      <c r="AE72" s="97" t="str">
         <f t="shared" si="27"/>
         <v/>
       </c>
@@ -7954,7 +8169,7 @@
       </c>
       <c r="AA73" s="64"/>
       <c r="AB73" s="94"/>
-      <c r="AE73" s="101" t="str">
+      <c r="AE73" s="97" t="str">
         <f t="shared" si="27"/>
         <v/>
       </c>
@@ -8018,7 +8233,7 @@
       </c>
       <c r="AA74" s="64"/>
       <c r="AB74" s="94"/>
-      <c r="AE74" s="101" t="str">
+      <c r="AE74" s="97" t="str">
         <f t="shared" si="27"/>
         <v/>
       </c>
@@ -8082,7 +8297,7 @@
       </c>
       <c r="AA75" s="64"/>
       <c r="AB75" s="94"/>
-      <c r="AE75" s="101" t="str">
+      <c r="AE75" s="97" t="str">
         <f t="shared" si="27"/>
         <v/>
       </c>
@@ -8146,7 +8361,7 @@
       </c>
       <c r="AA76" s="64"/>
       <c r="AB76" s="94"/>
-      <c r="AE76" s="101" t="str">
+      <c r="AE76" s="97" t="str">
         <f t="shared" si="27"/>
         <v/>
       </c>
@@ -8210,7 +8425,7 @@
       </c>
       <c r="AA77" s="64"/>
       <c r="AB77" s="94"/>
-      <c r="AE77" s="101" t="str">
+      <c r="AE77" s="97" t="str">
         <f t="shared" si="27"/>
         <v/>
       </c>
@@ -8274,7 +8489,7 @@
       </c>
       <c r="AA78" s="64"/>
       <c r="AB78" s="94"/>
-      <c r="AE78" s="101" t="str">
+      <c r="AE78" s="97" t="str">
         <f t="shared" si="27"/>
         <v/>
       </c>
@@ -8338,7 +8553,7 @@
       </c>
       <c r="AA79" s="64"/>
       <c r="AB79" s="94"/>
-      <c r="AE79" s="101" t="str">
+      <c r="AE79" s="97" t="str">
         <f t="shared" si="27"/>
         <v/>
       </c>
@@ -8402,7 +8617,7 @@
       </c>
       <c r="AA80" s="64"/>
       <c r="AB80" s="94"/>
-      <c r="AE80" s="101" t="str">
+      <c r="AE80" s="97" t="str">
         <f t="shared" si="27"/>
         <v/>
       </c>
@@ -8466,7 +8681,7 @@
       </c>
       <c r="AA81" s="64"/>
       <c r="AB81" s="94"/>
-      <c r="AE81" s="101" t="str">
+      <c r="AE81" s="97" t="str">
         <f t="shared" si="27"/>
         <v/>
       </c>
@@ -8530,7 +8745,7 @@
       </c>
       <c r="AA82" s="64"/>
       <c r="AB82" s="94"/>
-      <c r="AE82" s="101" t="str">
+      <c r="AE82" s="97" t="str">
         <f t="shared" si="27"/>
         <v/>
       </c>
@@ -8594,7 +8809,7 @@
       </c>
       <c r="AA83" s="64"/>
       <c r="AB83" s="94"/>
-      <c r="AE83" s="101" t="str">
+      <c r="AE83" s="97" t="str">
         <f t="shared" si="27"/>
         <v/>
       </c>
@@ -8658,7 +8873,7 @@
       </c>
       <c r="AA84" s="64"/>
       <c r="AB84" s="94"/>
-      <c r="AE84" s="101" t="str">
+      <c r="AE84" s="97" t="str">
         <f t="shared" si="27"/>
         <v/>
       </c>
@@ -8722,7 +8937,7 @@
       </c>
       <c r="AA85" s="64"/>
       <c r="AB85" s="94"/>
-      <c r="AE85" s="101" t="str">
+      <c r="AE85" s="97" t="str">
         <f t="shared" si="27"/>
         <v/>
       </c>
@@ -8786,7 +9001,7 @@
       </c>
       <c r="AA86" s="64"/>
       <c r="AB86" s="94"/>
-      <c r="AE86" s="101" t="str">
+      <c r="AE86" s="97" t="str">
         <f t="shared" si="27"/>
         <v/>
       </c>
@@ -8850,7 +9065,7 @@
       </c>
       <c r="AA87" s="64"/>
       <c r="AB87" s="94"/>
-      <c r="AE87" s="101" t="str">
+      <c r="AE87" s="97" t="str">
         <f t="shared" si="27"/>
         <v/>
       </c>
@@ -8914,7 +9129,7 @@
       </c>
       <c r="AA88" s="64"/>
       <c r="AB88" s="94"/>
-      <c r="AE88" s="101" t="str">
+      <c r="AE88" s="97" t="str">
         <f t="shared" si="27"/>
         <v/>
       </c>
@@ -8978,7 +9193,7 @@
       </c>
       <c r="AA89" s="64"/>
       <c r="AB89" s="94"/>
-      <c r="AE89" s="101" t="str">
+      <c r="AE89" s="97" t="str">
         <f t="shared" si="27"/>
         <v/>
       </c>
@@ -9042,7 +9257,7 @@
       </c>
       <c r="AA90" s="64"/>
       <c r="AB90" s="94"/>
-      <c r="AE90" s="101" t="str">
+      <c r="AE90" s="97" t="str">
         <f t="shared" si="27"/>
         <v/>
       </c>
@@ -9106,7 +9321,7 @@
       </c>
       <c r="AA91" s="64"/>
       <c r="AB91" s="94"/>
-      <c r="AE91" s="101" t="str">
+      <c r="AE91" s="97" t="str">
         <f t="shared" si="27"/>
         <v/>
       </c>
@@ -9170,7 +9385,7 @@
       </c>
       <c r="AA92" s="64"/>
       <c r="AB92" s="94"/>
-      <c r="AE92" s="101" t="str">
+      <c r="AE92" s="97" t="str">
         <f t="shared" si="27"/>
         <v/>
       </c>
@@ -9234,7 +9449,7 @@
       </c>
       <c r="AA93" s="64"/>
       <c r="AB93" s="94"/>
-      <c r="AE93" s="101" t="str">
+      <c r="AE93" s="97" t="str">
         <f t="shared" si="27"/>
         <v/>
       </c>
@@ -9298,7 +9513,7 @@
       </c>
       <c r="AA94" s="64"/>
       <c r="AB94" s="94"/>
-      <c r="AE94" s="101" t="str">
+      <c r="AE94" s="97" t="str">
         <f t="shared" si="27"/>
         <v/>
       </c>
@@ -9362,7 +9577,7 @@
       </c>
       <c r="AA95" s="64"/>
       <c r="AB95" s="94"/>
-      <c r="AE95" s="101" t="str">
+      <c r="AE95" s="97" t="str">
         <f t="shared" si="27"/>
         <v/>
       </c>
@@ -9426,7 +9641,7 @@
       </c>
       <c r="AA96" s="64"/>
       <c r="AB96" s="94"/>
-      <c r="AE96" s="101" t="str">
+      <c r="AE96" s="97" t="str">
         <f t="shared" si="27"/>
         <v/>
       </c>
@@ -9490,7 +9705,7 @@
       </c>
       <c r="AA97" s="64"/>
       <c r="AB97" s="94"/>
-      <c r="AE97" s="101" t="str">
+      <c r="AE97" s="97" t="str">
         <f t="shared" si="27"/>
         <v/>
       </c>
@@ -9554,7 +9769,7 @@
       </c>
       <c r="AA98" s="64"/>
       <c r="AB98" s="94"/>
-      <c r="AE98" s="101" t="str">
+      <c r="AE98" s="97" t="str">
         <f t="shared" si="27"/>
         <v/>
       </c>
@@ -9618,7 +9833,7 @@
       </c>
       <c r="AA99" s="64"/>
       <c r="AB99" s="94"/>
-      <c r="AE99" s="101" t="str">
+      <c r="AE99" s="97" t="str">
         <f t="shared" si="27"/>
         <v/>
       </c>
@@ -9682,7 +9897,7 @@
       </c>
       <c r="AA100" s="64"/>
       <c r="AB100" s="94"/>
-      <c r="AE100" s="101" t="str">
+      <c r="AE100" s="97" t="str">
         <f t="shared" si="27"/>
         <v/>
       </c>
@@ -9746,7 +9961,7 @@
       </c>
       <c r="AA101" s="64"/>
       <c r="AB101" s="94"/>
-      <c r="AE101" s="101" t="str">
+      <c r="AE101" s="97" t="str">
         <f t="shared" si="27"/>
         <v/>
       </c>
@@ -9810,7 +10025,7 @@
       </c>
       <c r="AA102" s="64"/>
       <c r="AB102" s="94"/>
-      <c r="AE102" s="101" t="str">
+      <c r="AE102" s="97" t="str">
         <f t="shared" si="27"/>
         <v/>
       </c>
@@ -9874,7 +10089,7 @@
       </c>
       <c r="AA103" s="64"/>
       <c r="AB103" s="94"/>
-      <c r="AE103" s="101" t="str">
+      <c r="AE103" s="97" t="str">
         <f t="shared" si="27"/>
         <v/>
       </c>
@@ -9938,7 +10153,7 @@
       </c>
       <c r="AA104" s="64"/>
       <c r="AB104" s="94"/>
-      <c r="AE104" s="101" t="str">
+      <c r="AE104" s="97" t="str">
         <f t="shared" si="27"/>
         <v/>
       </c>
@@ -10002,7 +10217,7 @@
       </c>
       <c r="AA105" s="64"/>
       <c r="AB105" s="94"/>
-      <c r="AE105" s="101" t="str">
+      <c r="AE105" s="97" t="str">
         <f t="shared" si="27"/>
         <v/>
       </c>
@@ -10066,7 +10281,7 @@
       </c>
       <c r="AA106" s="64"/>
       <c r="AB106" s="94"/>
-      <c r="AE106" s="101" t="str">
+      <c r="AE106" s="97" t="str">
         <f t="shared" si="27"/>
         <v/>
       </c>
@@ -10130,7 +10345,7 @@
       </c>
       <c r="AA107" s="64"/>
       <c r="AB107" s="94"/>
-      <c r="AE107" s="101" t="str">
+      <c r="AE107" s="97" t="str">
         <f t="shared" si="27"/>
         <v/>
       </c>
@@ -10194,7 +10409,7 @@
       </c>
       <c r="AA108" s="64"/>
       <c r="AB108" s="94"/>
-      <c r="AE108" s="101" t="str">
+      <c r="AE108" s="97" t="str">
         <f t="shared" si="27"/>
         <v/>
       </c>
@@ -10258,7 +10473,7 @@
       </c>
       <c r="AA109" s="64"/>
       <c r="AB109" s="94"/>
-      <c r="AE109" s="101" t="str">
+      <c r="AE109" s="97" t="str">
         <f t="shared" si="27"/>
         <v/>
       </c>
@@ -10322,7 +10537,7 @@
       </c>
       <c r="AA110" s="64"/>
       <c r="AB110" s="94"/>
-      <c r="AE110" s="101" t="str">
+      <c r="AE110" s="97" t="str">
         <f t="shared" si="27"/>
         <v/>
       </c>
@@ -10386,7 +10601,7 @@
       </c>
       <c r="AA111" s="64"/>
       <c r="AB111" s="94"/>
-      <c r="AE111" s="101" t="str">
+      <c r="AE111" s="97" t="str">
         <f t="shared" si="27"/>
         <v/>
       </c>
@@ -10450,7 +10665,7 @@
       </c>
       <c r="AA112" s="64"/>
       <c r="AB112" s="94"/>
-      <c r="AE112" s="101" t="str">
+      <c r="AE112" s="97" t="str">
         <f t="shared" si="27"/>
         <v/>
       </c>
@@ -10514,7 +10729,7 @@
       </c>
       <c r="AA113" s="64"/>
       <c r="AB113" s="94"/>
-      <c r="AE113" s="101" t="str">
+      <c r="AE113" s="97" t="str">
         <f t="shared" si="27"/>
         <v/>
       </c>
@@ -10578,7 +10793,7 @@
       </c>
       <c r="AA114" s="64"/>
       <c r="AB114" s="94"/>
-      <c r="AE114" s="101" t="str">
+      <c r="AE114" s="97" t="str">
         <f t="shared" si="27"/>
         <v/>
       </c>
@@ -10642,7 +10857,7 @@
       </c>
       <c r="AA115" s="64"/>
       <c r="AB115" s="94"/>
-      <c r="AE115" s="101" t="str">
+      <c r="AE115" s="97" t="str">
         <f t="shared" si="27"/>
         <v/>
       </c>
@@ -10706,7 +10921,7 @@
       </c>
       <c r="AA116" s="64"/>
       <c r="AB116" s="94"/>
-      <c r="AE116" s="101" t="str">
+      <c r="AE116" s="97" t="str">
         <f t="shared" si="27"/>
         <v/>
       </c>
@@ -10770,7 +10985,7 @@
       </c>
       <c r="AA117" s="64"/>
       <c r="AB117" s="94"/>
-      <c r="AE117" s="101" t="str">
+      <c r="AE117" s="97" t="str">
         <f t="shared" si="27"/>
         <v/>
       </c>
@@ -10834,7 +11049,7 @@
       </c>
       <c r="AA118" s="64"/>
       <c r="AB118" s="94"/>
-      <c r="AE118" s="101" t="str">
+      <c r="AE118" s="97" t="str">
         <f t="shared" si="27"/>
         <v/>
       </c>
@@ -10898,7 +11113,7 @@
       </c>
       <c r="AA119" s="64"/>
       <c r="AB119" s="94"/>
-      <c r="AE119" s="101" t="str">
+      <c r="AE119" s="97" t="str">
         <f t="shared" si="27"/>
         <v/>
       </c>
@@ -10962,7 +11177,7 @@
       </c>
       <c r="AA120" s="64"/>
       <c r="AB120" s="94"/>
-      <c r="AE120" s="101" t="str">
+      <c r="AE120" s="97" t="str">
         <f t="shared" si="27"/>
         <v/>
       </c>
@@ -11026,7 +11241,7 @@
       </c>
       <c r="AA121" s="64"/>
       <c r="AB121" s="94"/>
-      <c r="AE121" s="101" t="str">
+      <c r="AE121" s="97" t="str">
         <f t="shared" si="27"/>
         <v/>
       </c>
@@ -11090,7 +11305,7 @@
       </c>
       <c r="AA122" s="64"/>
       <c r="AB122" s="94"/>
-      <c r="AE122" s="101" t="str">
+      <c r="AE122" s="97" t="str">
         <f t="shared" si="27"/>
         <v/>
       </c>
@@ -11154,7 +11369,7 @@
       </c>
       <c r="AA123" s="64"/>
       <c r="AB123" s="94"/>
-      <c r="AE123" s="101" t="str">
+      <c r="AE123" s="97" t="str">
         <f t="shared" si="27"/>
         <v/>
       </c>
@@ -11218,7 +11433,7 @@
       </c>
       <c r="AA124" s="64"/>
       <c r="AB124" s="94"/>
-      <c r="AE124" s="101" t="str">
+      <c r="AE124" s="97" t="str">
         <f t="shared" si="27"/>
         <v/>
       </c>
@@ -11282,7 +11497,7 @@
       </c>
       <c r="AA125" s="64"/>
       <c r="AB125" s="94"/>
-      <c r="AE125" s="101" t="str">
+      <c r="AE125" s="97" t="str">
         <f t="shared" si="27"/>
         <v/>
       </c>
@@ -11346,7 +11561,7 @@
       </c>
       <c r="AA126" s="64"/>
       <c r="AB126" s="94"/>
-      <c r="AE126" s="101" t="str">
+      <c r="AE126" s="97" t="str">
         <f t="shared" si="27"/>
         <v/>
       </c>
@@ -11410,7 +11625,7 @@
       </c>
       <c r="AA127" s="64"/>
       <c r="AB127" s="94"/>
-      <c r="AE127" s="101" t="str">
+      <c r="AE127" s="97" t="str">
         <f t="shared" si="27"/>
         <v/>
       </c>
@@ -11474,7 +11689,7 @@
       </c>
       <c r="AA128" s="64"/>
       <c r="AB128" s="94"/>
-      <c r="AE128" s="101" t="str">
+      <c r="AE128" s="97" t="str">
         <f t="shared" si="27"/>
         <v/>
       </c>
@@ -11538,7 +11753,7 @@
       </c>
       <c r="AA129" s="64"/>
       <c r="AB129" s="94"/>
-      <c r="AE129" s="101" t="str">
+      <c r="AE129" s="97" t="str">
         <f t="shared" si="27"/>
         <v/>
       </c>
@@ -11602,7 +11817,7 @@
       </c>
       <c r="AA130" s="64"/>
       <c r="AB130" s="94"/>
-      <c r="AE130" s="101" t="str">
+      <c r="AE130" s="97" t="str">
         <f t="shared" si="27"/>
         <v/>
       </c>
@@ -11666,7 +11881,7 @@
       </c>
       <c r="AA131" s="64"/>
       <c r="AB131" s="94"/>
-      <c r="AE131" s="101" t="str">
+      <c r="AE131" s="97" t="str">
         <f t="shared" si="27"/>
         <v/>
       </c>
@@ -11730,7 +11945,7 @@
       </c>
       <c r="AA132" s="64"/>
       <c r="AB132" s="94"/>
-      <c r="AE132" s="101" t="str">
+      <c r="AE132" s="97" t="str">
         <f t="shared" si="27"/>
         <v/>
       </c>
@@ -11794,7 +12009,7 @@
       </c>
       <c r="AA133" s="64"/>
       <c r="AB133" s="94"/>
-      <c r="AE133" s="101" t="str">
+      <c r="AE133" s="97" t="str">
         <f t="shared" si="27"/>
         <v/>
       </c>
@@ -11858,7 +12073,7 @@
       </c>
       <c r="AA134" s="64"/>
       <c r="AB134" s="94"/>
-      <c r="AE134" s="101" t="str">
+      <c r="AE134" s="97" t="str">
         <f t="shared" si="27"/>
         <v/>
       </c>
@@ -11922,7 +12137,7 @@
       </c>
       <c r="AA135" s="64"/>
       <c r="AB135" s="94"/>
-      <c r="AE135" s="101" t="str">
+      <c r="AE135" s="97" t="str">
         <f t="shared" ref="AE135:AE198" si="45">IF((AC135+AD135)=0,"",AC135+AD135)</f>
         <v/>
       </c>
@@ -11986,7 +12201,7 @@
       </c>
       <c r="AA136" s="64"/>
       <c r="AB136" s="94"/>
-      <c r="AE136" s="101" t="str">
+      <c r="AE136" s="97" t="str">
         <f t="shared" si="45"/>
         <v/>
       </c>
@@ -12050,7 +12265,7 @@
       </c>
       <c r="AA137" s="64"/>
       <c r="AB137" s="94"/>
-      <c r="AE137" s="101" t="str">
+      <c r="AE137" s="97" t="str">
         <f t="shared" si="45"/>
         <v/>
       </c>
@@ -12114,7 +12329,7 @@
       </c>
       <c r="AA138" s="64"/>
       <c r="AB138" s="94"/>
-      <c r="AE138" s="101" t="str">
+      <c r="AE138" s="97" t="str">
         <f t="shared" si="45"/>
         <v/>
       </c>
@@ -12178,7 +12393,7 @@
       </c>
       <c r="AA139" s="64"/>
       <c r="AB139" s="94"/>
-      <c r="AE139" s="101" t="str">
+      <c r="AE139" s="97" t="str">
         <f t="shared" si="45"/>
         <v/>
       </c>
@@ -12242,7 +12457,7 @@
       </c>
       <c r="AA140" s="64"/>
       <c r="AB140" s="94"/>
-      <c r="AE140" s="101" t="str">
+      <c r="AE140" s="97" t="str">
         <f t="shared" si="45"/>
         <v/>
       </c>
@@ -12306,7 +12521,7 @@
       </c>
       <c r="AA141" s="64"/>
       <c r="AB141" s="94"/>
-      <c r="AE141" s="101" t="str">
+      <c r="AE141" s="97" t="str">
         <f t="shared" si="45"/>
         <v/>
       </c>
@@ -12370,7 +12585,7 @@
       </c>
       <c r="AA142" s="64"/>
       <c r="AB142" s="94"/>
-      <c r="AE142" s="101" t="str">
+      <c r="AE142" s="97" t="str">
         <f t="shared" si="45"/>
         <v/>
       </c>
@@ -12434,7 +12649,7 @@
       </c>
       <c r="AA143" s="64"/>
       <c r="AB143" s="94"/>
-      <c r="AE143" s="101" t="str">
+      <c r="AE143" s="97" t="str">
         <f t="shared" si="45"/>
         <v/>
       </c>
@@ -12498,7 +12713,7 @@
       </c>
       <c r="AA144" s="64"/>
       <c r="AB144" s="94"/>
-      <c r="AE144" s="101" t="str">
+      <c r="AE144" s="97" t="str">
         <f t="shared" si="45"/>
         <v/>
       </c>
@@ -12562,7 +12777,7 @@
       </c>
       <c r="AA145" s="64"/>
       <c r="AB145" s="94"/>
-      <c r="AE145" s="101" t="str">
+      <c r="AE145" s="97" t="str">
         <f t="shared" si="45"/>
         <v/>
       </c>
@@ -12626,7 +12841,7 @@
       </c>
       <c r="AA146" s="64"/>
       <c r="AB146" s="94"/>
-      <c r="AE146" s="101" t="str">
+      <c r="AE146" s="97" t="str">
         <f t="shared" si="45"/>
         <v/>
       </c>
@@ -12690,7 +12905,7 @@
       </c>
       <c r="AA147" s="64"/>
       <c r="AB147" s="94"/>
-      <c r="AE147" s="101" t="str">
+      <c r="AE147" s="97" t="str">
         <f t="shared" si="45"/>
         <v/>
       </c>
@@ -12754,7 +12969,7 @@
       </c>
       <c r="AA148" s="64"/>
       <c r="AB148" s="94"/>
-      <c r="AE148" s="101" t="str">
+      <c r="AE148" s="97" t="str">
         <f t="shared" si="45"/>
         <v/>
       </c>
@@ -12818,7 +13033,7 @@
       </c>
       <c r="AA149" s="64"/>
       <c r="AB149" s="94"/>
-      <c r="AE149" s="101" t="str">
+      <c r="AE149" s="97" t="str">
         <f t="shared" si="45"/>
         <v/>
       </c>
@@ -12882,7 +13097,7 @@
       </c>
       <c r="AA150" s="64"/>
       <c r="AB150" s="94"/>
-      <c r="AE150" s="101" t="str">
+      <c r="AE150" s="97" t="str">
         <f t="shared" si="45"/>
         <v/>
       </c>
@@ -12946,7 +13161,7 @@
       </c>
       <c r="AA151" s="64"/>
       <c r="AB151" s="94"/>
-      <c r="AE151" s="101" t="str">
+      <c r="AE151" s="97" t="str">
         <f t="shared" si="45"/>
         <v/>
       </c>
@@ -13010,7 +13225,7 @@
       </c>
       <c r="AA152" s="64"/>
       <c r="AB152" s="94"/>
-      <c r="AE152" s="101" t="str">
+      <c r="AE152" s="97" t="str">
         <f t="shared" si="45"/>
         <v/>
       </c>
@@ -13074,7 +13289,7 @@
       </c>
       <c r="AA153" s="64"/>
       <c r="AB153" s="94"/>
-      <c r="AE153" s="101" t="str">
+      <c r="AE153" s="97" t="str">
         <f t="shared" si="45"/>
         <v/>
       </c>
@@ -13138,7 +13353,7 @@
       </c>
       <c r="AA154" s="64"/>
       <c r="AB154" s="94"/>
-      <c r="AE154" s="101" t="str">
+      <c r="AE154" s="97" t="str">
         <f t="shared" si="45"/>
         <v/>
       </c>
@@ -13202,7 +13417,7 @@
       </c>
       <c r="AA155" s="64"/>
       <c r="AB155" s="94"/>
-      <c r="AE155" s="101" t="str">
+      <c r="AE155" s="97" t="str">
         <f t="shared" si="45"/>
         <v/>
       </c>
@@ -13266,7 +13481,7 @@
       </c>
       <c r="AA156" s="64"/>
       <c r="AB156" s="94"/>
-      <c r="AE156" s="101" t="str">
+      <c r="AE156" s="97" t="str">
         <f t="shared" si="45"/>
         <v/>
       </c>
@@ -13330,7 +13545,7 @@
       </c>
       <c r="AA157" s="64"/>
       <c r="AB157" s="94"/>
-      <c r="AE157" s="101" t="str">
+      <c r="AE157" s="97" t="str">
         <f t="shared" si="45"/>
         <v/>
       </c>
@@ -13394,7 +13609,7 @@
       </c>
       <c r="AA158" s="64"/>
       <c r="AB158" s="94"/>
-      <c r="AE158" s="101" t="str">
+      <c r="AE158" s="97" t="str">
         <f t="shared" si="45"/>
         <v/>
       </c>
@@ -13458,7 +13673,7 @@
       </c>
       <c r="AA159" s="64"/>
       <c r="AB159" s="94"/>
-      <c r="AE159" s="101" t="str">
+      <c r="AE159" s="97" t="str">
         <f t="shared" si="45"/>
         <v/>
       </c>
@@ -13522,7 +13737,7 @@
       </c>
       <c r="AA160" s="64"/>
       <c r="AB160" s="94"/>
-      <c r="AE160" s="101" t="str">
+      <c r="AE160" s="97" t="str">
         <f t="shared" si="45"/>
         <v/>
       </c>
@@ -13586,7 +13801,7 @@
       </c>
       <c r="AA161" s="64"/>
       <c r="AB161" s="94"/>
-      <c r="AE161" s="101" t="str">
+      <c r="AE161" s="97" t="str">
         <f t="shared" si="45"/>
         <v/>
       </c>
@@ -13650,7 +13865,7 @@
       </c>
       <c r="AA162" s="64"/>
       <c r="AB162" s="94"/>
-      <c r="AE162" s="101" t="str">
+      <c r="AE162" s="97" t="str">
         <f t="shared" si="45"/>
         <v/>
       </c>
@@ -13714,7 +13929,7 @@
       </c>
       <c r="AA163" s="64"/>
       <c r="AB163" s="94"/>
-      <c r="AE163" s="101" t="str">
+      <c r="AE163" s="97" t="str">
         <f t="shared" si="45"/>
         <v/>
       </c>
@@ -13778,7 +13993,7 @@
       </c>
       <c r="AA164" s="64"/>
       <c r="AB164" s="94"/>
-      <c r="AE164" s="101" t="str">
+      <c r="AE164" s="97" t="str">
         <f t="shared" si="45"/>
         <v/>
       </c>
@@ -13842,7 +14057,7 @@
       </c>
       <c r="AA165" s="64"/>
       <c r="AB165" s="94"/>
-      <c r="AE165" s="101" t="str">
+      <c r="AE165" s="97" t="str">
         <f t="shared" si="45"/>
         <v/>
       </c>
@@ -13906,7 +14121,7 @@
       </c>
       <c r="AA166" s="64"/>
       <c r="AB166" s="94"/>
-      <c r="AE166" s="101" t="str">
+      <c r="AE166" s="97" t="str">
         <f t="shared" si="45"/>
         <v/>
       </c>
@@ -13970,7 +14185,7 @@
       </c>
       <c r="AA167" s="64"/>
       <c r="AB167" s="94"/>
-      <c r="AE167" s="101" t="str">
+      <c r="AE167" s="97" t="str">
         <f t="shared" si="45"/>
         <v/>
       </c>
@@ -14034,7 +14249,7 @@
       </c>
       <c r="AA168" s="64"/>
       <c r="AB168" s="94"/>
-      <c r="AE168" s="101" t="str">
+      <c r="AE168" s="97" t="str">
         <f t="shared" si="45"/>
         <v/>
       </c>
@@ -14098,7 +14313,7 @@
       </c>
       <c r="AA169" s="64"/>
       <c r="AB169" s="94"/>
-      <c r="AE169" s="101" t="str">
+      <c r="AE169" s="97" t="str">
         <f t="shared" si="45"/>
         <v/>
       </c>
@@ -14162,7 +14377,7 @@
       </c>
       <c r="AA170" s="64"/>
       <c r="AB170" s="94"/>
-      <c r="AE170" s="101" t="str">
+      <c r="AE170" s="97" t="str">
         <f t="shared" si="45"/>
         <v/>
       </c>
@@ -14226,7 +14441,7 @@
       </c>
       <c r="AA171" s="64"/>
       <c r="AB171" s="94"/>
-      <c r="AE171" s="101" t="str">
+      <c r="AE171" s="97" t="str">
         <f t="shared" si="45"/>
         <v/>
       </c>
@@ -14290,7 +14505,7 @@
       </c>
       <c r="AA172" s="64"/>
       <c r="AB172" s="94"/>
-      <c r="AE172" s="101" t="str">
+      <c r="AE172" s="97" t="str">
         <f t="shared" si="45"/>
         <v/>
       </c>
@@ -14354,7 +14569,7 @@
       </c>
       <c r="AA173" s="64"/>
       <c r="AB173" s="94"/>
-      <c r="AE173" s="101" t="str">
+      <c r="AE173" s="97" t="str">
         <f t="shared" si="45"/>
         <v/>
       </c>
@@ -14418,7 +14633,7 @@
       </c>
       <c r="AA174" s="64"/>
       <c r="AB174" s="94"/>
-      <c r="AE174" s="101" t="str">
+      <c r="AE174" s="97" t="str">
         <f t="shared" si="45"/>
         <v/>
       </c>
@@ -14482,7 +14697,7 @@
       </c>
       <c r="AA175" s="64"/>
       <c r="AB175" s="94"/>
-      <c r="AE175" s="101" t="str">
+      <c r="AE175" s="97" t="str">
         <f t="shared" si="45"/>
         <v/>
       </c>
@@ -14546,7 +14761,7 @@
       </c>
       <c r="AA176" s="64"/>
       <c r="AB176" s="94"/>
-      <c r="AE176" s="101" t="str">
+      <c r="AE176" s="97" t="str">
         <f t="shared" si="45"/>
         <v/>
       </c>
@@ -14610,7 +14825,7 @@
       </c>
       <c r="AA177" s="64"/>
       <c r="AB177" s="94"/>
-      <c r="AE177" s="101" t="str">
+      <c r="AE177" s="97" t="str">
         <f t="shared" si="45"/>
         <v/>
       </c>
@@ -14674,7 +14889,7 @@
       </c>
       <c r="AA178" s="64"/>
       <c r="AB178" s="94"/>
-      <c r="AE178" s="101" t="str">
+      <c r="AE178" s="97" t="str">
         <f t="shared" si="45"/>
         <v/>
       </c>
@@ -14738,7 +14953,7 @@
       </c>
       <c r="AA179" s="64"/>
       <c r="AB179" s="94"/>
-      <c r="AE179" s="101" t="str">
+      <c r="AE179" s="97" t="str">
         <f t="shared" si="45"/>
         <v/>
       </c>
@@ -14802,7 +15017,7 @@
       </c>
       <c r="AA180" s="64"/>
       <c r="AB180" s="94"/>
-      <c r="AE180" s="101" t="str">
+      <c r="AE180" s="97" t="str">
         <f t="shared" si="45"/>
         <v/>
       </c>
@@ -14866,7 +15081,7 @@
       </c>
       <c r="AA181" s="64"/>
       <c r="AB181" s="94"/>
-      <c r="AE181" s="101" t="str">
+      <c r="AE181" s="97" t="str">
         <f t="shared" si="45"/>
         <v/>
       </c>
@@ -14930,7 +15145,7 @@
       </c>
       <c r="AA182" s="64"/>
       <c r="AB182" s="94"/>
-      <c r="AE182" s="101" t="str">
+      <c r="AE182" s="97" t="str">
         <f t="shared" si="45"/>
         <v/>
       </c>
@@ -14994,7 +15209,7 @@
       </c>
       <c r="AA183" s="64"/>
       <c r="AB183" s="94"/>
-      <c r="AE183" s="101" t="str">
+      <c r="AE183" s="97" t="str">
         <f t="shared" si="45"/>
         <v/>
       </c>
@@ -15058,7 +15273,7 @@
       </c>
       <c r="AA184" s="64"/>
       <c r="AB184" s="94"/>
-      <c r="AE184" s="101" t="str">
+      <c r="AE184" s="97" t="str">
         <f t="shared" si="45"/>
         <v/>
       </c>
@@ -15122,7 +15337,7 @@
       </c>
       <c r="AA185" s="64"/>
       <c r="AB185" s="94"/>
-      <c r="AE185" s="101" t="str">
+      <c r="AE185" s="97" t="str">
         <f t="shared" si="45"/>
         <v/>
       </c>
@@ -15186,7 +15401,7 @@
       </c>
       <c r="AA186" s="64"/>
       <c r="AB186" s="94"/>
-      <c r="AE186" s="101" t="str">
+      <c r="AE186" s="97" t="str">
         <f t="shared" si="45"/>
         <v/>
       </c>
@@ -15250,7 +15465,7 @@
       </c>
       <c r="AA187" s="64"/>
       <c r="AB187" s="94"/>
-      <c r="AE187" s="101" t="str">
+      <c r="AE187" s="97" t="str">
         <f t="shared" si="45"/>
         <v/>
       </c>
@@ -15314,7 +15529,7 @@
       </c>
       <c r="AA188" s="64"/>
       <c r="AB188" s="94"/>
-      <c r="AE188" s="101" t="str">
+      <c r="AE188" s="97" t="str">
         <f t="shared" si="45"/>
         <v/>
       </c>
@@ -15378,7 +15593,7 @@
       </c>
       <c r="AA189" s="64"/>
       <c r="AB189" s="94"/>
-      <c r="AE189" s="101" t="str">
+      <c r="AE189" s="97" t="str">
         <f t="shared" si="45"/>
         <v/>
       </c>
@@ -15442,7 +15657,7 @@
       </c>
       <c r="AA190" s="64"/>
       <c r="AB190" s="94"/>
-      <c r="AE190" s="101" t="str">
+      <c r="AE190" s="97" t="str">
         <f t="shared" si="45"/>
         <v/>
       </c>
@@ -15506,7 +15721,7 @@
       </c>
       <c r="AA191" s="64"/>
       <c r="AB191" s="94"/>
-      <c r="AE191" s="101" t="str">
+      <c r="AE191" s="97" t="str">
         <f t="shared" si="45"/>
         <v/>
       </c>
@@ -15570,7 +15785,7 @@
       </c>
       <c r="AA192" s="64"/>
       <c r="AB192" s="94"/>
-      <c r="AE192" s="101" t="str">
+      <c r="AE192" s="97" t="str">
         <f t="shared" si="45"/>
         <v/>
       </c>
@@ -15634,7 +15849,7 @@
       </c>
       <c r="AA193" s="64"/>
       <c r="AB193" s="94"/>
-      <c r="AE193" s="101" t="str">
+      <c r="AE193" s="97" t="str">
         <f t="shared" si="45"/>
         <v/>
       </c>
@@ -15698,7 +15913,7 @@
       </c>
       <c r="AA194" s="64"/>
       <c r="AB194" s="94"/>
-      <c r="AE194" s="101" t="str">
+      <c r="AE194" s="97" t="str">
         <f t="shared" si="45"/>
         <v/>
       </c>
@@ -15762,7 +15977,7 @@
       </c>
       <c r="AA195" s="64"/>
       <c r="AB195" s="94"/>
-      <c r="AE195" s="101" t="str">
+      <c r="AE195" s="97" t="str">
         <f t="shared" si="45"/>
         <v/>
       </c>
@@ -15826,7 +16041,7 @@
       </c>
       <c r="AA196" s="64"/>
       <c r="AB196" s="94"/>
-      <c r="AE196" s="101" t="str">
+      <c r="AE196" s="97" t="str">
         <f t="shared" si="45"/>
         <v/>
       </c>
@@ -15890,7 +16105,7 @@
       </c>
       <c r="AA197" s="64"/>
       <c r="AB197" s="94"/>
-      <c r="AE197" s="101" t="str">
+      <c r="AE197" s="97" t="str">
         <f t="shared" si="45"/>
         <v/>
       </c>
@@ -15954,7 +16169,7 @@
       </c>
       <c r="AA198" s="64"/>
       <c r="AB198" s="94"/>
-      <c r="AE198" s="101" t="str">
+      <c r="AE198" s="97" t="str">
         <f t="shared" si="45"/>
         <v/>
       </c>
@@ -16018,7 +16233,7 @@
       </c>
       <c r="AA199" s="64"/>
       <c r="AB199" s="94"/>
-      <c r="AE199" s="101" t="str">
+      <c r="AE199" s="97" t="str">
         <f t="shared" ref="AE199:AE203" si="63">IF((AC199+AD199)=0,"",AC199+AD199)</f>
         <v/>
       </c>
@@ -16082,7 +16297,7 @@
       </c>
       <c r="AA200" s="64"/>
       <c r="AB200" s="94"/>
-      <c r="AE200" s="101" t="str">
+      <c r="AE200" s="97" t="str">
         <f t="shared" si="63"/>
         <v/>
       </c>
@@ -16146,7 +16361,7 @@
       </c>
       <c r="AA201" s="64"/>
       <c r="AB201" s="94"/>
-      <c r="AE201" s="101" t="str">
+      <c r="AE201" s="97" t="str">
         <f t="shared" si="63"/>
         <v/>
       </c>
@@ -16210,7 +16425,7 @@
       </c>
       <c r="AA202" s="64"/>
       <c r="AB202" s="94"/>
-      <c r="AE202" s="101" t="str">
+      <c r="AE202" s="97" t="str">
         <f t="shared" si="63"/>
         <v/>
       </c>
@@ -16274,127 +16489,127 @@
       </c>
       <c r="AA203" s="73"/>
       <c r="AB203" s="94"/>
-      <c r="AE203" s="101" t="str">
+      <c r="AE203" s="97" t="str">
         <f t="shared" si="63"/>
         <v/>
       </c>
     </row>
     <row r="204" spans="1:31" ht="15.75">
-      <c r="AE204" s="101"/>
+      <c r="AE204" s="97"/>
     </row>
     <row r="205" spans="1:31" ht="15.75">
-      <c r="AE205" s="101"/>
+      <c r="AE205" s="97"/>
     </row>
     <row r="206" spans="1:31" ht="15.75">
-      <c r="AE206" s="101"/>
+      <c r="AE206" s="97"/>
     </row>
     <row r="207" spans="1:31" ht="15.75">
-      <c r="AE207" s="101"/>
+      <c r="AE207" s="97"/>
     </row>
     <row r="208" spans="1:31" ht="15.75">
-      <c r="AE208" s="101"/>
+      <c r="AE208" s="97"/>
     </row>
     <row r="209" spans="31:31" ht="15.75">
-      <c r="AE209" s="101"/>
+      <c r="AE209" s="97"/>
     </row>
     <row r="210" spans="31:31" ht="15.75">
-      <c r="AE210" s="101"/>
+      <c r="AE210" s="97"/>
     </row>
     <row r="211" spans="31:31" ht="15.75">
-      <c r="AE211" s="101"/>
+      <c r="AE211" s="97"/>
     </row>
     <row r="212" spans="31:31" ht="15.75">
-      <c r="AE212" s="101"/>
+      <c r="AE212" s="97"/>
     </row>
     <row r="213" spans="31:31" ht="15.75">
-      <c r="AE213" s="101"/>
+      <c r="AE213" s="97"/>
     </row>
     <row r="214" spans="31:31" ht="15.75">
-      <c r="AE214" s="101"/>
+      <c r="AE214" s="97"/>
     </row>
     <row r="215" spans="31:31" ht="15.75">
-      <c r="AE215" s="101"/>
+      <c r="AE215" s="97"/>
     </row>
     <row r="216" spans="31:31" ht="15.75">
-      <c r="AE216" s="101"/>
+      <c r="AE216" s="97"/>
     </row>
     <row r="217" spans="31:31" ht="15.75">
-      <c r="AE217" s="101"/>
+      <c r="AE217" s="97"/>
     </row>
     <row r="218" spans="31:31" ht="15.75">
-      <c r="AE218" s="101"/>
+      <c r="AE218" s="97"/>
     </row>
     <row r="219" spans="31:31" ht="15.75">
-      <c r="AE219" s="101"/>
+      <c r="AE219" s="97"/>
     </row>
     <row r="220" spans="31:31" ht="15.75">
-      <c r="AE220" s="101"/>
+      <c r="AE220" s="97"/>
     </row>
     <row r="221" spans="31:31" ht="15.75">
-      <c r="AE221" s="101"/>
+      <c r="AE221" s="97"/>
     </row>
     <row r="222" spans="31:31" ht="15.75">
-      <c r="AE222" s="101"/>
+      <c r="AE222" s="97"/>
     </row>
     <row r="223" spans="31:31" ht="15.75">
-      <c r="AE223" s="101"/>
+      <c r="AE223" s="97"/>
     </row>
     <row r="224" spans="31:31" ht="15.75">
-      <c r="AE224" s="101"/>
+      <c r="AE224" s="97"/>
     </row>
     <row r="225" spans="31:31" ht="15.75">
-      <c r="AE225" s="101"/>
+      <c r="AE225" s="97"/>
     </row>
     <row r="226" spans="31:31" ht="15.75">
-      <c r="AE226" s="101"/>
+      <c r="AE226" s="97"/>
     </row>
     <row r="227" spans="31:31" ht="15.75">
-      <c r="AE227" s="101"/>
+      <c r="AE227" s="97"/>
     </row>
     <row r="228" spans="31:31" ht="15.75">
-      <c r="AE228" s="101"/>
+      <c r="AE228" s="97"/>
     </row>
     <row r="229" spans="31:31" ht="15.75">
-      <c r="AE229" s="101"/>
+      <c r="AE229" s="97"/>
     </row>
     <row r="230" spans="31:31" ht="15.75">
-      <c r="AE230" s="101"/>
+      <c r="AE230" s="97"/>
     </row>
     <row r="231" spans="31:31" ht="15.75">
-      <c r="AE231" s="101"/>
+      <c r="AE231" s="97"/>
     </row>
     <row r="232" spans="31:31" ht="15.75">
-      <c r="AE232" s="101"/>
+      <c r="AE232" s="97"/>
     </row>
     <row r="233" spans="31:31" ht="15.75">
-      <c r="AE233" s="101"/>
+      <c r="AE233" s="97"/>
     </row>
     <row r="234" spans="31:31" ht="15.75">
-      <c r="AE234" s="101"/>
+      <c r="AE234" s="97"/>
     </row>
     <row r="235" spans="31:31" ht="15.75">
-      <c r="AE235" s="101"/>
+      <c r="AE235" s="97"/>
     </row>
     <row r="236" spans="31:31" ht="15.75">
-      <c r="AE236" s="101"/>
+      <c r="AE236" s="97"/>
     </row>
     <row r="237" spans="31:31" ht="15.75">
-      <c r="AE237" s="101"/>
+      <c r="AE237" s="97"/>
     </row>
     <row r="238" spans="31:31" ht="15.75">
-      <c r="AE238" s="101"/>
+      <c r="AE238" s="97"/>
     </row>
     <row r="239" spans="31:31" ht="15.75">
-      <c r="AE239" s="101"/>
+      <c r="AE239" s="97"/>
     </row>
     <row r="240" spans="31:31" ht="15.75">
-      <c r="AE240" s="101"/>
+      <c r="AE240" s="97"/>
     </row>
     <row r="241" spans="31:31" ht="15.75">
-      <c r="AE241" s="101"/>
+      <c r="AE241" s="97"/>
     </row>
     <row r="242" spans="31:31" ht="15.75">
-      <c r="AE242" s="101"/>
+      <c r="AE242" s="97"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -16403,55 +16618,51 @@
     <mergeCell ref="AG4:AH4"/>
   </mergeCells>
   <conditionalFormatting sqref="A6:J1000">
-    <cfRule type="expression" dxfId="19" priority="8">
+    <cfRule type="expression" dxfId="15" priority="8">
       <formula>$J6="Cortesia"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="14" priority="9" stopIfTrue="1">
+      <formula>AND(ISNUMBER($D6),$D6&lt;TODAY())</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="13" priority="10">
+      <formula>AND(ISNUMBER($D6),$D6&lt;TODAY())</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U6:U63">
-    <cfRule type="cellIs" dxfId="18" priority="7" operator="lessThan">
+    <cfRule type="cellIs" dxfId="12" priority="7" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y6:Y203">
-    <cfRule type="expression" dxfId="17" priority="6">
+    <cfRule type="expression" dxfId="11" priority="6">
       <formula>Y6&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Z6:Z63">
-    <cfRule type="expression" dxfId="16" priority="4">
+    <cfRule type="expression" dxfId="10" priority="4">
       <formula>Z6="CONFLITO"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="15" priority="5">
+    <cfRule type="expression" dxfId="9" priority="5">
       <formula>Z6="OK"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A6:J1000">
-    <cfRule type="expression" dxfId="10" priority="9" stopIfTrue="1">
-      <formula>AND(ISNUMBER($D6),$D6&lt;TODAY())</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A6:J1000">
-    <cfRule type="expression" dxfId="14" priority="10">
-      <formula>AND(ISNUMBER($D6),$D6&lt;TODAY())</formula>
+  <conditionalFormatting sqref="AE6:AE1000">
+    <cfRule type="expression" dxfId="8" priority="11">
+      <formula>AND(ISNUMBER($AE6),$AE6&gt;6)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AG6:AG1048576">
-    <cfRule type="cellIs" dxfId="13" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="7" priority="3" operator="greaterThan">
       <formula>6</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AH6">
-    <cfRule type="cellIs" dxfId="12" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="6" priority="2" operator="greaterThan">
       <formula>6</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AE6:AE1000">
-    <cfRule type="expression" dxfId="11" priority="11">
-      <formula>AND(ISNUMBER($AE6),$AE6&gt;6)</formula>
-    </cfRule>
-  </conditionalFormatting>
   <dataValidations count="7">
-    <dataValidation type="list" sqref="H6:H9" xr:uid="{00000000-0002-0000-0200-000000000000}">
+    <dataValidation type="list" sqref="H6:H7 H9" xr:uid="{00000000-0002-0000-0200-000000000000}">
       <formula1>"Normal,Férias escolares,Feriado,Natal,Réveillon,Natal / Réveillon,Carnaval,Páscoa,Temporada de verão,Final de semana prolongado,Evento local,Outro"</formula1>
     </dataValidation>
     <dataValidation type="list" sqref="I6:I203" xr:uid="{00000000-0002-0000-0200-000001000000}">
@@ -16469,7 +16680,7 @@
     <dataValidation type="list" sqref="AB6:AB203" xr:uid="{00000000-0002-0000-0200-000005000000}">
       <formula1>"Casa Cinza,Casa Laranja"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="H10:H203" xr:uid="{315E0772-C836-474B-A702-0BAA8E4361DE}">
+    <dataValidation type="list" sqref="H10:H203 H8" xr:uid="{315E0772-C836-474B-A702-0BAA8E4361DE}">
       <formula1>"Normal,Férias,Feriado,Natal,Réveillon,Natal / Réveillon,Carnaval,Páscoa,Temporada de verão,Final de semana prolongado,Evento local,Outro"</formula1>
     </dataValidation>
   </dataValidations>
@@ -16494,24 +16705,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="24" customHeight="1">
-      <c r="A1" s="96" t="s">
+      <c r="A1" s="119" t="s">
         <v>91</v>
       </c>
-      <c r="B1" s="96"/>
-      <c r="C1" s="96"/>
-      <c r="D1" s="96"/>
-      <c r="E1" s="96"/>
-      <c r="F1" s="96"/>
+      <c r="B1" s="119"/>
+      <c r="C1" s="119"/>
+      <c r="D1" s="119"/>
+      <c r="E1" s="119"/>
+      <c r="F1" s="119"/>
     </row>
     <row r="3" spans="1:7" ht="27.2" customHeight="1">
-      <c r="A3" s="99" t="s">
+      <c r="A3" s="122" t="s">
         <v>92</v>
       </c>
-      <c r="B3" s="99"/>
-      <c r="C3" s="99"/>
-      <c r="D3" s="99"/>
-      <c r="E3" s="99"/>
-      <c r="F3" s="99"/>
+      <c r="B3" s="122"/>
+      <c r="C3" s="122"/>
+      <c r="D3" s="122"/>
+      <c r="E3" s="122"/>
+      <c r="F3" s="122"/>
     </row>
     <row r="5" spans="1:7" ht="24" customHeight="1">
       <c r="A5" s="2" t="s">
@@ -19274,12 +19485,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="24" customHeight="1">
-      <c r="A1" s="96" t="s">
+      <c r="A1" s="119" t="s">
         <v>100</v>
       </c>
-      <c r="B1" s="96"/>
-      <c r="C1" s="96"/>
-      <c r="D1" s="96"/>
+      <c r="B1" s="119"/>
+      <c r="C1" s="119"/>
+      <c r="D1" s="119"/>
     </row>
     <row r="3" spans="1:7" ht="24" customHeight="1">
       <c r="A3" s="2" t="s">
@@ -19489,4 +19700,1762 @@
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{678387DC-C927-425E-93AA-07C94B888A68}">
+  <dimension ref="B2:Z203"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
+  <cols>
+    <col min="2" max="2" width="12.625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="25.625" customWidth="1"/>
+    <col min="4" max="4" width="11.75" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19.375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="31.25" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="30" customWidth="1"/>
+    <col min="8" max="8" width="13.375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="7.5" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.25" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.75" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="15.25" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="8.125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="35.5" customWidth="1"/>
+    <col min="18" max="18" width="27" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="11.75" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="15.25" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="8.375" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="11.25" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="13.375" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="10.75" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="15.25" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:26" ht="16.5" thickBot="1">
+      <c r="B2" s="100" t="s">
+        <v>134</v>
+      </c>
+      <c r="C2" s="100" t="s">
+        <v>136</v>
+      </c>
+      <c r="D2" s="100" t="s">
+        <v>135</v>
+      </c>
+      <c r="E2" s="100" t="s">
+        <v>154</v>
+      </c>
+      <c r="F2" s="104" t="s">
+        <v>137</v>
+      </c>
+      <c r="G2" s="104"/>
+      <c r="H2" s="104"/>
+      <c r="I2" s="104"/>
+      <c r="J2" s="104"/>
+      <c r="K2" s="104"/>
+      <c r="L2" s="104"/>
+      <c r="M2" s="104"/>
+      <c r="N2" s="104"/>
+      <c r="O2" s="104"/>
+      <c r="P2" s="104"/>
+      <c r="R2" s="104" t="s">
+        <v>145</v>
+      </c>
+      <c r="S2" s="104"/>
+      <c r="T2" s="104"/>
+      <c r="U2" s="104"/>
+      <c r="V2" s="104"/>
+      <c r="W2" s="104"/>
+      <c r="X2" s="104"/>
+      <c r="Y2" s="104"/>
+      <c r="Z2" s="104"/>
+    </row>
+    <row r="3" spans="2:26" ht="16.5" thickTop="1" thickBot="1">
+      <c r="B3" t="str" cm="1">
+        <f t="array" ref="B3:D5">_xlfn._xlws.FILTER(CHOOSE({1,2,3},RESERVAS!A6:A203,RESERVAS!B6:B203,RESERVAS!G6:G203),(RESERVAS!J6:J203="Direto")*(RESERVAS!J6:J203&lt;&gt;"Cortesia"),"")</f>
+        <v>LOC-001</v>
+      </c>
+      <c r="C3" s="103" t="str">
+        <v>Carlos - Natal/Ano Novo</v>
+      </c>
+      <c r="D3" s="102">
+        <v>11000</v>
+      </c>
+      <c r="E3" t="str" cm="1">
+        <f t="array" ref="E3:E5">_xlfn.LET(_xlpm.ids,_xlfn._xlws.FILTER(RESERVAS!A6:A203,(RESERVAS!J6:J203="Direto")*(RESERVAS!J6:J203&lt;&gt;"Cortesia"),""),IF(_xlpm.ids="","",IF((COUNTIF($S$4,_xlpm.ids)+COUNTIF($V$4:$V$5,_xlpm.ids))&gt;0,"Configurado","Configurar pagamento")))</f>
+        <v>Configurado</v>
+      </c>
+      <c r="F3" s="106" t="s">
+        <v>134</v>
+      </c>
+      <c r="G3" s="106" t="s">
+        <v>136</v>
+      </c>
+      <c r="H3" s="106" t="s">
+        <v>138</v>
+      </c>
+      <c r="I3" s="106" t="s">
+        <v>139</v>
+      </c>
+      <c r="J3" s="106" t="s">
+        <v>140</v>
+      </c>
+      <c r="K3" s="106" t="s">
+        <v>141</v>
+      </c>
+      <c r="L3" s="106" t="s">
+        <v>142</v>
+      </c>
+      <c r="M3" s="106" t="s">
+        <v>143</v>
+      </c>
+      <c r="N3" s="106" t="s">
+        <v>62</v>
+      </c>
+      <c r="O3" s="106" t="s">
+        <v>144</v>
+      </c>
+      <c r="P3" s="100" t="s">
+        <v>155</v>
+      </c>
+      <c r="R3" s="105" t="s">
+        <v>146</v>
+      </c>
+      <c r="S3" s="105" t="s">
+        <v>147</v>
+      </c>
+      <c r="V3" s="105" t="s">
+        <v>151</v>
+      </c>
+      <c r="W3" s="105" t="s">
+        <v>140</v>
+      </c>
+      <c r="X3" s="105" t="s">
+        <v>141</v>
+      </c>
+      <c r="Y3" s="105" t="s">
+        <v>142</v>
+      </c>
+      <c r="Z3" s="105" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="4" spans="2:26">
+      <c r="B4" t="str">
+        <v>LOC-005</v>
+      </c>
+      <c r="C4" s="103" t="str">
+        <v>Miguel - Férias</v>
+      </c>
+      <c r="D4" s="102">
+        <v>6600</v>
+      </c>
+      <c r="E4" t="str">
+        <v>Configurado</v>
+      </c>
+      <c r="F4" s="112" t="str">
+        <f>IF(1&lt;=$S$8,$S$4,"")</f>
+        <v>LOC-001</v>
+      </c>
+      <c r="G4" s="112" t="str">
+        <f>IF(F4="","",_xlfn.XLOOKUP(F4,RESERVAS!$A$6:$A$203,RESERVAS!$B$6:$B$203,""))</f>
+        <v>Carlos - Natal/Ano Novo</v>
+      </c>
+      <c r="H4" s="113">
+        <f t="shared" ref="H4:H15" si="0">IF(F4="","",$S$7)</f>
+        <v>11000</v>
+      </c>
+      <c r="I4" s="114" t="str">
+        <f>IF(F4="","",1&amp;" de "&amp;$S$8)</f>
+        <v>1 de 5</v>
+      </c>
+      <c r="J4" s="115">
+        <f>IF(F4="","",EDATE($S$5,0))</f>
+        <v>46251</v>
+      </c>
+      <c r="K4" s="113">
+        <f>IF(F4="","",MIN($S$6,MAX(0,$S$7-$S$6*(1-1))))</f>
+        <v>2200</v>
+      </c>
+      <c r="L4" s="113">
+        <v>2200</v>
+      </c>
+      <c r="M4" s="115">
+        <v>46251</v>
+      </c>
+      <c r="N4" s="116" t="str">
+        <f ca="1">IF(F4="","",IF(AND(ISNUMBER(L4),L4&gt;=K4),"Pago",IF(J4&lt;TODAY(),"Atrasado","A vencer")))</f>
+        <v>Pago</v>
+      </c>
+      <c r="O4" s="113">
+        <f>IF(F4="","",MAX(0,H4-SUM($L$4:L4)))</f>
+        <v>8800</v>
+      </c>
+      <c r="P4" t="str">
+        <f>IF(F4="","",IF(MAX($J$4:$J$15)&gt;_xlfn.XLOOKUP($S$4,RESERVAS!$A$6:$A$203,RESERVAS!$D$6:$D$203),"ALERTA: última parcela após a saída","OK"))</f>
+        <v>OK</v>
+      </c>
+      <c r="R4" t="s">
+        <v>134</v>
+      </c>
+      <c r="S4" s="108" t="s">
+        <v>99</v>
+      </c>
+      <c r="V4" s="108" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="5" spans="2:26">
+      <c r="B5" t="str">
+        <v>LOC-006</v>
+      </c>
+      <c r="C5" s="103" t="str">
+        <v>Miguel - Férias</v>
+      </c>
+      <c r="D5" s="102">
+        <v>9100</v>
+      </c>
+      <c r="E5" t="str">
+        <v>Configurado</v>
+      </c>
+      <c r="F5" s="112" t="str">
+        <f>IF(2&lt;=$S$8,$S$4,"")</f>
+        <v>LOC-001</v>
+      </c>
+      <c r="G5" s="112" t="str">
+        <f>IF(F5="","",_xlfn.XLOOKUP(F5,RESERVAS!$A$6:$A$203,RESERVAS!$B$6:$B$203,""))</f>
+        <v>Carlos - Natal/Ano Novo</v>
+      </c>
+      <c r="H5" s="113">
+        <f t="shared" si="0"/>
+        <v>11000</v>
+      </c>
+      <c r="I5" s="114" t="str">
+        <f>IF(F5="","",2&amp;" de "&amp;$S$8)</f>
+        <v>2 de 5</v>
+      </c>
+      <c r="J5" s="115">
+        <f>IF(F5="","",EDATE($S$5,1))</f>
+        <v>46282</v>
+      </c>
+      <c r="K5" s="113">
+        <f>IF(F5="","",MIN($S$6,MAX(0,$S$7-$S$6*(2-1))))</f>
+        <v>2200</v>
+      </c>
+      <c r="L5" s="113">
+        <v>2200</v>
+      </c>
+      <c r="M5" s="115">
+        <v>46275</v>
+      </c>
+      <c r="N5" s="116" t="str">
+        <f t="shared" ref="N4:N15" ca="1" si="1">IF(F5="","",IF(AND(ISNUMBER(L5),L5&gt;=K5),"Pago",IF(J5&lt;TODAY(),"Atrasado","A vencer")))</f>
+        <v>Pago</v>
+      </c>
+      <c r="O5" s="113">
+        <f>IF(F5="","",MAX(0,H5-SUM($L$4:L5)))</f>
+        <v>6600</v>
+      </c>
+      <c r="P5" t="str">
+        <f>IF(F5="","",IF(MAX($J$4:$J$15)&gt;_xlfn.XLOOKUP($S$4,RESERVAS!$A$6:$A$203,RESERVAS!$D$6:$D$203),"ALERTA: última parcela após a saída","OK"))</f>
+        <v>OK</v>
+      </c>
+      <c r="R5" t="s">
+        <v>148</v>
+      </c>
+      <c r="S5" s="111">
+        <v>46251</v>
+      </c>
+      <c r="V5" s="108" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="6" spans="2:26">
+      <c r="C6" s="103"/>
+      <c r="D6" s="102"/>
+      <c r="F6" s="112" t="str">
+        <f>IF(3&lt;=$S$8,$S$4,"")</f>
+        <v>LOC-001</v>
+      </c>
+      <c r="G6" s="112" t="str">
+        <f>IF(F6="","",_xlfn.XLOOKUP(F6,RESERVAS!$A$6:$A$203,RESERVAS!$B$6:$B$203,""))</f>
+        <v>Carlos - Natal/Ano Novo</v>
+      </c>
+      <c r="H6" s="113">
+        <f t="shared" si="0"/>
+        <v>11000</v>
+      </c>
+      <c r="I6" s="114" t="str">
+        <f>IF(F6="","",3&amp;" de "&amp;$S$8)</f>
+        <v>3 de 5</v>
+      </c>
+      <c r="J6" s="115">
+        <f>IF(F6="","",EDATE($S$5,2))</f>
+        <v>46312</v>
+      </c>
+      <c r="K6" s="113">
+        <f>IF(F6="","",MIN($S$6,MAX(0,$S$7-$S$6*(3-1))))</f>
+        <v>2200</v>
+      </c>
+      <c r="L6" s="113" t="str">
+        <f>IF(F6="","",IF($S$13="","",$S$13))</f>
+        <v/>
+      </c>
+      <c r="M6" s="115" t="str">
+        <f>IF(F6="","",IF($T$13="","",$T$13))</f>
+        <v/>
+      </c>
+      <c r="N6" s="116" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v>A vencer</v>
+      </c>
+      <c r="O6" s="113">
+        <f>IF(F6="","",MAX(0,H6-SUM($L$4:L6)))</f>
+        <v>6600</v>
+      </c>
+      <c r="P6" t="str">
+        <f>IF(F6="","",IF(MAX($J$4:$J$15)&gt;_xlfn.XLOOKUP($S$4,RESERVAS!$A$6:$A$203,RESERVAS!$D$6:$D$203),"ALERTA: última parcela após a saída","OK"))</f>
+        <v>OK</v>
+      </c>
+      <c r="R6" t="s">
+        <v>149</v>
+      </c>
+      <c r="S6" s="110">
+        <v>2200</v>
+      </c>
+    </row>
+    <row r="7" spans="2:26">
+      <c r="C7" s="103"/>
+      <c r="D7" s="102"/>
+      <c r="F7" s="112" t="str">
+        <f>IF(4&lt;=$S$8,$S$4,"")</f>
+        <v>LOC-001</v>
+      </c>
+      <c r="G7" s="112" t="str">
+        <f>IF(F7="","",_xlfn.XLOOKUP(F7,RESERVAS!$A$6:$A$203,RESERVAS!$B$6:$B$203,""))</f>
+        <v>Carlos - Natal/Ano Novo</v>
+      </c>
+      <c r="H7" s="113">
+        <f t="shared" si="0"/>
+        <v>11000</v>
+      </c>
+      <c r="I7" s="114" t="str">
+        <f>IF(F7="","",4&amp;" de "&amp;$S$8)</f>
+        <v>4 de 5</v>
+      </c>
+      <c r="J7" s="115">
+        <f>IF(F7="","",EDATE($S$5,3))</f>
+        <v>46343</v>
+      </c>
+      <c r="K7" s="113">
+        <f>IF(F7="","",MIN($S$6,MAX(0,$S$7-$S$6*(4-1))))</f>
+        <v>2200</v>
+      </c>
+      <c r="L7" s="113" t="str">
+        <f>IF(F7="","",IF($S$14="","",$S$14))</f>
+        <v/>
+      </c>
+      <c r="M7" s="115" t="str">
+        <f>IF(F7="","",IF($T$14="","",$T$14))</f>
+        <v/>
+      </c>
+      <c r="N7" s="116" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v>A vencer</v>
+      </c>
+      <c r="O7" s="113">
+        <f>IF(F7="","",MAX(0,H7-SUM($L$4:L7)))</f>
+        <v>6600</v>
+      </c>
+      <c r="P7" t="str">
+        <f>IF(F7="","",IF(MAX($J$4:$J$15)&gt;_xlfn.XLOOKUP($S$4,RESERVAS!$A$6:$A$203,RESERVAS!$D$6:$D$203),"ALERTA: última parcela após a saída","OK"))</f>
+        <v>OK</v>
+      </c>
+      <c r="R7" t="s">
+        <v>138</v>
+      </c>
+      <c r="S7" s="109">
+        <f>SUMIFS(RESERVAS!$G$6:$G$203,RESERVAS!$A$6:$A$203,S4)</f>
+        <v>11000</v>
+      </c>
+      <c r="V7">
+        <v>1</v>
+      </c>
+      <c r="W7" s="111">
+        <v>46283</v>
+      </c>
+      <c r="X7" s="110">
+        <v>3925</v>
+      </c>
+      <c r="Y7" s="110">
+        <v>3925</v>
+      </c>
+      <c r="Z7" s="111">
+        <v>46283</v>
+      </c>
+    </row>
+    <row r="8" spans="2:26">
+      <c r="C8" s="103"/>
+      <c r="D8" s="102"/>
+      <c r="F8" s="112" t="str">
+        <f>IF(5&lt;=$S$8,$S$4,"")</f>
+        <v>LOC-001</v>
+      </c>
+      <c r="G8" s="112" t="str">
+        <f>IF(F8="","",_xlfn.XLOOKUP(F8,RESERVAS!$A$6:$A$203,RESERVAS!$B$6:$B$203,""))</f>
+        <v>Carlos - Natal/Ano Novo</v>
+      </c>
+      <c r="H8" s="113">
+        <f t="shared" si="0"/>
+        <v>11000</v>
+      </c>
+      <c r="I8" s="114" t="str">
+        <f>IF(F8="","",5&amp;" de "&amp;$S$8)</f>
+        <v>5 de 5</v>
+      </c>
+      <c r="J8" s="115">
+        <f>IF(F8="","",EDATE($S$5,4))</f>
+        <v>46373</v>
+      </c>
+      <c r="K8" s="113">
+        <f>IF(F8="","",MIN($S$6,MAX(0,$S$7-$S$6*(5-1))))</f>
+        <v>2200</v>
+      </c>
+      <c r="L8" s="113" t="str">
+        <f>IF(F8="","",IF($S$15="","",$S$15))</f>
+        <v/>
+      </c>
+      <c r="M8" s="115" t="str">
+        <f>IF(F8="","",IF($T$15="","",$T$15))</f>
+        <v/>
+      </c>
+      <c r="N8" s="116" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v>A vencer</v>
+      </c>
+      <c r="O8" s="113">
+        <f>IF(F8="","",MAX(0,H8-SUM($L$4:L8)))</f>
+        <v>6600</v>
+      </c>
+      <c r="P8" t="str">
+        <f>IF(F8="","",IF(MAX($J$4:$J$15)&gt;_xlfn.XLOOKUP($S$4,RESERVAS!$A$6:$A$203,RESERVAS!$D$6:$D$203),"ALERTA: última parcela após a saída","OK"))</f>
+        <v>OK</v>
+      </c>
+      <c r="R8" t="s">
+        <v>150</v>
+      </c>
+      <c r="S8" s="107">
+        <v>5</v>
+      </c>
+      <c r="V8">
+        <v>2</v>
+      </c>
+      <c r="W8" s="111">
+        <v>46376</v>
+      </c>
+      <c r="X8" s="110">
+        <v>8831.25</v>
+      </c>
+      <c r="Y8" s="110"/>
+      <c r="Z8" s="111"/>
+    </row>
+    <row r="9" spans="2:26">
+      <c r="C9" s="103"/>
+      <c r="D9" s="102"/>
+      <c r="F9" s="112" t="str">
+        <f>IF(6&lt;=$S$8,$S$4,"")</f>
+        <v/>
+      </c>
+      <c r="G9" s="112" t="str">
+        <f>IF(F9="","",_xlfn.XLOOKUP(F9,RESERVAS!$A$6:$A$203,RESERVAS!$B$6:$B$203,""))</f>
+        <v/>
+      </c>
+      <c r="H9" s="113" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="I9" s="114" t="str">
+        <f>IF(F9="","",6&amp;" de "&amp;$S$8)</f>
+        <v/>
+      </c>
+      <c r="J9" s="115" t="str">
+        <f>IF(F9="","",EDATE($S$5,5))</f>
+        <v/>
+      </c>
+      <c r="K9" s="113" t="str">
+        <f>IF(F9="","",MIN($S$6,MAX(0,$S$7-$S$6*(6-1))))</f>
+        <v/>
+      </c>
+      <c r="L9" s="113" t="str">
+        <f>IF(F9="","",IF($S$16="","",$S$16))</f>
+        <v/>
+      </c>
+      <c r="M9" s="115" t="str">
+        <f>IF(F9="","",IF($T$16="","",$T$16))</f>
+        <v/>
+      </c>
+      <c r="N9" s="116" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="O9" s="113" t="str">
+        <f>IF(F9="","",MAX(0,H9-SUM($L$4:L9)))</f>
+        <v/>
+      </c>
+      <c r="P9" t="str">
+        <f>IF(F9="","",IF(MAX($J$4:$J$15)&gt;_xlfn.XLOOKUP($S$4,RESERVAS!$A$6:$A$203,RESERVAS!$D$6:$D$203),"ALERTA: última parcela após a saída","OK"))</f>
+        <v/>
+      </c>
+      <c r="V9">
+        <v>3</v>
+      </c>
+      <c r="W9" s="111">
+        <v>46399</v>
+      </c>
+      <c r="X9" s="110">
+        <v>2943.75</v>
+      </c>
+      <c r="Y9" s="110"/>
+      <c r="Z9" s="111"/>
+    </row>
+    <row r="10" spans="2:26" ht="15">
+      <c r="C10" s="103"/>
+      <c r="D10" s="102"/>
+      <c r="F10" s="112" t="str">
+        <f>IF(7&lt;=$S$8,$S$4,"")</f>
+        <v/>
+      </c>
+      <c r="G10" s="112" t="str">
+        <f>IF(F10="","",_xlfn.XLOOKUP(F10,RESERVAS!$A$6:$A$203,RESERVAS!$B$6:$B$203,""))</f>
+        <v/>
+      </c>
+      <c r="H10" s="113" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="I10" s="114" t="str">
+        <f>IF(F10="","",7&amp;" de "&amp;$S$8)</f>
+        <v/>
+      </c>
+      <c r="J10" s="115" t="str">
+        <f>IF(F10="","",EDATE($S$5,6))</f>
+        <v/>
+      </c>
+      <c r="K10" s="113" t="str">
+        <f>IF(F10="","",MIN($S$6,MAX(0,$S$7-$S$6*(7-1))))</f>
+        <v/>
+      </c>
+      <c r="L10" s="113" t="str">
+        <f>IF(F10="","",IF($S$17="","",$S$17))</f>
+        <v/>
+      </c>
+      <c r="M10" s="115" t="str">
+        <f>IF(F10="","",IF($T$17="","",$T$17))</f>
+        <v/>
+      </c>
+      <c r="N10" s="116" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="O10" s="113" t="str">
+        <f>IF(F10="","",MAX(0,H10-SUM($L$4:L10)))</f>
+        <v/>
+      </c>
+      <c r="P10" t="str">
+        <f>IF(F10="","",IF(MAX($J$4:$J$15)&gt;_xlfn.XLOOKUP($S$4,RESERVAS!$A$6:$A$203,RESERVAS!$D$6:$D$203),"ALERTA: última parcela após a saída","OK"))</f>
+        <v/>
+      </c>
+      <c r="R10" s="124"/>
+      <c r="S10" s="124"/>
+      <c r="T10" s="124"/>
+    </row>
+    <row r="11" spans="2:26">
+      <c r="C11" s="103"/>
+      <c r="D11" s="102"/>
+      <c r="F11" s="112" t="str">
+        <f>IF(8&lt;=$S$8,$S$4,"")</f>
+        <v/>
+      </c>
+      <c r="G11" s="112" t="str">
+        <f>IF(F11="","",_xlfn.XLOOKUP(F11,RESERVAS!$A$6:$A$203,RESERVAS!$B$6:$B$203,""))</f>
+        <v/>
+      </c>
+      <c r="H11" s="113" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="I11" s="114" t="str">
+        <f>IF(F11="","",8&amp;" de "&amp;$S$8)</f>
+        <v/>
+      </c>
+      <c r="J11" s="115" t="str">
+        <f>IF(F11="","",EDATE($S$5,7))</f>
+        <v/>
+      </c>
+      <c r="K11" s="113" t="str">
+        <f>IF(F11="","",MIN($S$6,MAX(0,$S$7-$S$6*(8-1))))</f>
+        <v/>
+      </c>
+      <c r="L11" s="113" t="str">
+        <f>IF(F11="","",IF($S$18="","",$S$18))</f>
+        <v/>
+      </c>
+      <c r="M11" s="115" t="str">
+        <f>IF(F11="","",IF($T$18="","",$T$18))</f>
+        <v/>
+      </c>
+      <c r="N11" s="116" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="O11" s="113" t="str">
+        <f>IF(F11="","",MAX(0,H11-SUM($L$4:L11)))</f>
+        <v/>
+      </c>
+      <c r="P11" t="str">
+        <f>IF(F11="","",IF(MAX($J$4:$J$15)&gt;_xlfn.XLOOKUP($S$4,RESERVAS!$A$6:$A$203,RESERVAS!$D$6:$D$203),"ALERTA: última parcela após a saída","OK"))</f>
+        <v/>
+      </c>
+      <c r="R11" s="125"/>
+      <c r="S11" s="126"/>
+      <c r="T11" s="127"/>
+    </row>
+    <row r="12" spans="2:26">
+      <c r="C12" s="103"/>
+      <c r="D12" s="102"/>
+      <c r="F12" s="112" t="str">
+        <f>IF(9&lt;=$S$8,$S$4,"")</f>
+        <v/>
+      </c>
+      <c r="G12" s="112" t="str">
+        <f>IF(F12="","",_xlfn.XLOOKUP(F12,RESERVAS!$A$6:$A$203,RESERVAS!$B$6:$B$203,""))</f>
+        <v/>
+      </c>
+      <c r="H12" s="113" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="I12" s="114" t="str">
+        <f>IF(F12="","",9&amp;" de "&amp;$S$8)</f>
+        <v/>
+      </c>
+      <c r="J12" s="115" t="str">
+        <f>IF(F12="","",EDATE($S$5,8))</f>
+        <v/>
+      </c>
+      <c r="K12" s="113" t="str">
+        <f>IF(F12="","",MIN($S$6,MAX(0,$S$7-$S$6*(9-1))))</f>
+        <v/>
+      </c>
+      <c r="L12" s="113" t="str">
+        <f>IF(F12="","",IF($S$19="","",$S$19))</f>
+        <v/>
+      </c>
+      <c r="M12" s="115" t="str">
+        <f>IF(F12="","",IF($T$19="","",$T$19))</f>
+        <v/>
+      </c>
+      <c r="N12" s="116" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="O12" s="113" t="str">
+        <f>IF(F12="","",MAX(0,H12-SUM($L$4:L12)))</f>
+        <v/>
+      </c>
+      <c r="P12" t="str">
+        <f>IF(F12="","",IF(MAX($J$4:$J$15)&gt;_xlfn.XLOOKUP($S$4,RESERVAS!$A$6:$A$203,RESERVAS!$D$6:$D$203),"ALERTA: última parcela após a saída","OK"))</f>
+        <v/>
+      </c>
+      <c r="R12" s="125"/>
+      <c r="S12" s="126"/>
+      <c r="T12" s="127"/>
+    </row>
+    <row r="13" spans="2:26">
+      <c r="C13" s="103"/>
+      <c r="D13" s="102"/>
+      <c r="F13" s="101" t="str">
+        <f>IF(10&lt;=$S$8,$S$4,"")</f>
+        <v/>
+      </c>
+      <c r="G13" s="101" t="str">
+        <f>IF(F13="","",_xlfn.XLOOKUP(F13,RESERVAS!$A$6:$A$203,RESERVAS!$B$6:$B$203,""))</f>
+        <v/>
+      </c>
+      <c r="H13" s="113" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="I13" s="101" t="str">
+        <f>IF(F13="","",10&amp;" de "&amp;$S$8)</f>
+        <v/>
+      </c>
+      <c r="J13" s="117" t="str">
+        <f>IF(F13="","",EDATE($S$5,9))</f>
+        <v/>
+      </c>
+      <c r="K13" s="118" t="str">
+        <f>IF(F13="","",MIN($S$6,MAX(0,$S$7-$S$6*(10-1))))</f>
+        <v/>
+      </c>
+      <c r="L13" s="118" t="str">
+        <f>IF(F13="","",IF($S$20="","",$S$20))</f>
+        <v/>
+      </c>
+      <c r="M13" s="117" t="str">
+        <f>IF(F13="","",IF($T$20="","",$T$20))</f>
+        <v/>
+      </c>
+      <c r="N13" s="116" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="O13" s="113" t="str">
+        <f>IF(F13="","",MAX(0,H13-SUM($L$4:L13)))</f>
+        <v/>
+      </c>
+      <c r="P13" t="str">
+        <f>IF(F13="","",IF(MAX($J$4:$J$15)&gt;_xlfn.XLOOKUP($S$4,RESERVAS!$A$6:$A$203,RESERVAS!$D$6:$D$203),"ALERTA: última parcela após a saída","OK"))</f>
+        <v/>
+      </c>
+      <c r="R13" s="125"/>
+      <c r="S13" s="126"/>
+      <c r="T13" s="127"/>
+    </row>
+    <row r="14" spans="2:26">
+      <c r="C14" s="103"/>
+      <c r="D14" s="102"/>
+      <c r="F14" s="101" t="str">
+        <f>IF(11&lt;=$S$8,$S$4,"")</f>
+        <v/>
+      </c>
+      <c r="G14" s="101" t="str">
+        <f>IF(F14="","",_xlfn.XLOOKUP(F14,RESERVAS!$A$6:$A$203,RESERVAS!$B$6:$B$203,""))</f>
+        <v/>
+      </c>
+      <c r="H14" s="113" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="I14" s="101" t="str">
+        <f>IF(F14="","",11&amp;" de "&amp;$S$8)</f>
+        <v/>
+      </c>
+      <c r="J14" s="117" t="str">
+        <f>IF(F14="","",EDATE($S$5,10))</f>
+        <v/>
+      </c>
+      <c r="K14" s="118" t="str">
+        <f>IF(F14="","",MIN($S$6,MAX(0,$S$7-$S$6*(11-1))))</f>
+        <v/>
+      </c>
+      <c r="L14" s="118" t="str">
+        <f>IF(F14="","",IF($S$21="","",$S$21))</f>
+        <v/>
+      </c>
+      <c r="M14" s="117" t="str">
+        <f>IF(F14="","",IF($T$21="","",$T$21))</f>
+        <v/>
+      </c>
+      <c r="N14" s="116" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="O14" s="113" t="str">
+        <f>IF(F14="","",MAX(0,H14-SUM($L$4:L14)))</f>
+        <v/>
+      </c>
+      <c r="P14" t="str">
+        <f>IF(F14="","",IF(MAX($J$4:$J$15)&gt;_xlfn.XLOOKUP($S$4,RESERVAS!$A$6:$A$203,RESERVAS!$D$6:$D$203),"ALERTA: última parcela após a saída","OK"))</f>
+        <v/>
+      </c>
+      <c r="R14" s="125"/>
+      <c r="S14" s="126"/>
+      <c r="T14" s="127"/>
+    </row>
+    <row r="15" spans="2:26">
+      <c r="C15" s="103"/>
+      <c r="D15" s="102"/>
+      <c r="F15" s="101" t="str">
+        <f>IF(12&lt;=$S$8,$S$4,"")</f>
+        <v/>
+      </c>
+      <c r="G15" s="101" t="str">
+        <f>IF(F15="","",_xlfn.XLOOKUP(F15,RESERVAS!$A$6:$A$203,RESERVAS!$B$6:$B$203,""))</f>
+        <v/>
+      </c>
+      <c r="H15" s="113" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="I15" s="101" t="str">
+        <f>IF(F15="","",12&amp;" de "&amp;$S$8)</f>
+        <v/>
+      </c>
+      <c r="J15" s="117" t="str">
+        <f>IF(F15="","",EDATE($S$5,11))</f>
+        <v/>
+      </c>
+      <c r="K15" s="118" t="str">
+        <f>IF(F15="","",MIN($S$6,MAX(0,$S$7-$S$6*(12-1))))</f>
+        <v/>
+      </c>
+      <c r="L15" s="118" t="str">
+        <f>IF(F15="","",IF($S$22="","",$S$22))</f>
+        <v/>
+      </c>
+      <c r="M15" s="117" t="str">
+        <f>IF(F15="","",IF($T$22="","",$T$22))</f>
+        <v/>
+      </c>
+      <c r="N15" s="116" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="O15" s="113" t="str">
+        <f>IF(F15="","",MAX(0,H15-SUM($L$4:L15)))</f>
+        <v/>
+      </c>
+      <c r="P15" t="str">
+        <f>IF(F15="","",IF(MAX($J$4:$J$15)&gt;_xlfn.XLOOKUP($S$4,RESERVAS!$A$6:$A$203,RESERVAS!$D$6:$D$203),"ALERTA: última parcela após a saída","OK"))</f>
+        <v/>
+      </c>
+      <c r="R15" s="125"/>
+      <c r="S15" s="126"/>
+      <c r="T15" s="127"/>
+    </row>
+    <row r="16" spans="2:26">
+      <c r="C16" s="103"/>
+      <c r="D16" s="102"/>
+      <c r="F16" s="101"/>
+      <c r="G16" s="101"/>
+      <c r="H16" s="118"/>
+      <c r="I16" s="101"/>
+      <c r="J16" s="117"/>
+      <c r="K16" s="118"/>
+      <c r="L16" s="118"/>
+      <c r="M16" s="117"/>
+      <c r="N16" s="101"/>
+      <c r="O16" s="118"/>
+      <c r="R16" s="125"/>
+      <c r="S16" s="126"/>
+      <c r="T16" s="127"/>
+    </row>
+    <row r="17" spans="3:20">
+      <c r="C17" s="103"/>
+      <c r="D17" s="102"/>
+      <c r="F17" s="101" t="str">
+        <f>IF(W7="","",$V$4&amp;" + "&amp;$V$5)</f>
+        <v>LOC-005 + LOC-006</v>
+      </c>
+      <c r="G17" s="101" t="str">
+        <f>IF(F17="","",_xlfn.XLOOKUP($V$4,RESERVAS!$A$6:$A$203,RESERVAS!$B$6:$B$203,""))</f>
+        <v>Miguel - Férias</v>
+      </c>
+      <c r="H17" s="113">
+        <f>IF(F17="","",SUMIFS(RESERVAS!$G$6:$G$203,RESERVAS!$A$6:$A$203,$V$4)+SUMIFS(RESERVAS!$G$6:$G$203,RESERVAS!$A$6:$A$203,$V$5))</f>
+        <v>15700</v>
+      </c>
+      <c r="I17" s="101" t="str">
+        <f>IF(F17="","",1&amp;" de "&amp;COUNT($W$7:$W$9))</f>
+        <v>1 de 3</v>
+      </c>
+      <c r="J17" s="117">
+        <f>IF(F17="","",W7)</f>
+        <v>46283</v>
+      </c>
+      <c r="K17" s="118">
+        <f>IF(F17="","",X7)</f>
+        <v>3925</v>
+      </c>
+      <c r="L17" s="118">
+        <f>IF(F17="","",IF(Y7="","",Y7))</f>
+        <v>3925</v>
+      </c>
+      <c r="M17" s="117">
+        <f>IF(F17="","",IF(Z7="","",Z7))</f>
+        <v>46283</v>
+      </c>
+      <c r="N17" s="116" t="str">
+        <f ca="1">IF(F17="","",IF(AND(ISNUMBER(L17),L17&gt;=K17),"Pago",IF(J17&lt;TODAY(),"Atrasado","A vencer")))</f>
+        <v>Pago</v>
+      </c>
+      <c r="O17" s="113">
+        <f>IF(F17="","",MAX(0,H17-SUM($L$17:L17)))</f>
+        <v>11775</v>
+      </c>
+      <c r="P17" t="str">
+        <f>IF(F17="","",IF(MAX($J$17:$J$19)&gt;MAX(_xlfn.XLOOKUP($V$4,RESERVAS!$A$6:$A$203,RESERVAS!$D$6:$D$203),_xlfn.XLOOKUP($V$5,RESERVAS!$A$6:$A$203,RESERVAS!$D$6:$D$203)),"ALERTA: última parcela após a saída","OK"))</f>
+        <v>OK</v>
+      </c>
+      <c r="R17" s="125"/>
+      <c r="S17" s="126"/>
+      <c r="T17" s="127"/>
+    </row>
+    <row r="18" spans="3:20">
+      <c r="C18" s="103"/>
+      <c r="D18" s="102"/>
+      <c r="F18" s="101" t="str">
+        <f>IF(W8="","",$V$4&amp;" + "&amp;$V$5)</f>
+        <v>LOC-005 + LOC-006</v>
+      </c>
+      <c r="G18" s="101" t="str">
+        <f>IF(F18="","",_xlfn.XLOOKUP($V$4,RESERVAS!$A$6:$A$203,RESERVAS!$B$6:$B$203,""))</f>
+        <v>Miguel - Férias</v>
+      </c>
+      <c r="H18" s="118">
+        <f>IF(F18="","",SUMIFS(RESERVAS!$G$6:$G$203,RESERVAS!$A$6:$A$203,$V$4)+SUMIFS(RESERVAS!$G$6:$G$203,RESERVAS!$A$6:$A$203,$V$5))</f>
+        <v>15700</v>
+      </c>
+      <c r="I18" s="101" t="str">
+        <f>IF(F18="","",2&amp;" de "&amp;COUNT($W$7:$W$9))</f>
+        <v>2 de 3</v>
+      </c>
+      <c r="J18" s="117">
+        <f>IF(F18="","",W8)</f>
+        <v>46376</v>
+      </c>
+      <c r="K18" s="118">
+        <f>IF(F18="","",X8)</f>
+        <v>8831.25</v>
+      </c>
+      <c r="L18" s="118" t="str">
+        <f>IF(F18="","",IF(Y8="","",Y8))</f>
+        <v/>
+      </c>
+      <c r="M18" s="117" t="str">
+        <f>IF(F18="","",IF(Z8="","",Z8))</f>
+        <v/>
+      </c>
+      <c r="N18" s="116" t="str">
+        <f ca="1">IF(F18="","",IF(AND(ISNUMBER(L18),L18&gt;=K18),"Pago",IF(J18&lt;TODAY(),"Atrasado","A vencer")))</f>
+        <v>A vencer</v>
+      </c>
+      <c r="O18" s="118">
+        <f>IF(F18="","",MAX(0,H18-SUM($L$17:L18)))</f>
+        <v>11775</v>
+      </c>
+      <c r="P18" t="str">
+        <f>IF(F18="","",IF(MAX($J$17:$J$19)&gt;MAX(_xlfn.XLOOKUP($V$4,RESERVAS!$A$6:$A$203,RESERVAS!$D$6:$D$203),_xlfn.XLOOKUP($V$5,RESERVAS!$A$6:$A$203,RESERVAS!$D$6:$D$203)),"ALERTA: última parcela após a saída","OK"))</f>
+        <v>OK</v>
+      </c>
+      <c r="R18" s="125"/>
+      <c r="S18" s="126"/>
+      <c r="T18" s="127"/>
+    </row>
+    <row r="19" spans="3:20">
+      <c r="C19" s="103"/>
+      <c r="D19" s="102"/>
+      <c r="F19" s="101" t="str">
+        <f>IF(W9="","",$V$4&amp;" + "&amp;$V$5)</f>
+        <v>LOC-005 + LOC-006</v>
+      </c>
+      <c r="G19" s="101" t="str">
+        <f>IF(F19="","",_xlfn.XLOOKUP($V$4,RESERVAS!$A$6:$A$203,RESERVAS!$B$6:$B$203,""))</f>
+        <v>Miguel - Férias</v>
+      </c>
+      <c r="H19" s="118">
+        <f>IF(F19="","",SUMIFS(RESERVAS!$G$6:$G$203,RESERVAS!$A$6:$A$203,$V$4)+SUMIFS(RESERVAS!$G$6:$G$203,RESERVAS!$A$6:$A$203,$V$5))</f>
+        <v>15700</v>
+      </c>
+      <c r="I19" s="101" t="str">
+        <f>IF(F19="","",3&amp;" de "&amp;COUNT($W$7:$W$9))</f>
+        <v>3 de 3</v>
+      </c>
+      <c r="J19" s="117">
+        <f>IF(F19="","",W9)</f>
+        <v>46399</v>
+      </c>
+      <c r="K19" s="118">
+        <f>IF(F19="","",X9)</f>
+        <v>2943.75</v>
+      </c>
+      <c r="L19" s="118" t="str">
+        <f>IF(F19="","",IF(Y9="","",Y9))</f>
+        <v/>
+      </c>
+      <c r="M19" s="117" t="str">
+        <f>IF(F19="","",IF(Z9="","",Z9))</f>
+        <v/>
+      </c>
+      <c r="N19" s="116" t="str">
+        <f ca="1">IF(F19="","",IF(AND(ISNUMBER(L19),L19&gt;=K19),"Pago",IF(J19&lt;TODAY(),"Atrasado","A vencer")))</f>
+        <v>A vencer</v>
+      </c>
+      <c r="O19" s="118">
+        <f>IF(F19="","",MAX(0,H19-SUM($L$17:L19)))</f>
+        <v>11775</v>
+      </c>
+      <c r="P19" t="str">
+        <f>IF(F19="","",IF(MAX($J$17:$J$19)&gt;MAX(_xlfn.XLOOKUP($V$4,RESERVAS!$A$6:$A$203,RESERVAS!$D$6:$D$203),_xlfn.XLOOKUP($V$5,RESERVAS!$A$6:$A$203,RESERVAS!$D$6:$D$203)),"ALERTA: última parcela após a saída","OK"))</f>
+        <v>OK</v>
+      </c>
+      <c r="R19" s="125"/>
+      <c r="S19" s="126"/>
+      <c r="T19" s="127"/>
+    </row>
+    <row r="20" spans="3:20">
+      <c r="C20" s="103"/>
+      <c r="D20" s="102"/>
+      <c r="R20" s="125"/>
+      <c r="S20" s="126"/>
+      <c r="T20" s="127"/>
+    </row>
+    <row r="21" spans="3:20">
+      <c r="C21" s="103"/>
+      <c r="D21" s="102"/>
+      <c r="R21" s="125"/>
+      <c r="S21" s="126"/>
+      <c r="T21" s="127"/>
+    </row>
+    <row r="22" spans="3:20">
+      <c r="C22" s="103"/>
+      <c r="D22" s="102"/>
+      <c r="R22" s="125"/>
+      <c r="S22" s="126"/>
+      <c r="T22" s="127"/>
+    </row>
+    <row r="23" spans="3:20">
+      <c r="C23" s="103"/>
+      <c r="D23" s="102"/>
+    </row>
+    <row r="24" spans="3:20">
+      <c r="C24" s="103"/>
+      <c r="D24" s="102"/>
+    </row>
+    <row r="25" spans="3:20">
+      <c r="C25" s="103"/>
+      <c r="D25" s="102"/>
+    </row>
+    <row r="26" spans="3:20">
+      <c r="C26" s="103"/>
+      <c r="D26" s="102"/>
+    </row>
+    <row r="27" spans="3:20">
+      <c r="C27" s="103"/>
+      <c r="D27" s="102"/>
+    </row>
+    <row r="28" spans="3:20">
+      <c r="C28" s="103"/>
+      <c r="D28" s="102"/>
+    </row>
+    <row r="29" spans="3:20">
+      <c r="C29" s="103"/>
+      <c r="D29" s="102"/>
+    </row>
+    <row r="30" spans="3:20">
+      <c r="C30" s="103"/>
+      <c r="D30" s="102"/>
+    </row>
+    <row r="31" spans="3:20">
+      <c r="C31" s="103"/>
+      <c r="D31" s="102"/>
+    </row>
+    <row r="32" spans="3:20">
+      <c r="C32" s="103"/>
+      <c r="D32" s="102"/>
+    </row>
+    <row r="33" spans="3:4">
+      <c r="C33" s="103"/>
+      <c r="D33" s="102"/>
+    </row>
+    <row r="34" spans="3:4">
+      <c r="C34" s="103"/>
+      <c r="D34" s="102"/>
+    </row>
+    <row r="35" spans="3:4">
+      <c r="C35" s="103"/>
+      <c r="D35" s="102"/>
+    </row>
+    <row r="36" spans="3:4">
+      <c r="C36" s="103"/>
+      <c r="D36" s="102"/>
+    </row>
+    <row r="37" spans="3:4">
+      <c r="C37" s="103"/>
+      <c r="D37" s="102"/>
+    </row>
+    <row r="38" spans="3:4">
+      <c r="C38" s="103"/>
+      <c r="D38" s="102"/>
+    </row>
+    <row r="39" spans="3:4">
+      <c r="C39" s="103"/>
+      <c r="D39" s="102"/>
+    </row>
+    <row r="40" spans="3:4">
+      <c r="C40" s="103"/>
+      <c r="D40" s="102"/>
+    </row>
+    <row r="41" spans="3:4">
+      <c r="C41" s="103"/>
+      <c r="D41" s="102"/>
+    </row>
+    <row r="42" spans="3:4">
+      <c r="C42" s="103"/>
+      <c r="D42" s="102"/>
+    </row>
+    <row r="43" spans="3:4">
+      <c r="C43" s="103"/>
+      <c r="D43" s="102"/>
+    </row>
+    <row r="44" spans="3:4">
+      <c r="C44" s="103"/>
+      <c r="D44" s="102"/>
+    </row>
+    <row r="45" spans="3:4">
+      <c r="C45" s="103"/>
+      <c r="D45" s="102"/>
+    </row>
+    <row r="46" spans="3:4">
+      <c r="C46" s="103"/>
+      <c r="D46" s="102"/>
+    </row>
+    <row r="47" spans="3:4">
+      <c r="C47" s="103"/>
+      <c r="D47" s="102"/>
+    </row>
+    <row r="48" spans="3:4">
+      <c r="C48" s="103"/>
+      <c r="D48" s="102"/>
+    </row>
+    <row r="49" spans="3:4">
+      <c r="C49" s="103"/>
+      <c r="D49" s="102"/>
+    </row>
+    <row r="50" spans="3:4">
+      <c r="C50" s="103"/>
+      <c r="D50" s="102"/>
+    </row>
+    <row r="51" spans="3:4">
+      <c r="C51" s="103"/>
+      <c r="D51" s="102"/>
+    </row>
+    <row r="52" spans="3:4">
+      <c r="C52" s="103"/>
+      <c r="D52" s="102"/>
+    </row>
+    <row r="53" spans="3:4">
+      <c r="C53" s="103"/>
+      <c r="D53" s="102"/>
+    </row>
+    <row r="54" spans="3:4">
+      <c r="C54" s="103"/>
+      <c r="D54" s="102"/>
+    </row>
+    <row r="55" spans="3:4">
+      <c r="C55" s="103"/>
+      <c r="D55" s="102"/>
+    </row>
+    <row r="56" spans="3:4">
+      <c r="C56" s="103"/>
+      <c r="D56" s="102"/>
+    </row>
+    <row r="57" spans="3:4">
+      <c r="C57" s="103"/>
+      <c r="D57" s="102"/>
+    </row>
+    <row r="58" spans="3:4">
+      <c r="C58" s="103"/>
+      <c r="D58" s="102"/>
+    </row>
+    <row r="59" spans="3:4">
+      <c r="C59" s="103"/>
+      <c r="D59" s="102"/>
+    </row>
+    <row r="60" spans="3:4">
+      <c r="C60" s="103"/>
+      <c r="D60" s="102"/>
+    </row>
+    <row r="61" spans="3:4">
+      <c r="C61" s="103"/>
+      <c r="D61" s="102"/>
+    </row>
+    <row r="62" spans="3:4">
+      <c r="C62" s="103"/>
+      <c r="D62" s="102"/>
+    </row>
+    <row r="63" spans="3:4">
+      <c r="C63" s="103"/>
+      <c r="D63" s="102"/>
+    </row>
+    <row r="64" spans="3:4">
+      <c r="C64" s="103"/>
+      <c r="D64" s="102"/>
+    </row>
+    <row r="65" spans="3:4">
+      <c r="C65" s="103"/>
+      <c r="D65" s="102"/>
+    </row>
+    <row r="66" spans="3:4">
+      <c r="C66" s="103"/>
+      <c r="D66" s="102"/>
+    </row>
+    <row r="67" spans="3:4">
+      <c r="C67" s="103"/>
+      <c r="D67" s="102"/>
+    </row>
+    <row r="68" spans="3:4">
+      <c r="C68" s="103"/>
+      <c r="D68" s="102"/>
+    </row>
+    <row r="69" spans="3:4">
+      <c r="C69" s="103"/>
+      <c r="D69" s="102"/>
+    </row>
+    <row r="70" spans="3:4">
+      <c r="C70" s="103"/>
+      <c r="D70" s="102"/>
+    </row>
+    <row r="71" spans="3:4">
+      <c r="C71" s="103"/>
+      <c r="D71" s="102"/>
+    </row>
+    <row r="72" spans="3:4">
+      <c r="C72" s="103"/>
+      <c r="D72" s="102"/>
+    </row>
+    <row r="73" spans="3:4">
+      <c r="C73" s="103"/>
+      <c r="D73" s="102"/>
+    </row>
+    <row r="74" spans="3:4">
+      <c r="C74" s="103"/>
+      <c r="D74" s="102"/>
+    </row>
+    <row r="75" spans="3:4">
+      <c r="C75" s="103"/>
+      <c r="D75" s="102"/>
+    </row>
+    <row r="76" spans="3:4">
+      <c r="C76" s="103"/>
+      <c r="D76" s="102"/>
+    </row>
+    <row r="77" spans="3:4">
+      <c r="C77" s="103"/>
+      <c r="D77" s="102"/>
+    </row>
+    <row r="78" spans="3:4">
+      <c r="C78" s="103"/>
+      <c r="D78" s="102"/>
+    </row>
+    <row r="79" spans="3:4">
+      <c r="C79" s="103"/>
+      <c r="D79" s="102"/>
+    </row>
+    <row r="80" spans="3:4">
+      <c r="C80" s="103"/>
+      <c r="D80" s="102"/>
+    </row>
+    <row r="81" spans="3:4">
+      <c r="C81" s="103"/>
+      <c r="D81" s="102"/>
+    </row>
+    <row r="82" spans="3:4">
+      <c r="C82" s="103"/>
+      <c r="D82" s="102"/>
+    </row>
+    <row r="83" spans="3:4">
+      <c r="C83" s="103"/>
+      <c r="D83" s="102"/>
+    </row>
+    <row r="84" spans="3:4">
+      <c r="C84" s="103"/>
+      <c r="D84" s="102"/>
+    </row>
+    <row r="85" spans="3:4">
+      <c r="C85" s="103"/>
+      <c r="D85" s="102"/>
+    </row>
+    <row r="86" spans="3:4">
+      <c r="C86" s="103"/>
+      <c r="D86" s="102"/>
+    </row>
+    <row r="87" spans="3:4">
+      <c r="C87" s="103"/>
+      <c r="D87" s="102"/>
+    </row>
+    <row r="88" spans="3:4">
+      <c r="C88" s="103"/>
+      <c r="D88" s="102"/>
+    </row>
+    <row r="89" spans="3:4">
+      <c r="C89" s="103"/>
+      <c r="D89" s="102"/>
+    </row>
+    <row r="90" spans="3:4">
+      <c r="C90" s="103"/>
+      <c r="D90" s="102"/>
+    </row>
+    <row r="91" spans="3:4">
+      <c r="C91" s="103"/>
+      <c r="D91" s="102"/>
+    </row>
+    <row r="92" spans="3:4">
+      <c r="C92" s="103"/>
+      <c r="D92" s="102"/>
+    </row>
+    <row r="93" spans="3:4">
+      <c r="C93" s="103"/>
+      <c r="D93" s="102"/>
+    </row>
+    <row r="94" spans="3:4">
+      <c r="C94" s="103"/>
+      <c r="D94" s="102"/>
+    </row>
+    <row r="95" spans="3:4">
+      <c r="C95" s="103"/>
+      <c r="D95" s="102"/>
+    </row>
+    <row r="96" spans="3:4">
+      <c r="C96" s="103"/>
+      <c r="D96" s="102"/>
+    </row>
+    <row r="97" spans="3:4">
+      <c r="C97" s="103"/>
+      <c r="D97" s="102"/>
+    </row>
+    <row r="98" spans="3:4">
+      <c r="C98" s="103"/>
+      <c r="D98" s="102"/>
+    </row>
+    <row r="99" spans="3:4">
+      <c r="C99" s="103"/>
+      <c r="D99" s="102"/>
+    </row>
+    <row r="100" spans="3:4">
+      <c r="C100" s="103"/>
+      <c r="D100" s="102"/>
+    </row>
+    <row r="101" spans="3:4">
+      <c r="C101" s="103"/>
+      <c r="D101" s="102"/>
+    </row>
+    <row r="102" spans="3:4">
+      <c r="C102" s="103"/>
+      <c r="D102" s="102"/>
+    </row>
+    <row r="103" spans="3:4">
+      <c r="C103" s="103"/>
+      <c r="D103" s="102"/>
+    </row>
+    <row r="104" spans="3:4">
+      <c r="C104" s="103"/>
+      <c r="D104" s="102"/>
+    </row>
+    <row r="105" spans="3:4">
+      <c r="C105" s="103"/>
+      <c r="D105" s="102"/>
+    </row>
+    <row r="106" spans="3:4">
+      <c r="C106" s="103"/>
+      <c r="D106" s="102"/>
+    </row>
+    <row r="107" spans="3:4">
+      <c r="C107" s="103"/>
+      <c r="D107" s="102"/>
+    </row>
+    <row r="108" spans="3:4">
+      <c r="C108" s="103"/>
+      <c r="D108" s="102"/>
+    </row>
+    <row r="109" spans="3:4">
+      <c r="C109" s="103"/>
+      <c r="D109" s="102"/>
+    </row>
+    <row r="110" spans="3:4">
+      <c r="C110" s="103"/>
+      <c r="D110" s="102"/>
+    </row>
+    <row r="111" spans="3:4">
+      <c r="C111" s="103"/>
+      <c r="D111" s="102"/>
+    </row>
+    <row r="112" spans="3:4">
+      <c r="C112" s="103"/>
+      <c r="D112" s="102"/>
+    </row>
+    <row r="113" spans="3:4">
+      <c r="C113" s="103"/>
+      <c r="D113" s="102"/>
+    </row>
+    <row r="114" spans="3:4">
+      <c r="C114" s="103"/>
+      <c r="D114" s="102"/>
+    </row>
+    <row r="115" spans="3:4">
+      <c r="C115" s="103"/>
+      <c r="D115" s="102"/>
+    </row>
+    <row r="116" spans="3:4">
+      <c r="C116" s="103"/>
+      <c r="D116" s="102"/>
+    </row>
+    <row r="117" spans="3:4">
+      <c r="C117" s="103"/>
+      <c r="D117" s="102"/>
+    </row>
+    <row r="118" spans="3:4">
+      <c r="C118" s="103"/>
+      <c r="D118" s="102"/>
+    </row>
+    <row r="119" spans="3:4">
+      <c r="C119" s="103"/>
+      <c r="D119" s="102"/>
+    </row>
+    <row r="120" spans="3:4">
+      <c r="C120" s="103"/>
+      <c r="D120" s="102"/>
+    </row>
+    <row r="121" spans="3:4">
+      <c r="C121" s="103"/>
+      <c r="D121" s="102"/>
+    </row>
+    <row r="122" spans="3:4">
+      <c r="C122" s="103"/>
+      <c r="D122" s="102"/>
+    </row>
+    <row r="123" spans="3:4">
+      <c r="C123" s="103"/>
+      <c r="D123" s="102"/>
+    </row>
+    <row r="124" spans="3:4">
+      <c r="C124" s="103"/>
+      <c r="D124" s="102"/>
+    </row>
+    <row r="125" spans="3:4">
+      <c r="C125" s="103"/>
+      <c r="D125" s="102"/>
+    </row>
+    <row r="126" spans="3:4">
+      <c r="C126" s="103"/>
+      <c r="D126" s="102"/>
+    </row>
+    <row r="127" spans="3:4">
+      <c r="C127" s="103"/>
+      <c r="D127" s="102"/>
+    </row>
+    <row r="128" spans="3:4">
+      <c r="C128" s="103"/>
+      <c r="D128" s="102"/>
+    </row>
+    <row r="129" spans="3:4">
+      <c r="C129" s="103"/>
+      <c r="D129" s="102"/>
+    </row>
+    <row r="130" spans="3:4">
+      <c r="C130" s="103"/>
+      <c r="D130" s="102"/>
+    </row>
+    <row r="131" spans="3:4">
+      <c r="C131" s="103"/>
+      <c r="D131" s="102"/>
+    </row>
+    <row r="132" spans="3:4">
+      <c r="C132" s="103"/>
+      <c r="D132" s="102"/>
+    </row>
+    <row r="133" spans="3:4">
+      <c r="C133" s="103"/>
+      <c r="D133" s="102"/>
+    </row>
+    <row r="134" spans="3:4">
+      <c r="C134" s="103"/>
+      <c r="D134" s="102"/>
+    </row>
+    <row r="135" spans="3:4">
+      <c r="C135" s="103"/>
+      <c r="D135" s="102"/>
+    </row>
+    <row r="136" spans="3:4">
+      <c r="C136" s="103"/>
+      <c r="D136" s="102"/>
+    </row>
+    <row r="137" spans="3:4">
+      <c r="C137" s="103"/>
+      <c r="D137" s="102"/>
+    </row>
+    <row r="138" spans="3:4">
+      <c r="C138" s="103"/>
+      <c r="D138" s="102"/>
+    </row>
+    <row r="139" spans="3:4">
+      <c r="C139" s="103"/>
+      <c r="D139" s="102"/>
+    </row>
+    <row r="140" spans="3:4">
+      <c r="C140" s="103"/>
+      <c r="D140" s="102"/>
+    </row>
+    <row r="141" spans="3:4">
+      <c r="C141" s="103"/>
+      <c r="D141" s="102"/>
+    </row>
+    <row r="142" spans="3:4">
+      <c r="C142" s="103"/>
+      <c r="D142" s="102"/>
+    </row>
+    <row r="143" spans="3:4">
+      <c r="C143" s="103"/>
+      <c r="D143" s="102"/>
+    </row>
+    <row r="144" spans="3:4">
+      <c r="C144" s="103"/>
+      <c r="D144" s="102"/>
+    </row>
+    <row r="145" spans="3:4">
+      <c r="C145" s="103"/>
+      <c r="D145" s="102"/>
+    </row>
+    <row r="146" spans="3:4">
+      <c r="C146" s="103"/>
+      <c r="D146" s="102"/>
+    </row>
+    <row r="147" spans="3:4">
+      <c r="C147" s="103"/>
+      <c r="D147" s="102"/>
+    </row>
+    <row r="148" spans="3:4">
+      <c r="C148" s="103"/>
+      <c r="D148" s="102"/>
+    </row>
+    <row r="149" spans="3:4">
+      <c r="C149" s="103"/>
+      <c r="D149" s="102"/>
+    </row>
+    <row r="150" spans="3:4">
+      <c r="C150" s="103"/>
+      <c r="D150" s="102"/>
+    </row>
+    <row r="151" spans="3:4">
+      <c r="C151" s="103"/>
+      <c r="D151" s="102"/>
+    </row>
+    <row r="152" spans="3:4">
+      <c r="C152" s="103"/>
+      <c r="D152" s="102"/>
+    </row>
+    <row r="153" spans="3:4">
+      <c r="C153" s="103"/>
+      <c r="D153" s="102"/>
+    </row>
+    <row r="154" spans="3:4">
+      <c r="C154" s="103"/>
+      <c r="D154" s="102"/>
+    </row>
+    <row r="155" spans="3:4">
+      <c r="C155" s="103"/>
+      <c r="D155" s="102"/>
+    </row>
+    <row r="156" spans="3:4">
+      <c r="C156" s="103"/>
+      <c r="D156" s="102"/>
+    </row>
+    <row r="157" spans="3:4">
+      <c r="C157" s="103"/>
+      <c r="D157" s="102"/>
+    </row>
+    <row r="158" spans="3:4">
+      <c r="C158" s="103"/>
+      <c r="D158" s="102"/>
+    </row>
+    <row r="159" spans="3:4">
+      <c r="C159" s="103"/>
+      <c r="D159" s="102"/>
+    </row>
+    <row r="160" spans="3:4">
+      <c r="C160" s="103"/>
+      <c r="D160" s="102"/>
+    </row>
+    <row r="161" spans="3:4">
+      <c r="C161" s="103"/>
+      <c r="D161" s="102"/>
+    </row>
+    <row r="162" spans="3:4">
+      <c r="C162" s="103"/>
+      <c r="D162" s="102"/>
+    </row>
+    <row r="163" spans="3:4">
+      <c r="C163" s="103"/>
+      <c r="D163" s="102"/>
+    </row>
+    <row r="164" spans="3:4">
+      <c r="C164" s="103"/>
+      <c r="D164" s="102"/>
+    </row>
+    <row r="165" spans="3:4">
+      <c r="C165" s="103"/>
+      <c r="D165" s="102"/>
+    </row>
+    <row r="166" spans="3:4">
+      <c r="C166" s="103"/>
+      <c r="D166" s="102"/>
+    </row>
+    <row r="167" spans="3:4">
+      <c r="C167" s="103"/>
+      <c r="D167" s="102"/>
+    </row>
+    <row r="168" spans="3:4">
+      <c r="C168" s="103"/>
+      <c r="D168" s="102"/>
+    </row>
+    <row r="169" spans="3:4">
+      <c r="C169" s="103"/>
+      <c r="D169" s="102"/>
+    </row>
+    <row r="170" spans="3:4">
+      <c r="C170" s="103"/>
+      <c r="D170" s="102"/>
+    </row>
+    <row r="171" spans="3:4">
+      <c r="C171" s="103"/>
+      <c r="D171" s="102"/>
+    </row>
+    <row r="172" spans="3:4">
+      <c r="C172" s="103"/>
+      <c r="D172" s="102"/>
+    </row>
+    <row r="173" spans="3:4">
+      <c r="C173" s="103"/>
+      <c r="D173" s="102"/>
+    </row>
+    <row r="174" spans="3:4">
+      <c r="C174" s="103"/>
+      <c r="D174" s="102"/>
+    </row>
+    <row r="175" spans="3:4">
+      <c r="C175" s="103"/>
+      <c r="D175" s="102"/>
+    </row>
+    <row r="176" spans="3:4">
+      <c r="C176" s="103"/>
+      <c r="D176" s="102"/>
+    </row>
+    <row r="177" spans="3:4">
+      <c r="C177" s="103"/>
+      <c r="D177" s="102"/>
+    </row>
+    <row r="178" spans="3:4">
+      <c r="C178" s="103"/>
+      <c r="D178" s="102"/>
+    </row>
+    <row r="179" spans="3:4">
+      <c r="C179" s="103"/>
+      <c r="D179" s="102"/>
+    </row>
+    <row r="180" spans="3:4">
+      <c r="C180" s="103"/>
+      <c r="D180" s="102"/>
+    </row>
+    <row r="181" spans="3:4">
+      <c r="C181" s="103"/>
+      <c r="D181" s="102"/>
+    </row>
+    <row r="182" spans="3:4">
+      <c r="C182" s="103"/>
+      <c r="D182" s="102"/>
+    </row>
+    <row r="183" spans="3:4">
+      <c r="C183" s="103"/>
+      <c r="D183" s="102"/>
+    </row>
+    <row r="184" spans="3:4">
+      <c r="C184" s="103"/>
+      <c r="D184" s="102"/>
+    </row>
+    <row r="185" spans="3:4">
+      <c r="C185" s="103"/>
+      <c r="D185" s="102"/>
+    </row>
+    <row r="186" spans="3:4">
+      <c r="C186" s="103"/>
+      <c r="D186" s="102"/>
+    </row>
+    <row r="187" spans="3:4">
+      <c r="C187" s="103"/>
+      <c r="D187" s="102"/>
+    </row>
+    <row r="188" spans="3:4">
+      <c r="C188" s="103"/>
+      <c r="D188" s="102"/>
+    </row>
+    <row r="189" spans="3:4">
+      <c r="C189" s="103"/>
+      <c r="D189" s="102"/>
+    </row>
+    <row r="190" spans="3:4">
+      <c r="C190" s="103"/>
+      <c r="D190" s="102"/>
+    </row>
+    <row r="191" spans="3:4">
+      <c r="C191" s="103"/>
+      <c r="D191" s="102"/>
+    </row>
+    <row r="192" spans="3:4">
+      <c r="C192" s="103"/>
+      <c r="D192" s="102"/>
+    </row>
+    <row r="193" spans="3:4">
+      <c r="C193" s="103"/>
+      <c r="D193" s="102"/>
+    </row>
+    <row r="194" spans="3:4">
+      <c r="C194" s="103"/>
+      <c r="D194" s="102"/>
+    </row>
+    <row r="195" spans="3:4">
+      <c r="C195" s="103"/>
+      <c r="D195" s="102"/>
+    </row>
+    <row r="196" spans="3:4">
+      <c r="C196" s="103"/>
+      <c r="D196" s="102"/>
+    </row>
+    <row r="197" spans="3:4">
+      <c r="C197" s="103"/>
+      <c r="D197" s="102"/>
+    </row>
+    <row r="198" spans="3:4">
+      <c r="C198" s="103"/>
+      <c r="D198" s="102"/>
+    </row>
+    <row r="199" spans="3:4">
+      <c r="C199" s="103"/>
+      <c r="D199" s="102"/>
+    </row>
+    <row r="200" spans="3:4">
+      <c r="C200" s="103"/>
+      <c r="D200" s="102"/>
+    </row>
+    <row r="201" spans="3:4">
+      <c r="C201" s="103"/>
+      <c r="D201" s="102"/>
+    </row>
+    <row r="202" spans="3:4">
+      <c r="C202" s="103"/>
+      <c r="D202" s="102"/>
+    </row>
+    <row r="203" spans="3:4">
+      <c r="C203" s="103"/>
+      <c r="D203" s="102"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="P4:P226">
+    <cfRule type="cellIs" dxfId="5" priority="2" operator="equal">
+      <formula>"OK"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P4:P1048576">
+    <cfRule type="cellIs" dxfId="4" priority="1" operator="equal">
+      <formula>"ALERTA: última parcela após a saída"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F4:O120">
+    <cfRule type="expression" dxfId="3" priority="3">
+      <formula>$N4="A vencer"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <legacyDrawing r:id="rId1"/>
+</worksheet>
 </file>
--- a/Controle_Locacao.xlsx
+++ b/Controle_Locacao.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Renato.Neves\Documents\TRABALHOS 2025\LOCAÇÃO PRAIA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96554C20-B748-44EA-A023-30CCBC7ED24B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{911C9A2D-3C9D-4E82-9740-D77F14B1CEEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PAINEL" sheetId="1" r:id="rId1"/>
@@ -114,7 +114,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="157">
   <si>
     <t>PAINEL FINANCEIRO E DE OCUPAÇÃO</t>
   </si>
@@ -582,6 +582,9 @@
   </si>
   <si>
     <t>Alerta prazo</t>
+  </si>
+  <si>
+    <t>Ana Paula</t>
   </si>
 </sst>
 </file>
@@ -1129,7 +1132,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="128">
+  <cellXfs count="125">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1299,6 +1302,7 @@
     </xf>
     <xf numFmtId="14" fontId="23" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="170" fontId="23" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1314,34 +1318,19 @@
     <xf numFmtId="0" fontId="12" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="170" fontId="27" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="14" fontId="27" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="20">
+  <dxfs count="37">
     <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FF7F6000"/>
-      </font>
       <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFF2CC"/>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color theme="0"/>
-      </font>
       <fill>
         <patternFill>
           <bgColor rgb="FFFF0000"/>
@@ -1350,20 +1339,7 @@
     </dxf>
     <dxf>
       <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color theme="0"/>
+        <color rgb="FF9C0006"/>
       </font>
       <fill>
         <patternFill patternType="solid">
@@ -1374,10 +1350,99 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF166534"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFDCFCE7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <b/>
-        <i val="0"/>
-        <color theme="0"/>
+        <color rgb="FF991B1B"/>
       </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFEE2E2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF92400E"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFEF3C7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF991B1B"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFEE2E2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF0BFDA1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF000000"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="8" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF000000"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFF85D3"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <fill>
         <patternFill>
           <bgColor rgb="FFFF0000"/>
@@ -1386,12 +1451,77 @@
     </dxf>
     <dxf>
       <font>
-        <b/>
-        <i val="0"/>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF166534"/>
       </font>
       <fill>
         <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
+          <bgColor rgb="FFDCFCE7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF991B1B"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFEE2E2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF92400E"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFEF3C7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF991B1B"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFEE2E2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF0BFDA1"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1499,6 +1629,42 @@
     <dxf>
       <font>
         <b/>
+        <i val="0"/>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
         <color rgb="FF991B1B"/>
       </font>
       <fill>
@@ -1544,6 +1710,7 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FFFF85D3"/>
       <color rgb="FF0BFDA1"/>
     </mruColors>
   </colors>
@@ -1987,6 +2154,60 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>1676400</xdr:colOff>
+      <xdr:row>51</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="9" name="AutoShape 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{41B6A02C-DCC1-B931-A043-3B5140B72776}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="9525000" cy="10439400"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst/>
+          <a:ahLst/>
+          <a:cxnLst/>
+          <a:rect l="0" t="0" r="0" b="0"/>
+          <a:pathLst/>
+        </a:custGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:round/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -2225,22 +2446,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="24" customHeight="1">
-      <c r="A1" s="119" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="119"/>
-      <c r="C1" s="119"/>
-      <c r="D1" s="119"/>
-      <c r="E1" s="119"/>
-      <c r="F1" s="119"/>
-      <c r="G1" s="119"/>
-      <c r="H1" s="119"/>
-      <c r="I1" s="119"/>
-      <c r="J1" s="119"/>
-      <c r="K1" s="119"/>
-      <c r="L1" s="119"/>
-      <c r="M1" s="119"/>
-      <c r="N1" s="119"/>
+      <c r="A1" s="120" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="120"/>
+      <c r="C1" s="120"/>
+      <c r="D1" s="120"/>
+      <c r="E1" s="120"/>
+      <c r="F1" s="120"/>
+      <c r="G1" s="120"/>
+      <c r="H1" s="120"/>
+      <c r="I1" s="120"/>
+      <c r="J1" s="120"/>
+      <c r="K1" s="120"/>
+      <c r="L1" s="120"/>
+      <c r="M1" s="120"/>
+      <c r="N1" s="120"/>
     </row>
     <row r="3" spans="1:14" ht="23.25">
       <c r="A3" s="1" t="s">
@@ -2254,7 +2475,7 @@
       </c>
       <c r="N3" s="85">
         <f>SUMIFS(RESERVAS!$U$6:$U$203,RESERVAS!$I$6:$I$203,"&lt;&gt;Cancelada",RESERVAS!$I$6:$I$203,"&lt;&gt;Consulta")</f>
-        <v>44209.619999999995</v>
+        <v>48093.619999999995</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="20.25">
@@ -2349,11 +2570,11 @@
       <c r="J12" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="L12" s="120" t="s">
+      <c r="L12" s="121" t="s">
         <v>18</v>
       </c>
-      <c r="M12" s="120"/>
-      <c r="N12" s="120"/>
+      <c r="M12" s="121"/>
+      <c r="N12" s="121"/>
     </row>
     <row r="13" spans="1:14" ht="18">
       <c r="A13" s="15" t="s">
@@ -2916,7 +3137,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I13:I24">
-    <cfRule type="cellIs" dxfId="19" priority="2" operator="lessThan">
+    <cfRule type="cellIs" dxfId="36" priority="2" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2958,20 +3179,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="24" customHeight="1">
-      <c r="A1" s="119" t="s">
+      <c r="A1" s="120" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="119"/>
-      <c r="C1" s="119"/>
-      <c r="D1" s="119"/>
-      <c r="E1" s="119"/>
-      <c r="F1" s="119"/>
-      <c r="G1" s="119"/>
-      <c r="H1" s="119"/>
-      <c r="I1" s="119"/>
-      <c r="J1" s="119"/>
-      <c r="K1" s="119"/>
-      <c r="L1" s="119"/>
+      <c r="B1" s="120"/>
+      <c r="C1" s="120"/>
+      <c r="D1" s="120"/>
+      <c r="E1" s="120"/>
+      <c r="F1" s="120"/>
+      <c r="G1" s="120"/>
+      <c r="H1" s="120"/>
+      <c r="I1" s="120"/>
+      <c r="J1" s="120"/>
+      <c r="K1" s="120"/>
+      <c r="L1" s="120"/>
     </row>
     <row r="2" spans="1:12" ht="15">
       <c r="A2" s="1" t="s">
@@ -3016,12 +3237,12 @@
       <c r="G4" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="I4" s="121" t="s">
+      <c r="I4" s="122" t="s">
         <v>47</v>
       </c>
-      <c r="J4" s="121"/>
-      <c r="K4" s="121"/>
-      <c r="L4" s="121"/>
+      <c r="J4" s="122"/>
+      <c r="K4" s="122"/>
+      <c r="L4" s="122"/>
     </row>
     <row r="5" spans="1:12" ht="60.75" customHeight="1">
       <c r="A5" s="29" t="str">
@@ -3291,12 +3512,12 @@
       <c r="E12" s="92"/>
       <c r="F12" s="92"/>
       <c r="G12" s="92"/>
-      <c r="I12" s="120" t="s">
+      <c r="I12" s="121" t="s">
         <v>48</v>
       </c>
-      <c r="J12" s="120"/>
-      <c r="K12" s="120"/>
-      <c r="L12" s="120"/>
+      <c r="J12" s="121"/>
+      <c r="K12" s="121"/>
+      <c r="L12" s="121"/>
     </row>
     <row r="13" spans="1:12" ht="15">
       <c r="A13" s="92"/>
@@ -3343,13 +3564,13 @@
     <mergeCell ref="I12:L12"/>
   </mergeCells>
   <conditionalFormatting sqref="A5:G10">
-    <cfRule type="expression" dxfId="18" priority="1">
+    <cfRule type="expression" dxfId="35" priority="1">
       <formula>ISNUMBER(SEARCH("DISPONÍVEL",A5))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="17" priority="2">
+    <cfRule type="expression" dxfId="34" priority="2">
       <formula>ISNUMBER(SEARCH("ALUGADA",A5))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="16" priority="3">
+    <cfRule type="expression" dxfId="33" priority="3">
       <formula>ISNUMBER(SEARCH("CONFLITO",A5))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3397,72 +3618,72 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:34" ht="24" customHeight="1">
-      <c r="A1" s="119" t="s">
+      <c r="A1" s="120" t="s">
         <v>55</v>
       </c>
-      <c r="B1" s="119"/>
-      <c r="C1" s="119"/>
-      <c r="D1" s="119"/>
-      <c r="E1" s="119"/>
-      <c r="F1" s="119"/>
-      <c r="G1" s="119"/>
-      <c r="H1" s="119"/>
-      <c r="I1" s="119"/>
-      <c r="J1" s="119"/>
-      <c r="K1" s="119"/>
-      <c r="L1" s="119"/>
-      <c r="M1" s="119"/>
-      <c r="N1" s="119"/>
-      <c r="O1" s="119"/>
-      <c r="P1" s="119"/>
-      <c r="Q1" s="119"/>
-      <c r="R1" s="119"/>
-      <c r="S1" s="119"/>
-      <c r="T1" s="119"/>
-      <c r="U1" s="119"/>
-      <c r="V1" s="119"/>
-      <c r="W1" s="119"/>
-      <c r="X1" s="119"/>
-      <c r="Y1" s="119"/>
-      <c r="Z1" s="119"/>
-      <c r="AA1" s="119"/>
+      <c r="B1" s="120"/>
+      <c r="C1" s="120"/>
+      <c r="D1" s="120"/>
+      <c r="E1" s="120"/>
+      <c r="F1" s="120"/>
+      <c r="G1" s="120"/>
+      <c r="H1" s="120"/>
+      <c r="I1" s="120"/>
+      <c r="J1" s="120"/>
+      <c r="K1" s="120"/>
+      <c r="L1" s="120"/>
+      <c r="M1" s="120"/>
+      <c r="N1" s="120"/>
+      <c r="O1" s="120"/>
+      <c r="P1" s="120"/>
+      <c r="Q1" s="120"/>
+      <c r="R1" s="120"/>
+      <c r="S1" s="120"/>
+      <c r="T1" s="120"/>
+      <c r="U1" s="120"/>
+      <c r="V1" s="120"/>
+      <c r="W1" s="120"/>
+      <c r="X1" s="120"/>
+      <c r="Y1" s="120"/>
+      <c r="Z1" s="120"/>
+      <c r="AA1" s="120"/>
     </row>
     <row r="3" spans="1:34">
-      <c r="A3" s="122" t="s">
+      <c r="A3" s="123" t="s">
         <v>117</v>
       </c>
-      <c r="B3" s="122"/>
-      <c r="C3" s="122"/>
-      <c r="D3" s="122"/>
-      <c r="E3" s="122"/>
-      <c r="F3" s="122"/>
-      <c r="G3" s="122"/>
-      <c r="H3" s="122"/>
-      <c r="I3" s="122"/>
-      <c r="J3" s="122"/>
-      <c r="K3" s="122"/>
-      <c r="L3" s="122"/>
-      <c r="M3" s="122"/>
-      <c r="N3" s="122"/>
-      <c r="O3" s="122"/>
-      <c r="P3" s="122"/>
-      <c r="Q3" s="122"/>
-      <c r="R3" s="122"/>
-      <c r="S3" s="122"/>
-      <c r="T3" s="122"/>
-      <c r="U3" s="122"/>
-      <c r="V3" s="122"/>
-      <c r="W3" s="122"/>
-      <c r="X3" s="122"/>
-      <c r="Y3" s="122"/>
-      <c r="Z3" s="122"/>
-      <c r="AA3" s="122"/>
+      <c r="B3" s="123"/>
+      <c r="C3" s="123"/>
+      <c r="D3" s="123"/>
+      <c r="E3" s="123"/>
+      <c r="F3" s="123"/>
+      <c r="G3" s="123"/>
+      <c r="H3" s="123"/>
+      <c r="I3" s="123"/>
+      <c r="J3" s="123"/>
+      <c r="K3" s="123"/>
+      <c r="L3" s="123"/>
+      <c r="M3" s="123"/>
+      <c r="N3" s="123"/>
+      <c r="O3" s="123"/>
+      <c r="P3" s="123"/>
+      <c r="Q3" s="123"/>
+      <c r="R3" s="123"/>
+      <c r="S3" s="123"/>
+      <c r="T3" s="123"/>
+      <c r="U3" s="123"/>
+      <c r="V3" s="123"/>
+      <c r="W3" s="123"/>
+      <c r="X3" s="123"/>
+      <c r="Y3" s="123"/>
+      <c r="Z3" s="123"/>
+      <c r="AA3" s="123"/>
     </row>
     <row r="4" spans="1:34" ht="15">
-      <c r="AG4" s="123" t="s">
+      <c r="AG4" s="124" t="s">
         <v>133</v>
       </c>
-      <c r="AH4" s="123"/>
+      <c r="AH4" s="124"/>
     </row>
     <row r="5" spans="1:34" ht="24" customHeight="1">
       <c r="A5" s="2" t="s">
@@ -3674,7 +3895,7 @@
       </c>
       <c r="AG6" s="99">
         <f>IFERROR(SUMIF($AB$6:$AB$1000,AG$5,$AE$6:$AE$1000)/COUNTIFS($AB$6:$AB$1000,AG$5,$AE$6:$AE$1000,"&gt;0"),"")</f>
-        <v>4.166666666666667</v>
+        <v>3.8571428571428572</v>
       </c>
       <c r="AH6" s="99">
         <f>IFERROR(SUMIF($AB$6:$AB$1000,AH$5,$AE$6:$AE$1000)/COUNTIFS($AB$6:$AB$1000,AH$5,$AE$6:$AE$1000,"&gt;0"),"")</f>
@@ -4167,10 +4388,12 @@
         <f t="shared" si="6"/>
         <v>1</v>
       </c>
-      <c r="X12" s="47"/>
+      <c r="X12" s="47">
+        <v>3874.25</v>
+      </c>
       <c r="Y12" s="58">
         <f t="shared" si="7"/>
-        <v>3874.25</v>
+        <v>0</v>
       </c>
       <c r="Z12" s="49" t="str">
         <f t="shared" si="8"/>
@@ -4180,9 +4403,12 @@
       <c r="AB12" s="94" t="s">
         <v>119</v>
       </c>
-      <c r="AE12" s="97" t="str">
+      <c r="AC12">
+        <v>2</v>
+      </c>
+      <c r="AE12" s="97">
         <f t="shared" si="9"/>
-        <v/>
+        <v>2</v>
       </c>
     </row>
     <row r="13" spans="1:34" ht="15.75">
@@ -4529,23 +4755,38 @@
     <row r="17" spans="1:31" ht="15.75">
       <c r="A17" s="62" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="B17" s="43"/>
-      <c r="C17" s="45"/>
-      <c r="D17" s="45"/>
+        <v>LOC-012</v>
+      </c>
+      <c r="B17" s="43" t="s">
+        <v>156</v>
+      </c>
+      <c r="C17" s="45">
+        <v>46402</v>
+      </c>
+      <c r="D17" s="45">
+        <v>46407</v>
+      </c>
       <c r="E17" s="50">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="F17" s="47"/>
+        <v>5</v>
+      </c>
+      <c r="F17" s="47">
+        <f>3884/E17</f>
+        <v>776.8</v>
+      </c>
       <c r="G17" s="51">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H17" s="43"/>
-      <c r="I17" s="43"/>
-      <c r="J17" s="54"/>
+        <v>3884</v>
+      </c>
+      <c r="H17" s="43" t="s">
+        <v>89</v>
+      </c>
+      <c r="I17" s="43" t="s">
+        <v>82</v>
+      </c>
+      <c r="J17" s="54" t="s">
+        <v>87</v>
+      </c>
       <c r="K17" s="47"/>
       <c r="L17" s="47"/>
       <c r="M17" s="47"/>
@@ -4564,24 +4805,24 @@
       </c>
       <c r="U17" s="51">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>3884</v>
       </c>
       <c r="V17" s="51">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>776.8</v>
       </c>
       <c r="W17" s="52">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X17" s="47"/>
       <c r="Y17" s="58">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>3884</v>
       </c>
       <c r="Z17" s="49" t="str">
         <f t="shared" si="8"/>
-        <v/>
+        <v>OK</v>
       </c>
       <c r="AA17" s="63"/>
       <c r="AB17" s="94"/>
@@ -16618,46 +16859,46 @@
     <mergeCell ref="AG4:AH4"/>
   </mergeCells>
   <conditionalFormatting sqref="A6:J1000">
-    <cfRule type="expression" dxfId="15" priority="8">
+    <cfRule type="expression" dxfId="10" priority="8" stopIfTrue="1">
       <formula>$J6="Cortesia"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="14" priority="9" stopIfTrue="1">
+    <cfRule type="expression" dxfId="19" priority="9">
       <formula>AND(ISNUMBER($D6),$D6&lt;TODAY())</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="13" priority="10">
+    <cfRule type="expression" dxfId="18" priority="10">
       <formula>AND(ISNUMBER($D6),$D6&lt;TODAY())</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U6:U63">
-    <cfRule type="cellIs" dxfId="12" priority="7" operator="lessThan">
+    <cfRule type="cellIs" dxfId="17" priority="7" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y6:Y203">
-    <cfRule type="expression" dxfId="11" priority="6">
+    <cfRule type="expression" dxfId="16" priority="6">
       <formula>Y6&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Z6:Z63">
-    <cfRule type="expression" dxfId="10" priority="4">
+    <cfRule type="expression" dxfId="15" priority="4">
       <formula>Z6="CONFLITO"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="9" priority="5">
+    <cfRule type="expression" dxfId="14" priority="5">
       <formula>Z6="OK"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE6:AE1000">
-    <cfRule type="expression" dxfId="8" priority="11">
+    <cfRule type="expression" dxfId="13" priority="11">
       <formula>AND(ISNUMBER($AE6),$AE6&gt;6)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AG6:AG1048576">
-    <cfRule type="cellIs" dxfId="7" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="12" priority="3" operator="greaterThan">
       <formula>6</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AH6">
-    <cfRule type="cellIs" dxfId="6" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="11" priority="2" operator="greaterThan">
       <formula>6</formula>
     </cfRule>
   </conditionalFormatting>
@@ -16705,24 +16946,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="24" customHeight="1">
-      <c r="A1" s="119" t="s">
+      <c r="A1" s="120" t="s">
         <v>91</v>
       </c>
-      <c r="B1" s="119"/>
-      <c r="C1" s="119"/>
-      <c r="D1" s="119"/>
-      <c r="E1" s="119"/>
-      <c r="F1" s="119"/>
+      <c r="B1" s="120"/>
+      <c r="C1" s="120"/>
+      <c r="D1" s="120"/>
+      <c r="E1" s="120"/>
+      <c r="F1" s="120"/>
     </row>
     <row r="3" spans="1:7" ht="27.2" customHeight="1">
-      <c r="A3" s="122" t="s">
+      <c r="A3" s="123" t="s">
         <v>92</v>
       </c>
-      <c r="B3" s="122"/>
-      <c r="C3" s="122"/>
-      <c r="D3" s="122"/>
-      <c r="E3" s="122"/>
-      <c r="F3" s="122"/>
+      <c r="B3" s="123"/>
+      <c r="C3" s="123"/>
+      <c r="D3" s="123"/>
+      <c r="E3" s="123"/>
+      <c r="F3" s="123"/>
     </row>
     <row r="5" spans="1:7" ht="24" customHeight="1">
       <c r="A5" s="2" t="s">
@@ -19485,12 +19726,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="24" customHeight="1">
-      <c r="A1" s="119" t="s">
+      <c r="A1" s="120" t="s">
         <v>100</v>
       </c>
-      <c r="B1" s="119"/>
-      <c r="C1" s="119"/>
-      <c r="D1" s="119"/>
+      <c r="B1" s="120"/>
+      <c r="C1" s="120"/>
+      <c r="D1" s="120"/>
     </row>
     <row r="3" spans="1:7" ht="24" customHeight="1">
       <c r="A3" s="2" t="s">
@@ -19949,7 +20190,7 @@
         <v>46275</v>
       </c>
       <c r="N5" s="116" t="str">
-        <f t="shared" ref="N4:N15" ca="1" si="1">IF(F5="","",IF(AND(ISNUMBER(L5),L5&gt;=K5),"Pago",IF(J5&lt;TODAY(),"Atrasado","A vencer")))</f>
+        <f t="shared" ref="N5:N15" ca="1" si="1">IF(F5="","",IF(AND(ISNUMBER(L5),L5&gt;=K5),"Pago",IF(J5&lt;TODAY(),"Atrasado","A vencer")))</f>
         <v>Pago</v>
       </c>
       <c r="O5" s="113">
@@ -19997,21 +20238,19 @@
         <f>IF(F6="","",MIN($S$6,MAX(0,$S$7-$S$6*(3-1))))</f>
         <v>2200</v>
       </c>
-      <c r="L6" s="113" t="str">
-        <f>IF(F6="","",IF($S$13="","",$S$13))</f>
-        <v/>
-      </c>
-      <c r="M6" s="115" t="str">
-        <f>IF(F6="","",IF($T$13="","",$T$13))</f>
-        <v/>
+      <c r="L6" s="113">
+        <v>2200</v>
+      </c>
+      <c r="M6" s="115">
+        <v>46305</v>
       </c>
       <c r="N6" s="116" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>A vencer</v>
+        <v>Pago</v>
       </c>
       <c r="O6" s="113">
         <f>IF(F6="","",MAX(0,H6-SUM($L$4:L6)))</f>
-        <v>6600</v>
+        <v>4400</v>
       </c>
       <c r="P6" t="str">
         <f>IF(F6="","",IF(MAX($J$4:$J$15)&gt;_xlfn.XLOOKUP($S$4,RESERVAS!$A$6:$A$203,RESERVAS!$D$6:$D$203),"ALERTA: última parcela após a saída","OK"))</f>
@@ -20065,7 +20304,7 @@
       </c>
       <c r="O7" s="113">
         <f>IF(F7="","",MAX(0,H7-SUM($L$4:L7)))</f>
-        <v>6600</v>
+        <v>4400</v>
       </c>
       <c r="P7" t="str">
         <f>IF(F7="","",IF(MAX($J$4:$J$15)&gt;_xlfn.XLOOKUP($S$4,RESERVAS!$A$6:$A$203,RESERVAS!$D$6:$D$203),"ALERTA: última parcela após a saída","OK"))</f>
@@ -20135,7 +20374,7 @@
       </c>
       <c r="O8" s="113">
         <f>IF(F8="","",MAX(0,H8-SUM($L$4:L8)))</f>
-        <v>6600</v>
+        <v>4400</v>
       </c>
       <c r="P8" t="str">
         <f>IF(F8="","",IF(MAX($J$4:$J$15)&gt;_xlfn.XLOOKUP($S$4,RESERVAS!$A$6:$A$203,RESERVAS!$D$6:$D$203),"ALERTA: última parcela após a saída","OK"))</f>
@@ -20265,9 +20504,9 @@
         <f>IF(F10="","",IF(MAX($J$4:$J$15)&gt;_xlfn.XLOOKUP($S$4,RESERVAS!$A$6:$A$203,RESERVAS!$D$6:$D$203),"ALERTA: última parcela após a saída","OK"))</f>
         <v/>
       </c>
-      <c r="R10" s="124"/>
-      <c r="S10" s="124"/>
-      <c r="T10" s="124"/>
+      <c r="R10" s="119"/>
+      <c r="S10" s="119"/>
+      <c r="T10" s="119"/>
     </row>
     <row r="11" spans="2:26">
       <c r="C11" s="103"/>
@@ -20316,9 +20555,8 @@
         <f>IF(F11="","",IF(MAX($J$4:$J$15)&gt;_xlfn.XLOOKUP($S$4,RESERVAS!$A$6:$A$203,RESERVAS!$D$6:$D$203),"ALERTA: última parcela após a saída","OK"))</f>
         <v/>
       </c>
-      <c r="R11" s="125"/>
-      <c r="S11" s="126"/>
-      <c r="T11" s="127"/>
+      <c r="S11" s="110"/>
+      <c r="T11" s="111"/>
     </row>
     <row r="12" spans="2:26">
       <c r="C12" s="103"/>
@@ -20367,9 +20605,8 @@
         <f>IF(F12="","",IF(MAX($J$4:$J$15)&gt;_xlfn.XLOOKUP($S$4,RESERVAS!$A$6:$A$203,RESERVAS!$D$6:$D$203),"ALERTA: última parcela após a saída","OK"))</f>
         <v/>
       </c>
-      <c r="R12" s="125"/>
-      <c r="S12" s="126"/>
-      <c r="T12" s="127"/>
+      <c r="S12" s="110"/>
+      <c r="T12" s="111"/>
     </row>
     <row r="13" spans="2:26">
       <c r="C13" s="103"/>
@@ -20418,9 +20655,8 @@
         <f>IF(F13="","",IF(MAX($J$4:$J$15)&gt;_xlfn.XLOOKUP($S$4,RESERVAS!$A$6:$A$203,RESERVAS!$D$6:$D$203),"ALERTA: última parcela após a saída","OK"))</f>
         <v/>
       </c>
-      <c r="R13" s="125"/>
-      <c r="S13" s="126"/>
-      <c r="T13" s="127"/>
+      <c r="S13" s="110"/>
+      <c r="T13" s="111"/>
     </row>
     <row r="14" spans="2:26">
       <c r="C14" s="103"/>
@@ -20469,9 +20705,8 @@
         <f>IF(F14="","",IF(MAX($J$4:$J$15)&gt;_xlfn.XLOOKUP($S$4,RESERVAS!$A$6:$A$203,RESERVAS!$D$6:$D$203),"ALERTA: última parcela após a saída","OK"))</f>
         <v/>
       </c>
-      <c r="R14" s="125"/>
-      <c r="S14" s="126"/>
-      <c r="T14" s="127"/>
+      <c r="S14" s="110"/>
+      <c r="T14" s="111"/>
     </row>
     <row r="15" spans="2:26">
       <c r="C15" s="103"/>
@@ -20520,9 +20755,8 @@
         <f>IF(F15="","",IF(MAX($J$4:$J$15)&gt;_xlfn.XLOOKUP($S$4,RESERVAS!$A$6:$A$203,RESERVAS!$D$6:$D$203),"ALERTA: última parcela após a saída","OK"))</f>
         <v/>
       </c>
-      <c r="R15" s="125"/>
-      <c r="S15" s="126"/>
-      <c r="T15" s="127"/>
+      <c r="S15" s="110"/>
+      <c r="T15" s="111"/>
     </row>
     <row r="16" spans="2:26">
       <c r="C16" s="103"/>
@@ -20537,9 +20771,8 @@
       <c r="M16" s="117"/>
       <c r="N16" s="101"/>
       <c r="O16" s="118"/>
-      <c r="R16" s="125"/>
-      <c r="S16" s="126"/>
-      <c r="T16" s="127"/>
+      <c r="S16" s="110"/>
+      <c r="T16" s="111"/>
     </row>
     <row r="17" spans="3:20">
       <c r="C17" s="103"/>
@@ -20588,9 +20821,8 @@
         <f>IF(F17="","",IF(MAX($J$17:$J$19)&gt;MAX(_xlfn.XLOOKUP($V$4,RESERVAS!$A$6:$A$203,RESERVAS!$D$6:$D$203),_xlfn.XLOOKUP($V$5,RESERVAS!$A$6:$A$203,RESERVAS!$D$6:$D$203)),"ALERTA: última parcela após a saída","OK"))</f>
         <v>OK</v>
       </c>
-      <c r="R17" s="125"/>
-      <c r="S17" s="126"/>
-      <c r="T17" s="127"/>
+      <c r="S17" s="110"/>
+      <c r="T17" s="111"/>
     </row>
     <row r="18" spans="3:20">
       <c r="C18" s="103"/>
@@ -20639,9 +20871,8 @@
         <f>IF(F18="","",IF(MAX($J$17:$J$19)&gt;MAX(_xlfn.XLOOKUP($V$4,RESERVAS!$A$6:$A$203,RESERVAS!$D$6:$D$203),_xlfn.XLOOKUP($V$5,RESERVAS!$A$6:$A$203,RESERVAS!$D$6:$D$203)),"ALERTA: última parcela após a saída","OK"))</f>
         <v>OK</v>
       </c>
-      <c r="R18" s="125"/>
-      <c r="S18" s="126"/>
-      <c r="T18" s="127"/>
+      <c r="S18" s="110"/>
+      <c r="T18" s="111"/>
     </row>
     <row r="19" spans="3:20">
       <c r="C19" s="103"/>
@@ -20690,30 +20921,26 @@
         <f>IF(F19="","",IF(MAX($J$17:$J$19)&gt;MAX(_xlfn.XLOOKUP($V$4,RESERVAS!$A$6:$A$203,RESERVAS!$D$6:$D$203),_xlfn.XLOOKUP($V$5,RESERVAS!$A$6:$A$203,RESERVAS!$D$6:$D$203)),"ALERTA: última parcela após a saída","OK"))</f>
         <v>OK</v>
       </c>
-      <c r="R19" s="125"/>
-      <c r="S19" s="126"/>
-      <c r="T19" s="127"/>
+      <c r="S19" s="110"/>
+      <c r="T19" s="111"/>
     </row>
     <row r="20" spans="3:20">
       <c r="C20" s="103"/>
       <c r="D20" s="102"/>
-      <c r="R20" s="125"/>
-      <c r="S20" s="126"/>
-      <c r="T20" s="127"/>
+      <c r="S20" s="110"/>
+      <c r="T20" s="111"/>
     </row>
     <row r="21" spans="3:20">
       <c r="C21" s="103"/>
       <c r="D21" s="102"/>
-      <c r="R21" s="125"/>
-      <c r="S21" s="126"/>
-      <c r="T21" s="127"/>
+      <c r="S21" s="110"/>
+      <c r="T21" s="111"/>
     </row>
     <row r="22" spans="3:20">
       <c r="C22" s="103"/>
       <c r="D22" s="102"/>
-      <c r="R22" s="125"/>
-      <c r="S22" s="126"/>
-      <c r="T22" s="127"/>
+      <c r="S22" s="110"/>
+      <c r="T22" s="111"/>
     </row>
     <row r="23" spans="3:20">
       <c r="C23" s="103"/>
@@ -21440,19 +21667,19 @@
       <c r="D203" s="102"/>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="F4:O120">
+    <cfRule type="expression" dxfId="32" priority="3">
+      <formula>$N4="A vencer"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="P4:P226">
-    <cfRule type="cellIs" dxfId="5" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="31" priority="2" operator="equal">
       <formula>"OK"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P4:P1048576">
-    <cfRule type="cellIs" dxfId="4" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="30" priority="1" operator="equal">
       <formula>"ALERTA: última parcela após a saída"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F4:O120">
-    <cfRule type="expression" dxfId="3" priority="3">
-      <formula>$N4="A vencer"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
